--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
         <v>121801</v>
       </c>
       <c r="F2" t="n">
-        <v>170654</v>
+        <v>171260.59375</v>
       </c>
       <c r="G2" t="n">
         <v>100</v>
@@ -501,7 +501,7 @@
         <v>117.110001</v>
       </c>
       <c r="F3" t="n">
-        <v>167.559998</v>
+        <v>168.350006</v>
       </c>
       <c r="G3" t="n">
         <v>100</v>
@@ -526,7 +526,7 @@
         <v>141.800003</v>
       </c>
       <c r="F4" t="n">
-        <v>105.550003</v>
+        <v>105.809998</v>
       </c>
       <c r="G4" t="n">
         <v>100</v>
@@ -551,7 +551,7 @@
         <v>250.350006</v>
       </c>
       <c r="F5" t="n">
-        <v>433.700012</v>
+        <v>435.450012</v>
       </c>
       <c r="G5" t="n">
         <v>100</v>
@@ -576,7 +576,7 @@
         <v>5.0804</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1431</v>
+        <v>5.1453</v>
       </c>
       <c r="G6" t="n">
         <v>100</v>
@@ -601,7 +601,7 @@
         <v>6.0387</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8966</v>
+        <v>5.8964</v>
       </c>
       <c r="G7" t="n">
         <v>100</v>
@@ -626,7 +626,7 @@
         <v>4395.259766</v>
       </c>
       <c r="F8" t="n">
-        <v>7482.709961</v>
+        <v>7492.100098</v>
       </c>
       <c r="G8" t="n">
         <v>100</v>
@@ -651,7 +651,7 @@
         <v>14672.679688</v>
       </c>
       <c r="F9" t="n">
-        <v>25870.650391</v>
+        <v>25918.525391</v>
       </c>
       <c r="G9" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
         <v>34935.46875</v>
       </c>
       <c r="F10" t="n">
-        <v>52348.390625</v>
+        <v>52299.730469</v>
       </c>
       <c r="G10" t="n">
         <v>100</v>
@@ -701,7 +701,7 @@
         <v>1812.599976</v>
       </c>
       <c r="F11" t="n">
-        <v>4125.299805</v>
+        <v>4133.700195</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
@@ -726,7 +726,7 @@
         <v>73.949997</v>
       </c>
       <c r="F12" t="n">
-        <v>73.989998</v>
+        <v>73.129997</v>
       </c>
       <c r="G12" t="n">
         <v>100</v>
@@ -751,7 +751,7 @@
         <v>76.33000199999999</v>
       </c>
       <c r="F13" t="n">
-        <v>78.650002</v>
+        <v>77.910004</v>
       </c>
       <c r="G13" t="n">
         <v>100</v>
@@ -776,7 +776,7 @@
         <v>1414.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1187.5</v>
+        <v>1185.5</v>
       </c>
       <c r="G14" t="n">
         <v>100</v>
@@ -801,7 +801,7 @@
         <v>547</v>
       </c>
       <c r="F15" t="n">
-        <v>451</v>
+        <v>451.5</v>
       </c>
       <c r="G15" t="n">
         <v>100</v>
@@ -826,7 +826,7 @@
         <v>-2.479454</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.796401</v>
+        <v>-0.443779</v>
       </c>
       <c r="G16" t="n">
         <v>98.36065600000001</v>
@@ -851,7 +851,7 @@
         <v>-2.58731</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.881399</v>
+        <v>-0.414077</v>
       </c>
       <c r="G17" t="n">
         <v>98.36065600000001</v>
@@ -876,7 +876,7 @@
         <v>-3.857547</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.250417</v>
+        <v>-2.009637</v>
       </c>
       <c r="G18" t="n">
         <v>98.36065600000001</v>
@@ -901,7 +901,7 @@
         <v>1.457956</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.447603</v>
+        <v>-0.045904</v>
       </c>
       <c r="G19" t="n">
         <v>98.36065600000001</v>
@@ -926,7 +926,7 @@
         <v>2.017557</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7466</v>
+        <v>-0.704141</v>
       </c>
       <c r="G20" t="n">
         <v>98.36065600000001</v>
@@ -951,7 +951,7 @@
         <v>1.212177</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.347468</v>
+        <v>-0.350845</v>
       </c>
       <c r="G21" t="n">
         <v>98.36065600000001</v>
@@ -976,7 +976,7 @@
         <v>2.899042</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.222018</v>
+        <v>-0.096805</v>
       </c>
       <c r="G22" t="n">
         <v>98.36065600000001</v>
@@ -1001,7 +1001,7 @@
         <v>3.997638</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.308743</v>
+        <v>-1.12611</v>
       </c>
       <c r="G23" t="n">
         <v>98.36065600000001</v>
@@ -1026,7 +1026,7 @@
         <v>1.217278</v>
       </c>
       <c r="F24" t="n">
-        <v>0.055795</v>
+        <v>-0.037211</v>
       </c>
       <c r="G24" t="n">
         <v>98.36065600000001</v>
@@ -1051,7 +1051,7 @@
         <v>0.132408</v>
       </c>
       <c r="F25" t="n">
-        <v>2.545425</v>
+        <v>2.754239</v>
       </c>
       <c r="G25" t="n">
         <v>98.36065600000001</v>
@@ -1076,7 +1076,7 @@
         <v>-7.369841</v>
       </c>
       <c r="F26" t="n">
-        <v>6.460429</v>
+        <v>5.223018</v>
       </c>
       <c r="G26" t="n">
         <v>98.36065600000001</v>
@@ -1101,7 +1101,7 @@
         <v>-4.375742</v>
       </c>
       <c r="F27" t="n">
-        <v>7.857931</v>
+        <v>6.843123</v>
       </c>
       <c r="G27" t="n">
         <v>98.36065600000001</v>
@@ -1126,7 +1126,7 @@
         <v>-8.199329000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>6.335348</v>
+        <v>6.156257</v>
       </c>
       <c r="G28" t="n">
         <v>98.36065600000001</v>
@@ -1151,7 +1151,7 @@
         <v>-2.3766</v>
       </c>
       <c r="F29" t="n">
-        <v>9.267111</v>
+        <v>9.388249999999999</v>
       </c>
       <c r="G29" t="n">
         <v>98.36065600000001</v>
@@ -1385,32 +1385,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_compra_usd</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D39" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E39" t="n">
-        <v>5.121</v>
+        <v>4271865</v>
       </c>
       <c r="F39" t="n">
-        <v>5.1546</v>
+        <v>7299615</v>
       </c>
       <c r="G39" t="n">
-        <v>100</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
@@ -1423,10 +1423,10 @@
         <v>59</v>
       </c>
       <c r="E40" t="n">
-        <v>4271865</v>
+        <v>1833179</v>
       </c>
       <c r="F40" t="n">
-        <v>7299615</v>
+        <v>2704550</v>
       </c>
       <c r="G40" t="n">
         <v>96.721311</v>
@@ -1435,7 +1435,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
@@ -1448,10 +1448,10 @@
         <v>59</v>
       </c>
       <c r="E41" t="n">
-        <v>1833179</v>
+        <v>2438686</v>
       </c>
       <c r="F41" t="n">
-        <v>2704550</v>
+        <v>4595065</v>
       </c>
       <c r="G41" t="n">
         <v>96.721311</v>
@@ -1460,7 +1460,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
@@ -1473,10 +1473,10 @@
         <v>59</v>
       </c>
       <c r="E42" t="n">
-        <v>2438686</v>
+        <v>2.36</v>
       </c>
       <c r="F42" t="n">
-        <v>4595065</v>
+        <v>4.74</v>
       </c>
       <c r="G42" t="n">
         <v>96.721311</v>
@@ -1485,7 +1485,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
@@ -1498,10 +1498,10 @@
         <v>59</v>
       </c>
       <c r="E43" t="n">
-        <v>2.36</v>
+        <v>1.58</v>
       </c>
       <c r="F43" t="n">
-        <v>4.74</v>
+        <v>3.24</v>
       </c>
       <c r="G43" t="n">
         <v>96.721311</v>
@@ -1510,7 +1510,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
@@ -1523,10 +1523,10 @@
         <v>59</v>
       </c>
       <c r="E44" t="n">
-        <v>1.58</v>
+        <v>2.94</v>
       </c>
       <c r="F44" t="n">
-        <v>3.24</v>
+        <v>5.62</v>
       </c>
       <c r="G44" t="n">
         <v>96.721311</v>
@@ -1535,7 +1535,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
@@ -1548,10 +1548,10 @@
         <v>59</v>
       </c>
       <c r="E45" t="n">
-        <v>2.94</v>
+        <v>20.26</v>
       </c>
       <c r="F45" t="n">
-        <v>5.62</v>
+        <v>33.42</v>
       </c>
       <c r="G45" t="n">
         <v>96.721311</v>
@@ -1560,57 +1560,57 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D46" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E46" t="n">
-        <v>20.26</v>
+        <v>355671</v>
       </c>
       <c r="F46" t="n">
-        <v>33.42</v>
+        <v>367558</v>
       </c>
       <c r="G46" t="n">
-        <v>96.721311</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46203</v>
+        <v>46142</v>
       </c>
       <c r="D47" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E47" t="n">
-        <v>355671</v>
+        <v>0.631159</v>
       </c>
       <c r="F47" t="n">
-        <v>367558</v>
+        <v>0.511964</v>
       </c>
       <c r="G47" t="n">
-        <v>98.36065600000001</v>
+        <v>93.442623</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
@@ -1623,10 +1623,10 @@
         <v>57</v>
       </c>
       <c r="E48" t="n">
-        <v>0.631159</v>
+        <v>-0.641498</v>
       </c>
       <c r="F48" t="n">
-        <v>0.511964</v>
+        <v>-3.561276</v>
       </c>
       <c r="G48" t="n">
         <v>93.442623</v>
@@ -1635,82 +1635,82 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46142</v>
+        <v>46234</v>
       </c>
       <c r="D49" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.641498</v>
+        <v>0.423696</v>
       </c>
       <c r="F49" t="n">
-        <v>-3.561276</v>
+        <v>-0.413399</v>
       </c>
       <c r="G49" t="n">
-        <v>93.442623</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D50" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E50" t="n">
-        <v>0.423696</v>
+        <v>1.736829</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.413399</v>
+        <v>0.565068</v>
       </c>
       <c r="G50" t="n">
-        <v>98.36065600000001</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D51" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E51" t="n">
-        <v>0.423745</v>
+        <v>0.972464</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.413447</v>
+        <v>0.742264</v>
       </c>
       <c r="G51" t="n">
-        <v>98.36065600000001</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
@@ -1723,10 +1723,10 @@
         <v>58</v>
       </c>
       <c r="E52" t="n">
-        <v>1.736829</v>
+        <v>2.311409</v>
       </c>
       <c r="F52" t="n">
-        <v>0.565068</v>
+        <v>0.461065</v>
       </c>
       <c r="G52" t="n">
         <v>95.08196700000001</v>
@@ -1735,82 +1735,82 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D53" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E53" t="n">
-        <v>0.972464</v>
+        <v>4.139781</v>
       </c>
       <c r="F53" t="n">
-        <v>0.742264</v>
+        <v>-0.964334</v>
       </c>
       <c r="G53" t="n">
-        <v>95.08196700000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>44439</v>
+        <v>44742</v>
       </c>
       <c r="C54" s="1" t="n">
         <v>46173</v>
       </c>
       <c r="D54" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="E54" t="n">
-        <v>2.311409</v>
+        <v>11.88673</v>
       </c>
       <c r="F54" t="n">
-        <v>0.461065</v>
+        <v>4.724907</v>
       </c>
       <c r="G54" t="n">
-        <v>95.08196700000001</v>
+        <v>78.688525</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>44439</v>
+        <v>44742</v>
       </c>
       <c r="C55" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D55" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E55" t="n">
-        <v>4.139781</v>
+        <v>10.700862</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.964334</v>
+        <v>3.177699</v>
       </c>
       <c r="G55" t="n">
-        <v>96.721311</v>
+        <v>80.32786900000001</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
@@ -1823,10 +1823,10 @@
         <v>48</v>
       </c>
       <c r="E56" t="n">
-        <v>11.88673</v>
+        <v>11.919595</v>
       </c>
       <c r="F56" t="n">
-        <v>4.724907</v>
+        <v>4.420848</v>
       </c>
       <c r="G56" t="n">
         <v>78.688525</v>
@@ -1835,57 +1835,57 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>44742</v>
+        <v>44439</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D57" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E57" t="n">
-        <v>10.700862</v>
+        <v>1</v>
       </c>
       <c r="F57" t="n">
-        <v>3.177699</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>80.32786900000001</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>44742</v>
+        <v>44439</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D58" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="E58" t="n">
-        <v>11.919595</v>
+        <v>0.003276</v>
       </c>
       <c r="F58" t="n">
-        <v>4.420848</v>
+        <v>-0.000497</v>
       </c>
       <c r="G58" t="n">
-        <v>78.688525</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
@@ -1898,10 +1898,10 @@
         <v>60</v>
       </c>
       <c r="E59" t="n">
-        <v>1</v>
+        <v>0.003276</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>-0.000497</v>
       </c>
       <c r="G59" t="n">
         <v>98.36065600000001</v>
@@ -1910,57 +1910,57 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D60" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E60" t="n">
-        <v>0.003276</v>
+        <v>0.01</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.000497</v>
+        <v>0.11</v>
       </c>
       <c r="G60" t="n">
-        <v>98.36065600000001</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D61" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E61" t="n">
-        <v>0.003276</v>
+        <v>-0.02</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.000497</v>
+        <v>0.09</v>
       </c>
       <c r="G61" t="n">
-        <v>98.36065600000001</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
@@ -1973,7 +1973,7 @@
         <v>58</v>
       </c>
       <c r="E62" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F62" t="n">
         <v>0.11</v>
@@ -1985,7 +1985,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
@@ -1998,62 +1998,12 @@
         <v>58</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.02</v>
+        <v>0.66</v>
       </c>
       <c r="F63" t="n">
-        <v>0.09</v>
+        <v>-0.09</v>
       </c>
       <c r="G63" t="n">
-        <v>95.08196700000001</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
-        </is>
-      </c>
-      <c r="B64" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="C64" s="1" t="n">
-        <v>46173</v>
-      </c>
-      <c r="D64" t="n">
-        <v>58</v>
-      </c>
-      <c r="E64" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F64" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="G64" t="n">
-        <v>95.08196700000001</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
-        </is>
-      </c>
-      <c r="B65" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="C65" s="1" t="n">
-        <v>46173</v>
-      </c>
-      <c r="D65" t="n">
-        <v>58</v>
-      </c>
-      <c r="E65" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="F65" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="G65" t="n">
         <v>95.08196700000001</v>
       </c>
     </row>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
         <v>121801</v>
       </c>
       <c r="F2" t="n">
-        <v>171260.59375</v>
+        <v>172742</v>
       </c>
       <c r="G2" t="n">
         <v>100</v>
@@ -501,7 +501,7 @@
         <v>117.110001</v>
       </c>
       <c r="F3" t="n">
-        <v>168.350006</v>
+        <v>169.800003</v>
       </c>
       <c r="G3" t="n">
         <v>100</v>
@@ -526,7 +526,7 @@
         <v>141.800003</v>
       </c>
       <c r="F4" t="n">
-        <v>105.809998</v>
+        <v>107.760002</v>
       </c>
       <c r="G4" t="n">
         <v>100</v>
@@ -551,7 +551,7 @@
         <v>250.350006</v>
       </c>
       <c r="F5" t="n">
-        <v>435.450012</v>
+        <v>435.079987</v>
       </c>
       <c r="G5" t="n">
         <v>100</v>
@@ -576,7 +576,7 @@
         <v>5.0804</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1453</v>
+        <v>5.1146</v>
       </c>
       <c r="G6" t="n">
         <v>100</v>
@@ -601,7 +601,7 @@
         <v>6.0387</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8964</v>
+        <v>5.8474</v>
       </c>
       <c r="G7" t="n">
         <v>100</v>
@@ -626,7 +626,7 @@
         <v>4395.259766</v>
       </c>
       <c r="F8" t="n">
-        <v>7492.100098</v>
+        <v>7543.640137</v>
       </c>
       <c r="G8" t="n">
         <v>100</v>
@@ -651,7 +651,7 @@
         <v>14672.679688</v>
       </c>
       <c r="F9" t="n">
-        <v>25918.525391</v>
+        <v>26206.890625</v>
       </c>
       <c r="G9" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
         <v>34935.46875</v>
       </c>
       <c r="F10" t="n">
-        <v>52299.730469</v>
+        <v>52487.410156</v>
       </c>
       <c r="G10" t="n">
         <v>100</v>
@@ -701,7 +701,7 @@
         <v>1812.599976</v>
       </c>
       <c r="F11" t="n">
-        <v>4133.700195</v>
+        <v>4117.700195</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
@@ -726,7 +726,7 @@
         <v>73.949997</v>
       </c>
       <c r="F12" t="n">
-        <v>73.129997</v>
+        <v>71.949997</v>
       </c>
       <c r="G12" t="n">
         <v>100</v>
@@ -751,7 +751,7 @@
         <v>76.33000199999999</v>
       </c>
       <c r="F13" t="n">
-        <v>77.910004</v>
+        <v>76.360001</v>
       </c>
       <c r="G13" t="n">
         <v>100</v>
@@ -776,7 +776,7 @@
         <v>1414.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1185.5</v>
+        <v>1180.25</v>
       </c>
       <c r="G14" t="n">
         <v>100</v>
@@ -801,7 +801,7 @@
         <v>547</v>
       </c>
       <c r="F15" t="n">
-        <v>451.5</v>
+        <v>451.75</v>
       </c>
       <c r="G15" t="n">
         <v>100</v>
@@ -826,7 +826,7 @@
         <v>-2.479454</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.443779</v>
+        <v>0.417384</v>
       </c>
       <c r="G16" t="n">
         <v>98.36065600000001</v>
@@ -851,7 +851,7 @@
         <v>-2.58731</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.414077</v>
+        <v>0.443656</v>
       </c>
       <c r="G17" t="n">
         <v>98.36065600000001</v>
@@ -876,7 +876,7 @@
         <v>-3.857547</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.009637</v>
+        <v>-0.203743</v>
       </c>
       <c r="G18" t="n">
         <v>98.36065600000001</v>
@@ -901,7 +901,7 @@
         <v>1.457956</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.045904</v>
+        <v>-0.130841</v>
       </c>
       <c r="G19" t="n">
         <v>98.36065600000001</v>
@@ -926,7 +926,7 @@
         <v>2.017557</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.704141</v>
+        <v>-1.296596</v>
       </c>
       <c r="G20" t="n">
         <v>98.36065600000001</v>
@@ -951,7 +951,7 @@
         <v>1.212177</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.350845</v>
+        <v>-1.178941</v>
       </c>
       <c r="G21" t="n">
         <v>98.36065600000001</v>
@@ -976,7 +976,7 @@
         <v>2.899042</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.096805</v>
+        <v>0.590454</v>
       </c>
       <c r="G22" t="n">
         <v>98.36065600000001</v>
@@ -1001,7 +1001,7 @@
         <v>3.997638</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.12611</v>
+        <v>-0.026055</v>
       </c>
       <c r="G23" t="n">
         <v>98.36065600000001</v>
@@ -1026,7 +1026,7 @@
         <v>1.217278</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.037211</v>
+        <v>0.321509</v>
       </c>
       <c r="G24" t="n">
         <v>98.36065600000001</v>
@@ -1051,7 +1051,7 @@
         <v>0.132408</v>
       </c>
       <c r="F25" t="n">
-        <v>2.754239</v>
+        <v>2.356516</v>
       </c>
       <c r="G25" t="n">
         <v>98.36065600000001</v>
@@ -1076,7 +1076,7 @@
         <v>-7.369841</v>
       </c>
       <c r="F26" t="n">
-        <v>5.223018</v>
+        <v>3.525175</v>
       </c>
       <c r="G26" t="n">
         <v>98.36065600000001</v>
@@ -1101,7 +1101,7 @@
         <v>-4.375742</v>
       </c>
       <c r="F27" t="n">
-        <v>6.843123</v>
+        <v>4.717502</v>
       </c>
       <c r="G27" t="n">
         <v>98.36065600000001</v>
@@ -1126,7 +1126,7 @@
         <v>-8.199329000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>6.156257</v>
+        <v>5.686143</v>
       </c>
       <c r="G28" t="n">
         <v>98.36065600000001</v>
@@ -1151,7 +1151,7 @@
         <v>-2.3766</v>
       </c>
       <c r="F29" t="n">
-        <v>9.388249999999999</v>
+        <v>9.448819</v>
       </c>
       <c r="G29" t="n">
         <v>98.36065600000001</v>
@@ -1376,7 +1376,7 @@
         <v>5.1216</v>
       </c>
       <c r="F38" t="n">
-        <v>5.1552</v>
+        <v>5.1329</v>
       </c>
       <c r="G38" t="n">
         <v>100</v>
@@ -1385,32 +1385,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D39" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E39" t="n">
-        <v>4271865</v>
+        <v>5.121</v>
       </c>
       <c r="F39" t="n">
-        <v>7299615</v>
+        <v>5.1323</v>
       </c>
       <c r="G39" t="n">
-        <v>96.721311</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
@@ -1423,10 +1423,10 @@
         <v>59</v>
       </c>
       <c r="E40" t="n">
-        <v>1833179</v>
+        <v>4271865</v>
       </c>
       <c r="F40" t="n">
-        <v>2704550</v>
+        <v>7299615</v>
       </c>
       <c r="G40" t="n">
         <v>96.721311</v>
@@ -1435,7 +1435,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
@@ -1448,10 +1448,10 @@
         <v>59</v>
       </c>
       <c r="E41" t="n">
-        <v>2438686</v>
+        <v>1833179</v>
       </c>
       <c r="F41" t="n">
-        <v>4595065</v>
+        <v>2704550</v>
       </c>
       <c r="G41" t="n">
         <v>96.721311</v>
@@ -1460,7 +1460,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
@@ -1473,10 +1473,10 @@
         <v>59</v>
       </c>
       <c r="E42" t="n">
-        <v>2.36</v>
+        <v>2438686</v>
       </c>
       <c r="F42" t="n">
-        <v>4.74</v>
+        <v>4595065</v>
       </c>
       <c r="G42" t="n">
         <v>96.721311</v>
@@ -1485,7 +1485,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
@@ -1498,10 +1498,10 @@
         <v>59</v>
       </c>
       <c r="E43" t="n">
-        <v>1.58</v>
+        <v>2.36</v>
       </c>
       <c r="F43" t="n">
-        <v>3.24</v>
+        <v>4.74</v>
       </c>
       <c r="G43" t="n">
         <v>96.721311</v>
@@ -1510,7 +1510,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
@@ -1523,10 +1523,10 @@
         <v>59</v>
       </c>
       <c r="E44" t="n">
-        <v>2.94</v>
+        <v>1.58</v>
       </c>
       <c r="F44" t="n">
-        <v>5.62</v>
+        <v>3.24</v>
       </c>
       <c r="G44" t="n">
         <v>96.721311</v>
@@ -1535,7 +1535,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
@@ -1548,10 +1548,10 @@
         <v>59</v>
       </c>
       <c r="E45" t="n">
-        <v>20.26</v>
+        <v>2.94</v>
       </c>
       <c r="F45" t="n">
-        <v>33.42</v>
+        <v>5.62</v>
       </c>
       <c r="G45" t="n">
         <v>96.721311</v>
@@ -1560,57 +1560,57 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="D46" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E46" t="n">
-        <v>355671</v>
+        <v>20.26</v>
       </c>
       <c r="F46" t="n">
-        <v>367558</v>
+        <v>33.42</v>
       </c>
       <c r="G46" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46142</v>
+        <v>46203</v>
       </c>
       <c r="D47" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E47" t="n">
-        <v>0.631159</v>
+        <v>355671</v>
       </c>
       <c r="F47" t="n">
-        <v>0.511964</v>
+        <v>367558</v>
       </c>
       <c r="G47" t="n">
-        <v>93.442623</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
@@ -1623,10 +1623,10 @@
         <v>57</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.641498</v>
+        <v>0.631159</v>
       </c>
       <c r="F48" t="n">
-        <v>-3.561276</v>
+        <v>0.511964</v>
       </c>
       <c r="G48" t="n">
         <v>93.442623</v>
@@ -1635,82 +1635,82 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46234</v>
+        <v>46142</v>
       </c>
       <c r="D49" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E49" t="n">
-        <v>0.423696</v>
+        <v>-0.641498</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.413399</v>
+        <v>-3.561276</v>
       </c>
       <c r="G49" t="n">
-        <v>98.36065600000001</v>
+        <v>93.442623</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D50" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E50" t="n">
-        <v>1.736829</v>
+        <v>0.423696</v>
       </c>
       <c r="F50" t="n">
-        <v>0.565068</v>
+        <v>-0.844183</v>
       </c>
       <c r="G50" t="n">
-        <v>95.08196700000001</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D51" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E51" t="n">
-        <v>0.972464</v>
+        <v>0.423745</v>
       </c>
       <c r="F51" t="n">
-        <v>0.742264</v>
+        <v>-0.8442809999999999</v>
       </c>
       <c r="G51" t="n">
-        <v>95.08196700000001</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
@@ -1723,10 +1723,10 @@
         <v>58</v>
       </c>
       <c r="E52" t="n">
-        <v>2.311409</v>
+        <v>1.736829</v>
       </c>
       <c r="F52" t="n">
-        <v>0.461065</v>
+        <v>0.565068</v>
       </c>
       <c r="G52" t="n">
         <v>95.08196700000001</v>
@@ -1735,82 +1735,82 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="D53" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E53" t="n">
-        <v>4.139781</v>
+        <v>0.972464</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.964334</v>
+        <v>0.742264</v>
       </c>
       <c r="G53" t="n">
-        <v>96.721311</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>44742</v>
+        <v>44439</v>
       </c>
       <c r="C54" s="1" t="n">
         <v>46173</v>
       </c>
       <c r="D54" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="E54" t="n">
-        <v>11.88673</v>
+        <v>2.311409</v>
       </c>
       <c r="F54" t="n">
-        <v>4.724907</v>
+        <v>0.461065</v>
       </c>
       <c r="G54" t="n">
-        <v>78.688525</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>44742</v>
+        <v>44439</v>
       </c>
       <c r="C55" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D55" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E55" t="n">
-        <v>10.700862</v>
+        <v>4.139781</v>
       </c>
       <c r="F55" t="n">
-        <v>3.177699</v>
+        <v>-0.964334</v>
       </c>
       <c r="G55" t="n">
-        <v>80.32786900000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
@@ -1823,10 +1823,10 @@
         <v>48</v>
       </c>
       <c r="E56" t="n">
-        <v>11.919595</v>
+        <v>11.88673</v>
       </c>
       <c r="F56" t="n">
-        <v>4.420848</v>
+        <v>4.724907</v>
       </c>
       <c r="G56" t="n">
         <v>78.688525</v>
@@ -1835,57 +1835,57 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>44439</v>
+        <v>44742</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D57" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>10.700862</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>3.177699</v>
       </c>
       <c r="G57" t="n">
-        <v>98.36065600000001</v>
+        <v>80.32786900000001</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>44439</v>
+        <v>44742</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D58" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="E58" t="n">
-        <v>0.003276</v>
+        <v>11.919595</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.000497</v>
+        <v>4.420848</v>
       </c>
       <c r="G58" t="n">
-        <v>98.36065600000001</v>
+        <v>78.688525</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
@@ -1898,10 +1898,10 @@
         <v>60</v>
       </c>
       <c r="E59" t="n">
-        <v>0.003276</v>
+        <v>1</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.000497</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
         <v>98.36065600000001</v>
@@ -1910,57 +1910,57 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D60" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E60" t="n">
-        <v>0.01</v>
+        <v>0.003276</v>
       </c>
       <c r="F60" t="n">
-        <v>0.11</v>
+        <v>-0.000497</v>
       </c>
       <c r="G60" t="n">
-        <v>95.08196700000001</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D61" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.02</v>
+        <v>0.003276</v>
       </c>
       <c r="F61" t="n">
-        <v>0.09</v>
+        <v>-0.000497</v>
       </c>
       <c r="G61" t="n">
-        <v>95.08196700000001</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
@@ -1973,7 +1973,7 @@
         <v>58</v>
       </c>
       <c r="E62" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F62" t="n">
         <v>0.11</v>
@@ -1985,7 +1985,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
@@ -1998,12 +1998,62 @@
         <v>58</v>
       </c>
       <c r="E63" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="G63" t="n">
+        <v>95.08196700000001</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
+        </is>
+      </c>
+      <c r="B64" s="1" t="n">
+        <v>44439</v>
+      </c>
+      <c r="C64" s="1" t="n">
+        <v>46173</v>
+      </c>
+      <c r="D64" t="n">
+        <v>58</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="G64" t="n">
+        <v>95.08196700000001</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_juros_credito_total</t>
+        </is>
+      </c>
+      <c r="B65" s="1" t="n">
+        <v>44439</v>
+      </c>
+      <c r="C65" s="1" t="n">
+        <v>46173</v>
+      </c>
+      <c r="D65" t="n">
+        <v>58</v>
+      </c>
+      <c r="E65" t="n">
         <v>0.66</v>
       </c>
-      <c r="F63" t="n">
+      <c r="F65" t="n">
         <v>-0.09</v>
       </c>
-      <c r="G63" t="n">
+      <c r="G65" t="n">
         <v>95.08196700000001</v>
       </c>
     </row>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -476,7 +476,7 @@
         <v>121801</v>
       </c>
       <c r="F2" t="n">
-        <v>172742</v>
+        <v>177866</v>
       </c>
       <c r="G2" t="n">
         <v>100</v>
@@ -501,7 +501,7 @@
         <v>117.110001</v>
       </c>
       <c r="F3" t="n">
-        <v>169.800003</v>
+        <v>175.009995</v>
       </c>
       <c r="G3" t="n">
         <v>100</v>
@@ -526,7 +526,7 @@
         <v>141.800003</v>
       </c>
       <c r="F4" t="n">
-        <v>107.760002</v>
+        <v>111.080002</v>
       </c>
       <c r="G4" t="n">
         <v>100</v>
@@ -551,7 +551,7 @@
         <v>250.350006</v>
       </c>
       <c r="F5" t="n">
-        <v>435.079987</v>
+        <v>436.290009</v>
       </c>
       <c r="G5" t="n">
         <v>100</v>
@@ -576,7 +576,7 @@
         <v>5.0804</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1146</v>
+        <v>5.1075</v>
       </c>
       <c r="G6" t="n">
         <v>100</v>
@@ -601,7 +601,7 @@
         <v>6.0387</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8474</v>
+        <v>5.8296</v>
       </c>
       <c r="G7" t="n">
         <v>100</v>
@@ -626,7 +626,7 @@
         <v>4395.259766</v>
       </c>
       <c r="F8" t="n">
-        <v>7543.640137</v>
+        <v>7575.390137</v>
       </c>
       <c r="G8" t="n">
         <v>100</v>
@@ -651,7 +651,7 @@
         <v>14672.679688</v>
       </c>
       <c r="F9" t="n">
-        <v>26206.890625</v>
+        <v>26281.609375</v>
       </c>
       <c r="G9" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
         <v>34935.46875</v>
       </c>
       <c r="F10" t="n">
-        <v>52487.410156</v>
+        <v>52637.011719</v>
       </c>
       <c r="G10" t="n">
         <v>100</v>
@@ -701,7 +701,7 @@
         <v>1812.599976</v>
       </c>
       <c r="F11" t="n">
-        <v>4117.700195</v>
+        <v>4104.100098</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
@@ -726,7 +726,7 @@
         <v>73.949997</v>
       </c>
       <c r="F12" t="n">
-        <v>71.949997</v>
+        <v>71.410004</v>
       </c>
       <c r="G12" t="n">
         <v>100</v>
@@ -751,7 +751,7 @@
         <v>76.33000199999999</v>
       </c>
       <c r="F13" t="n">
-        <v>76.360001</v>
+        <v>76.010002</v>
       </c>
       <c r="G13" t="n">
         <v>100</v>
@@ -776,7 +776,7 @@
         <v>1414.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1180.25</v>
+        <v>1196.5</v>
       </c>
       <c r="G14" t="n">
         <v>100</v>
@@ -801,7 +801,7 @@
         <v>547</v>
       </c>
       <c r="F15" t="n">
-        <v>451.75</v>
+        <v>438</v>
       </c>
       <c r="G15" t="n">
         <v>100</v>
@@ -826,7 +826,7 @@
         <v>-2.479454</v>
       </c>
       <c r="F16" t="n">
-        <v>0.417384</v>
+        <v>3.396038</v>
       </c>
       <c r="G16" t="n">
         <v>98.36065600000001</v>
@@ -851,7 +851,7 @@
         <v>-2.58731</v>
       </c>
       <c r="F17" t="n">
-        <v>0.443656</v>
+        <v>3.525579</v>
       </c>
       <c r="G17" t="n">
         <v>98.36065600000001</v>
@@ -876,7 +876,7 @@
         <v>-3.857547</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.203743</v>
+        <v>2.870901</v>
       </c>
       <c r="G18" t="n">
         <v>98.36065600000001</v>
@@ -901,7 +901,7 @@
         <v>1.457956</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.130841</v>
+        <v>0.14691</v>
       </c>
       <c r="G19" t="n">
         <v>98.36065600000001</v>
@@ -926,7 +926,7 @@
         <v>2.017557</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.296596</v>
+        <v>-1.433616</v>
       </c>
       <c r="G20" t="n">
         <v>98.36065600000001</v>
@@ -951,7 +951,7 @@
         <v>1.212177</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.178941</v>
+        <v>-1.479767</v>
       </c>
       <c r="G21" t="n">
         <v>98.36065600000001</v>
@@ -976,7 +976,7 @@
         <v>2.899042</v>
       </c>
       <c r="F22" t="n">
-        <v>0.590454</v>
+        <v>1.013824</v>
       </c>
       <c r="G22" t="n">
         <v>98.36065600000001</v>
@@ -1001,7 +1001,7 @@
         <v>3.997638</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.026055</v>
+        <v>0.258981</v>
       </c>
       <c r="G23" t="n">
         <v>98.36065600000001</v>
@@ -1026,7 +1026,7 @@
         <v>1.217278</v>
       </c>
       <c r="F24" t="n">
-        <v>0.321509</v>
+        <v>0.607449</v>
       </c>
       <c r="G24" t="n">
         <v>98.36065600000001</v>
@@ -1051,7 +1051,7 @@
         <v>0.132408</v>
       </c>
       <c r="F25" t="n">
-        <v>2.356516</v>
+        <v>2.018449</v>
       </c>
       <c r="G25" t="n">
         <v>98.36065600000001</v>
@@ -1076,7 +1076,7 @@
         <v>-7.369841</v>
       </c>
       <c r="F26" t="n">
-        <v>3.525175</v>
+        <v>2.748207</v>
       </c>
       <c r="G26" t="n">
         <v>98.36065600000001</v>
@@ -1101,7 +1101,7 @@
         <v>-4.375742</v>
       </c>
       <c r="F27" t="n">
-        <v>4.717502</v>
+        <v>4.237526</v>
       </c>
       <c r="G27" t="n">
         <v>98.36065600000001</v>
@@ -1126,7 +1126,7 @@
         <v>-8.199329000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>5.686143</v>
+        <v>7.141258</v>
       </c>
       <c r="G28" t="n">
         <v>98.36065600000001</v>
@@ -1151,7 +1151,7 @@
         <v>-2.3766</v>
       </c>
       <c r="F29" t="n">
-        <v>9.448819</v>
+        <v>6.117505</v>
       </c>
       <c r="G29" t="n">
         <v>98.36065600000001</v>
@@ -1242,19 +1242,19 @@
         <v>44408</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D33" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E33" t="n">
         <v>0.96</v>
       </c>
       <c r="F33" t="n">
-        <v>0.58</v>
+        <v>0.16</v>
       </c>
       <c r="G33" t="n">
-        <v>96.721311</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="34">
@@ -1292,19 +1292,19 @@
         <v>44408</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D35" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E35" t="n">
         <v>1.02</v>
       </c>
       <c r="F35" t="n">
-        <v>0.65</v>
+        <v>0.14</v>
       </c>
       <c r="G35" t="n">
-        <v>96.721311</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="36">
@@ -1376,7 +1376,7 @@
         <v>5.1216</v>
       </c>
       <c r="F38" t="n">
-        <v>5.1329</v>
+        <v>5.1088</v>
       </c>
       <c r="G38" t="n">
         <v>100</v>
@@ -1401,7 +1401,7 @@
         <v>5.121</v>
       </c>
       <c r="F39" t="n">
-        <v>5.1323</v>
+        <v>5.1082</v>
       </c>
       <c r="G39" t="n">
         <v>100</v>
@@ -1676,7 +1676,7 @@
         <v>0.423696</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.844183</v>
+        <v>-1.30974</v>
       </c>
       <c r="G50" t="n">
         <v>98.36065600000001</v>
@@ -1701,7 +1701,7 @@
         <v>0.423745</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.8442809999999999</v>
+        <v>-1.309892</v>
       </c>
       <c r="G51" t="n">
         <v>98.36065600000001</v>
@@ -1817,19 +1817,19 @@
         <v>44742</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D56" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E56" t="n">
         <v>11.88673</v>
       </c>
       <c r="F56" t="n">
-        <v>4.724907</v>
+        <v>4.641328</v>
       </c>
       <c r="G56" t="n">
-        <v>78.688525</v>
+        <v>80.32786900000001</v>
       </c>
     </row>
     <row r="57">
@@ -1867,19 +1867,19 @@
         <v>44742</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D58" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E58" t="n">
         <v>11.919595</v>
       </c>
       <c r="F58" t="n">
-        <v>4.420848</v>
+        <v>4.327084</v>
       </c>
       <c r="G58" t="n">
-        <v>78.688525</v>
+        <v>80.32786900000001</v>
       </c>
     </row>
     <row r="59">

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -701,7 +701,7 @@
         <v>1812.599976</v>
       </c>
       <c r="F11" t="n">
-        <v>4104.100098</v>
+        <v>4113.700195</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
@@ -776,7 +776,7 @@
         <v>1414.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1196.5</v>
+        <v>1190.75</v>
       </c>
       <c r="G14" t="n">
         <v>100</v>
@@ -801,7 +801,7 @@
         <v>547</v>
       </c>
       <c r="F15" t="n">
-        <v>438</v>
+        <v>461</v>
       </c>
       <c r="G15" t="n">
         <v>100</v>
@@ -1051,7 +1051,7 @@
         <v>0.132408</v>
       </c>
       <c r="F25" t="n">
-        <v>2.018449</v>
+        <v>2.257086</v>
       </c>
       <c r="G25" t="n">
         <v>98.36065600000001</v>
@@ -1126,7 +1126,7 @@
         <v>-8.199329000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>7.141258</v>
+        <v>6.626371</v>
       </c>
       <c r="G28" t="n">
         <v>98.36065600000001</v>
@@ -1151,7 +1151,7 @@
         <v>-2.3766</v>
       </c>
       <c r="F29" t="n">
-        <v>6.117505</v>
+        <v>11.689885</v>
       </c>
       <c r="G29" t="n">
         <v>98.36065600000001</v>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -576,7 +576,7 @@
         <v>5.0804</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1075</v>
+        <v>5.1165</v>
       </c>
       <c r="G6" t="n">
         <v>100</v>
@@ -601,7 +601,7 @@
         <v>6.0387</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8296</v>
+        <v>5.8455</v>
       </c>
       <c r="G7" t="n">
         <v>100</v>
@@ -701,7 +701,7 @@
         <v>1812.599976</v>
       </c>
       <c r="F11" t="n">
-        <v>4113.700195</v>
+        <v>4067.899902</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
@@ -726,7 +726,7 @@
         <v>73.949997</v>
       </c>
       <c r="F12" t="n">
-        <v>71.410004</v>
+        <v>74.129997</v>
       </c>
       <c r="G12" t="n">
         <v>100</v>
@@ -751,7 +751,7 @@
         <v>76.33000199999999</v>
       </c>
       <c r="F13" t="n">
-        <v>76.010002</v>
+        <v>78.879997</v>
       </c>
       <c r="G13" t="n">
         <v>100</v>
@@ -776,7 +776,7 @@
         <v>1414.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1190.75</v>
+        <v>1196.25</v>
       </c>
       <c r="G14" t="n">
         <v>100</v>
@@ -801,7 +801,7 @@
         <v>547</v>
       </c>
       <c r="F15" t="n">
-        <v>461</v>
+        <v>467.25</v>
       </c>
       <c r="G15" t="n">
         <v>100</v>
@@ -926,7 +926,7 @@
         <v>2.017557</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.433616</v>
+        <v>-1.259934</v>
       </c>
       <c r="G20" t="n">
         <v>98.36065600000001</v>
@@ -951,7 +951,7 @@
         <v>1.212177</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.479767</v>
+        <v>-1.211055</v>
       </c>
       <c r="G21" t="n">
         <v>98.36065600000001</v>
@@ -1051,7 +1051,7 @@
         <v>0.132408</v>
       </c>
       <c r="F25" t="n">
-        <v>2.257086</v>
+        <v>1.118596</v>
       </c>
       <c r="G25" t="n">
         <v>98.36065600000001</v>
@@ -1076,7 +1076,7 @@
         <v>-7.369841</v>
       </c>
       <c r="F26" t="n">
-        <v>2.748207</v>
+        <v>6.661867</v>
       </c>
       <c r="G26" t="n">
         <v>98.36065600000001</v>
@@ -1101,7 +1101,7 @@
         <v>-4.375742</v>
       </c>
       <c r="F27" t="n">
-        <v>4.237526</v>
+        <v>8.17334</v>
       </c>
       <c r="G27" t="n">
         <v>98.36065600000001</v>
@@ -1126,7 +1126,7 @@
         <v>-8.199329000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>6.626371</v>
+        <v>7.118872</v>
       </c>
       <c r="G28" t="n">
         <v>98.36065600000001</v>
@@ -1151,7 +1151,7 @@
         <v>-2.3766</v>
       </c>
       <c r="F29" t="n">
-        <v>11.689885</v>
+        <v>13.204119</v>
       </c>
       <c r="G29" t="n">
         <v>98.36065600000001</v>
@@ -1260,7 +1260,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m</t>
+          <t>bcb_sgs_inpc</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1273,10 +1273,10 @@
         <v>60</v>
       </c>
       <c r="E34" t="n">
-        <v>0.78</v>
+        <v>1.02</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.5</v>
+        <v>0.14</v>
       </c>
       <c r="G34" t="n">
         <v>98.36065600000001</v>
@@ -1285,32 +1285,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc</t>
+          <t>bcb_sgs_ibc_br_sa</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46203</v>
+        <v>46142</v>
       </c>
       <c r="D35" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E35" t="n">
-        <v>1.02</v>
+        <v>96.42256999999999</v>
       </c>
       <c r="F35" t="n">
-        <v>0.14</v>
+        <v>111.15205</v>
       </c>
       <c r="G35" t="n">
-        <v>98.36065600000001</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br_sa</t>
+          <t>bcb_sgs_ibc_br</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
@@ -1323,10 +1323,10 @@
         <v>58</v>
       </c>
       <c r="E36" t="n">
-        <v>96.42256999999999</v>
+        <v>99.83515</v>
       </c>
       <c r="F36" t="n">
-        <v>111.15205</v>
+        <v>113.72712</v>
       </c>
       <c r="G36" t="n">
         <v>95.08196700000001</v>
@@ -1335,32 +1335,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br</t>
+          <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46142</v>
+        <v>46234</v>
       </c>
       <c r="D37" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E37" t="n">
-        <v>99.83515</v>
+        <v>5.1216</v>
       </c>
       <c r="F37" t="n">
-        <v>113.72712</v>
+        <v>5.1088</v>
       </c>
       <c r="G37" t="n">
-        <v>95.08196700000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_venda_usd</t>
+          <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
@@ -1373,10 +1373,10 @@
         <v>61</v>
       </c>
       <c r="E38" t="n">
-        <v>5.1216</v>
+        <v>5.121</v>
       </c>
       <c r="F38" t="n">
-        <v>5.1088</v>
+        <v>5.1082</v>
       </c>
       <c r="G38" t="n">
         <v>100</v>
@@ -1385,32 +1385,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_compra_usd</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D39" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E39" t="n">
-        <v>5.121</v>
+        <v>4271865</v>
       </c>
       <c r="F39" t="n">
-        <v>5.1082</v>
+        <v>7299615</v>
       </c>
       <c r="G39" t="n">
-        <v>100</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
@@ -1423,10 +1423,10 @@
         <v>59</v>
       </c>
       <c r="E40" t="n">
-        <v>4271865</v>
+        <v>1833179</v>
       </c>
       <c r="F40" t="n">
-        <v>7299615</v>
+        <v>2704550</v>
       </c>
       <c r="G40" t="n">
         <v>96.721311</v>
@@ -1435,7 +1435,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
@@ -1448,10 +1448,10 @@
         <v>59</v>
       </c>
       <c r="E41" t="n">
-        <v>1833179</v>
+        <v>2438686</v>
       </c>
       <c r="F41" t="n">
-        <v>2704550</v>
+        <v>4595065</v>
       </c>
       <c r="G41" t="n">
         <v>96.721311</v>
@@ -1460,7 +1460,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
@@ -1473,10 +1473,10 @@
         <v>59</v>
       </c>
       <c r="E42" t="n">
-        <v>2438686</v>
+        <v>2.36</v>
       </c>
       <c r="F42" t="n">
-        <v>4595065</v>
+        <v>4.74</v>
       </c>
       <c r="G42" t="n">
         <v>96.721311</v>
@@ -1485,7 +1485,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
@@ -1498,10 +1498,10 @@
         <v>59</v>
       </c>
       <c r="E43" t="n">
-        <v>2.36</v>
+        <v>1.58</v>
       </c>
       <c r="F43" t="n">
-        <v>4.74</v>
+        <v>3.24</v>
       </c>
       <c r="G43" t="n">
         <v>96.721311</v>
@@ -1510,7 +1510,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
@@ -1523,10 +1523,10 @@
         <v>59</v>
       </c>
       <c r="E44" t="n">
-        <v>1.58</v>
+        <v>2.94</v>
       </c>
       <c r="F44" t="n">
-        <v>3.24</v>
+        <v>5.62</v>
       </c>
       <c r="G44" t="n">
         <v>96.721311</v>
@@ -1535,7 +1535,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
@@ -1548,10 +1548,10 @@
         <v>59</v>
       </c>
       <c r="E45" t="n">
-        <v>2.94</v>
+        <v>20.26</v>
       </c>
       <c r="F45" t="n">
-        <v>5.62</v>
+        <v>33.42</v>
       </c>
       <c r="G45" t="n">
         <v>96.721311</v>
@@ -1560,57 +1560,57 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D46" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E46" t="n">
-        <v>20.26</v>
+        <v>355671</v>
       </c>
       <c r="F46" t="n">
-        <v>33.42</v>
+        <v>367558</v>
       </c>
       <c r="G46" t="n">
-        <v>96.721311</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46203</v>
+        <v>46142</v>
       </c>
       <c r="D47" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E47" t="n">
-        <v>355671</v>
+        <v>0.631159</v>
       </c>
       <c r="F47" t="n">
-        <v>367558</v>
+        <v>0.511964</v>
       </c>
       <c r="G47" t="n">
-        <v>98.36065600000001</v>
+        <v>93.442623</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
@@ -1623,10 +1623,10 @@
         <v>57</v>
       </c>
       <c r="E48" t="n">
-        <v>0.631159</v>
+        <v>-0.641498</v>
       </c>
       <c r="F48" t="n">
-        <v>0.511964</v>
+        <v>-3.561276</v>
       </c>
       <c r="G48" t="n">
         <v>93.442623</v>
@@ -1635,32 +1635,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46142</v>
+        <v>46234</v>
       </c>
       <c r="D49" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.641498</v>
+        <v>0.423696</v>
       </c>
       <c r="F49" t="n">
-        <v>-3.561276</v>
+        <v>-1.30974</v>
       </c>
       <c r="G49" t="n">
-        <v>93.442623</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
@@ -1673,10 +1673,10 @@
         <v>60</v>
       </c>
       <c r="E50" t="n">
-        <v>0.423696</v>
+        <v>0.423745</v>
       </c>
       <c r="F50" t="n">
-        <v>-1.30974</v>
+        <v>-1.309892</v>
       </c>
       <c r="G50" t="n">
         <v>98.36065600000001</v>
@@ -1685,32 +1685,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D51" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E51" t="n">
-        <v>0.423745</v>
+        <v>1.736829</v>
       </c>
       <c r="F51" t="n">
-        <v>-1.309892</v>
+        <v>0.565068</v>
       </c>
       <c r="G51" t="n">
-        <v>98.36065600000001</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
@@ -1723,10 +1723,10 @@
         <v>58</v>
       </c>
       <c r="E52" t="n">
-        <v>1.736829</v>
+        <v>0.972464</v>
       </c>
       <c r="F52" t="n">
-        <v>0.565068</v>
+        <v>0.742264</v>
       </c>
       <c r="G52" t="n">
         <v>95.08196700000001</v>
@@ -1735,7 +1735,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
@@ -1748,10 +1748,10 @@
         <v>58</v>
       </c>
       <c r="E53" t="n">
-        <v>0.972464</v>
+        <v>2.311409</v>
       </c>
       <c r="F53" t="n">
-        <v>0.742264</v>
+        <v>0.461065</v>
       </c>
       <c r="G53" t="n">
         <v>95.08196700000001</v>
@@ -1760,57 +1760,57 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D54" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E54" t="n">
-        <v>2.311409</v>
+        <v>4.139781</v>
       </c>
       <c r="F54" t="n">
-        <v>0.461065</v>
+        <v>-0.964334</v>
       </c>
       <c r="G54" t="n">
-        <v>95.08196700000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>44439</v>
+        <v>44742</v>
       </c>
       <c r="C55" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D55" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E55" t="n">
-        <v>4.139781</v>
+        <v>11.88673</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.964334</v>
+        <v>4.641328</v>
       </c>
       <c r="G55" t="n">
-        <v>96.721311</v>
+        <v>80.32786900000001</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
@@ -1823,10 +1823,10 @@
         <v>49</v>
       </c>
       <c r="E56" t="n">
-        <v>11.88673</v>
+        <v>11.919595</v>
       </c>
       <c r="F56" t="n">
-        <v>4.641328</v>
+        <v>4.327084</v>
       </c>
       <c r="G56" t="n">
         <v>80.32786900000001</v>
@@ -1835,57 +1835,57 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>44742</v>
+        <v>44439</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D57" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E57" t="n">
-        <v>10.700862</v>
+        <v>1</v>
       </c>
       <c r="F57" t="n">
-        <v>3.177699</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>80.32786900000001</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>44742</v>
+        <v>44439</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D58" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E58" t="n">
-        <v>11.919595</v>
+        <v>0.003276</v>
       </c>
       <c r="F58" t="n">
-        <v>4.327084</v>
+        <v>-0.000497</v>
       </c>
       <c r="G58" t="n">
-        <v>80.32786900000001</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
@@ -1898,10 +1898,10 @@
         <v>60</v>
       </c>
       <c r="E59" t="n">
-        <v>1</v>
+        <v>0.003276</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>-0.000497</v>
       </c>
       <c r="G59" t="n">
         <v>98.36065600000001</v>
@@ -1910,57 +1910,57 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D60" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E60" t="n">
-        <v>0.003276</v>
+        <v>0.01</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.000497</v>
+        <v>0.11</v>
       </c>
       <c r="G60" t="n">
-        <v>98.36065600000001</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D61" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E61" t="n">
-        <v>0.003276</v>
+        <v>-0.02</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.000497</v>
+        <v>0.09</v>
       </c>
       <c r="G61" t="n">
-        <v>98.36065600000001</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
@@ -1973,7 +1973,7 @@
         <v>58</v>
       </c>
       <c r="E62" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F62" t="n">
         <v>0.11</v>
@@ -1985,7 +1985,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
@@ -1998,62 +1998,12 @@
         <v>58</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.02</v>
+        <v>0.66</v>
       </c>
       <c r="F63" t="n">
-        <v>0.09</v>
+        <v>-0.09</v>
       </c>
       <c r="G63" t="n">
-        <v>95.08196700000001</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
-        </is>
-      </c>
-      <c r="B64" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="C64" s="1" t="n">
-        <v>46173</v>
-      </c>
-      <c r="D64" t="n">
-        <v>58</v>
-      </c>
-      <c r="E64" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F64" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="G64" t="n">
-        <v>95.08196700000001</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
-        </is>
-      </c>
-      <c r="B65" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="C65" s="1" t="n">
-        <v>46173</v>
-      </c>
-      <c r="D65" t="n">
-        <v>58</v>
-      </c>
-      <c r="E65" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="F65" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="G65" t="n">
         <v>95.08196700000001</v>
       </c>
     </row>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
         <v>121801</v>
       </c>
       <c r="F2" t="n">
-        <v>177866</v>
+        <v>175739</v>
       </c>
       <c r="G2" t="n">
         <v>100</v>
@@ -501,7 +501,7 @@
         <v>117.110001</v>
       </c>
       <c r="F3" t="n">
-        <v>175.009995</v>
+        <v>172.25</v>
       </c>
       <c r="G3" t="n">
         <v>100</v>
@@ -526,7 +526,7 @@
         <v>141.800003</v>
       </c>
       <c r="F4" t="n">
-        <v>111.080002</v>
+        <v>109.199997</v>
       </c>
       <c r="G4" t="n">
         <v>100</v>
@@ -551,7 +551,7 @@
         <v>250.350006</v>
       </c>
       <c r="F5" t="n">
-        <v>436.290009</v>
+        <v>434.600006</v>
       </c>
       <c r="G5" t="n">
         <v>100</v>
@@ -576,7 +576,7 @@
         <v>5.0804</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1165</v>
+        <v>5.1318</v>
       </c>
       <c r="G6" t="n">
         <v>100</v>
@@ -601,7 +601,7 @@
         <v>6.0387</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8455</v>
+        <v>5.8466</v>
       </c>
       <c r="G7" t="n">
         <v>100</v>
@@ -626,7 +626,7 @@
         <v>4395.259766</v>
       </c>
       <c r="F8" t="n">
-        <v>7575.390137</v>
+        <v>7515.339844</v>
       </c>
       <c r="G8" t="n">
         <v>100</v>
@@ -651,7 +651,7 @@
         <v>14672.679688</v>
       </c>
       <c r="F9" t="n">
-        <v>26281.609375</v>
+        <v>25873.179688</v>
       </c>
       <c r="G9" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
         <v>34935.46875</v>
       </c>
       <c r="F10" t="n">
-        <v>52637.011719</v>
+        <v>52498.640625</v>
       </c>
       <c r="G10" t="n">
         <v>100</v>
@@ -701,7 +701,7 @@
         <v>1812.599976</v>
       </c>
       <c r="F11" t="n">
-        <v>4067.899902</v>
+        <v>4029</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
@@ -726,7 +726,7 @@
         <v>73.949997</v>
       </c>
       <c r="F12" t="n">
-        <v>74.129997</v>
+        <v>80.510002</v>
       </c>
       <c r="G12" t="n">
         <v>100</v>
@@ -751,7 +751,7 @@
         <v>76.33000199999999</v>
       </c>
       <c r="F13" t="n">
-        <v>78.879997</v>
+        <v>86.900002</v>
       </c>
       <c r="G13" t="n">
         <v>100</v>
@@ -776,7 +776,7 @@
         <v>1414.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1196.25</v>
+        <v>1187.5</v>
       </c>
       <c r="G14" t="n">
         <v>100</v>
@@ -801,7 +801,7 @@
         <v>547</v>
       </c>
       <c r="F15" t="n">
-        <v>467.25</v>
+        <v>457.5</v>
       </c>
       <c r="G15" t="n">
         <v>100</v>
@@ -826,7 +826,7 @@
         <v>-2.479454</v>
       </c>
       <c r="F16" t="n">
-        <v>3.396038</v>
+        <v>2.159582</v>
       </c>
       <c r="G16" t="n">
         <v>98.36065600000001</v>
@@ -851,7 +851,7 @@
         <v>-2.58731</v>
       </c>
       <c r="F17" t="n">
-        <v>3.525579</v>
+        <v>1.892929</v>
       </c>
       <c r="G17" t="n">
         <v>98.36065600000001</v>
@@ -876,7 +876,7 @@
         <v>-3.857547</v>
       </c>
       <c r="F18" t="n">
-        <v>2.870901</v>
+        <v>1.129833</v>
       </c>
       <c r="G18" t="n">
         <v>98.36065600000001</v>
@@ -901,7 +901,7 @@
         <v>1.457956</v>
       </c>
       <c r="F19" t="n">
-        <v>0.14691</v>
+        <v>-0.241016</v>
       </c>
       <c r="G19" t="n">
         <v>98.36065600000001</v>
@@ -926,7 +926,7 @@
         <v>2.017557</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.259934</v>
+        <v>-0.964664</v>
       </c>
       <c r="G20" t="n">
         <v>98.36065600000001</v>
@@ -951,7 +951,7 @@
         <v>1.212177</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.211055</v>
+        <v>-1.192464</v>
       </c>
       <c r="G21" t="n">
         <v>98.36065600000001</v>
@@ -976,7 +976,7 @@
         <v>2.899042</v>
       </c>
       <c r="F22" t="n">
-        <v>1.013824</v>
+        <v>0.213085</v>
       </c>
       <c r="G22" t="n">
         <v>98.36065600000001</v>
@@ -1001,7 +1001,7 @@
         <v>3.997638</v>
       </c>
       <c r="F23" t="n">
-        <v>0.258981</v>
+        <v>-1.299095</v>
       </c>
       <c r="G23" t="n">
         <v>98.36065600000001</v>
@@ -1026,7 +1026,7 @@
         <v>1.217278</v>
       </c>
       <c r="F24" t="n">
-        <v>0.607449</v>
+        <v>0.342974</v>
       </c>
       <c r="G24" t="n">
         <v>98.36065600000001</v>
@@ -1051,7 +1051,7 @@
         <v>0.132408</v>
       </c>
       <c r="F25" t="n">
-        <v>1.118596</v>
+        <v>0.151634</v>
       </c>
       <c r="G25" t="n">
         <v>98.36065600000001</v>
@@ -1076,7 +1076,7 @@
         <v>-7.369841</v>
       </c>
       <c r="F26" t="n">
-        <v>6.661867</v>
+        <v>15.84173</v>
       </c>
       <c r="G26" t="n">
         <v>98.36065600000001</v>
@@ -1101,7 +1101,7 @@
         <v>-4.375742</v>
       </c>
       <c r="F27" t="n">
-        <v>8.17334</v>
+        <v>19.1717</v>
       </c>
       <c r="G27" t="n">
         <v>98.36065600000001</v>
@@ -1126,7 +1126,7 @@
         <v>-8.199329000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>7.118872</v>
+        <v>6.335348</v>
       </c>
       <c r="G28" t="n">
         <v>98.36065600000001</v>
@@ -1151,7 +1151,7 @@
         <v>-2.3766</v>
       </c>
       <c r="F29" t="n">
-        <v>13.204119</v>
+        <v>10.841914</v>
       </c>
       <c r="G29" t="n">
         <v>98.36065600000001</v>
@@ -1260,7 +1260,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc</t>
+          <t>bcb_sgs_igp_m</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1273,10 +1273,10 @@
         <v>60</v>
       </c>
       <c r="E34" t="n">
-        <v>1.02</v>
+        <v>0.78</v>
       </c>
       <c r="F34" t="n">
-        <v>0.14</v>
+        <v>-0.5</v>
       </c>
       <c r="G34" t="n">
         <v>98.36065600000001</v>
@@ -1285,32 +1285,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br_sa</t>
+          <t>bcb_sgs_inpc</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46142</v>
+        <v>46203</v>
       </c>
       <c r="D35" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E35" t="n">
-        <v>96.42256999999999</v>
+        <v>1.02</v>
       </c>
       <c r="F35" t="n">
-        <v>111.15205</v>
+        <v>0.14</v>
       </c>
       <c r="G35" t="n">
-        <v>95.08196700000001</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br</t>
+          <t>bcb_sgs_ibc_br_sa</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
@@ -1323,10 +1323,10 @@
         <v>58</v>
       </c>
       <c r="E36" t="n">
-        <v>99.83515</v>
+        <v>96.42256999999999</v>
       </c>
       <c r="F36" t="n">
-        <v>113.72712</v>
+        <v>111.15205</v>
       </c>
       <c r="G36" t="n">
         <v>95.08196700000001</v>
@@ -1335,32 +1335,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_venda_usd</t>
+          <t>bcb_sgs_ibc_br</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46234</v>
+        <v>46142</v>
       </c>
       <c r="D37" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E37" t="n">
-        <v>5.1216</v>
+        <v>99.83515</v>
       </c>
       <c r="F37" t="n">
-        <v>5.1088</v>
+        <v>113.72712</v>
       </c>
       <c r="G37" t="n">
-        <v>100</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_compra_usd</t>
+          <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
@@ -1373,10 +1373,10 @@
         <v>61</v>
       </c>
       <c r="E38" t="n">
-        <v>5.121</v>
+        <v>5.1216</v>
       </c>
       <c r="F38" t="n">
-        <v>5.1082</v>
+        <v>5.1183</v>
       </c>
       <c r="G38" t="n">
         <v>100</v>
@@ -1385,32 +1385,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D39" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E39" t="n">
-        <v>4271865</v>
+        <v>5.121</v>
       </c>
       <c r="F39" t="n">
-        <v>7299615</v>
+        <v>5.1177</v>
       </c>
       <c r="G39" t="n">
-        <v>96.721311</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
@@ -1423,10 +1423,10 @@
         <v>59</v>
       </c>
       <c r="E40" t="n">
-        <v>1833179</v>
+        <v>4271865</v>
       </c>
       <c r="F40" t="n">
-        <v>2704550</v>
+        <v>7299615</v>
       </c>
       <c r="G40" t="n">
         <v>96.721311</v>
@@ -1435,7 +1435,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
@@ -1448,10 +1448,10 @@
         <v>59</v>
       </c>
       <c r="E41" t="n">
-        <v>2438686</v>
+        <v>1833179</v>
       </c>
       <c r="F41" t="n">
-        <v>4595065</v>
+        <v>2704550</v>
       </c>
       <c r="G41" t="n">
         <v>96.721311</v>
@@ -1460,7 +1460,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
@@ -1473,10 +1473,10 @@
         <v>59</v>
       </c>
       <c r="E42" t="n">
-        <v>2.36</v>
+        <v>2438686</v>
       </c>
       <c r="F42" t="n">
-        <v>4.74</v>
+        <v>4595065</v>
       </c>
       <c r="G42" t="n">
         <v>96.721311</v>
@@ -1485,7 +1485,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
@@ -1498,10 +1498,10 @@
         <v>59</v>
       </c>
       <c r="E43" t="n">
-        <v>1.58</v>
+        <v>2.36</v>
       </c>
       <c r="F43" t="n">
-        <v>3.24</v>
+        <v>4.74</v>
       </c>
       <c r="G43" t="n">
         <v>96.721311</v>
@@ -1510,7 +1510,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
@@ -1523,10 +1523,10 @@
         <v>59</v>
       </c>
       <c r="E44" t="n">
-        <v>2.94</v>
+        <v>1.58</v>
       </c>
       <c r="F44" t="n">
-        <v>5.62</v>
+        <v>3.24</v>
       </c>
       <c r="G44" t="n">
         <v>96.721311</v>
@@ -1535,7 +1535,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
@@ -1548,10 +1548,10 @@
         <v>59</v>
       </c>
       <c r="E45" t="n">
-        <v>20.26</v>
+        <v>2.94</v>
       </c>
       <c r="F45" t="n">
-        <v>33.42</v>
+        <v>5.62</v>
       </c>
       <c r="G45" t="n">
         <v>96.721311</v>
@@ -1560,57 +1560,57 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="D46" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E46" t="n">
-        <v>355671</v>
+        <v>20.26</v>
       </c>
       <c r="F46" t="n">
-        <v>367558</v>
+        <v>33.42</v>
       </c>
       <c r="G46" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46142</v>
+        <v>46203</v>
       </c>
       <c r="D47" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E47" t="n">
-        <v>0.631159</v>
+        <v>355671</v>
       </c>
       <c r="F47" t="n">
-        <v>0.511964</v>
+        <v>367558</v>
       </c>
       <c r="G47" t="n">
-        <v>93.442623</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
@@ -1623,10 +1623,10 @@
         <v>57</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.641498</v>
+        <v>0.631159</v>
       </c>
       <c r="F48" t="n">
-        <v>-3.561276</v>
+        <v>0.511964</v>
       </c>
       <c r="G48" t="n">
         <v>93.442623</v>
@@ -1635,32 +1635,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46234</v>
+        <v>46142</v>
       </c>
       <c r="D49" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E49" t="n">
-        <v>0.423696</v>
+        <v>-0.641498</v>
       </c>
       <c r="F49" t="n">
-        <v>-1.30974</v>
+        <v>-3.561276</v>
       </c>
       <c r="G49" t="n">
-        <v>98.36065600000001</v>
+        <v>93.442623</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
@@ -1673,10 +1673,10 @@
         <v>60</v>
       </c>
       <c r="E50" t="n">
-        <v>0.423745</v>
+        <v>0.423696</v>
       </c>
       <c r="F50" t="n">
-        <v>-1.309892</v>
+        <v>-1.126222</v>
       </c>
       <c r="G50" t="n">
         <v>98.36065600000001</v>
@@ -1685,32 +1685,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D51" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E51" t="n">
-        <v>1.736829</v>
+        <v>0.423745</v>
       </c>
       <c r="F51" t="n">
-        <v>0.565068</v>
+        <v>-1.126352</v>
       </c>
       <c r="G51" t="n">
-        <v>95.08196700000001</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
@@ -1723,10 +1723,10 @@
         <v>58</v>
       </c>
       <c r="E52" t="n">
-        <v>0.972464</v>
+        <v>1.736829</v>
       </c>
       <c r="F52" t="n">
-        <v>0.742264</v>
+        <v>0.565068</v>
       </c>
       <c r="G52" t="n">
         <v>95.08196700000001</v>
@@ -1735,7 +1735,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
@@ -1748,10 +1748,10 @@
         <v>58</v>
       </c>
       <c r="E53" t="n">
-        <v>2.311409</v>
+        <v>0.972464</v>
       </c>
       <c r="F53" t="n">
-        <v>0.461065</v>
+        <v>0.742264</v>
       </c>
       <c r="G53" t="n">
         <v>95.08196700000001</v>
@@ -1760,57 +1760,57 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="D54" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E54" t="n">
-        <v>4.139781</v>
+        <v>2.311409</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.964334</v>
+        <v>0.461065</v>
       </c>
       <c r="G54" t="n">
-        <v>96.721311</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>44742</v>
+        <v>44439</v>
       </c>
       <c r="C55" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D55" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E55" t="n">
-        <v>11.88673</v>
+        <v>4.139781</v>
       </c>
       <c r="F55" t="n">
-        <v>4.641328</v>
+        <v>-0.964334</v>
       </c>
       <c r="G55" t="n">
-        <v>80.32786900000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
@@ -1823,10 +1823,10 @@
         <v>49</v>
       </c>
       <c r="E56" t="n">
-        <v>11.919595</v>
+        <v>11.88673</v>
       </c>
       <c r="F56" t="n">
-        <v>4.327084</v>
+        <v>4.641328</v>
       </c>
       <c r="G56" t="n">
         <v>80.32786900000001</v>
@@ -1835,57 +1835,57 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>44439</v>
+        <v>44742</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D57" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>10.700862</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>3.177699</v>
       </c>
       <c r="G57" t="n">
-        <v>98.36065600000001</v>
+        <v>80.32786900000001</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>44439</v>
+        <v>44742</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D58" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E58" t="n">
-        <v>0.003276</v>
+        <v>11.919595</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.000497</v>
+        <v>4.327084</v>
       </c>
       <c r="G58" t="n">
-        <v>98.36065600000001</v>
+        <v>80.32786900000001</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
@@ -1898,10 +1898,10 @@
         <v>60</v>
       </c>
       <c r="E59" t="n">
-        <v>0.003276</v>
+        <v>1</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.000497</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
         <v>98.36065600000001</v>
@@ -1910,57 +1910,57 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D60" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E60" t="n">
-        <v>0.01</v>
+        <v>0.003276</v>
       </c>
       <c r="F60" t="n">
-        <v>0.11</v>
+        <v>-0.000497</v>
       </c>
       <c r="G60" t="n">
-        <v>95.08196700000001</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D61" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.02</v>
+        <v>0.003276</v>
       </c>
       <c r="F61" t="n">
-        <v>0.09</v>
+        <v>-0.000497</v>
       </c>
       <c r="G61" t="n">
-        <v>95.08196700000001</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
@@ -1973,7 +1973,7 @@
         <v>58</v>
       </c>
       <c r="E62" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F62" t="n">
         <v>0.11</v>
@@ -1985,7 +1985,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
@@ -1998,12 +1998,62 @@
         <v>58</v>
       </c>
       <c r="E63" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="G63" t="n">
+        <v>95.08196700000001</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
+        </is>
+      </c>
+      <c r="B64" s="1" t="n">
+        <v>44439</v>
+      </c>
+      <c r="C64" s="1" t="n">
+        <v>46173</v>
+      </c>
+      <c r="D64" t="n">
+        <v>58</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="G64" t="n">
+        <v>95.08196700000001</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_juros_credito_total</t>
+        </is>
+      </c>
+      <c r="B65" s="1" t="n">
+        <v>44439</v>
+      </c>
+      <c r="C65" s="1" t="n">
+        <v>46173</v>
+      </c>
+      <c r="D65" t="n">
+        <v>58</v>
+      </c>
+      <c r="E65" t="n">
         <v>0.66</v>
       </c>
-      <c r="F63" t="n">
+      <c r="F65" t="n">
         <v>-0.09</v>
       </c>
-      <c r="G63" t="n">
+      <c r="G65" t="n">
         <v>95.08196700000001</v>
       </c>
     </row>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -501,7 +501,7 @@
         <v>117.110001</v>
       </c>
       <c r="F3" t="n">
-        <v>172.25</v>
+        <v>173.600006</v>
       </c>
       <c r="G3" t="n">
         <v>100</v>
@@ -526,7 +526,7 @@
         <v>141.800003</v>
       </c>
       <c r="F4" t="n">
-        <v>109.199997</v>
+        <v>110.400002</v>
       </c>
       <c r="G4" t="n">
         <v>100</v>
@@ -551,7 +551,7 @@
         <v>250.350006</v>
       </c>
       <c r="F5" t="n">
-        <v>434.600006</v>
+        <v>432</v>
       </c>
       <c r="G5" t="n">
         <v>100</v>
@@ -576,7 +576,7 @@
         <v>5.0804</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1318</v>
+        <v>5.0745</v>
       </c>
       <c r="G6" t="n">
         <v>100</v>
@@ -601,7 +601,7 @@
         <v>6.0387</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8466</v>
+        <v>5.7922</v>
       </c>
       <c r="G7" t="n">
         <v>100</v>
@@ -701,7 +701,7 @@
         <v>1812.599976</v>
       </c>
       <c r="F11" t="n">
-        <v>4029</v>
+        <v>4035.899902</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
@@ -726,7 +726,7 @@
         <v>73.949997</v>
       </c>
       <c r="F12" t="n">
-        <v>80.510002</v>
+        <v>79.81999999999999</v>
       </c>
       <c r="G12" t="n">
         <v>100</v>
@@ -751,7 +751,7 @@
         <v>76.33000199999999</v>
       </c>
       <c r="F13" t="n">
-        <v>86.900002</v>
+        <v>85.260002</v>
       </c>
       <c r="G13" t="n">
         <v>100</v>
@@ -776,7 +776,7 @@
         <v>1414.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1187.5</v>
+        <v>1195.5</v>
       </c>
       <c r="G14" t="n">
         <v>100</v>
@@ -801,7 +801,7 @@
         <v>547</v>
       </c>
       <c r="F15" t="n">
-        <v>457.5</v>
+        <v>465</v>
       </c>
       <c r="G15" t="n">
         <v>100</v>
@@ -851,7 +851,7 @@
         <v>-2.58731</v>
       </c>
       <c r="F17" t="n">
-        <v>1.892929</v>
+        <v>2.691513</v>
       </c>
       <c r="G17" t="n">
         <v>98.36065600000001</v>
@@ -876,7 +876,7 @@
         <v>-3.857547</v>
       </c>
       <c r="F18" t="n">
-        <v>1.129833</v>
+        <v>2.241154</v>
       </c>
       <c r="G18" t="n">
         <v>98.36065600000001</v>
@@ -901,7 +901,7 @@
         <v>1.457956</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.241016</v>
+        <v>-0.837827</v>
       </c>
       <c r="G19" t="n">
         <v>98.36065600000001</v>
@@ -926,7 +926,7 @@
         <v>2.017557</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.964664</v>
+        <v>-2.070462</v>
       </c>
       <c r="G20" t="n">
         <v>98.36065600000001</v>
@@ -951,7 +951,7 @@
         <v>1.212177</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.192464</v>
+        <v>-2.111823</v>
       </c>
       <c r="G21" t="n">
         <v>98.36065600000001</v>
@@ -1051,7 +1051,7 @@
         <v>0.132408</v>
       </c>
       <c r="F25" t="n">
-        <v>0.151634</v>
+        <v>0.32315</v>
       </c>
       <c r="G25" t="n">
         <v>98.36065600000001</v>
@@ -1076,7 +1076,7 @@
         <v>-7.369841</v>
       </c>
       <c r="F26" t="n">
-        <v>15.84173</v>
+        <v>14.84892</v>
       </c>
       <c r="G26" t="n">
         <v>98.36065600000001</v>
@@ -1101,7 +1101,7 @@
         <v>-4.375742</v>
       </c>
       <c r="F27" t="n">
-        <v>19.1717</v>
+        <v>16.922661</v>
       </c>
       <c r="G27" t="n">
         <v>98.36065600000001</v>
@@ -1126,7 +1126,7 @@
         <v>-8.199329000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>6.335348</v>
+        <v>7.051713</v>
       </c>
       <c r="G28" t="n">
         <v>98.36065600000001</v>
@@ -1151,7 +1151,7 @@
         <v>-2.3766</v>
       </c>
       <c r="F29" t="n">
-        <v>10.841914</v>
+        <v>12.658995</v>
       </c>
       <c r="G29" t="n">
         <v>98.36065600000001</v>
@@ -1376,7 +1376,7 @@
         <v>5.1216</v>
       </c>
       <c r="F38" t="n">
-        <v>5.1183</v>
+        <v>5.0742</v>
       </c>
       <c r="G38" t="n">
         <v>100</v>
@@ -1401,7 +1401,7 @@
         <v>5.121</v>
       </c>
       <c r="F39" t="n">
-        <v>5.1177</v>
+        <v>5.0736</v>
       </c>
       <c r="G39" t="n">
         <v>100</v>
@@ -1676,7 +1676,7 @@
         <v>0.423696</v>
       </c>
       <c r="F50" t="n">
-        <v>-1.126222</v>
+        <v>-1.978132</v>
       </c>
       <c r="G50" t="n">
         <v>98.36065600000001</v>
@@ -1701,7 +1701,7 @@
         <v>0.423745</v>
       </c>
       <c r="F51" t="n">
-        <v>-1.126352</v>
+        <v>-1.978362</v>
       </c>
       <c r="G51" t="n">
         <v>98.36065600000001</v>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
         <v>121801</v>
       </c>
       <c r="F2" t="n">
-        <v>175739</v>
+        <v>175690.03125</v>
       </c>
       <c r="G2" t="n">
         <v>100</v>
@@ -501,7 +501,7 @@
         <v>117.110001</v>
       </c>
       <c r="F3" t="n">
-        <v>173.600006</v>
+        <v>172.649994</v>
       </c>
       <c r="G3" t="n">
         <v>100</v>
@@ -526,7 +526,7 @@
         <v>141.800003</v>
       </c>
       <c r="F4" t="n">
-        <v>110.400002</v>
+        <v>109.639999</v>
       </c>
       <c r="G4" t="n">
         <v>100</v>
@@ -551,7 +551,7 @@
         <v>250.350006</v>
       </c>
       <c r="F5" t="n">
-        <v>432</v>
+        <v>432.140015</v>
       </c>
       <c r="G5" t="n">
         <v>100</v>
@@ -576,7 +576,7 @@
         <v>5.0804</v>
       </c>
       <c r="F6" t="n">
-        <v>5.0745</v>
+        <v>5.0804</v>
       </c>
       <c r="G6" t="n">
         <v>100</v>
@@ -601,7 +601,7 @@
         <v>6.0387</v>
       </c>
       <c r="F7" t="n">
-        <v>5.7922</v>
+        <v>5.8103</v>
       </c>
       <c r="G7" t="n">
         <v>100</v>
@@ -626,7 +626,7 @@
         <v>4395.259766</v>
       </c>
       <c r="F8" t="n">
-        <v>7515.339844</v>
+        <v>7533.77002</v>
       </c>
       <c r="G8" t="n">
         <v>100</v>
@@ -651,7 +651,7 @@
         <v>14672.679688</v>
       </c>
       <c r="F9" t="n">
-        <v>25873.179688</v>
+        <v>26095.494141</v>
       </c>
       <c r="G9" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
         <v>34935.46875</v>
       </c>
       <c r="F10" t="n">
-        <v>52498.640625</v>
+        <v>52471</v>
       </c>
       <c r="G10" t="n">
         <v>100</v>
@@ -701,7 +701,7 @@
         <v>1812.599976</v>
       </c>
       <c r="F11" t="n">
-        <v>4035.899902</v>
+        <v>4041.800049</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
@@ -726,7 +726,7 @@
         <v>73.949997</v>
       </c>
       <c r="F12" t="n">
-        <v>79.81999999999999</v>
+        <v>79.040001</v>
       </c>
       <c r="G12" t="n">
         <v>100</v>
@@ -751,7 +751,7 @@
         <v>76.33000199999999</v>
       </c>
       <c r="F13" t="n">
-        <v>85.260002</v>
+        <v>84.449997</v>
       </c>
       <c r="G13" t="n">
         <v>100</v>
@@ -776,7 +776,7 @@
         <v>1414.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1195.5</v>
+        <v>1195</v>
       </c>
       <c r="G14" t="n">
         <v>100</v>
@@ -801,7 +801,7 @@
         <v>547</v>
       </c>
       <c r="F15" t="n">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="G15" t="n">
         <v>100</v>
@@ -826,7 +826,7 @@
         <v>-2.479454</v>
       </c>
       <c r="F16" t="n">
-        <v>2.159582</v>
+        <v>2.131116</v>
       </c>
       <c r="G16" t="n">
         <v>98.36065600000001</v>
@@ -851,7 +851,7 @@
         <v>-2.58731</v>
       </c>
       <c r="F17" t="n">
-        <v>2.691513</v>
+        <v>2.129542</v>
       </c>
       <c r="G17" t="n">
         <v>98.36065600000001</v>
@@ -876,7 +876,7 @@
         <v>-3.857547</v>
       </c>
       <c r="F18" t="n">
-        <v>2.241154</v>
+        <v>1.537318</v>
       </c>
       <c r="G18" t="n">
         <v>98.36065600000001</v>
@@ -901,7 +901,7 @@
         <v>1.457956</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.837827</v>
+        <v>-0.805688</v>
       </c>
       <c r="G19" t="n">
         <v>98.36065600000001</v>
@@ -926,7 +926,7 @@
         <v>2.017557</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.070462</v>
+        <v>-1.956603</v>
       </c>
       <c r="G20" t="n">
         <v>98.36065600000001</v>
@@ -951,7 +951,7 @@
         <v>1.212177</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.111823</v>
+        <v>-1.805937</v>
       </c>
       <c r="G21" t="n">
         <v>98.36065600000001</v>
@@ -976,7 +976,7 @@
         <v>2.899042</v>
       </c>
       <c r="F22" t="n">
-        <v>0.213085</v>
+        <v>0.458841</v>
       </c>
       <c r="G22" t="n">
         <v>98.36065600000001</v>
@@ -1001,7 +1001,7 @@
         <v>3.997638</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.299095</v>
+        <v>-0.45101</v>
       </c>
       <c r="G23" t="n">
         <v>98.36065600000001</v>
@@ -1026,7 +1026,7 @@
         <v>1.217278</v>
       </c>
       <c r="F24" t="n">
-        <v>0.342974</v>
+        <v>0.290144</v>
       </c>
       <c r="G24" t="n">
         <v>98.36065600000001</v>
@@ -1051,7 +1051,7 @@
         <v>0.132408</v>
       </c>
       <c r="F25" t="n">
-        <v>0.32315</v>
+        <v>0.469814</v>
       </c>
       <c r="G25" t="n">
         <v>98.36065600000001</v>
@@ -1076,7 +1076,7 @@
         <v>-7.369841</v>
       </c>
       <c r="F26" t="n">
-        <v>14.84892</v>
+        <v>13.72662</v>
       </c>
       <c r="G26" t="n">
         <v>98.36065600000001</v>
@@ -1101,7 +1101,7 @@
         <v>-4.375742</v>
       </c>
       <c r="F27" t="n">
-        <v>16.922661</v>
+        <v>15.811847</v>
       </c>
       <c r="G27" t="n">
         <v>98.36065600000001</v>
@@ -1126,7 +1126,7 @@
         <v>-8.199329000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>7.051713</v>
+        <v>7.00694</v>
       </c>
       <c r="G28" t="n">
         <v>98.36065600000001</v>
@@ -1151,7 +1151,7 @@
         <v>-2.3766</v>
       </c>
       <c r="F29" t="n">
-        <v>12.658995</v>
+        <v>13.385827</v>
       </c>
       <c r="G29" t="n">
         <v>98.36065600000001</v>
@@ -1376,7 +1376,7 @@
         <v>5.1216</v>
       </c>
       <c r="F38" t="n">
-        <v>5.0742</v>
+        <v>5.0727</v>
       </c>
       <c r="G38" t="n">
         <v>100</v>
@@ -1401,7 +1401,7 @@
         <v>5.121</v>
       </c>
       <c r="F39" t="n">
-        <v>5.0736</v>
+        <v>5.0721</v>
       </c>
       <c r="G39" t="n">
         <v>100</v>
@@ -1535,7 +1535,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
@@ -1548,10 +1548,10 @@
         <v>59</v>
       </c>
       <c r="E45" t="n">
-        <v>2.94</v>
+        <v>20.26</v>
       </c>
       <c r="F45" t="n">
-        <v>5.62</v>
+        <v>33.42</v>
       </c>
       <c r="G45" t="n">
         <v>96.721311</v>
@@ -1560,57 +1560,57 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D46" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E46" t="n">
-        <v>20.26</v>
+        <v>355671</v>
       </c>
       <c r="F46" t="n">
-        <v>33.42</v>
+        <v>367558</v>
       </c>
       <c r="G46" t="n">
-        <v>96.721311</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46203</v>
+        <v>46142</v>
       </c>
       <c r="D47" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E47" t="n">
-        <v>355671</v>
+        <v>0.631159</v>
       </c>
       <c r="F47" t="n">
-        <v>367558</v>
+        <v>0.511964</v>
       </c>
       <c r="G47" t="n">
-        <v>98.36065600000001</v>
+        <v>93.442623</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
@@ -1623,10 +1623,10 @@
         <v>57</v>
       </c>
       <c r="E48" t="n">
-        <v>0.631159</v>
+        <v>-0.641498</v>
       </c>
       <c r="F48" t="n">
-        <v>0.511964</v>
+        <v>-3.561276</v>
       </c>
       <c r="G48" t="n">
         <v>93.442623</v>
@@ -1635,32 +1635,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46142</v>
+        <v>46234</v>
       </c>
       <c r="D49" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.641498</v>
+        <v>0.423696</v>
       </c>
       <c r="F49" t="n">
-        <v>-3.561276</v>
+        <v>-2.007109</v>
       </c>
       <c r="G49" t="n">
-        <v>93.442623</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
@@ -1673,10 +1673,10 @@
         <v>60</v>
       </c>
       <c r="E50" t="n">
-        <v>0.423696</v>
+        <v>0.423745</v>
       </c>
       <c r="F50" t="n">
-        <v>-1.978132</v>
+        <v>-2.007342</v>
       </c>
       <c r="G50" t="n">
         <v>98.36065600000001</v>
@@ -1685,32 +1685,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D51" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E51" t="n">
-        <v>0.423745</v>
+        <v>1.736829</v>
       </c>
       <c r="F51" t="n">
-        <v>-1.978362</v>
+        <v>0.565068</v>
       </c>
       <c r="G51" t="n">
-        <v>98.36065600000001</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
@@ -1723,10 +1723,10 @@
         <v>58</v>
       </c>
       <c r="E52" t="n">
-        <v>1.736829</v>
+        <v>0.972464</v>
       </c>
       <c r="F52" t="n">
-        <v>0.565068</v>
+        <v>0.742264</v>
       </c>
       <c r="G52" t="n">
         <v>95.08196700000001</v>
@@ -1735,7 +1735,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
@@ -1748,10 +1748,10 @@
         <v>58</v>
       </c>
       <c r="E53" t="n">
-        <v>0.972464</v>
+        <v>2.311409</v>
       </c>
       <c r="F53" t="n">
-        <v>0.742264</v>
+        <v>0.461065</v>
       </c>
       <c r="G53" t="n">
         <v>95.08196700000001</v>
@@ -1760,57 +1760,57 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D54" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E54" t="n">
-        <v>2.311409</v>
+        <v>4.139781</v>
       </c>
       <c r="F54" t="n">
-        <v>0.461065</v>
+        <v>-0.964334</v>
       </c>
       <c r="G54" t="n">
-        <v>95.08196700000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>44439</v>
+        <v>44742</v>
       </c>
       <c r="C55" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D55" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E55" t="n">
-        <v>4.139781</v>
+        <v>11.88673</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.964334</v>
+        <v>4.641328</v>
       </c>
       <c r="G55" t="n">
-        <v>96.721311</v>
+        <v>80.32786900000001</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
@@ -1823,10 +1823,10 @@
         <v>49</v>
       </c>
       <c r="E56" t="n">
-        <v>11.88673</v>
+        <v>10.700862</v>
       </c>
       <c r="F56" t="n">
-        <v>4.641328</v>
+        <v>3.177699</v>
       </c>
       <c r="G56" t="n">
         <v>80.32786900000001</v>
@@ -1835,7 +1835,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
@@ -1848,10 +1848,10 @@
         <v>49</v>
       </c>
       <c r="E57" t="n">
-        <v>10.700862</v>
+        <v>11.919595</v>
       </c>
       <c r="F57" t="n">
-        <v>3.177699</v>
+        <v>4.327084</v>
       </c>
       <c r="G57" t="n">
         <v>80.32786900000001</v>
@@ -1860,32 +1860,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>44742</v>
+        <v>44439</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D58" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E58" t="n">
-        <v>11.919595</v>
+        <v>1</v>
       </c>
       <c r="F58" t="n">
-        <v>4.327084</v>
+        <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>80.32786900000001</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
@@ -1898,10 +1898,10 @@
         <v>60</v>
       </c>
       <c r="E59" t="n">
-        <v>1</v>
+        <v>0.003276</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>-0.000497</v>
       </c>
       <c r="G59" t="n">
         <v>98.36065600000001</v>
@@ -1910,7 +1910,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
@@ -1935,32 +1935,32 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D61" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E61" t="n">
-        <v>0.003276</v>
+        <v>0.01</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.000497</v>
+        <v>0.11</v>
       </c>
       <c r="G61" t="n">
-        <v>98.36065600000001</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
@@ -1973,10 +1973,10 @@
         <v>58</v>
       </c>
       <c r="E62" t="n">
-        <v>0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="F62" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="G62" t="n">
         <v>95.08196700000001</v>
@@ -1985,7 +1985,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
@@ -1998,62 +1998,12 @@
         <v>58</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.02</v>
+        <v>0.66</v>
       </c>
       <c r="F63" t="n">
-        <v>0.09</v>
+        <v>-0.09</v>
       </c>
       <c r="G63" t="n">
-        <v>95.08196700000001</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
-        </is>
-      </c>
-      <c r="B64" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="C64" s="1" t="n">
-        <v>46173</v>
-      </c>
-      <c r="D64" t="n">
-        <v>58</v>
-      </c>
-      <c r="E64" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F64" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="G64" t="n">
-        <v>95.08196700000001</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
-        </is>
-      </c>
-      <c r="B65" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="C65" s="1" t="n">
-        <v>46173</v>
-      </c>
-      <c r="D65" t="n">
-        <v>58</v>
-      </c>
-      <c r="E65" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="F65" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="G65" t="n">
         <v>95.08196700000001</v>
       </c>
     </row>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
         <v>121801</v>
       </c>
       <c r="F2" t="n">
-        <v>175690.03125</v>
+        <v>176011</v>
       </c>
       <c r="G2" t="n">
         <v>100</v>
@@ -501,7 +501,7 @@
         <v>117.110001</v>
       </c>
       <c r="F3" t="n">
-        <v>172.649994</v>
+        <v>172.759995</v>
       </c>
       <c r="G3" t="n">
         <v>100</v>
@@ -526,7 +526,7 @@
         <v>141.800003</v>
       </c>
       <c r="F4" t="n">
-        <v>109.639999</v>
+        <v>109.690002</v>
       </c>
       <c r="G4" t="n">
         <v>100</v>
@@ -551,7 +551,7 @@
         <v>250.350006</v>
       </c>
       <c r="F5" t="n">
-        <v>432.140015</v>
+        <v>433.399994</v>
       </c>
       <c r="G5" t="n">
         <v>100</v>
@@ -576,7 +576,7 @@
         <v>5.0804</v>
       </c>
       <c r="F6" t="n">
-        <v>5.0804</v>
+        <v>5.0761</v>
       </c>
       <c r="G6" t="n">
         <v>100</v>
@@ -601,7 +601,7 @@
         <v>6.0387</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8103</v>
+        <v>5.8178</v>
       </c>
       <c r="G7" t="n">
         <v>100</v>
@@ -626,7 +626,7 @@
         <v>4395.259766</v>
       </c>
       <c r="F8" t="n">
-        <v>7533.77002</v>
+        <v>7572.399902</v>
       </c>
       <c r="G8" t="n">
         <v>100</v>
@@ -651,7 +651,7 @@
         <v>14672.679688</v>
       </c>
       <c r="F9" t="n">
-        <v>26095.494141</v>
+        <v>26269.230469</v>
       </c>
       <c r="G9" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
         <v>34935.46875</v>
       </c>
       <c r="F10" t="n">
-        <v>52471</v>
+        <v>52658.640625</v>
       </c>
       <c r="G10" t="n">
         <v>100</v>
@@ -701,7 +701,7 @@
         <v>1812.599976</v>
       </c>
       <c r="F11" t="n">
-        <v>4041.800049</v>
+        <v>4029.300049</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
@@ -726,7 +726,7 @@
         <v>73.949997</v>
       </c>
       <c r="F12" t="n">
-        <v>79.040001</v>
+        <v>79.489998</v>
       </c>
       <c r="G12" t="n">
         <v>100</v>
@@ -751,7 +751,7 @@
         <v>76.33000199999999</v>
       </c>
       <c r="F13" t="n">
-        <v>84.449997</v>
+        <v>84.660004</v>
       </c>
       <c r="G13" t="n">
         <v>100</v>
@@ -776,7 +776,7 @@
         <v>1414.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1195</v>
+        <v>1204.5</v>
       </c>
       <c r="G14" t="n">
         <v>100</v>
@@ -801,7 +801,7 @@
         <v>547</v>
       </c>
       <c r="F15" t="n">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="G15" t="n">
         <v>100</v>
@@ -826,7 +826,7 @@
         <v>-2.479454</v>
       </c>
       <c r="F16" t="n">
-        <v>2.131116</v>
+        <v>2.3177</v>
       </c>
       <c r="G16" t="n">
         <v>98.36065600000001</v>
@@ -851,7 +851,7 @@
         <v>-2.58731</v>
       </c>
       <c r="F17" t="n">
-        <v>2.129542</v>
+        <v>2.194612</v>
       </c>
       <c r="G17" t="n">
         <v>98.36065600000001</v>
@@ -876,7 +876,7 @@
         <v>-3.857547</v>
       </c>
       <c r="F18" t="n">
-        <v>1.537318</v>
+        <v>1.583626</v>
       </c>
       <c r="G18" t="n">
         <v>98.36065600000001</v>
@@ -901,7 +901,7 @@
         <v>1.457956</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.805688</v>
+        <v>-0.51647</v>
       </c>
       <c r="G19" t="n">
         <v>98.36065600000001</v>
@@ -926,7 +926,7 @@
         <v>2.017557</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.956603</v>
+        <v>-2.039589</v>
       </c>
       <c r="G20" t="n">
         <v>98.36065600000001</v>
@@ -951,7 +951,7 @@
         <v>1.212177</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.805937</v>
+        <v>-1.679184</v>
       </c>
       <c r="G21" t="n">
         <v>98.36065600000001</v>
@@ -976,7 +976,7 @@
         <v>2.899042</v>
       </c>
       <c r="F22" t="n">
-        <v>0.458841</v>
+        <v>0.97395</v>
       </c>
       <c r="G22" t="n">
         <v>98.36065600000001</v>
@@ -1001,7 +1001,7 @@
         <v>3.997638</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.45101</v>
+        <v>0.211758</v>
       </c>
       <c r="G23" t="n">
         <v>98.36065600000001</v>
@@ -1026,7 +1026,7 @@
         <v>1.217278</v>
       </c>
       <c r="F24" t="n">
-        <v>0.290144</v>
+        <v>0.6487889999999999</v>
       </c>
       <c r="G24" t="n">
         <v>98.36065600000001</v>
@@ -1051,7 +1051,7 @@
         <v>0.132408</v>
       </c>
       <c r="F25" t="n">
-        <v>0.469814</v>
+        <v>0.159093</v>
       </c>
       <c r="G25" t="n">
         <v>98.36065600000001</v>
@@ -1076,7 +1076,7 @@
         <v>-7.369841</v>
       </c>
       <c r="F26" t="n">
-        <v>13.72662</v>
+        <v>14.374098</v>
       </c>
       <c r="G26" t="n">
         <v>98.36065600000001</v>
@@ -1101,7 +1101,7 @@
         <v>-4.375742</v>
       </c>
       <c r="F27" t="n">
-        <v>15.811847</v>
+        <v>16.099843</v>
       </c>
       <c r="G27" t="n">
         <v>98.36065600000001</v>
@@ -1126,7 +1126,7 @@
         <v>-8.199329000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>7.00694</v>
+        <v>7.857623</v>
       </c>
       <c r="G28" t="n">
         <v>98.36065600000001</v>
@@ -1151,7 +1151,7 @@
         <v>-2.3766</v>
       </c>
       <c r="F29" t="n">
-        <v>13.385827</v>
+        <v>14.112659</v>
       </c>
       <c r="G29" t="n">
         <v>98.36065600000001</v>
@@ -1535,7 +1535,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
@@ -1548,10 +1548,10 @@
         <v>59</v>
       </c>
       <c r="E45" t="n">
-        <v>20.26</v>
+        <v>2.94</v>
       </c>
       <c r="F45" t="n">
-        <v>33.42</v>
+        <v>5.62</v>
       </c>
       <c r="G45" t="n">
         <v>96.721311</v>
@@ -1560,57 +1560,57 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="D46" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E46" t="n">
-        <v>355671</v>
+        <v>20.26</v>
       </c>
       <c r="F46" t="n">
-        <v>367558</v>
+        <v>33.42</v>
       </c>
       <c r="G46" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46142</v>
+        <v>46203</v>
       </c>
       <c r="D47" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E47" t="n">
-        <v>0.631159</v>
+        <v>355671</v>
       </c>
       <c r="F47" t="n">
-        <v>0.511964</v>
+        <v>367558</v>
       </c>
       <c r="G47" t="n">
-        <v>93.442623</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
@@ -1623,10 +1623,10 @@
         <v>57</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.641498</v>
+        <v>0.631159</v>
       </c>
       <c r="F48" t="n">
-        <v>-3.561276</v>
+        <v>0.511964</v>
       </c>
       <c r="G48" t="n">
         <v>93.442623</v>
@@ -1635,32 +1635,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46234</v>
+        <v>46142</v>
       </c>
       <c r="D49" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E49" t="n">
-        <v>0.423696</v>
+        <v>-0.641498</v>
       </c>
       <c r="F49" t="n">
-        <v>-2.007109</v>
+        <v>-3.561276</v>
       </c>
       <c r="G49" t="n">
-        <v>98.36065600000001</v>
+        <v>93.442623</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
@@ -1673,10 +1673,10 @@
         <v>60</v>
       </c>
       <c r="E50" t="n">
-        <v>0.423745</v>
+        <v>0.423696</v>
       </c>
       <c r="F50" t="n">
-        <v>-2.007342</v>
+        <v>-2.007109</v>
       </c>
       <c r="G50" t="n">
         <v>98.36065600000001</v>
@@ -1685,32 +1685,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D51" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E51" t="n">
-        <v>1.736829</v>
+        <v>0.423745</v>
       </c>
       <c r="F51" t="n">
-        <v>0.565068</v>
+        <v>-2.007342</v>
       </c>
       <c r="G51" t="n">
-        <v>95.08196700000001</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
@@ -1723,10 +1723,10 @@
         <v>58</v>
       </c>
       <c r="E52" t="n">
-        <v>0.972464</v>
+        <v>1.736829</v>
       </c>
       <c r="F52" t="n">
-        <v>0.742264</v>
+        <v>0.565068</v>
       </c>
       <c r="G52" t="n">
         <v>95.08196700000001</v>
@@ -1735,7 +1735,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
@@ -1748,10 +1748,10 @@
         <v>58</v>
       </c>
       <c r="E53" t="n">
-        <v>2.311409</v>
+        <v>0.972464</v>
       </c>
       <c r="F53" t="n">
-        <v>0.461065</v>
+        <v>0.742264</v>
       </c>
       <c r="G53" t="n">
         <v>95.08196700000001</v>
@@ -1760,57 +1760,57 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="D54" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E54" t="n">
-        <v>4.139781</v>
+        <v>2.311409</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.964334</v>
+        <v>0.461065</v>
       </c>
       <c r="G54" t="n">
-        <v>96.721311</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>44742</v>
+        <v>44439</v>
       </c>
       <c r="C55" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D55" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E55" t="n">
-        <v>11.88673</v>
+        <v>4.139781</v>
       </c>
       <c r="F55" t="n">
-        <v>4.641328</v>
+        <v>-0.964334</v>
       </c>
       <c r="G55" t="n">
-        <v>80.32786900000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
@@ -1823,10 +1823,10 @@
         <v>49</v>
       </c>
       <c r="E56" t="n">
-        <v>10.700862</v>
+        <v>11.88673</v>
       </c>
       <c r="F56" t="n">
-        <v>3.177699</v>
+        <v>4.641328</v>
       </c>
       <c r="G56" t="n">
         <v>80.32786900000001</v>
@@ -1835,7 +1835,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
@@ -1848,10 +1848,10 @@
         <v>49</v>
       </c>
       <c r="E57" t="n">
-        <v>11.919595</v>
+        <v>10.700862</v>
       </c>
       <c r="F57" t="n">
-        <v>4.327084</v>
+        <v>3.177699</v>
       </c>
       <c r="G57" t="n">
         <v>80.32786900000001</v>
@@ -1860,32 +1860,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>44439</v>
+        <v>44742</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D58" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E58" t="n">
-        <v>1</v>
+        <v>11.919595</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>4.327084</v>
       </c>
       <c r="G58" t="n">
-        <v>98.36065600000001</v>
+        <v>80.32786900000001</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
@@ -1898,10 +1898,10 @@
         <v>60</v>
       </c>
       <c r="E59" t="n">
-        <v>0.003276</v>
+        <v>1</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.000497</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
         <v>98.36065600000001</v>
@@ -1910,7 +1910,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
@@ -1935,32 +1935,32 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D61" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E61" t="n">
-        <v>0.01</v>
+        <v>0.003276</v>
       </c>
       <c r="F61" t="n">
-        <v>0.11</v>
+        <v>-0.000497</v>
       </c>
       <c r="G61" t="n">
-        <v>95.08196700000001</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
@@ -1973,10 +1973,10 @@
         <v>58</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F62" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="G62" t="n">
         <v>95.08196700000001</v>
@@ -1985,7 +1985,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
@@ -1998,12 +1998,62 @@
         <v>58</v>
       </c>
       <c r="E63" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="G63" t="n">
+        <v>95.08196700000001</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
+        </is>
+      </c>
+      <c r="B64" s="1" t="n">
+        <v>44439</v>
+      </c>
+      <c r="C64" s="1" t="n">
+        <v>46173</v>
+      </c>
+      <c r="D64" t="n">
+        <v>58</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="G64" t="n">
+        <v>95.08196700000001</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_juros_credito_total</t>
+        </is>
+      </c>
+      <c r="B65" s="1" t="n">
+        <v>44439</v>
+      </c>
+      <c r="C65" s="1" t="n">
+        <v>46173</v>
+      </c>
+      <c r="D65" t="n">
+        <v>58</v>
+      </c>
+      <c r="E65" t="n">
         <v>0.66</v>
       </c>
-      <c r="F63" t="n">
+      <c r="F65" t="n">
         <v>-0.09</v>
       </c>
-      <c r="G63" t="n">
+      <c r="G65" t="n">
         <v>95.08196700000001</v>
       </c>
     </row>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -476,7 +476,7 @@
         <v>121801</v>
       </c>
       <c r="F2" t="n">
-        <v>176011</v>
+        <v>173825</v>
       </c>
       <c r="G2" t="n">
         <v>100</v>
@@ -501,7 +501,7 @@
         <v>117.110001</v>
       </c>
       <c r="F3" t="n">
-        <v>172.759995</v>
+        <v>170.770004</v>
       </c>
       <c r="G3" t="n">
         <v>100</v>
@@ -526,7 +526,7 @@
         <v>141.800003</v>
       </c>
       <c r="F4" t="n">
-        <v>109.690002</v>
+        <v>108.419998</v>
       </c>
       <c r="G4" t="n">
         <v>100</v>
@@ -551,7 +551,7 @@
         <v>250.350006</v>
       </c>
       <c r="F5" t="n">
-        <v>433.399994</v>
+        <v>433.040009</v>
       </c>
       <c r="G5" t="n">
         <v>100</v>
@@ -576,7 +576,7 @@
         <v>5.0804</v>
       </c>
       <c r="F6" t="n">
-        <v>5.0761</v>
+        <v>5.1028</v>
       </c>
       <c r="G6" t="n">
         <v>100</v>
@@ -601,7 +601,7 @@
         <v>6.0387</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8178</v>
+        <v>5.8311</v>
       </c>
       <c r="G7" t="n">
         <v>100</v>
@@ -626,7 +626,7 @@
         <v>4395.259766</v>
       </c>
       <c r="F8" t="n">
-        <v>7572.399902</v>
+        <v>7533.77002</v>
       </c>
       <c r="G8" t="n">
         <v>100</v>
@@ -651,7 +651,7 @@
         <v>14672.679688</v>
       </c>
       <c r="F9" t="n">
-        <v>26269.230469</v>
+        <v>25881.949219</v>
       </c>
       <c r="G9" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
         <v>34935.46875</v>
       </c>
       <c r="F10" t="n">
-        <v>52658.640625</v>
+        <v>52552.96875</v>
       </c>
       <c r="G10" t="n">
         <v>100</v>
@@ -701,7 +701,7 @@
         <v>1812.599976</v>
       </c>
       <c r="F11" t="n">
-        <v>4029.300049</v>
+        <v>3995.699951</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
@@ -726,7 +726,7 @@
         <v>73.949997</v>
       </c>
       <c r="F12" t="n">
-        <v>79.489998</v>
+        <v>80.139999</v>
       </c>
       <c r="G12" t="n">
         <v>100</v>
@@ -751,7 +751,7 @@
         <v>76.33000199999999</v>
       </c>
       <c r="F13" t="n">
-        <v>84.660004</v>
+        <v>85.949997</v>
       </c>
       <c r="G13" t="n">
         <v>100</v>
@@ -776,7 +776,7 @@
         <v>1414.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1204.5</v>
+        <v>1195</v>
       </c>
       <c r="G14" t="n">
         <v>100</v>
@@ -801,7 +801,7 @@
         <v>547</v>
       </c>
       <c r="F15" t="n">
-        <v>471</v>
+        <v>463.5</v>
       </c>
       <c r="G15" t="n">
         <v>100</v>
@@ -826,7 +826,7 @@
         <v>-2.479454</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3177</v>
+        <v>1.046947</v>
       </c>
       <c r="G16" t="n">
         <v>98.36065600000001</v>
@@ -851,7 +851,7 @@
         <v>-2.58731</v>
       </c>
       <c r="F17" t="n">
-        <v>2.194612</v>
+        <v>1.017451</v>
       </c>
       <c r="G17" t="n">
         <v>98.36065600000001</v>
@@ -876,7 +876,7 @@
         <v>-3.857547</v>
       </c>
       <c r="F18" t="n">
-        <v>1.583626</v>
+        <v>0.407478</v>
       </c>
       <c r="G18" t="n">
         <v>98.36065600000001</v>
@@ -901,7 +901,7 @@
         <v>1.457956</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.51647</v>
+        <v>-0.599101</v>
       </c>
       <c r="G19" t="n">
         <v>98.36065600000001</v>
@@ -926,7 +926,7 @@
         <v>2.017557</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.039589</v>
+        <v>-1.524322</v>
       </c>
       <c r="G20" t="n">
         <v>98.36065600000001</v>
@@ -951,7 +951,7 @@
         <v>1.212177</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.679184</v>
+        <v>-1.454415</v>
       </c>
       <c r="G21" t="n">
         <v>98.36065600000001</v>
@@ -976,7 +976,7 @@
         <v>2.899042</v>
       </c>
       <c r="F22" t="n">
-        <v>0.97395</v>
+        <v>0.458841</v>
       </c>
       <c r="G22" t="n">
         <v>98.36065600000001</v>
@@ -1001,7 +1001,7 @@
         <v>3.997638</v>
       </c>
       <c r="F23" t="n">
-        <v>0.211758</v>
+        <v>-1.265641</v>
       </c>
       <c r="G23" t="n">
         <v>98.36065600000001</v>
@@ -1026,7 +1026,7 @@
         <v>1.217278</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6487889999999999</v>
+        <v>0.446814</v>
       </c>
       <c r="G24" t="n">
         <v>98.36065600000001</v>
@@ -1051,7 +1051,7 @@
         <v>0.132408</v>
       </c>
       <c r="F25" t="n">
-        <v>0.159093</v>
+        <v>-0.676128</v>
       </c>
       <c r="G25" t="n">
         <v>98.36065600000001</v>
@@ -1076,7 +1076,7 @@
         <v>-7.369841</v>
       </c>
       <c r="F26" t="n">
-        <v>14.374098</v>
+        <v>15.309352</v>
       </c>
       <c r="G26" t="n">
         <v>98.36065600000001</v>
@@ -1101,7 +1101,7 @@
         <v>-4.375742</v>
       </c>
       <c r="F27" t="n">
-        <v>16.099843</v>
+        <v>17.868896</v>
       </c>
       <c r="G27" t="n">
         <v>98.36065600000001</v>
@@ -1126,7 +1126,7 @@
         <v>-8.199329000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>7.857623</v>
+        <v>7.00694</v>
       </c>
       <c r="G28" t="n">
         <v>98.36065600000001</v>
@@ -1151,7 +1151,7 @@
         <v>-2.3766</v>
       </c>
       <c r="F29" t="n">
-        <v>14.112659</v>
+        <v>12.295578</v>
       </c>
       <c r="G29" t="n">
         <v>98.36065600000001</v>
@@ -1376,7 +1376,7 @@
         <v>5.1216</v>
       </c>
       <c r="F38" t="n">
-        <v>5.0727</v>
+        <v>5.0975</v>
       </c>
       <c r="G38" t="n">
         <v>100</v>
@@ -1401,7 +1401,7 @@
         <v>5.121</v>
       </c>
       <c r="F39" t="n">
-        <v>5.0721</v>
+        <v>5.0969</v>
       </c>
       <c r="G39" t="n">
         <v>100</v>
@@ -1676,7 +1676,7 @@
         <v>0.423696</v>
       </c>
       <c r="F50" t="n">
-        <v>-2.007109</v>
+        <v>-1.52803</v>
       </c>
       <c r="G50" t="n">
         <v>98.36065600000001</v>
@@ -1701,7 +1701,7 @@
         <v>0.423745</v>
       </c>
       <c r="F51" t="n">
-        <v>-2.007342</v>
+        <v>-1.528207</v>
       </c>
       <c r="G51" t="n">
         <v>98.36065600000001</v>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -476,7 +476,7 @@
         <v>121801</v>
       </c>
       <c r="F2" t="n">
-        <v>173825</v>
+        <v>173714</v>
       </c>
       <c r="G2" t="n">
         <v>100</v>
@@ -501,7 +501,7 @@
         <v>117.110001</v>
       </c>
       <c r="F3" t="n">
-        <v>170.770004</v>
+        <v>170.630005</v>
       </c>
       <c r="G3" t="n">
         <v>100</v>
@@ -526,7 +526,7 @@
         <v>141.800003</v>
       </c>
       <c r="F4" t="n">
-        <v>108.419998</v>
+        <v>107.43</v>
       </c>
       <c r="G4" t="n">
         <v>100</v>
@@ -551,7 +551,7 @@
         <v>250.350006</v>
       </c>
       <c r="F5" t="n">
-        <v>433.040009</v>
+        <v>429.119995</v>
       </c>
       <c r="G5" t="n">
         <v>100</v>
@@ -576,7 +576,7 @@
         <v>5.0804</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1028</v>
+        <v>5.1108</v>
       </c>
       <c r="G6" t="n">
         <v>100</v>
@@ -601,7 +601,7 @@
         <v>6.0387</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8311</v>
+        <v>5.8439</v>
       </c>
       <c r="G7" t="n">
         <v>100</v>
@@ -626,7 +626,7 @@
         <v>4395.259766</v>
       </c>
       <c r="F8" t="n">
-        <v>7533.77002</v>
+        <v>7457.689941</v>
       </c>
       <c r="G8" t="n">
         <v>100</v>
@@ -651,7 +651,7 @@
         <v>14672.679688</v>
       </c>
       <c r="F9" t="n">
-        <v>25881.949219</v>
+        <v>25520.240234</v>
       </c>
       <c r="G9" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
         <v>34935.46875</v>
       </c>
       <c r="F10" t="n">
-        <v>52552.96875</v>
+        <v>52146.421875</v>
       </c>
       <c r="G10" t="n">
         <v>100</v>
@@ -701,7 +701,7 @@
         <v>1812.599976</v>
       </c>
       <c r="F11" t="n">
-        <v>3995.699951</v>
+        <v>4012.699951</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
@@ -726,7 +726,7 @@
         <v>73.949997</v>
       </c>
       <c r="F12" t="n">
-        <v>80.139999</v>
+        <v>82.489998</v>
       </c>
       <c r="G12" t="n">
         <v>100</v>
@@ -751,7 +751,7 @@
         <v>76.33000199999999</v>
       </c>
       <c r="F13" t="n">
-        <v>85.949997</v>
+        <v>88.099998</v>
       </c>
       <c r="G13" t="n">
         <v>100</v>
@@ -776,7 +776,7 @@
         <v>1414.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1195</v>
+        <v>1204.5</v>
       </c>
       <c r="G14" t="n">
         <v>100</v>
@@ -801,7 +801,7 @@
         <v>547</v>
       </c>
       <c r="F15" t="n">
-        <v>463.5</v>
+        <v>444.75</v>
       </c>
       <c r="G15" t="n">
         <v>100</v>
@@ -826,7 +826,7 @@
         <v>-2.479454</v>
       </c>
       <c r="F16" t="n">
-        <v>1.046947</v>
+        <v>0.982421</v>
       </c>
       <c r="G16" t="n">
         <v>98.36065600000001</v>
@@ -851,7 +851,7 @@
         <v>-2.58731</v>
       </c>
       <c r="F17" t="n">
-        <v>1.017451</v>
+        <v>0.934636</v>
       </c>
       <c r="G17" t="n">
         <v>98.36065600000001</v>
@@ -876,7 +876,7 @@
         <v>-3.857547</v>
       </c>
       <c r="F18" t="n">
-        <v>0.407478</v>
+        <v>-0.509356</v>
       </c>
       <c r="G18" t="n">
         <v>98.36065600000001</v>
@@ -901,7 +901,7 @@
         <v>1.457956</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.599101</v>
+        <v>-1.498909</v>
       </c>
       <c r="G19" t="n">
         <v>98.36065600000001</v>
@@ -926,7 +926,7 @@
         <v>2.017557</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.524322</v>
+        <v>-1.369937</v>
       </c>
       <c r="G20" t="n">
         <v>98.36065600000001</v>
@@ -951,7 +951,7 @@
         <v>1.212177</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.454415</v>
+        <v>-1.238091</v>
       </c>
       <c r="G21" t="n">
         <v>98.36065600000001</v>
@@ -976,7 +976,7 @@
         <v>2.899042</v>
       </c>
       <c r="F22" t="n">
-        <v>0.458841</v>
+        <v>-0.555646</v>
       </c>
       <c r="G22" t="n">
         <v>98.36065600000001</v>
@@ -1001,7 +1001,7 @@
         <v>3.997638</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.265641</v>
+        <v>-2.645487</v>
       </c>
       <c r="G23" t="n">
         <v>98.36065600000001</v>
@@ -1026,7 +1026,7 @@
         <v>1.217278</v>
       </c>
       <c r="F24" t="n">
-        <v>0.446814</v>
+        <v>-0.330237</v>
       </c>
       <c r="G24" t="n">
         <v>98.36065600000001</v>
@@ -1051,7 +1051,7 @@
         <v>0.132408</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.676128</v>
+        <v>-0.253547</v>
       </c>
       <c r="G25" t="n">
         <v>98.36065600000001</v>
@@ -1076,7 +1076,7 @@
         <v>-7.369841</v>
       </c>
       <c r="F26" t="n">
-        <v>15.309352</v>
+        <v>18.690644</v>
       </c>
       <c r="G26" t="n">
         <v>98.36065600000001</v>
@@ -1101,7 +1101,7 @@
         <v>-4.375742</v>
       </c>
       <c r="F27" t="n">
-        <v>17.868896</v>
+        <v>20.817335</v>
       </c>
       <c r="G27" t="n">
         <v>98.36065600000001</v>
@@ -1126,7 +1126,7 @@
         <v>-8.199329000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>7.00694</v>
+        <v>7.857623</v>
       </c>
       <c r="G28" t="n">
         <v>98.36065600000001</v>
@@ -1151,7 +1151,7 @@
         <v>-2.3766</v>
       </c>
       <c r="F29" t="n">
-        <v>12.295578</v>
+        <v>7.752877</v>
       </c>
       <c r="G29" t="n">
         <v>98.36065600000001</v>
@@ -1317,19 +1317,19 @@
         <v>44408</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="D36" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E36" t="n">
-        <v>96.42256999999999</v>
+        <v>96.31464</v>
       </c>
       <c r="F36" t="n">
-        <v>111.15205</v>
+        <v>111.03587</v>
       </c>
       <c r="G36" t="n">
-        <v>95.08196700000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="37">
@@ -1342,19 +1342,19 @@
         <v>44408</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="D37" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E37" t="n">
-        <v>99.83515</v>
+        <v>99.83978</v>
       </c>
       <c r="F37" t="n">
-        <v>113.72712</v>
+        <v>109.52993</v>
       </c>
       <c r="G37" t="n">
-        <v>95.08196700000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="38">
@@ -1376,7 +1376,7 @@
         <v>5.1216</v>
       </c>
       <c r="F38" t="n">
-        <v>5.0975</v>
+        <v>5.1176</v>
       </c>
       <c r="G38" t="n">
         <v>100</v>
@@ -1401,7 +1401,7 @@
         <v>5.121</v>
       </c>
       <c r="F39" t="n">
-        <v>5.0969</v>
+        <v>5.117</v>
       </c>
       <c r="G39" t="n">
         <v>100</v>
@@ -1617,19 +1617,19 @@
         <v>44439</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="D48" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E48" t="n">
-        <v>0.631159</v>
+        <v>0.79016</v>
       </c>
       <c r="F48" t="n">
-        <v>0.511964</v>
+        <v>0.07079299999999999</v>
       </c>
       <c r="G48" t="n">
-        <v>93.442623</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="49">
@@ -1642,19 +1642,19 @@
         <v>44439</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="D49" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.641498</v>
+        <v>-0.512311</v>
       </c>
       <c r="F49" t="n">
-        <v>-3.561276</v>
+        <v>-3.915762</v>
       </c>
       <c r="G49" t="n">
-        <v>93.442623</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="50">
@@ -1676,7 +1676,7 @@
         <v>0.423696</v>
       </c>
       <c r="F50" t="n">
-        <v>-1.52803</v>
+        <v>-1.139744</v>
       </c>
       <c r="G50" t="n">
         <v>98.36065600000001</v>
@@ -1701,7 +1701,7 @@
         <v>0.423745</v>
       </c>
       <c r="F51" t="n">
-        <v>-1.528207</v>
+        <v>-1.139876</v>
       </c>
       <c r="G51" t="n">
         <v>98.36065600000001</v>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -701,7 +701,7 @@
         <v>1812.599976</v>
       </c>
       <c r="F11" t="n">
-        <v>4012.699951</v>
+        <v>4018.800049</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
@@ -726,7 +726,7 @@
         <v>73.949997</v>
       </c>
       <c r="F12" t="n">
-        <v>82.489998</v>
+        <v>81.779999</v>
       </c>
       <c r="G12" t="n">
         <v>100</v>
@@ -776,7 +776,7 @@
         <v>1414.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1204.5</v>
+        <v>1203</v>
       </c>
       <c r="G14" t="n">
         <v>100</v>
@@ -801,7 +801,7 @@
         <v>547</v>
       </c>
       <c r="F15" t="n">
-        <v>444.75</v>
+        <v>467.5</v>
       </c>
       <c r="G15" t="n">
         <v>100</v>
@@ -1051,7 +1051,7 @@
         <v>0.132408</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.253547</v>
+        <v>-0.101913</v>
       </c>
       <c r="G25" t="n">
         <v>98.36065600000001</v>
@@ -1076,7 +1076,7 @@
         <v>-7.369841</v>
       </c>
       <c r="F26" t="n">
-        <v>18.690644</v>
+        <v>17.669063</v>
       </c>
       <c r="G26" t="n">
         <v>98.36065600000001</v>
@@ -1126,7 +1126,7 @@
         <v>-8.199329000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>7.857623</v>
+        <v>7.723304</v>
       </c>
       <c r="G28" t="n">
         <v>98.36065600000001</v>
@@ -1151,7 +1151,7 @@
         <v>-2.3766</v>
       </c>
       <c r="F29" t="n">
-        <v>7.752877</v>
+        <v>13.264688</v>
       </c>
       <c r="G29" t="n">
         <v>98.36065600000001</v>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -576,7 +576,7 @@
         <v>5.0804</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1108</v>
+        <v>5.1072</v>
       </c>
       <c r="G6" t="n">
         <v>100</v>
@@ -601,7 +601,7 @@
         <v>6.0387</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8439</v>
+        <v>5.8329</v>
       </c>
       <c r="G7" t="n">
         <v>100</v>
@@ -701,7 +701,7 @@
         <v>1812.599976</v>
       </c>
       <c r="F11" t="n">
-        <v>4018.800049</v>
+        <v>4020</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
@@ -726,7 +726,7 @@
         <v>73.949997</v>
       </c>
       <c r="F12" t="n">
-        <v>81.779999</v>
+        <v>81.400002</v>
       </c>
       <c r="G12" t="n">
         <v>100</v>
@@ -751,7 +751,7 @@
         <v>76.33000199999999</v>
       </c>
       <c r="F13" t="n">
-        <v>88.099998</v>
+        <v>88.220001</v>
       </c>
       <c r="G13" t="n">
         <v>100</v>
@@ -776,7 +776,7 @@
         <v>1414.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1203</v>
+        <v>1220</v>
       </c>
       <c r="G14" t="n">
         <v>100</v>
@@ -801,7 +801,7 @@
         <v>547</v>
       </c>
       <c r="F15" t="n">
-        <v>467.5</v>
+        <v>475.25</v>
       </c>
       <c r="G15" t="n">
         <v>100</v>
@@ -926,7 +926,7 @@
         <v>2.017557</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.369937</v>
+        <v>-1.439404</v>
       </c>
       <c r="G20" t="n">
         <v>98.36065600000001</v>
@@ -951,7 +951,7 @@
         <v>1.212177</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.238091</v>
+        <v>-1.423994</v>
       </c>
       <c r="G21" t="n">
         <v>98.36065600000001</v>
@@ -1051,7 +1051,7 @@
         <v>0.132408</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.101913</v>
+        <v>-0.072085</v>
       </c>
       <c r="G25" t="n">
         <v>98.36065600000001</v>
@@ -1076,7 +1076,7 @@
         <v>-7.369841</v>
       </c>
       <c r="F26" t="n">
-        <v>17.669063</v>
+        <v>17.122304</v>
       </c>
       <c r="G26" t="n">
         <v>98.36065600000001</v>
@@ -1101,7 +1101,7 @@
         <v>-4.375742</v>
       </c>
       <c r="F27" t="n">
-        <v>20.817335</v>
+        <v>20.981903</v>
       </c>
       <c r="G27" t="n">
         <v>98.36065600000001</v>
@@ -1126,7 +1126,7 @@
         <v>-8.199329000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>7.723304</v>
+        <v>9.245578999999999</v>
       </c>
       <c r="G28" t="n">
         <v>98.36065600000001</v>
@@ -1151,7 +1151,7 @@
         <v>-2.3766</v>
       </c>
       <c r="F29" t="n">
-        <v>13.264688</v>
+        <v>15.142338</v>
       </c>
       <c r="G29" t="n">
         <v>98.36065600000001</v>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -476,7 +476,7 @@
         <v>121801</v>
       </c>
       <c r="F2" t="n">
-        <v>173714</v>
+        <v>173371</v>
       </c>
       <c r="G2" t="n">
         <v>100</v>
@@ -501,7 +501,7 @@
         <v>117.110001</v>
       </c>
       <c r="F3" t="n">
-        <v>170.630005</v>
+        <v>170.300003</v>
       </c>
       <c r="G3" t="n">
         <v>100</v>
@@ -526,7 +526,7 @@
         <v>141.800003</v>
       </c>
       <c r="F4" t="n">
-        <v>107.43</v>
+        <v>106.230003</v>
       </c>
       <c r="G4" t="n">
         <v>100</v>
@@ -551,7 +551,7 @@
         <v>250.350006</v>
       </c>
       <c r="F5" t="n">
-        <v>429.119995</v>
+        <v>426.970001</v>
       </c>
       <c r="G5" t="n">
         <v>100</v>
@@ -576,7 +576,7 @@
         <v>5.0804</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1072</v>
+        <v>5.0921</v>
       </c>
       <c r="G6" t="n">
         <v>100</v>
@@ -601,7 +601,7 @@
         <v>6.0387</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8329</v>
+        <v>5.8157</v>
       </c>
       <c r="G7" t="n">
         <v>100</v>
@@ -626,7 +626,7 @@
         <v>4395.259766</v>
       </c>
       <c r="F8" t="n">
-        <v>7457.689941</v>
+        <v>7443.279785</v>
       </c>
       <c r="G8" t="n">
         <v>100</v>
@@ -651,7 +651,7 @@
         <v>14672.679688</v>
       </c>
       <c r="F9" t="n">
-        <v>25520.240234</v>
+        <v>25508.070312</v>
       </c>
       <c r="G9" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
         <v>34935.46875</v>
       </c>
       <c r="F10" t="n">
-        <v>52146.421875</v>
+        <v>51839.261719</v>
       </c>
       <c r="G10" t="n">
         <v>100</v>
@@ -701,7 +701,7 @@
         <v>1812.599976</v>
       </c>
       <c r="F11" t="n">
-        <v>4020</v>
+        <v>4064.800049</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
@@ -726,7 +726,7 @@
         <v>73.949997</v>
       </c>
       <c r="F12" t="n">
-        <v>81.400002</v>
+        <v>83.620003</v>
       </c>
       <c r="G12" t="n">
         <v>100</v>
@@ -751,7 +751,7 @@
         <v>76.33000199999999</v>
       </c>
       <c r="F13" t="n">
-        <v>88.220001</v>
+        <v>90.400002</v>
       </c>
       <c r="G13" t="n">
         <v>100</v>
@@ -776,7 +776,7 @@
         <v>1414.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1220</v>
+        <v>1226.5</v>
       </c>
       <c r="G14" t="n">
         <v>100</v>
@@ -801,7 +801,7 @@
         <v>547</v>
       </c>
       <c r="F15" t="n">
-        <v>475.25</v>
+        <v>471.5</v>
       </c>
       <c r="G15" t="n">
         <v>100</v>
@@ -826,7 +826,7 @@
         <v>-2.479454</v>
       </c>
       <c r="F16" t="n">
-        <v>0.982421</v>
+        <v>0.78303</v>
       </c>
       <c r="G16" t="n">
         <v>98.36065600000001</v>
@@ -851,7 +851,7 @@
         <v>-2.58731</v>
       </c>
       <c r="F17" t="n">
-        <v>0.934636</v>
+        <v>0.739426</v>
       </c>
       <c r="G17" t="n">
         <v>98.36065600000001</v>
@@ -876,7 +876,7 @@
         <v>-3.857547</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.509356</v>
+        <v>-1.62067</v>
       </c>
       <c r="G18" t="n">
         <v>98.36065600000001</v>
@@ -901,7 +901,7 @@
         <v>1.457956</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.498909</v>
+        <v>-1.992423</v>
       </c>
       <c r="G19" t="n">
         <v>98.36065600000001</v>
@@ -926,7 +926,7 @@
         <v>2.017557</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.439404</v>
+        <v>-1.73081</v>
       </c>
       <c r="G20" t="n">
         <v>98.36065600000001</v>
@@ -951,7 +951,7 @@
         <v>1.212177</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.423994</v>
+        <v>-1.714674</v>
       </c>
       <c r="G21" t="n">
         <v>98.36065600000001</v>
@@ -976,7 +976,7 @@
         <v>2.899042</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.555646</v>
+        <v>-0.747798</v>
       </c>
       <c r="G22" t="n">
         <v>98.36065600000001</v>
@@ -1001,7 +1001,7 @@
         <v>3.997638</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.645487</v>
+        <v>-2.691912</v>
       </c>
       <c r="G23" t="n">
         <v>98.36065600000001</v>
@@ -1026,7 +1026,7 @@
         <v>1.217278</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.330237</v>
+        <v>-0.917326</v>
       </c>
       <c r="G24" t="n">
         <v>98.36065600000001</v>
@@ -1051,7 +1051,7 @@
         <v>0.132408</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.072085</v>
+        <v>1.041541</v>
       </c>
       <c r="G25" t="n">
         <v>98.36065600000001</v>
@@ -1076,7 +1076,7 @@
         <v>-7.369841</v>
       </c>
       <c r="F26" t="n">
-        <v>17.122304</v>
+        <v>20.316551</v>
       </c>
       <c r="G26" t="n">
         <v>98.36065600000001</v>
@@ -1101,7 +1101,7 @@
         <v>-4.375742</v>
       </c>
       <c r="F27" t="n">
-        <v>20.981903</v>
+        <v>23.971481</v>
       </c>
       <c r="G27" t="n">
         <v>98.36065600000001</v>
@@ -1126,7 +1126,7 @@
         <v>-8.199329000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>9.245578999999999</v>
+        <v>9.827624999999999</v>
       </c>
       <c r="G28" t="n">
         <v>98.36065600000001</v>
@@ -1151,7 +1151,7 @@
         <v>-2.3766</v>
       </c>
       <c r="F29" t="n">
-        <v>15.142338</v>
+        <v>14.233798</v>
       </c>
       <c r="G29" t="n">
         <v>98.36065600000001</v>
@@ -1376,7 +1376,7 @@
         <v>5.1216</v>
       </c>
       <c r="F38" t="n">
-        <v>5.1176</v>
+        <v>5.0894</v>
       </c>
       <c r="G38" t="n">
         <v>100</v>
@@ -1401,7 +1401,7 @@
         <v>5.121</v>
       </c>
       <c r="F39" t="n">
-        <v>5.117</v>
+        <v>5.0888</v>
       </c>
       <c r="G39" t="n">
         <v>100</v>
@@ -1676,7 +1676,7 @@
         <v>0.423696</v>
       </c>
       <c r="F50" t="n">
-        <v>-1.139744</v>
+        <v>-1.684503</v>
       </c>
       <c r="G50" t="n">
         <v>98.36065600000001</v>
@@ -1701,7 +1701,7 @@
         <v>0.423745</v>
       </c>
       <c r="F51" t="n">
-        <v>-1.139876</v>
+        <v>-1.684699</v>
       </c>
       <c r="G51" t="n">
         <v>98.36065600000001</v>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -476,7 +476,7 @@
         <v>121801</v>
       </c>
       <c r="F2" t="n">
-        <v>173371</v>
+        <v>173326</v>
       </c>
       <c r="G2" t="n">
         <v>100</v>
@@ -501,7 +501,7 @@
         <v>117.110001</v>
       </c>
       <c r="F3" t="n">
-        <v>170.300003</v>
+        <v>170.339996</v>
       </c>
       <c r="G3" t="n">
         <v>100</v>
@@ -526,7 +526,7 @@
         <v>141.800003</v>
       </c>
       <c r="F4" t="n">
-        <v>106.230003</v>
+        <v>105.949997</v>
       </c>
       <c r="G4" t="n">
         <v>100</v>
@@ -551,7 +551,7 @@
         <v>250.350006</v>
       </c>
       <c r="F5" t="n">
-        <v>426.970001</v>
+        <v>430.109985</v>
       </c>
       <c r="G5" t="n">
         <v>100</v>
@@ -576,7 +576,7 @@
         <v>5.0804</v>
       </c>
       <c r="F6" t="n">
-        <v>5.0921</v>
+        <v>5.072</v>
       </c>
       <c r="G6" t="n">
         <v>100</v>
@@ -601,7 +601,7 @@
         <v>6.0387</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8157</v>
+        <v>5.7838</v>
       </c>
       <c r="G7" t="n">
         <v>100</v>
@@ -626,7 +626,7 @@
         <v>4395.259766</v>
       </c>
       <c r="F8" t="n">
-        <v>7443.279785</v>
+        <v>7509.200195</v>
       </c>
       <c r="G8" t="n">
         <v>100</v>
@@ -651,7 +651,7 @@
         <v>14672.679688</v>
       </c>
       <c r="F9" t="n">
-        <v>25508.070312</v>
+        <v>25837.210938</v>
       </c>
       <c r="G9" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
         <v>34935.46875</v>
       </c>
       <c r="F10" t="n">
-        <v>51839.261719</v>
+        <v>52224.640625</v>
       </c>
       <c r="G10" t="n">
         <v>100</v>
@@ -701,7 +701,7 @@
         <v>1812.599976</v>
       </c>
       <c r="F11" t="n">
-        <v>4064.800049</v>
+        <v>4122.799805</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
@@ -726,7 +726,7 @@
         <v>73.949997</v>
       </c>
       <c r="F12" t="n">
-        <v>83.620003</v>
+        <v>87.129997</v>
       </c>
       <c r="G12" t="n">
         <v>100</v>
@@ -751,7 +751,7 @@
         <v>76.33000199999999</v>
       </c>
       <c r="F13" t="n">
-        <v>90.400002</v>
+        <v>84.800003</v>
       </c>
       <c r="G13" t="n">
         <v>100</v>
@@ -776,7 +776,7 @@
         <v>1414.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1226.5</v>
+        <v>1227</v>
       </c>
       <c r="G14" t="n">
         <v>100</v>
@@ -801,7 +801,7 @@
         <v>547</v>
       </c>
       <c r="F15" t="n">
-        <v>471.5</v>
+        <v>481</v>
       </c>
       <c r="G15" t="n">
         <v>100</v>
@@ -826,7 +826,7 @@
         <v>-2.479454</v>
       </c>
       <c r="F16" t="n">
-        <v>0.78303</v>
+        <v>0.756871</v>
       </c>
       <c r="G16" t="n">
         <v>98.36065600000001</v>
@@ -851,7 +851,7 @@
         <v>-2.58731</v>
       </c>
       <c r="F17" t="n">
-        <v>0.739426</v>
+        <v>0.763084</v>
       </c>
       <c r="G17" t="n">
         <v>98.36065600000001</v>
@@ -876,7 +876,7 @@
         <v>-3.857547</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.62067</v>
+        <v>-1.879984</v>
       </c>
       <c r="G18" t="n">
         <v>98.36065600000001</v>
@@ -901,7 +901,7 @@
         <v>1.457956</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.992423</v>
+        <v>-1.271665</v>
       </c>
       <c r="G19" t="n">
         <v>98.36065600000001</v>
@@ -926,7 +926,7 @@
         <v>2.017557</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.73081</v>
+        <v>-2.118709</v>
       </c>
       <c r="G20" t="n">
         <v>98.36065600000001</v>
@@ -951,7 +951,7 @@
         <v>1.212177</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.714674</v>
+        <v>-2.253782</v>
       </c>
       <c r="G21" t="n">
         <v>98.36065600000001</v>
@@ -976,7 +976,7 @@
         <v>2.899042</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.747798</v>
+        <v>0.131216</v>
       </c>
       <c r="G22" t="n">
         <v>98.36065600000001</v>
@@ -1001,7 +1001,7 @@
         <v>3.997638</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.691912</v>
+        <v>-1.436308</v>
       </c>
       <c r="G23" t="n">
         <v>98.36065600000001</v>
@@ -1026,7 +1026,7 @@
         <v>1.217278</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.917326</v>
+        <v>-0.180734</v>
       </c>
       <c r="G24" t="n">
         <v>98.36065600000001</v>
@@ -1051,7 +1051,7 @@
         <v>0.132408</v>
       </c>
       <c r="F25" t="n">
-        <v>1.041541</v>
+        <v>2.483281</v>
       </c>
       <c r="G25" t="n">
         <v>98.36065600000001</v>
@@ -1076,7 +1076,7 @@
         <v>-7.369841</v>
       </c>
       <c r="F26" t="n">
-        <v>20.316551</v>
+        <v>25.366903</v>
       </c>
       <c r="G26" t="n">
         <v>98.36065600000001</v>
@@ -1101,7 +1101,7 @@
         <v>-4.375742</v>
       </c>
       <c r="F27" t="n">
-        <v>23.971481</v>
+        <v>16.291834</v>
       </c>
       <c r="G27" t="n">
         <v>98.36065600000001</v>
@@ -1126,7 +1126,7 @@
         <v>-8.199329000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>9.827624999999999</v>
+        <v>9.872398</v>
       </c>
       <c r="G28" t="n">
         <v>98.36065600000001</v>
@@ -1151,7 +1151,7 @@
         <v>-2.3766</v>
       </c>
       <c r="F29" t="n">
-        <v>14.233798</v>
+        <v>16.535433</v>
       </c>
       <c r="G29" t="n">
         <v>98.36065600000001</v>
@@ -1376,7 +1376,7 @@
         <v>5.1216</v>
       </c>
       <c r="F38" t="n">
-        <v>5.0894</v>
+        <v>5.078</v>
       </c>
       <c r="G38" t="n">
         <v>100</v>
@@ -1401,7 +1401,7 @@
         <v>5.121</v>
       </c>
       <c r="F39" t="n">
-        <v>5.0888</v>
+        <v>5.0774</v>
       </c>
       <c r="G39" t="n">
         <v>100</v>
@@ -1676,7 +1676,7 @@
         <v>0.423696</v>
       </c>
       <c r="F50" t="n">
-        <v>-1.684503</v>
+        <v>-1.904725</v>
       </c>
       <c r="G50" t="n">
         <v>98.36065600000001</v>
@@ -1701,7 +1701,7 @@
         <v>0.423745</v>
       </c>
       <c r="F51" t="n">
-        <v>-1.684699</v>
+        <v>-1.904946</v>
       </c>
       <c r="G51" t="n">
         <v>98.36065600000001</v>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -476,7 +476,7 @@
         <v>121801</v>
       </c>
       <c r="F2" t="n">
-        <v>173326</v>
+        <v>177548</v>
       </c>
       <c r="G2" t="n">
         <v>100</v>
@@ -501,7 +501,7 @@
         <v>117.110001</v>
       </c>
       <c r="F3" t="n">
-        <v>170.339996</v>
+        <v>174.699997</v>
       </c>
       <c r="G3" t="n">
         <v>100</v>
@@ -526,7 +526,7 @@
         <v>141.800003</v>
       </c>
       <c r="F4" t="n">
-        <v>105.949997</v>
+        <v>107.5</v>
       </c>
       <c r="G4" t="n">
         <v>100</v>
@@ -551,7 +551,7 @@
         <v>250.350006</v>
       </c>
       <c r="F5" t="n">
-        <v>430.109985</v>
+        <v>428.859985</v>
       </c>
       <c r="G5" t="n">
         <v>100</v>
@@ -576,7 +576,7 @@
         <v>5.0804</v>
       </c>
       <c r="F6" t="n">
-        <v>5.072</v>
+        <v>5.0572</v>
       </c>
       <c r="G6" t="n">
         <v>100</v>
@@ -601,7 +601,7 @@
         <v>6.0387</v>
       </c>
       <c r="F7" t="n">
-        <v>5.7838</v>
+        <v>5.7601</v>
       </c>
       <c r="G7" t="n">
         <v>100</v>
@@ -626,7 +626,7 @@
         <v>4395.259766</v>
       </c>
       <c r="F8" t="n">
-        <v>7509.200195</v>
+        <v>7498.959961</v>
       </c>
       <c r="G8" t="n">
         <v>100</v>
@@ -651,7 +651,7 @@
         <v>14672.679688</v>
       </c>
       <c r="F9" t="n">
-        <v>25837.210938</v>
+        <v>25690.900391</v>
       </c>
       <c r="G9" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
         <v>34935.46875</v>
       </c>
       <c r="F10" t="n">
-        <v>52224.640625</v>
+        <v>52218.578125</v>
       </c>
       <c r="G10" t="n">
         <v>100</v>
@@ -701,7 +701,7 @@
         <v>1812.599976</v>
       </c>
       <c r="F11" t="n">
-        <v>4122.799805</v>
+        <v>4077.899902</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
@@ -726,7 +726,7 @@
         <v>73.949997</v>
       </c>
       <c r="F12" t="n">
-        <v>87.129997</v>
+        <v>91.06999999999999</v>
       </c>
       <c r="G12" t="n">
         <v>100</v>
@@ -751,7 +751,7 @@
         <v>76.33000199999999</v>
       </c>
       <c r="F13" t="n">
-        <v>84.800003</v>
+        <v>93.30999799999999</v>
       </c>
       <c r="G13" t="n">
         <v>100</v>
@@ -776,7 +776,7 @@
         <v>1414.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1227</v>
+        <v>1244</v>
       </c>
       <c r="G14" t="n">
         <v>100</v>
@@ -801,7 +801,7 @@
         <v>547</v>
       </c>
       <c r="F15" t="n">
-        <v>481</v>
+        <v>488.75</v>
       </c>
       <c r="G15" t="n">
         <v>100</v>
@@ -826,7 +826,7 @@
         <v>-2.479454</v>
       </c>
       <c r="F16" t="n">
-        <v>0.756871</v>
+        <v>3.21118</v>
       </c>
       <c r="G16" t="n">
         <v>98.36065600000001</v>
@@ -851,7 +851,7 @@
         <v>-2.58731</v>
       </c>
       <c r="F17" t="n">
-        <v>0.763084</v>
+        <v>3.342203</v>
       </c>
       <c r="G17" t="n">
         <v>98.36065600000001</v>
@@ -876,7 +876,7 @@
         <v>-3.857547</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.879984</v>
+        <v>-0.44453</v>
       </c>
       <c r="G18" t="n">
         <v>98.36065600000001</v>
@@ -901,7 +901,7 @@
         <v>1.457956</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.271665</v>
+        <v>-1.558593</v>
       </c>
       <c r="G19" t="n">
         <v>98.36065600000001</v>
@@ -926,7 +926,7 @@
         <v>2.017557</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.118709</v>
+        <v>-2.404326</v>
       </c>
       <c r="G20" t="n">
         <v>98.36065600000001</v>
@@ -951,7 +951,7 @@
         <v>1.212177</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.253782</v>
+        <v>-2.654316</v>
       </c>
       <c r="G21" t="n">
         <v>98.36065600000001</v>
@@ -976,7 +976,7 @@
         <v>2.899042</v>
       </c>
       <c r="F22" t="n">
-        <v>0.131216</v>
+        <v>-0.005332</v>
       </c>
       <c r="G22" t="n">
         <v>98.36065600000001</v>
@@ -1001,7 +1001,7 @@
         <v>3.997638</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.436308</v>
+        <v>-1.994453</v>
       </c>
       <c r="G23" t="n">
         <v>98.36065600000001</v>
@@ -1026,7 +1026,7 @@
         <v>1.217278</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.180734</v>
+        <v>-0.192322</v>
       </c>
       <c r="G24" t="n">
         <v>98.36065600000001</v>
@@ -1051,7 +1051,7 @@
         <v>0.132408</v>
       </c>
       <c r="F25" t="n">
-        <v>2.483281</v>
+        <v>1.367173</v>
       </c>
       <c r="G25" t="n">
         <v>98.36065600000001</v>
@@ -1076,7 +1076,7 @@
         <v>-7.369841</v>
       </c>
       <c r="F26" t="n">
-        <v>25.366903</v>
+        <v>31.035971</v>
       </c>
       <c r="G26" t="n">
         <v>98.36065600000001</v>
@@ -1101,7 +1101,7 @@
         <v>-4.375742</v>
       </c>
       <c r="F27" t="n">
-        <v>16.291834</v>
+        <v>27.96215</v>
       </c>
       <c r="G27" t="n">
         <v>98.36065600000001</v>
@@ -1126,7 +1126,7 @@
         <v>-8.199329000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>9.872398</v>
+        <v>11.394672</v>
       </c>
       <c r="G28" t="n">
         <v>98.36065600000001</v>
@@ -1151,7 +1151,7 @@
         <v>-2.3766</v>
       </c>
       <c r="F29" t="n">
-        <v>16.535433</v>
+        <v>18.413083</v>
       </c>
       <c r="G29" t="n">
         <v>98.36065600000001</v>
@@ -1376,7 +1376,7 @@
         <v>5.1216</v>
       </c>
       <c r="F38" t="n">
-        <v>5.078</v>
+        <v>5.0638</v>
       </c>
       <c r="G38" t="n">
         <v>100</v>
@@ -1401,7 +1401,7 @@
         <v>5.121</v>
       </c>
       <c r="F39" t="n">
-        <v>5.0774</v>
+        <v>5.0632</v>
       </c>
       <c r="G39" t="n">
         <v>100</v>
@@ -1676,7 +1676,7 @@
         <v>0.423696</v>
       </c>
       <c r="F50" t="n">
-        <v>-1.904725</v>
+        <v>-2.179036</v>
       </c>
       <c r="G50" t="n">
         <v>98.36065600000001</v>
@@ -1701,7 +1701,7 @@
         <v>0.423745</v>
       </c>
       <c r="F51" t="n">
-        <v>-1.904946</v>
+        <v>-2.179289</v>
       </c>
       <c r="G51" t="n">
         <v>98.36065600000001</v>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -476,7 +476,7 @@
         <v>121801</v>
       </c>
       <c r="F2" t="n">
-        <v>177548</v>
+        <v>176724</v>
       </c>
       <c r="G2" t="n">
         <v>100</v>
@@ -501,7 +501,7 @@
         <v>117.110001</v>
       </c>
       <c r="F3" t="n">
-        <v>174.699997</v>
+        <v>173.449997</v>
       </c>
       <c r="G3" t="n">
         <v>100</v>
@@ -526,7 +526,7 @@
         <v>141.800003</v>
       </c>
       <c r="F4" t="n">
-        <v>107.5</v>
+        <v>106.18</v>
       </c>
       <c r="G4" t="n">
         <v>100</v>
@@ -551,7 +551,7 @@
         <v>250.350006</v>
       </c>
       <c r="F5" t="n">
-        <v>428.859985</v>
+        <v>425.519989</v>
       </c>
       <c r="G5" t="n">
         <v>100</v>
@@ -576,7 +576,7 @@
         <v>5.0804</v>
       </c>
       <c r="F6" t="n">
-        <v>5.0572</v>
+        <v>5.0821</v>
       </c>
       <c r="G6" t="n">
         <v>100</v>
@@ -601,7 +601,7 @@
         <v>6.0387</v>
       </c>
       <c r="F7" t="n">
-        <v>5.7601</v>
+        <v>5.7826</v>
       </c>
       <c r="G7" t="n">
         <v>100</v>
@@ -626,7 +626,7 @@
         <v>4395.259766</v>
       </c>
       <c r="F8" t="n">
-        <v>7498.959961</v>
+        <v>7408.299805</v>
       </c>
       <c r="G8" t="n">
         <v>100</v>
@@ -651,7 +651,7 @@
         <v>14672.679688</v>
       </c>
       <c r="F9" t="n">
-        <v>25690.900391</v>
+        <v>25137.689453</v>
       </c>
       <c r="G9" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
         <v>34935.46875</v>
       </c>
       <c r="F10" t="n">
-        <v>52218.578125</v>
+        <v>51711.648438</v>
       </c>
       <c r="G10" t="n">
         <v>100</v>
@@ -701,7 +701,7 @@
         <v>1812.599976</v>
       </c>
       <c r="F11" t="n">
-        <v>4077.899902</v>
+        <v>4062.100098</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
@@ -726,7 +726,7 @@
         <v>73.949997</v>
       </c>
       <c r="F12" t="n">
-        <v>91.06999999999999</v>
+        <v>89.879997</v>
       </c>
       <c r="G12" t="n">
         <v>100</v>
@@ -751,7 +751,7 @@
         <v>76.33000199999999</v>
       </c>
       <c r="F13" t="n">
-        <v>93.30999799999999</v>
+        <v>92</v>
       </c>
       <c r="G13" t="n">
         <v>100</v>
@@ -776,7 +776,7 @@
         <v>1414.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1244</v>
+        <v>1247.5</v>
       </c>
       <c r="G14" t="n">
         <v>100</v>
@@ -801,7 +801,7 @@
         <v>547</v>
       </c>
       <c r="F15" t="n">
-        <v>488.75</v>
+        <v>487</v>
       </c>
       <c r="G15" t="n">
         <v>100</v>
@@ -826,7 +826,7 @@
         <v>-2.479454</v>
       </c>
       <c r="F16" t="n">
-        <v>3.21118</v>
+        <v>2.732177</v>
       </c>
       <c r="G16" t="n">
         <v>98.36065600000001</v>
@@ -851,7 +851,7 @@
         <v>-2.58731</v>
       </c>
       <c r="F17" t="n">
-        <v>3.342203</v>
+        <v>2.602777</v>
       </c>
       <c r="G17" t="n">
         <v>98.36065600000001</v>
@@ -876,7 +876,7 @@
         <v>-3.857547</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.44453</v>
+        <v>-1.666978</v>
       </c>
       <c r="G18" t="n">
         <v>98.36065600000001</v>
@@ -901,7 +901,7 @@
         <v>1.457956</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.558593</v>
+        <v>-2.325262</v>
       </c>
       <c r="G19" t="n">
         <v>98.36065600000001</v>
@@ -926,7 +926,7 @@
         <v>2.017557</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.404326</v>
+        <v>-1.923798</v>
       </c>
       <c r="G20" t="n">
         <v>98.36065600000001</v>
@@ -951,7 +951,7 @@
         <v>1.212177</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.654316</v>
+        <v>-2.274066</v>
       </c>
       <c r="G21" t="n">
         <v>98.36065600000001</v>
@@ -976,7 +976,7 @@
         <v>2.899042</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.005332</v>
+        <v>-1.214238</v>
       </c>
       <c r="G22" t="n">
         <v>98.36065600000001</v>
@@ -1001,7 +1001,7 @@
         <v>3.997638</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.994453</v>
+        <v>-4.10484</v>
       </c>
       <c r="G23" t="n">
         <v>98.36065600000001</v>
@@ -1026,7 +1026,7 @@
         <v>1.217278</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.192322</v>
+        <v>-1.161239</v>
       </c>
       <c r="G24" t="n">
         <v>98.36065600000001</v>
@@ -1051,7 +1051,7 @@
         <v>0.132408</v>
       </c>
       <c r="F25" t="n">
-        <v>1.367173</v>
+        <v>0.974426</v>
       </c>
       <c r="G25" t="n">
         <v>98.36065600000001</v>
@@ -1076,7 +1076,7 @@
         <v>-7.369841</v>
       </c>
       <c r="F26" t="n">
-        <v>31.035971</v>
+        <v>29.323737</v>
       </c>
       <c r="G26" t="n">
         <v>98.36065600000001</v>
@@ -1101,7 +1101,7 @@
         <v>-4.375742</v>
       </c>
       <c r="F27" t="n">
-        <v>27.96215</v>
+        <v>26.165664</v>
       </c>
       <c r="G27" t="n">
         <v>98.36065600000001</v>
@@ -1126,7 +1126,7 @@
         <v>-8.199329000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>11.394672</v>
+        <v>11.708081</v>
       </c>
       <c r="G28" t="n">
         <v>98.36065600000001</v>
@@ -1151,7 +1151,7 @@
         <v>-2.3766</v>
       </c>
       <c r="F29" t="n">
-        <v>18.413083</v>
+        <v>17.989098</v>
       </c>
       <c r="G29" t="n">
         <v>98.36065600000001</v>
@@ -1376,7 +1376,7 @@
         <v>5.1216</v>
       </c>
       <c r="F38" t="n">
-        <v>5.0638</v>
+        <v>5.0807</v>
       </c>
       <c r="G38" t="n">
         <v>100</v>
@@ -1401,7 +1401,7 @@
         <v>5.121</v>
       </c>
       <c r="F39" t="n">
-        <v>5.0632</v>
+        <v>5.0801</v>
       </c>
       <c r="G39" t="n">
         <v>100</v>
@@ -1676,7 +1676,7 @@
         <v>0.423696</v>
       </c>
       <c r="F50" t="n">
-        <v>-2.179036</v>
+        <v>-1.852567</v>
       </c>
       <c r="G50" t="n">
         <v>98.36065600000001</v>
@@ -1701,7 +1701,7 @@
         <v>0.423745</v>
       </c>
       <c r="F51" t="n">
-        <v>-2.179289</v>
+        <v>-1.852782</v>
       </c>
       <c r="G51" t="n">
         <v>98.36065600000001</v>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
         <v>121801</v>
       </c>
       <c r="F2" t="n">
-        <v>176724</v>
+        <v>174042</v>
       </c>
       <c r="G2" t="n">
         <v>100</v>
@@ -501,7 +501,7 @@
         <v>117.110001</v>
       </c>
       <c r="F3" t="n">
-        <v>173.449997</v>
+        <v>170.949997</v>
       </c>
       <c r="G3" t="n">
         <v>100</v>
@@ -526,7 +526,7 @@
         <v>141.800003</v>
       </c>
       <c r="F4" t="n">
-        <v>106.18</v>
+        <v>105.050003</v>
       </c>
       <c r="G4" t="n">
         <v>100</v>
@@ -551,7 +551,7 @@
         <v>250.350006</v>
       </c>
       <c r="F5" t="n">
-        <v>425.519989</v>
+        <v>425.049988</v>
       </c>
       <c r="G5" t="n">
         <v>100</v>
@@ -576,7 +576,7 @@
         <v>5.0804</v>
       </c>
       <c r="F6" t="n">
-        <v>5.0821</v>
+        <v>5.0751</v>
       </c>
       <c r="G6" t="n">
         <v>100</v>
@@ -601,7 +601,7 @@
         <v>6.0387</v>
       </c>
       <c r="F7" t="n">
-        <v>5.7826</v>
+        <v>5.7816</v>
       </c>
       <c r="G7" t="n">
         <v>100</v>
@@ -626,7 +626,7 @@
         <v>4395.259766</v>
       </c>
       <c r="F8" t="n">
-        <v>7408.299805</v>
+        <v>7411.97998</v>
       </c>
       <c r="G8" t="n">
         <v>100</v>
@@ -651,7 +651,7 @@
         <v>14672.679688</v>
       </c>
       <c r="F9" t="n">
-        <v>25137.689453</v>
+        <v>24975.820312</v>
       </c>
       <c r="G9" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
         <v>34935.46875</v>
       </c>
       <c r="F10" t="n">
-        <v>51711.648438</v>
+        <v>51947.25</v>
       </c>
       <c r="G10" t="n">
         <v>100</v>
@@ -701,7 +701,7 @@
         <v>1812.599976</v>
       </c>
       <c r="F11" t="n">
-        <v>4062.100098</v>
+        <v>4067.600098</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
@@ -726,7 +726,7 @@
         <v>73.949997</v>
       </c>
       <c r="F12" t="n">
-        <v>89.879997</v>
+        <v>89.30999799999999</v>
       </c>
       <c r="G12" t="n">
         <v>100</v>
@@ -751,7 +751,7 @@
         <v>76.33000199999999</v>
       </c>
       <c r="F13" t="n">
-        <v>92</v>
+        <v>96.779999</v>
       </c>
       <c r="G13" t="n">
         <v>100</v>
@@ -776,7 +776,7 @@
         <v>1414.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1247.5</v>
+        <v>1248</v>
       </c>
       <c r="G14" t="n">
         <v>100</v>
@@ -801,7 +801,7 @@
         <v>547</v>
       </c>
       <c r="F15" t="n">
-        <v>487</v>
+        <v>464.25</v>
       </c>
       <c r="G15" t="n">
         <v>100</v>
@@ -826,7 +826,7 @@
         <v>-2.479454</v>
       </c>
       <c r="F16" t="n">
-        <v>2.732177</v>
+        <v>1.173092</v>
       </c>
       <c r="G16" t="n">
         <v>98.36065600000001</v>
@@ -851,7 +851,7 @@
         <v>-2.58731</v>
       </c>
       <c r="F17" t="n">
-        <v>2.602777</v>
+        <v>1.123924</v>
       </c>
       <c r="G17" t="n">
         <v>98.36065600000001</v>
@@ -876,7 +876,7 @@
         <v>-3.857547</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.666978</v>
+        <v>-2.713466</v>
       </c>
       <c r="G18" t="n">
         <v>98.36065600000001</v>
@@ -901,7 +901,7 @@
         <v>1.457956</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.325262</v>
+        <v>-2.433147</v>
       </c>
       <c r="G19" t="n">
         <v>98.36065600000001</v>
@@ -926,7 +926,7 @@
         <v>2.017557</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.923798</v>
+        <v>-2.058886</v>
       </c>
       <c r="G20" t="n">
         <v>98.36065600000001</v>
@@ -951,7 +951,7 @@
         <v>1.212177</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.274066</v>
+        <v>-2.290964</v>
       </c>
       <c r="G21" t="n">
         <v>98.36065600000001</v>
@@ -976,7 +976,7 @@
         <v>2.899042</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.214238</v>
+        <v>-1.165165</v>
       </c>
       <c r="G22" t="n">
         <v>98.36065600000001</v>
@@ -1001,7 +1001,7 @@
         <v>3.997638</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.10484</v>
+        <v>-4.722338</v>
       </c>
       <c r="G23" t="n">
         <v>98.36065600000001</v>
@@ -1026,7 +1026,7 @@
         <v>1.217278</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.161239</v>
+        <v>-0.710923</v>
       </c>
       <c r="G24" t="n">
         <v>98.36065600000001</v>
@@ -1051,7 +1051,7 @@
         <v>0.132408</v>
       </c>
       <c r="F25" t="n">
-        <v>0.974426</v>
+        <v>1.111144</v>
       </c>
       <c r="G25" t="n">
         <v>98.36065600000001</v>
@@ -1076,7 +1076,7 @@
         <v>-7.369841</v>
       </c>
       <c r="F26" t="n">
-        <v>29.323737</v>
+        <v>28.503594</v>
       </c>
       <c r="G26" t="n">
         <v>98.36065600000001</v>
@@ -1101,7 +1101,7 @@
         <v>-4.375742</v>
       </c>
       <c r="F27" t="n">
-        <v>26.165664</v>
+        <v>32.720792</v>
       </c>
       <c r="G27" t="n">
         <v>98.36065600000001</v>
@@ -1126,7 +1126,7 @@
         <v>-8.199329000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>11.708081</v>
+        <v>11.752854</v>
       </c>
       <c r="G28" t="n">
         <v>98.36065600000001</v>
@@ -1151,7 +1151,7 @@
         <v>-2.3766</v>
       </c>
       <c r="F29" t="n">
-        <v>17.989098</v>
+        <v>12.477286</v>
       </c>
       <c r="G29" t="n">
         <v>98.36065600000001</v>
@@ -1210,32 +1210,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bcb_sgs_cdi</t>
+          <t>bcb_sgs_ipca</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D32" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E32" t="n">
-        <v>0.016137</v>
+        <v>0.96</v>
       </c>
       <c r="F32" t="n">
-        <v>0.052531</v>
+        <v>0.16</v>
       </c>
       <c r="G32" t="n">
-        <v>100</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca</t>
+          <t>bcb_sgs_igp_m</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
@@ -1248,10 +1248,10 @@
         <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>0.96</v>
+        <v>0.78</v>
       </c>
       <c r="F33" t="n">
-        <v>0.16</v>
+        <v>-0.5</v>
       </c>
       <c r="G33" t="n">
         <v>98.36065600000001</v>
@@ -1260,7 +1260,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m</t>
+          <t>bcb_sgs_inpc</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1273,10 +1273,10 @@
         <v>60</v>
       </c>
       <c r="E34" t="n">
-        <v>0.78</v>
+        <v>1.02</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.5</v>
+        <v>0.14</v>
       </c>
       <c r="G34" t="n">
         <v>98.36065600000001</v>
@@ -1285,32 +1285,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc</t>
+          <t>bcb_sgs_ibc_br_sa</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="D35" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E35" t="n">
-        <v>1.02</v>
+        <v>96.31464</v>
       </c>
       <c r="F35" t="n">
-        <v>0.14</v>
+        <v>111.03587</v>
       </c>
       <c r="G35" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br_sa</t>
+          <t>bcb_sgs_ibc_br</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
@@ -1323,10 +1323,10 @@
         <v>59</v>
       </c>
       <c r="E36" t="n">
-        <v>96.31464</v>
+        <v>99.83978</v>
       </c>
       <c r="F36" t="n">
-        <v>111.03587</v>
+        <v>109.52993</v>
       </c>
       <c r="G36" t="n">
         <v>96.721311</v>
@@ -1335,32 +1335,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br</t>
+          <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D37" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E37" t="n">
-        <v>99.83978</v>
+        <v>5.1216</v>
       </c>
       <c r="F37" t="n">
-        <v>109.52993</v>
+        <v>5.0666</v>
       </c>
       <c r="G37" t="n">
-        <v>96.721311</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_venda_usd</t>
+          <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
@@ -1373,10 +1373,10 @@
         <v>61</v>
       </c>
       <c r="E38" t="n">
-        <v>5.1216</v>
+        <v>5.121</v>
       </c>
       <c r="F38" t="n">
-        <v>5.0807</v>
+        <v>5.066</v>
       </c>
       <c r="G38" t="n">
         <v>100</v>
@@ -1385,32 +1385,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_compra_usd</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D39" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E39" t="n">
-        <v>5.121</v>
+        <v>4271865</v>
       </c>
       <c r="F39" t="n">
-        <v>5.0801</v>
+        <v>7299615</v>
       </c>
       <c r="G39" t="n">
-        <v>100</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
@@ -1423,10 +1423,10 @@
         <v>59</v>
       </c>
       <c r="E40" t="n">
-        <v>4271865</v>
+        <v>1833179</v>
       </c>
       <c r="F40" t="n">
-        <v>7299615</v>
+        <v>2704550</v>
       </c>
       <c r="G40" t="n">
         <v>96.721311</v>
@@ -1435,7 +1435,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
@@ -1448,10 +1448,10 @@
         <v>59</v>
       </c>
       <c r="E41" t="n">
-        <v>1833179</v>
+        <v>2438686</v>
       </c>
       <c r="F41" t="n">
-        <v>2704550</v>
+        <v>4595065</v>
       </c>
       <c r="G41" t="n">
         <v>96.721311</v>
@@ -1460,7 +1460,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
@@ -1473,10 +1473,10 @@
         <v>59</v>
       </c>
       <c r="E42" t="n">
-        <v>2438686</v>
+        <v>2.36</v>
       </c>
       <c r="F42" t="n">
-        <v>4595065</v>
+        <v>4.74</v>
       </c>
       <c r="G42" t="n">
         <v>96.721311</v>
@@ -1485,7 +1485,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
@@ -1498,10 +1498,10 @@
         <v>59</v>
       </c>
       <c r="E43" t="n">
-        <v>2.36</v>
+        <v>1.58</v>
       </c>
       <c r="F43" t="n">
-        <v>4.74</v>
+        <v>3.24</v>
       </c>
       <c r="G43" t="n">
         <v>96.721311</v>
@@ -1510,7 +1510,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
@@ -1523,10 +1523,10 @@
         <v>59</v>
       </c>
       <c r="E44" t="n">
-        <v>1.58</v>
+        <v>2.94</v>
       </c>
       <c r="F44" t="n">
-        <v>3.24</v>
+        <v>5.62</v>
       </c>
       <c r="G44" t="n">
         <v>96.721311</v>
@@ -1535,7 +1535,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
@@ -1548,10 +1548,10 @@
         <v>59</v>
       </c>
       <c r="E45" t="n">
-        <v>2.94</v>
+        <v>20.26</v>
       </c>
       <c r="F45" t="n">
-        <v>5.62</v>
+        <v>33.42</v>
       </c>
       <c r="G45" t="n">
         <v>96.721311</v>
@@ -1560,57 +1560,57 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D46" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E46" t="n">
-        <v>20.26</v>
+        <v>355671</v>
       </c>
       <c r="F46" t="n">
-        <v>33.42</v>
+        <v>367558</v>
       </c>
       <c r="G46" t="n">
-        <v>96.721311</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="D47" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E47" t="n">
-        <v>355671</v>
+        <v>0.79016</v>
       </c>
       <c r="F47" t="n">
-        <v>367558</v>
+        <v>0.07079299999999999</v>
       </c>
       <c r="G47" t="n">
-        <v>98.36065600000001</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
@@ -1623,10 +1623,10 @@
         <v>58</v>
       </c>
       <c r="E48" t="n">
-        <v>0.79016</v>
+        <v>-0.512311</v>
       </c>
       <c r="F48" t="n">
-        <v>0.07079299999999999</v>
+        <v>-3.915762</v>
       </c>
       <c r="G48" t="n">
         <v>95.08196700000001</v>
@@ -1635,32 +1635,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D49" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.512311</v>
+        <v>0.423696</v>
       </c>
       <c r="F49" t="n">
-        <v>-3.915762</v>
+        <v>-2.124947</v>
       </c>
       <c r="G49" t="n">
-        <v>95.08196700000001</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
@@ -1673,10 +1673,10 @@
         <v>60</v>
       </c>
       <c r="E50" t="n">
-        <v>0.423696</v>
+        <v>0.423745</v>
       </c>
       <c r="F50" t="n">
-        <v>-1.852567</v>
+        <v>-2.125193</v>
       </c>
       <c r="G50" t="n">
         <v>98.36065600000001</v>
@@ -1685,32 +1685,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D51" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E51" t="n">
-        <v>0.423745</v>
+        <v>1.736829</v>
       </c>
       <c r="F51" t="n">
-        <v>-1.852782</v>
+        <v>0.565068</v>
       </c>
       <c r="G51" t="n">
-        <v>98.36065600000001</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
@@ -1723,10 +1723,10 @@
         <v>58</v>
       </c>
       <c r="E52" t="n">
-        <v>1.736829</v>
+        <v>0.972464</v>
       </c>
       <c r="F52" t="n">
-        <v>0.565068</v>
+        <v>0.742264</v>
       </c>
       <c r="G52" t="n">
         <v>95.08196700000001</v>
@@ -1735,7 +1735,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
@@ -1748,10 +1748,10 @@
         <v>58</v>
       </c>
       <c r="E53" t="n">
-        <v>0.972464</v>
+        <v>2.311409</v>
       </c>
       <c r="F53" t="n">
-        <v>0.742264</v>
+        <v>0.461065</v>
       </c>
       <c r="G53" t="n">
         <v>95.08196700000001</v>
@@ -1760,57 +1760,57 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D54" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E54" t="n">
-        <v>2.311409</v>
+        <v>4.139781</v>
       </c>
       <c r="F54" t="n">
-        <v>0.461065</v>
+        <v>-0.964334</v>
       </c>
       <c r="G54" t="n">
-        <v>95.08196700000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>44439</v>
+        <v>44742</v>
       </c>
       <c r="C55" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D55" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E55" t="n">
-        <v>4.139781</v>
+        <v>11.88673</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.964334</v>
+        <v>4.641328</v>
       </c>
       <c r="G55" t="n">
-        <v>96.721311</v>
+        <v>80.32786900000001</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
@@ -1823,10 +1823,10 @@
         <v>49</v>
       </c>
       <c r="E56" t="n">
-        <v>11.88673</v>
+        <v>10.700862</v>
       </c>
       <c r="F56" t="n">
-        <v>4.641328</v>
+        <v>3.177699</v>
       </c>
       <c r="G56" t="n">
         <v>80.32786900000001</v>
@@ -1835,7 +1835,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
@@ -1848,10 +1848,10 @@
         <v>49</v>
       </c>
       <c r="E57" t="n">
-        <v>10.700862</v>
+        <v>11.919595</v>
       </c>
       <c r="F57" t="n">
-        <v>3.177699</v>
+        <v>4.327084</v>
       </c>
       <c r="G57" t="n">
         <v>80.32786900000001</v>
@@ -1860,32 +1860,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>44742</v>
+        <v>44439</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D58" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E58" t="n">
-        <v>11.919595</v>
+        <v>1</v>
       </c>
       <c r="F58" t="n">
-        <v>4.327084</v>
+        <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>80.32786900000001</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
@@ -1898,10 +1898,10 @@
         <v>60</v>
       </c>
       <c r="E59" t="n">
-        <v>1</v>
+        <v>0.003276</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>-0.000497</v>
       </c>
       <c r="G59" t="n">
         <v>98.36065600000001</v>
@@ -1910,57 +1910,57 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D60" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E60" t="n">
-        <v>0.003276</v>
+        <v>0.01</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.000497</v>
+        <v>0.11</v>
       </c>
       <c r="G60" t="n">
-        <v>98.36065600000001</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D61" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E61" t="n">
-        <v>0.003276</v>
+        <v>-0.02</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.000497</v>
+        <v>0.09</v>
       </c>
       <c r="G61" t="n">
-        <v>98.36065600000001</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
@@ -1973,7 +1973,7 @@
         <v>58</v>
       </c>
       <c r="E62" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F62" t="n">
         <v>0.11</v>
@@ -1985,7 +1985,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
@@ -1998,62 +1998,12 @@
         <v>58</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.02</v>
+        <v>0.66</v>
       </c>
       <c r="F63" t="n">
-        <v>0.09</v>
+        <v>-0.09</v>
       </c>
       <c r="G63" t="n">
-        <v>95.08196700000001</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
-        </is>
-      </c>
-      <c r="B64" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="C64" s="1" t="n">
-        <v>46173</v>
-      </c>
-      <c r="D64" t="n">
-        <v>58</v>
-      </c>
-      <c r="E64" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F64" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="G64" t="n">
-        <v>95.08196700000001</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
-        </is>
-      </c>
-      <c r="B65" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="C65" s="1" t="n">
-        <v>46173</v>
-      </c>
-      <c r="D65" t="n">
-        <v>58</v>
-      </c>
-      <c r="E65" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="F65" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="G65" t="n">
         <v>95.08196700000001</v>
       </c>
     </row>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
         <v>121801</v>
       </c>
       <c r="F2" t="n">
-        <v>174042</v>
+        <v>176724</v>
       </c>
       <c r="G2" t="n">
         <v>100</v>
@@ -626,7 +626,7 @@
         <v>4395.259766</v>
       </c>
       <c r="F8" t="n">
-        <v>7411.97998</v>
+        <v>7408.299805</v>
       </c>
       <c r="G8" t="n">
         <v>100</v>
@@ -651,7 +651,7 @@
         <v>14672.679688</v>
       </c>
       <c r="F9" t="n">
-        <v>24975.820312</v>
+        <v>25137.689453</v>
       </c>
       <c r="G9" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
         <v>34935.46875</v>
       </c>
       <c r="F10" t="n">
-        <v>51947.25</v>
+        <v>51711.648438</v>
       </c>
       <c r="G10" t="n">
         <v>100</v>
@@ -701,7 +701,7 @@
         <v>1812.599976</v>
       </c>
       <c r="F11" t="n">
-        <v>4067.600098</v>
+        <v>4070.800049</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
@@ -776,7 +776,7 @@
         <v>1414.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1248</v>
+        <v>1253.5</v>
       </c>
       <c r="G14" t="n">
         <v>100</v>
@@ -801,7 +801,7 @@
         <v>547</v>
       </c>
       <c r="F15" t="n">
-        <v>464.25</v>
+        <v>487.25</v>
       </c>
       <c r="G15" t="n">
         <v>100</v>
@@ -826,7 +826,7 @@
         <v>-2.479454</v>
       </c>
       <c r="F16" t="n">
-        <v>1.173092</v>
+        <v>2.732177</v>
       </c>
       <c r="G16" t="n">
         <v>98.36065600000001</v>
@@ -976,7 +976,7 @@
         <v>2.899042</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.165165</v>
+        <v>-1.214238</v>
       </c>
       <c r="G22" t="n">
         <v>98.36065600000001</v>
@@ -1001,7 +1001,7 @@
         <v>3.997638</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.722338</v>
+        <v>-4.10484</v>
       </c>
       <c r="G23" t="n">
         <v>98.36065600000001</v>
@@ -1026,7 +1026,7 @@
         <v>1.217278</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.710923</v>
+        <v>-1.161239</v>
       </c>
       <c r="G24" t="n">
         <v>98.36065600000001</v>
@@ -1051,7 +1051,7 @@
         <v>0.132408</v>
       </c>
       <c r="F25" t="n">
-        <v>1.111144</v>
+        <v>1.190687</v>
       </c>
       <c r="G25" t="n">
         <v>98.36065600000001</v>
@@ -1126,7 +1126,7 @@
         <v>-8.199329000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>11.752854</v>
+        <v>12.245355</v>
       </c>
       <c r="G28" t="n">
         <v>98.36065600000001</v>
@@ -1151,7 +1151,7 @@
         <v>-2.3766</v>
       </c>
       <c r="F29" t="n">
-        <v>12.477286</v>
+        <v>18.049667</v>
       </c>
       <c r="G29" t="n">
         <v>98.36065600000001</v>
@@ -1210,32 +1210,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca</t>
+          <t>bcb_sgs_cdi</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D32" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E32" t="n">
-        <v>0.96</v>
+        <v>0.016137</v>
       </c>
       <c r="F32" t="n">
-        <v>0.16</v>
+        <v>0.052531</v>
       </c>
       <c r="G32" t="n">
-        <v>98.36065600000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m</t>
+          <t>bcb_sgs_ipca</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
@@ -1248,10 +1248,10 @@
         <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>0.78</v>
+        <v>0.96</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.5</v>
+        <v>0.16</v>
       </c>
       <c r="G33" t="n">
         <v>98.36065600000001</v>
@@ -1260,7 +1260,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc</t>
+          <t>bcb_sgs_igp_m</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1273,10 +1273,10 @@
         <v>60</v>
       </c>
       <c r="E34" t="n">
-        <v>1.02</v>
+        <v>0.78</v>
       </c>
       <c r="F34" t="n">
-        <v>0.14</v>
+        <v>-0.5</v>
       </c>
       <c r="G34" t="n">
         <v>98.36065600000001</v>
@@ -1285,32 +1285,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br_sa</t>
+          <t>bcb_sgs_inpc</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D35" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E35" t="n">
-        <v>96.31464</v>
+        <v>1.02</v>
       </c>
       <c r="F35" t="n">
-        <v>111.03587</v>
+        <v>0.14</v>
       </c>
       <c r="G35" t="n">
-        <v>96.721311</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br</t>
+          <t>bcb_sgs_ibc_br_sa</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
@@ -1323,10 +1323,10 @@
         <v>59</v>
       </c>
       <c r="E36" t="n">
-        <v>99.83978</v>
+        <v>96.31464</v>
       </c>
       <c r="F36" t="n">
-        <v>109.52993</v>
+        <v>111.03587</v>
       </c>
       <c r="G36" t="n">
         <v>96.721311</v>
@@ -1335,32 +1335,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_venda_usd</t>
+          <t>bcb_sgs_ibc_br</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D37" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E37" t="n">
-        <v>5.1216</v>
+        <v>99.83978</v>
       </c>
       <c r="F37" t="n">
-        <v>5.0666</v>
+        <v>109.52993</v>
       </c>
       <c r="G37" t="n">
-        <v>100</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_compra_usd</t>
+          <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
@@ -1373,10 +1373,10 @@
         <v>61</v>
       </c>
       <c r="E38" t="n">
-        <v>5.121</v>
+        <v>5.1216</v>
       </c>
       <c r="F38" t="n">
-        <v>5.066</v>
+        <v>5.0666</v>
       </c>
       <c r="G38" t="n">
         <v>100</v>
@@ -1385,32 +1385,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D39" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E39" t="n">
-        <v>4271865</v>
+        <v>5.121</v>
       </c>
       <c r="F39" t="n">
-        <v>7299615</v>
+        <v>5.066</v>
       </c>
       <c r="G39" t="n">
-        <v>96.721311</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
@@ -1423,10 +1423,10 @@
         <v>59</v>
       </c>
       <c r="E40" t="n">
-        <v>1833179</v>
+        <v>4271865</v>
       </c>
       <c r="F40" t="n">
-        <v>2704550</v>
+        <v>7299615</v>
       </c>
       <c r="G40" t="n">
         <v>96.721311</v>
@@ -1435,7 +1435,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
@@ -1448,10 +1448,10 @@
         <v>59</v>
       </c>
       <c r="E41" t="n">
-        <v>2438686</v>
+        <v>1833179</v>
       </c>
       <c r="F41" t="n">
-        <v>4595065</v>
+        <v>2704550</v>
       </c>
       <c r="G41" t="n">
         <v>96.721311</v>
@@ -1460,7 +1460,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
@@ -1473,10 +1473,10 @@
         <v>59</v>
       </c>
       <c r="E42" t="n">
-        <v>2.36</v>
+        <v>2438686</v>
       </c>
       <c r="F42" t="n">
-        <v>4.74</v>
+        <v>4595065</v>
       </c>
       <c r="G42" t="n">
         <v>96.721311</v>
@@ -1485,7 +1485,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
@@ -1498,10 +1498,10 @@
         <v>59</v>
       </c>
       <c r="E43" t="n">
-        <v>1.58</v>
+        <v>2.36</v>
       </c>
       <c r="F43" t="n">
-        <v>3.24</v>
+        <v>4.74</v>
       </c>
       <c r="G43" t="n">
         <v>96.721311</v>
@@ -1510,7 +1510,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
@@ -1523,10 +1523,10 @@
         <v>59</v>
       </c>
       <c r="E44" t="n">
-        <v>2.94</v>
+        <v>1.58</v>
       </c>
       <c r="F44" t="n">
-        <v>5.62</v>
+        <v>3.24</v>
       </c>
       <c r="G44" t="n">
         <v>96.721311</v>
@@ -1535,7 +1535,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
@@ -1548,10 +1548,10 @@
         <v>59</v>
       </c>
       <c r="E45" t="n">
-        <v>20.26</v>
+        <v>2.94</v>
       </c>
       <c r="F45" t="n">
-        <v>33.42</v>
+        <v>5.62</v>
       </c>
       <c r="G45" t="n">
         <v>96.721311</v>
@@ -1560,57 +1560,57 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="D46" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E46" t="n">
-        <v>355671</v>
+        <v>20.26</v>
       </c>
       <c r="F46" t="n">
-        <v>367558</v>
+        <v>33.42</v>
       </c>
       <c r="G46" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D47" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E47" t="n">
-        <v>0.79016</v>
+        <v>355671</v>
       </c>
       <c r="F47" t="n">
-        <v>0.07079299999999999</v>
+        <v>367558</v>
       </c>
       <c r="G47" t="n">
-        <v>95.08196700000001</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
@@ -1623,10 +1623,10 @@
         <v>58</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.512311</v>
+        <v>0.79016</v>
       </c>
       <c r="F48" t="n">
-        <v>-3.915762</v>
+        <v>0.07079299999999999</v>
       </c>
       <c r="G48" t="n">
         <v>95.08196700000001</v>
@@ -1635,32 +1635,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D49" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E49" t="n">
-        <v>0.423696</v>
+        <v>-0.512311</v>
       </c>
       <c r="F49" t="n">
-        <v>-2.124947</v>
+        <v>-3.915762</v>
       </c>
       <c r="G49" t="n">
-        <v>98.36065600000001</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
@@ -1673,10 +1673,10 @@
         <v>60</v>
       </c>
       <c r="E50" t="n">
-        <v>0.423745</v>
+        <v>0.423696</v>
       </c>
       <c r="F50" t="n">
-        <v>-2.125193</v>
+        <v>-2.124947</v>
       </c>
       <c r="G50" t="n">
         <v>98.36065600000001</v>
@@ -1685,32 +1685,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D51" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E51" t="n">
-        <v>1.736829</v>
+        <v>0.423745</v>
       </c>
       <c r="F51" t="n">
-        <v>0.565068</v>
+        <v>-2.125193</v>
       </c>
       <c r="G51" t="n">
-        <v>95.08196700000001</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
@@ -1723,10 +1723,10 @@
         <v>58</v>
       </c>
       <c r="E52" t="n">
-        <v>0.972464</v>
+        <v>1.736829</v>
       </c>
       <c r="F52" t="n">
-        <v>0.742264</v>
+        <v>0.565068</v>
       </c>
       <c r="G52" t="n">
         <v>95.08196700000001</v>
@@ -1735,7 +1735,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
@@ -1748,10 +1748,10 @@
         <v>58</v>
       </c>
       <c r="E53" t="n">
-        <v>2.311409</v>
+        <v>0.972464</v>
       </c>
       <c r="F53" t="n">
-        <v>0.461065</v>
+        <v>0.742264</v>
       </c>
       <c r="G53" t="n">
         <v>95.08196700000001</v>
@@ -1760,57 +1760,57 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="D54" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E54" t="n">
-        <v>4.139781</v>
+        <v>2.311409</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.964334</v>
+        <v>0.461065</v>
       </c>
       <c r="G54" t="n">
-        <v>96.721311</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>44742</v>
+        <v>44439</v>
       </c>
       <c r="C55" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D55" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E55" t="n">
-        <v>11.88673</v>
+        <v>4.139781</v>
       </c>
       <c r="F55" t="n">
-        <v>4.641328</v>
+        <v>-0.964334</v>
       </c>
       <c r="G55" t="n">
-        <v>80.32786900000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
@@ -1823,10 +1823,10 @@
         <v>49</v>
       </c>
       <c r="E56" t="n">
-        <v>10.700862</v>
+        <v>11.88673</v>
       </c>
       <c r="F56" t="n">
-        <v>3.177699</v>
+        <v>4.641328</v>
       </c>
       <c r="G56" t="n">
         <v>80.32786900000001</v>
@@ -1835,7 +1835,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
@@ -1848,10 +1848,10 @@
         <v>49</v>
       </c>
       <c r="E57" t="n">
-        <v>11.919595</v>
+        <v>10.700862</v>
       </c>
       <c r="F57" t="n">
-        <v>4.327084</v>
+        <v>3.177699</v>
       </c>
       <c r="G57" t="n">
         <v>80.32786900000001</v>
@@ -1860,32 +1860,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>44439</v>
+        <v>44742</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D58" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E58" t="n">
-        <v>1</v>
+        <v>11.919595</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>4.327084</v>
       </c>
       <c r="G58" t="n">
-        <v>98.36065600000001</v>
+        <v>80.32786900000001</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
@@ -1898,10 +1898,10 @@
         <v>60</v>
       </c>
       <c r="E59" t="n">
-        <v>0.003276</v>
+        <v>1</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.000497</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
         <v>98.36065600000001</v>
@@ -1910,57 +1910,57 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D60" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E60" t="n">
-        <v>0.01</v>
+        <v>0.003276</v>
       </c>
       <c r="F60" t="n">
-        <v>0.11</v>
+        <v>-0.000497</v>
       </c>
       <c r="G60" t="n">
-        <v>95.08196700000001</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D61" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.02</v>
+        <v>0.003276</v>
       </c>
       <c r="F61" t="n">
-        <v>0.09</v>
+        <v>-0.000497</v>
       </c>
       <c r="G61" t="n">
-        <v>95.08196700000001</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
@@ -1973,7 +1973,7 @@
         <v>58</v>
       </c>
       <c r="E62" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F62" t="n">
         <v>0.11</v>
@@ -1985,7 +1985,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
@@ -1998,12 +1998,62 @@
         <v>58</v>
       </c>
       <c r="E63" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="G63" t="n">
+        <v>95.08196700000001</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
+        </is>
+      </c>
+      <c r="B64" s="1" t="n">
+        <v>44439</v>
+      </c>
+      <c r="C64" s="1" t="n">
+        <v>46173</v>
+      </c>
+      <c r="D64" t="n">
+        <v>58</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="G64" t="n">
+        <v>95.08196700000001</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_juros_credito_total</t>
+        </is>
+      </c>
+      <c r="B65" s="1" t="n">
+        <v>44439</v>
+      </c>
+      <c r="C65" s="1" t="n">
+        <v>46173</v>
+      </c>
+      <c r="D65" t="n">
+        <v>58</v>
+      </c>
+      <c r="E65" t="n">
         <v>0.66</v>
       </c>
-      <c r="F63" t="n">
+      <c r="F65" t="n">
         <v>-0.09</v>
       </c>
-      <c r="G63" t="n">
+      <c r="G65" t="n">
         <v>95.08196700000001</v>
       </c>
     </row>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -576,7 +576,7 @@
         <v>5.0804</v>
       </c>
       <c r="F6" t="n">
-        <v>5.0751</v>
+        <v>5.0846</v>
       </c>
       <c r="G6" t="n">
         <v>100</v>
@@ -601,7 +601,7 @@
         <v>6.0387</v>
       </c>
       <c r="F7" t="n">
-        <v>5.7816</v>
+        <v>5.7877</v>
       </c>
       <c r="G7" t="n">
         <v>100</v>
@@ -701,7 +701,7 @@
         <v>1812.599976</v>
       </c>
       <c r="F11" t="n">
-        <v>4070.800049</v>
+        <v>4089.899902</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
@@ -726,7 +726,7 @@
         <v>73.949997</v>
       </c>
       <c r="F12" t="n">
-        <v>89.30999799999999</v>
+        <v>83.93000000000001</v>
       </c>
       <c r="G12" t="n">
         <v>100</v>
@@ -751,7 +751,7 @@
         <v>76.33000199999999</v>
       </c>
       <c r="F13" t="n">
-        <v>96.779999</v>
+        <v>90.550003</v>
       </c>
       <c r="G13" t="n">
         <v>100</v>
@@ -776,7 +776,7 @@
         <v>1414.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1253.5</v>
+        <v>1220.25</v>
       </c>
       <c r="G14" t="n">
         <v>100</v>
@@ -801,7 +801,7 @@
         <v>547</v>
       </c>
       <c r="F15" t="n">
-        <v>487.25</v>
+        <v>473.75</v>
       </c>
       <c r="G15" t="n">
         <v>100</v>
@@ -926,7 +926,7 @@
         <v>2.017557</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.058886</v>
+        <v>-1.875551</v>
       </c>
       <c r="G20" t="n">
         <v>98.36065600000001</v>
@@ -951,7 +951,7 @@
         <v>1.212177</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.290964</v>
+        <v>-2.187871</v>
       </c>
       <c r="G21" t="n">
         <v>98.36065600000001</v>
@@ -1051,7 +1051,7 @@
         <v>0.132408</v>
       </c>
       <c r="F25" t="n">
-        <v>1.190687</v>
+        <v>1.665465</v>
       </c>
       <c r="G25" t="n">
         <v>98.36065600000001</v>
@@ -1076,7 +1076,7 @@
         <v>-7.369841</v>
       </c>
       <c r="F26" t="n">
-        <v>28.503594</v>
+        <v>20.76259</v>
       </c>
       <c r="G26" t="n">
         <v>98.36065600000001</v>
@@ -1101,7 +1101,7 @@
         <v>-4.375742</v>
       </c>
       <c r="F27" t="n">
-        <v>32.720792</v>
+        <v>24.177188</v>
       </c>
       <c r="G27" t="n">
         <v>98.36065600000001</v>
@@ -1126,7 +1126,7 @@
         <v>-8.199329000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>12.245355</v>
+        <v>9.267965</v>
       </c>
       <c r="G28" t="n">
         <v>98.36065600000001</v>
@@ -1151,7 +1151,7 @@
         <v>-2.3766</v>
       </c>
       <c r="F29" t="n">
-        <v>18.049667</v>
+        <v>14.778922</v>
       </c>
       <c r="G29" t="n">
         <v>98.36065600000001</v>
@@ -1310,7 +1310,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br_sa</t>
+          <t>bcb_sgs_ibc_br</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
@@ -1323,10 +1323,10 @@
         <v>59</v>
       </c>
       <c r="E36" t="n">
-        <v>96.31464</v>
+        <v>99.83978</v>
       </c>
       <c r="F36" t="n">
-        <v>111.03587</v>
+        <v>109.52993</v>
       </c>
       <c r="G36" t="n">
         <v>96.721311</v>
@@ -1335,32 +1335,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br</t>
+          <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D37" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E37" t="n">
-        <v>99.83978</v>
+        <v>5.1216</v>
       </c>
       <c r="F37" t="n">
-        <v>109.52993</v>
+        <v>5.0666</v>
       </c>
       <c r="G37" t="n">
-        <v>96.721311</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_venda_usd</t>
+          <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
@@ -1373,10 +1373,10 @@
         <v>61</v>
       </c>
       <c r="E38" t="n">
-        <v>5.1216</v>
+        <v>5.121</v>
       </c>
       <c r="F38" t="n">
-        <v>5.0666</v>
+        <v>5.066</v>
       </c>
       <c r="G38" t="n">
         <v>100</v>
@@ -1385,32 +1385,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_compra_usd</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D39" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E39" t="n">
-        <v>5.121</v>
+        <v>4271865</v>
       </c>
       <c r="F39" t="n">
-        <v>5.066</v>
+        <v>7299615</v>
       </c>
       <c r="G39" t="n">
-        <v>100</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
@@ -1423,10 +1423,10 @@
         <v>59</v>
       </c>
       <c r="E40" t="n">
-        <v>4271865</v>
+        <v>1833179</v>
       </c>
       <c r="F40" t="n">
-        <v>7299615</v>
+        <v>2704550</v>
       </c>
       <c r="G40" t="n">
         <v>96.721311</v>
@@ -1435,7 +1435,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
@@ -1448,10 +1448,10 @@
         <v>59</v>
       </c>
       <c r="E41" t="n">
-        <v>1833179</v>
+        <v>2438686</v>
       </c>
       <c r="F41" t="n">
-        <v>2704550</v>
+        <v>4595065</v>
       </c>
       <c r="G41" t="n">
         <v>96.721311</v>
@@ -1460,7 +1460,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
@@ -1473,10 +1473,10 @@
         <v>59</v>
       </c>
       <c r="E42" t="n">
-        <v>2438686</v>
+        <v>2.36</v>
       </c>
       <c r="F42" t="n">
-        <v>4595065</v>
+        <v>4.74</v>
       </c>
       <c r="G42" t="n">
         <v>96.721311</v>
@@ -1485,7 +1485,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
@@ -1498,10 +1498,10 @@
         <v>59</v>
       </c>
       <c r="E43" t="n">
-        <v>2.36</v>
+        <v>1.58</v>
       </c>
       <c r="F43" t="n">
-        <v>4.74</v>
+        <v>3.24</v>
       </c>
       <c r="G43" t="n">
         <v>96.721311</v>
@@ -1510,7 +1510,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
@@ -1523,10 +1523,10 @@
         <v>59</v>
       </c>
       <c r="E44" t="n">
-        <v>1.58</v>
+        <v>2.94</v>
       </c>
       <c r="F44" t="n">
-        <v>3.24</v>
+        <v>5.62</v>
       </c>
       <c r="G44" t="n">
         <v>96.721311</v>
@@ -1535,7 +1535,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
@@ -1548,10 +1548,10 @@
         <v>59</v>
       </c>
       <c r="E45" t="n">
-        <v>2.94</v>
+        <v>20.26</v>
       </c>
       <c r="F45" t="n">
-        <v>5.62</v>
+        <v>33.42</v>
       </c>
       <c r="G45" t="n">
         <v>96.721311</v>
@@ -1560,157 +1560,157 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D46" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E46" t="n">
-        <v>20.26</v>
+        <v>355671</v>
       </c>
       <c r="F46" t="n">
-        <v>33.42</v>
+        <v>367558</v>
       </c>
       <c r="G46" t="n">
-        <v>96.721311</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="D47" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E47" t="n">
-        <v>355671</v>
+        <v>-0.512311</v>
       </c>
       <c r="F47" t="n">
-        <v>367558</v>
+        <v>-3.915762</v>
       </c>
       <c r="G47" t="n">
-        <v>98.36065600000001</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D48" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E48" t="n">
-        <v>0.79016</v>
+        <v>0.423696</v>
       </c>
       <c r="F48" t="n">
-        <v>0.07079299999999999</v>
+        <v>-2.124947</v>
       </c>
       <c r="G48" t="n">
-        <v>95.08196700000001</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D49" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.512311</v>
+        <v>0.423745</v>
       </c>
       <c r="F49" t="n">
-        <v>-3.915762</v>
+        <v>-2.125193</v>
       </c>
       <c r="G49" t="n">
-        <v>95.08196700000001</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D50" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E50" t="n">
-        <v>0.423696</v>
+        <v>1.736829</v>
       </c>
       <c r="F50" t="n">
-        <v>-2.124947</v>
+        <v>0.565068</v>
       </c>
       <c r="G50" t="n">
-        <v>98.36065600000001</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D51" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E51" t="n">
-        <v>0.423745</v>
+        <v>0.972464</v>
       </c>
       <c r="F51" t="n">
-        <v>-2.125193</v>
+        <v>0.742264</v>
       </c>
       <c r="G51" t="n">
-        <v>98.36065600000001</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
@@ -1723,10 +1723,10 @@
         <v>58</v>
       </c>
       <c r="E52" t="n">
-        <v>1.736829</v>
+        <v>2.311409</v>
       </c>
       <c r="F52" t="n">
-        <v>0.565068</v>
+        <v>0.461065</v>
       </c>
       <c r="G52" t="n">
         <v>95.08196700000001</v>
@@ -1735,82 +1735,82 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D53" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E53" t="n">
-        <v>0.972464</v>
+        <v>4.139781</v>
       </c>
       <c r="F53" t="n">
-        <v>0.742264</v>
+        <v>-0.964334</v>
       </c>
       <c r="G53" t="n">
-        <v>95.08196700000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>44439</v>
+        <v>44742</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D54" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E54" t="n">
-        <v>2.311409</v>
+        <v>11.88673</v>
       </c>
       <c r="F54" t="n">
-        <v>0.461065</v>
+        <v>4.641328</v>
       </c>
       <c r="G54" t="n">
-        <v>95.08196700000001</v>
+        <v>80.32786900000001</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>44439</v>
+        <v>44742</v>
       </c>
       <c r="C55" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D55" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E55" t="n">
-        <v>4.139781</v>
+        <v>10.700862</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.964334</v>
+        <v>3.177699</v>
       </c>
       <c r="G55" t="n">
-        <v>96.721311</v>
+        <v>80.32786900000001</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
@@ -1823,10 +1823,10 @@
         <v>49</v>
       </c>
       <c r="E56" t="n">
-        <v>11.88673</v>
+        <v>11.919595</v>
       </c>
       <c r="F56" t="n">
-        <v>4.641328</v>
+        <v>4.327084</v>
       </c>
       <c r="G56" t="n">
         <v>80.32786900000001</v>
@@ -1835,57 +1835,57 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>44742</v>
+        <v>44439</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D57" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E57" t="n">
-        <v>10.700862</v>
+        <v>1</v>
       </c>
       <c r="F57" t="n">
-        <v>3.177699</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>80.32786900000001</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>44742</v>
+        <v>44439</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D58" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E58" t="n">
-        <v>11.919595</v>
+        <v>0.003276</v>
       </c>
       <c r="F58" t="n">
-        <v>4.327084</v>
+        <v>-0.000497</v>
       </c>
       <c r="G58" t="n">
-        <v>80.32786900000001</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
@@ -1898,10 +1898,10 @@
         <v>60</v>
       </c>
       <c r="E59" t="n">
-        <v>1</v>
+        <v>0.003276</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>-0.000497</v>
       </c>
       <c r="G59" t="n">
         <v>98.36065600000001</v>
@@ -1910,57 +1910,57 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D60" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E60" t="n">
-        <v>0.003276</v>
+        <v>0.01</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.000497</v>
+        <v>0.11</v>
       </c>
       <c r="G60" t="n">
-        <v>98.36065600000001</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D61" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E61" t="n">
-        <v>0.003276</v>
+        <v>-0.02</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.000497</v>
+        <v>0.09</v>
       </c>
       <c r="G61" t="n">
-        <v>98.36065600000001</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
@@ -1973,7 +1973,7 @@
         <v>58</v>
       </c>
       <c r="E62" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F62" t="n">
         <v>0.11</v>
@@ -1985,7 +1985,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
@@ -1998,62 +1998,12 @@
         <v>58</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.02</v>
+        <v>0.66</v>
       </c>
       <c r="F63" t="n">
-        <v>0.09</v>
+        <v>-0.09</v>
       </c>
       <c r="G63" t="n">
-        <v>95.08196700000001</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
-        </is>
-      </c>
-      <c r="B64" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="C64" s="1" t="n">
-        <v>46173</v>
-      </c>
-      <c r="D64" t="n">
-        <v>58</v>
-      </c>
-      <c r="E64" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F64" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="G64" t="n">
-        <v>95.08196700000001</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
-        </is>
-      </c>
-      <c r="B65" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="C65" s="1" t="n">
-        <v>46173</v>
-      </c>
-      <c r="D65" t="n">
-        <v>58</v>
-      </c>
-      <c r="E65" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="F65" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="G65" t="n">
         <v>95.08196700000001</v>
       </c>
     </row>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
         <v>121801</v>
       </c>
       <c r="F2" t="n">
-        <v>176724</v>
+        <v>175335</v>
       </c>
       <c r="G2" t="n">
         <v>100</v>
@@ -501,7 +501,7 @@
         <v>117.110001</v>
       </c>
       <c r="F3" t="n">
-        <v>170.949997</v>
+        <v>172.75</v>
       </c>
       <c r="G3" t="n">
         <v>100</v>
@@ -526,7 +526,7 @@
         <v>141.800003</v>
       </c>
       <c r="F4" t="n">
-        <v>105.050003</v>
+        <v>106.699997</v>
       </c>
       <c r="G4" t="n">
         <v>100</v>
@@ -551,7 +551,7 @@
         <v>250.350006</v>
       </c>
       <c r="F5" t="n">
-        <v>425.049988</v>
+        <v>426.859985</v>
       </c>
       <c r="G5" t="n">
         <v>100</v>
@@ -576,7 +576,7 @@
         <v>5.0804</v>
       </c>
       <c r="F6" t="n">
-        <v>5.0846</v>
+        <v>5.1097</v>
       </c>
       <c r="G6" t="n">
         <v>100</v>
@@ -601,7 +601,7 @@
         <v>6.0387</v>
       </c>
       <c r="F7" t="n">
-        <v>5.7877</v>
+        <v>5.8091</v>
       </c>
       <c r="G7" t="n">
         <v>100</v>
@@ -626,7 +626,7 @@
         <v>4395.259766</v>
       </c>
       <c r="F8" t="n">
-        <v>7408.299805</v>
+        <v>7413.180176</v>
       </c>
       <c r="G8" t="n">
         <v>100</v>
@@ -651,7 +651,7 @@
         <v>14672.679688</v>
       </c>
       <c r="F9" t="n">
-        <v>25137.689453</v>
+        <v>24932.080078</v>
       </c>
       <c r="G9" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
         <v>34935.46875</v>
       </c>
       <c r="F10" t="n">
-        <v>51711.648438</v>
+        <v>52210.078125</v>
       </c>
       <c r="G10" t="n">
         <v>100</v>
@@ -701,7 +701,7 @@
         <v>1812.599976</v>
       </c>
       <c r="F11" t="n">
-        <v>4089.899902</v>
+        <v>4026.600098</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
@@ -726,7 +726,7 @@
         <v>73.949997</v>
       </c>
       <c r="F12" t="n">
-        <v>83.93000000000001</v>
+        <v>81.860001</v>
       </c>
       <c r="G12" t="n">
         <v>100</v>
@@ -751,7 +751,7 @@
         <v>76.33000199999999</v>
       </c>
       <c r="F13" t="n">
-        <v>90.550003</v>
+        <v>87.160004</v>
       </c>
       <c r="G13" t="n">
         <v>100</v>
@@ -776,7 +776,7 @@
         <v>1414.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1220.25</v>
+        <v>1208.5</v>
       </c>
       <c r="G14" t="n">
         <v>100</v>
@@ -801,7 +801,7 @@
         <v>547</v>
       </c>
       <c r="F15" t="n">
-        <v>473.75</v>
+        <v>475.75</v>
       </c>
       <c r="G15" t="n">
         <v>100</v>
@@ -826,7 +826,7 @@
         <v>-2.479454</v>
       </c>
       <c r="F16" t="n">
-        <v>2.732177</v>
+        <v>1.924731</v>
       </c>
       <c r="G16" t="n">
         <v>98.36065600000001</v>
@@ -851,7 +851,7 @@
         <v>-2.58731</v>
       </c>
       <c r="F17" t="n">
-        <v>1.123924</v>
+        <v>2.1887</v>
       </c>
       <c r="G17" t="n">
         <v>98.36065600000001</v>
@@ -876,7 +876,7 @@
         <v>-3.857547</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.713466</v>
+        <v>-1.185411</v>
       </c>
       <c r="G18" t="n">
         <v>98.36065600000001</v>
@@ -901,7 +901,7 @@
         <v>1.457956</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.433147</v>
+        <v>-2.017677</v>
       </c>
       <c r="G19" t="n">
         <v>98.36065600000001</v>
@@ -926,7 +926,7 @@
         <v>2.017557</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.875551</v>
+        <v>-1.391157</v>
       </c>
       <c r="G20" t="n">
         <v>98.36065600000001</v>
@@ -951,7 +951,7 @@
         <v>1.212177</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.187871</v>
+        <v>-1.826212</v>
       </c>
       <c r="G21" t="n">
         <v>98.36065600000001</v>
@@ -976,7 +976,7 @@
         <v>2.899042</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.214238</v>
+        <v>-1.149161</v>
       </c>
       <c r="G22" t="n">
         <v>98.36065600000001</v>
@@ -1001,7 +1001,7 @@
         <v>3.997638</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.10484</v>
+        <v>-4.889198</v>
       </c>
       <c r="G23" t="n">
         <v>98.36065600000001</v>
@@ -1026,7 +1026,7 @@
         <v>1.217278</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.161239</v>
+        <v>-0.208568</v>
       </c>
       <c r="G24" t="n">
         <v>98.36065600000001</v>
@@ -1051,7 +1051,7 @@
         <v>0.132408</v>
       </c>
       <c r="F25" t="n">
-        <v>1.665465</v>
+        <v>0.091978</v>
       </c>
       <c r="G25" t="n">
         <v>98.36065600000001</v>
@@ -1076,7 +1076,7 @@
         <v>-7.369841</v>
       </c>
       <c r="F26" t="n">
-        <v>20.76259</v>
+        <v>17.784174</v>
       </c>
       <c r="G26" t="n">
         <v>98.36065600000001</v>
@@ -1101,7 +1101,7 @@
         <v>-4.375742</v>
       </c>
       <c r="F27" t="n">
-        <v>24.177188</v>
+        <v>19.528258</v>
       </c>
       <c r="G27" t="n">
         <v>98.36065600000001</v>
@@ -1126,7 +1126,7 @@
         <v>-8.199329000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>9.267965</v>
+        <v>8.215805</v>
       </c>
       <c r="G28" t="n">
         <v>98.36065600000001</v>
@@ -1151,7 +1151,7 @@
         <v>-2.3766</v>
       </c>
       <c r="F29" t="n">
-        <v>14.778922</v>
+        <v>15.263477</v>
       </c>
       <c r="G29" t="n">
         <v>98.36065600000001</v>
@@ -1310,7 +1310,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br</t>
+          <t>bcb_sgs_ibc_br_sa</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
@@ -1323,10 +1323,10 @@
         <v>59</v>
       </c>
       <c r="E36" t="n">
-        <v>99.83978</v>
+        <v>96.31464</v>
       </c>
       <c r="F36" t="n">
-        <v>109.52993</v>
+        <v>111.03587</v>
       </c>
       <c r="G36" t="n">
         <v>96.721311</v>
@@ -1335,32 +1335,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_venda_usd</t>
+          <t>bcb_sgs_ibc_br</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D37" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E37" t="n">
-        <v>5.1216</v>
+        <v>99.83978</v>
       </c>
       <c r="F37" t="n">
-        <v>5.0666</v>
+        <v>109.52993</v>
       </c>
       <c r="G37" t="n">
-        <v>100</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_compra_usd</t>
+          <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
@@ -1373,10 +1373,10 @@
         <v>61</v>
       </c>
       <c r="E38" t="n">
-        <v>5.121</v>
+        <v>5.1216</v>
       </c>
       <c r="F38" t="n">
-        <v>5.066</v>
+        <v>5.1005</v>
       </c>
       <c r="G38" t="n">
         <v>100</v>
@@ -1385,32 +1385,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D39" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E39" t="n">
-        <v>4271865</v>
+        <v>5.121</v>
       </c>
       <c r="F39" t="n">
-        <v>7299615</v>
+        <v>5.0998</v>
       </c>
       <c r="G39" t="n">
-        <v>96.721311</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
@@ -1423,10 +1423,10 @@
         <v>59</v>
       </c>
       <c r="E40" t="n">
-        <v>1833179</v>
+        <v>4271865</v>
       </c>
       <c r="F40" t="n">
-        <v>2704550</v>
+        <v>7299615</v>
       </c>
       <c r="G40" t="n">
         <v>96.721311</v>
@@ -1435,7 +1435,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
@@ -1448,10 +1448,10 @@
         <v>59</v>
       </c>
       <c r="E41" t="n">
-        <v>2438686</v>
+        <v>1833179</v>
       </c>
       <c r="F41" t="n">
-        <v>4595065</v>
+        <v>2704550</v>
       </c>
       <c r="G41" t="n">
         <v>96.721311</v>
@@ -1460,7 +1460,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
@@ -1473,10 +1473,10 @@
         <v>59</v>
       </c>
       <c r="E42" t="n">
-        <v>2.36</v>
+        <v>2438686</v>
       </c>
       <c r="F42" t="n">
-        <v>4.74</v>
+        <v>4595065</v>
       </c>
       <c r="G42" t="n">
         <v>96.721311</v>
@@ -1485,7 +1485,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
@@ -1498,10 +1498,10 @@
         <v>59</v>
       </c>
       <c r="E43" t="n">
-        <v>1.58</v>
+        <v>2.36</v>
       </c>
       <c r="F43" t="n">
-        <v>3.24</v>
+        <v>4.74</v>
       </c>
       <c r="G43" t="n">
         <v>96.721311</v>
@@ -1510,7 +1510,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
@@ -1523,10 +1523,10 @@
         <v>59</v>
       </c>
       <c r="E44" t="n">
-        <v>2.94</v>
+        <v>1.58</v>
       </c>
       <c r="F44" t="n">
-        <v>5.62</v>
+        <v>3.24</v>
       </c>
       <c r="G44" t="n">
         <v>96.721311</v>
@@ -1535,7 +1535,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
@@ -1548,10 +1548,10 @@
         <v>59</v>
       </c>
       <c r="E45" t="n">
-        <v>20.26</v>
+        <v>2.94</v>
       </c>
       <c r="F45" t="n">
-        <v>33.42</v>
+        <v>5.62</v>
       </c>
       <c r="G45" t="n">
         <v>96.721311</v>
@@ -1560,157 +1560,157 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="D46" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E46" t="n">
-        <v>355671</v>
+        <v>20.26</v>
       </c>
       <c r="F46" t="n">
-        <v>367558</v>
+        <v>33.42</v>
       </c>
       <c r="G46" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D47" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.512311</v>
+        <v>355671</v>
       </c>
       <c r="F47" t="n">
-        <v>-3.915762</v>
+        <v>367558</v>
       </c>
       <c r="G47" t="n">
-        <v>95.08196700000001</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D48" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E48" t="n">
-        <v>0.423696</v>
+        <v>0.79016</v>
       </c>
       <c r="F48" t="n">
-        <v>-2.124947</v>
+        <v>0.07079299999999999</v>
       </c>
       <c r="G48" t="n">
-        <v>98.36065600000001</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D49" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E49" t="n">
-        <v>0.423745</v>
+        <v>-0.512311</v>
       </c>
       <c r="F49" t="n">
-        <v>-2.125193</v>
+        <v>-3.915762</v>
       </c>
       <c r="G49" t="n">
-        <v>98.36065600000001</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D50" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E50" t="n">
-        <v>1.736829</v>
+        <v>0.423696</v>
       </c>
       <c r="F50" t="n">
-        <v>0.565068</v>
+        <v>-1.470077</v>
       </c>
       <c r="G50" t="n">
-        <v>95.08196700000001</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D51" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E51" t="n">
-        <v>0.972464</v>
+        <v>0.423745</v>
       </c>
       <c r="F51" t="n">
-        <v>0.742264</v>
+        <v>-1.472179</v>
       </c>
       <c r="G51" t="n">
-        <v>95.08196700000001</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
@@ -1723,10 +1723,10 @@
         <v>58</v>
       </c>
       <c r="E52" t="n">
-        <v>2.311409</v>
+        <v>1.736829</v>
       </c>
       <c r="F52" t="n">
-        <v>0.461065</v>
+        <v>0.565068</v>
       </c>
       <c r="G52" t="n">
         <v>95.08196700000001</v>
@@ -1735,82 +1735,82 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="D53" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E53" t="n">
-        <v>4.139781</v>
+        <v>0.972464</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.964334</v>
+        <v>0.742264</v>
       </c>
       <c r="G53" t="n">
-        <v>96.721311</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>44742</v>
+        <v>44439</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="D54" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E54" t="n">
-        <v>11.88673</v>
+        <v>2.311409</v>
       </c>
       <c r="F54" t="n">
-        <v>4.641328</v>
+        <v>0.461065</v>
       </c>
       <c r="G54" t="n">
-        <v>80.32786900000001</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>44742</v>
+        <v>44439</v>
       </c>
       <c r="C55" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D55" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E55" t="n">
-        <v>10.700862</v>
+        <v>4.139781</v>
       </c>
       <c r="F55" t="n">
-        <v>3.177699</v>
+        <v>-0.964334</v>
       </c>
       <c r="G55" t="n">
-        <v>80.32786900000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
@@ -1823,10 +1823,10 @@
         <v>49</v>
       </c>
       <c r="E56" t="n">
-        <v>11.919595</v>
+        <v>11.88673</v>
       </c>
       <c r="F56" t="n">
-        <v>4.327084</v>
+        <v>4.641328</v>
       </c>
       <c r="G56" t="n">
         <v>80.32786900000001</v>
@@ -1835,57 +1835,57 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>44439</v>
+        <v>44742</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D57" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>10.700862</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>3.177699</v>
       </c>
       <c r="G57" t="n">
-        <v>98.36065600000001</v>
+        <v>80.32786900000001</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>44439</v>
+        <v>44742</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D58" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E58" t="n">
-        <v>0.003276</v>
+        <v>11.919595</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.000497</v>
+        <v>4.327084</v>
       </c>
       <c r="G58" t="n">
-        <v>98.36065600000001</v>
+        <v>80.32786900000001</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
@@ -1898,10 +1898,10 @@
         <v>60</v>
       </c>
       <c r="E59" t="n">
-        <v>0.003276</v>
+        <v>1</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.000497</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
         <v>98.36065600000001</v>
@@ -1910,57 +1910,57 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D60" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E60" t="n">
-        <v>0.01</v>
+        <v>0.003276</v>
       </c>
       <c r="F60" t="n">
-        <v>0.11</v>
+        <v>-0.000497</v>
       </c>
       <c r="G60" t="n">
-        <v>95.08196700000001</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D61" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.02</v>
+        <v>0.003276</v>
       </c>
       <c r="F61" t="n">
-        <v>0.09</v>
+        <v>-0.000497</v>
       </c>
       <c r="G61" t="n">
-        <v>95.08196700000001</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
@@ -1973,7 +1973,7 @@
         <v>58</v>
       </c>
       <c r="E62" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F62" t="n">
         <v>0.11</v>
@@ -1985,7 +1985,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
@@ -1998,12 +1998,62 @@
         <v>58</v>
       </c>
       <c r="E63" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="G63" t="n">
+        <v>95.08196700000001</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
+        </is>
+      </c>
+      <c r="B64" s="1" t="n">
+        <v>44439</v>
+      </c>
+      <c r="C64" s="1" t="n">
+        <v>46173</v>
+      </c>
+      <c r="D64" t="n">
+        <v>58</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="G64" t="n">
+        <v>95.08196700000001</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_juros_credito_total</t>
+        </is>
+      </c>
+      <c r="B65" s="1" t="n">
+        <v>44439</v>
+      </c>
+      <c r="C65" s="1" t="n">
+        <v>46173</v>
+      </c>
+      <c r="D65" t="n">
+        <v>58</v>
+      </c>
+      <c r="E65" t="n">
         <v>0.66</v>
       </c>
-      <c r="F63" t="n">
+      <c r="F65" t="n">
         <v>-0.09</v>
       </c>
-      <c r="G63" t="n">
+      <c r="G65" t="n">
         <v>95.08196700000001</v>
       </c>
     </row>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,7 +501,7 @@
         <v>117.110001</v>
       </c>
       <c r="F3" t="n">
-        <v>172.75</v>
+        <v>173.740005</v>
       </c>
       <c r="G3" t="n">
         <v>100</v>
@@ -526,7 +526,7 @@
         <v>141.800003</v>
       </c>
       <c r="F4" t="n">
-        <v>106.699997</v>
+        <v>107.169998</v>
       </c>
       <c r="G4" t="n">
         <v>100</v>
@@ -551,7 +551,7 @@
         <v>250.350006</v>
       </c>
       <c r="F5" t="n">
-        <v>426.859985</v>
+        <v>428.609985</v>
       </c>
       <c r="G5" t="n">
         <v>100</v>
@@ -576,7 +576,7 @@
         <v>5.0804</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1097</v>
+        <v>5.1259</v>
       </c>
       <c r="G6" t="n">
         <v>100</v>
@@ -601,7 +601,7 @@
         <v>6.0387</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8091</v>
+        <v>5.8325</v>
       </c>
       <c r="G7" t="n">
         <v>100</v>
@@ -626,7 +626,7 @@
         <v>4395.259766</v>
       </c>
       <c r="F8" t="n">
-        <v>7413.180176</v>
+        <v>7428.779785</v>
       </c>
       <c r="G8" t="n">
         <v>100</v>
@@ -701,7 +701,7 @@
         <v>1812.599976</v>
       </c>
       <c r="F11" t="n">
-        <v>4026.600098</v>
+        <v>4092.399902</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
@@ -726,7 +726,7 @@
         <v>73.949997</v>
       </c>
       <c r="F12" t="n">
-        <v>81.860001</v>
+        <v>82.660004</v>
       </c>
       <c r="G12" t="n">
         <v>100</v>
@@ -751,7 +751,7 @@
         <v>76.33000199999999</v>
       </c>
       <c r="F13" t="n">
-        <v>87.160004</v>
+        <v>87.91999800000001</v>
       </c>
       <c r="G13" t="n">
         <v>100</v>
@@ -776,7 +776,7 @@
         <v>1414.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1208.5</v>
+        <v>1207.75</v>
       </c>
       <c r="G14" t="n">
         <v>100</v>
@@ -801,7 +801,7 @@
         <v>547</v>
       </c>
       <c r="F15" t="n">
-        <v>475.75</v>
+        <v>478.5</v>
       </c>
       <c r="G15" t="n">
         <v>100</v>
@@ -851,7 +851,7 @@
         <v>-2.58731</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1887</v>
+        <v>2.774329</v>
       </c>
       <c r="G17" t="n">
         <v>98.36065600000001</v>
@@ -876,7 +876,7 @@
         <v>-3.857547</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.185411</v>
+        <v>-0.750144</v>
       </c>
       <c r="G18" t="n">
         <v>98.36065600000001</v>
@@ -901,7 +901,7 @@
         <v>1.457956</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.017677</v>
+        <v>-1.615978</v>
       </c>
       <c r="G19" t="n">
         <v>98.36065600000001</v>
@@ -926,7 +926,7 @@
         <v>2.017557</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.391157</v>
+        <v>-1.078532</v>
       </c>
       <c r="G20" t="n">
         <v>98.36065600000001</v>
@@ -951,7 +951,7 @@
         <v>1.212177</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.826212</v>
+        <v>-1.430755</v>
       </c>
       <c r="G21" t="n">
         <v>98.36065600000001</v>
@@ -976,7 +976,7 @@
         <v>2.899042</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.149161</v>
+        <v>-0.941148</v>
       </c>
       <c r="G22" t="n">
         <v>98.36065600000001</v>
@@ -1051,7 +1051,7 @@
         <v>0.132408</v>
       </c>
       <c r="F25" t="n">
-        <v>0.091978</v>
+        <v>1.727609</v>
       </c>
       <c r="G25" t="n">
         <v>98.36065600000001</v>
@@ -1076,7 +1076,7 @@
         <v>-7.369841</v>
       </c>
       <c r="F26" t="n">
-        <v>17.784174</v>
+        <v>18.935257</v>
       </c>
       <c r="G26" t="n">
         <v>98.36065600000001</v>
@@ -1101,7 +1101,7 @@
         <v>-4.375742</v>
       </c>
       <c r="F27" t="n">
-        <v>19.528258</v>
+        <v>20.570489</v>
       </c>
       <c r="G27" t="n">
         <v>98.36065600000001</v>
@@ -1126,7 +1126,7 @@
         <v>-8.199329000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>8.215805</v>
+        <v>8.148645999999999</v>
       </c>
       <c r="G28" t="n">
         <v>98.36065600000001</v>
@@ -1151,7 +1151,7 @@
         <v>-2.3766</v>
       </c>
       <c r="F29" t="n">
-        <v>15.263477</v>
+        <v>15.92974</v>
       </c>
       <c r="G29" t="n">
         <v>98.36065600000001</v>
@@ -1210,32 +1210,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bcb_sgs_cdi</t>
+          <t>bcb_sgs_ipca</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D32" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E32" t="n">
-        <v>0.016137</v>
+        <v>0.96</v>
       </c>
       <c r="F32" t="n">
-        <v>0.052531</v>
+        <v>0.16</v>
       </c>
       <c r="G32" t="n">
-        <v>100</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca</t>
+          <t>bcb_sgs_igp_m</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
@@ -1248,10 +1248,10 @@
         <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>0.96</v>
+        <v>0.78</v>
       </c>
       <c r="F33" t="n">
-        <v>0.16</v>
+        <v>-0.5</v>
       </c>
       <c r="G33" t="n">
         <v>98.36065600000001</v>
@@ -1260,7 +1260,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m</t>
+          <t>bcb_sgs_inpc</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1273,10 +1273,10 @@
         <v>60</v>
       </c>
       <c r="E34" t="n">
-        <v>0.78</v>
+        <v>1.02</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.5</v>
+        <v>0.14</v>
       </c>
       <c r="G34" t="n">
         <v>98.36065600000001</v>
@@ -1285,132 +1285,132 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc</t>
+          <t>bcb_sgs_ibc_br</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="D35" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E35" t="n">
-        <v>1.02</v>
+        <v>99.83978</v>
       </c>
       <c r="F35" t="n">
-        <v>0.14</v>
+        <v>109.52993</v>
       </c>
       <c r="G35" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br_sa</t>
+          <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D36" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E36" t="n">
-        <v>96.31464</v>
+        <v>5.1216</v>
       </c>
       <c r="F36" t="n">
-        <v>111.03587</v>
+        <v>5.1177</v>
       </c>
       <c r="G36" t="n">
-        <v>96.721311</v>
+        <v>100</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br</t>
+          <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D37" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E37" t="n">
-        <v>99.83978</v>
+        <v>5.121</v>
       </c>
       <c r="F37" t="n">
-        <v>109.52993</v>
+        <v>5.1171</v>
       </c>
       <c r="G37" t="n">
-        <v>96.721311</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_venda_usd</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D38" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E38" t="n">
-        <v>5.1216</v>
+        <v>4271865</v>
       </c>
       <c r="F38" t="n">
-        <v>5.1005</v>
+        <v>7299615</v>
       </c>
       <c r="G38" t="n">
-        <v>100</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_compra_usd</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D39" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E39" t="n">
-        <v>5.121</v>
+        <v>1833179</v>
       </c>
       <c r="F39" t="n">
-        <v>5.0998</v>
+        <v>2704550</v>
       </c>
       <c r="G39" t="n">
-        <v>100</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
@@ -1423,10 +1423,10 @@
         <v>59</v>
       </c>
       <c r="E40" t="n">
-        <v>4271865</v>
+        <v>2.36</v>
       </c>
       <c r="F40" t="n">
-        <v>7299615</v>
+        <v>4.74</v>
       </c>
       <c r="G40" t="n">
         <v>96.721311</v>
@@ -1435,7 +1435,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
@@ -1448,10 +1448,10 @@
         <v>59</v>
       </c>
       <c r="E41" t="n">
-        <v>1833179</v>
+        <v>1.58</v>
       </c>
       <c r="F41" t="n">
-        <v>2704550</v>
+        <v>3.24</v>
       </c>
       <c r="G41" t="n">
         <v>96.721311</v>
@@ -1460,7 +1460,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
@@ -1473,10 +1473,10 @@
         <v>59</v>
       </c>
       <c r="E42" t="n">
-        <v>2438686</v>
+        <v>2.94</v>
       </c>
       <c r="F42" t="n">
-        <v>4595065</v>
+        <v>5.62</v>
       </c>
       <c r="G42" t="n">
         <v>96.721311</v>
@@ -1485,7 +1485,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
@@ -1498,10 +1498,10 @@
         <v>59</v>
       </c>
       <c r="E43" t="n">
-        <v>2.36</v>
+        <v>20.26</v>
       </c>
       <c r="F43" t="n">
-        <v>4.74</v>
+        <v>33.42</v>
       </c>
       <c r="G43" t="n">
         <v>96.721311</v>
@@ -1510,98 +1510,98 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D44" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E44" t="n">
-        <v>1.58</v>
+        <v>355671</v>
       </c>
       <c r="F44" t="n">
-        <v>3.24</v>
+        <v>367558</v>
       </c>
       <c r="G44" t="n">
-        <v>96.721311</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C45" s="1" t="n">
         <v>46173</v>
       </c>
       <c r="D45" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E45" t="n">
-        <v>2.94</v>
+        <v>-0.512311</v>
       </c>
       <c r="F45" t="n">
-        <v>5.62</v>
+        <v>-3.915762</v>
       </c>
       <c r="G45" t="n">
-        <v>96.721311</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D46" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E46" t="n">
-        <v>20.26</v>
+        <v>0.423696</v>
       </c>
       <c r="F46" t="n">
-        <v>33.42</v>
+        <v>-1.137812</v>
       </c>
       <c r="G46" t="n">
-        <v>96.721311</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D47" t="n">
         <v>60</v>
       </c>
       <c r="E47" t="n">
-        <v>355671</v>
+        <v>0.423745</v>
       </c>
       <c r="F47" t="n">
-        <v>367558</v>
+        <v>-1.137944</v>
       </c>
       <c r="G47" t="n">
         <v>98.36065600000001</v>
@@ -1610,7 +1610,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
@@ -1623,10 +1623,10 @@
         <v>58</v>
       </c>
       <c r="E48" t="n">
-        <v>0.79016</v>
+        <v>1.736829</v>
       </c>
       <c r="F48" t="n">
-        <v>0.07079299999999999</v>
+        <v>0.565068</v>
       </c>
       <c r="G48" t="n">
         <v>95.08196700000001</v>
@@ -1635,7 +1635,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
@@ -1648,10 +1648,10 @@
         <v>58</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.512311</v>
+        <v>0.972464</v>
       </c>
       <c r="F49" t="n">
-        <v>-3.915762</v>
+        <v>0.742264</v>
       </c>
       <c r="G49" t="n">
         <v>95.08196700000001</v>
@@ -1660,400 +1660,250 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D50" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E50" t="n">
-        <v>0.423696</v>
+        <v>4.139781</v>
       </c>
       <c r="F50" t="n">
-        <v>-1.470077</v>
+        <v>-0.964334</v>
       </c>
       <c r="G50" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
-        <v>44439</v>
+        <v>44742</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D51" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E51" t="n">
-        <v>0.423745</v>
+        <v>11.88673</v>
       </c>
       <c r="F51" t="n">
-        <v>-1.472179</v>
+        <v>4.641328</v>
       </c>
       <c r="G51" t="n">
-        <v>98.36065600000001</v>
+        <v>80.32786900000001</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
-        <v>44439</v>
+        <v>44742</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D52" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E52" t="n">
-        <v>1.736829</v>
+        <v>10.700862</v>
       </c>
       <c r="F52" t="n">
-        <v>0.565068</v>
+        <v>3.177699</v>
       </c>
       <c r="G52" t="n">
-        <v>95.08196700000001</v>
+        <v>80.32786900000001</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
-        <v>44439</v>
+        <v>44742</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D53" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E53" t="n">
-        <v>0.972464</v>
+        <v>11.919595</v>
       </c>
       <c r="F53" t="n">
-        <v>0.742264</v>
+        <v>4.327084</v>
       </c>
       <c r="G53" t="n">
-        <v>95.08196700000001</v>
+        <v>80.32786900000001</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D54" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E54" t="n">
-        <v>2.311409</v>
+        <v>1</v>
       </c>
       <c r="F54" t="n">
-        <v>0.461065</v>
+        <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>95.08196700000001</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D55" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E55" t="n">
-        <v>4.139781</v>
+        <v>0.003276</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.964334</v>
+        <v>-0.000497</v>
       </c>
       <c r="G55" t="n">
-        <v>96.721311</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>44742</v>
+        <v>44439</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="D56" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E56" t="n">
-        <v>11.88673</v>
+        <v>0.01</v>
       </c>
       <c r="F56" t="n">
-        <v>4.641328</v>
+        <v>0.11</v>
       </c>
       <c r="G56" t="n">
-        <v>80.32786900000001</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>44742</v>
+        <v>44439</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="D57" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E57" t="n">
-        <v>10.700862</v>
+        <v>-0.02</v>
       </c>
       <c r="F57" t="n">
-        <v>3.177699</v>
+        <v>0.09</v>
       </c>
       <c r="G57" t="n">
-        <v>80.32786900000001</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>44742</v>
+        <v>44439</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="D58" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E58" t="n">
-        <v>11.919595</v>
+        <v>0.02</v>
       </c>
       <c r="F58" t="n">
-        <v>4.327084</v>
+        <v>0.11</v>
       </c>
       <c r="G58" t="n">
-        <v>80.32786900000001</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D59" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E59" t="n">
-        <v>1</v>
+        <v>0.66</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="G59" t="n">
-        <v>98.36065600000001</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>bcb_sgs_dif_selic_over</t>
-        </is>
-      </c>
-      <c r="B60" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="C60" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="D60" t="n">
-        <v>60</v>
-      </c>
-      <c r="E60" t="n">
-        <v>0.003276</v>
-      </c>
-      <c r="F60" t="n">
-        <v>-0.000497</v>
-      </c>
-      <c r="G60" t="n">
-        <v>98.36065600000001</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>bcb_sgs_dif_cdi</t>
-        </is>
-      </c>
-      <c r="B61" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="C61" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="D61" t="n">
-        <v>60</v>
-      </c>
-      <c r="E61" t="n">
-        <v>0.003276</v>
-      </c>
-      <c r="F61" t="n">
-        <v>-0.000497</v>
-      </c>
-      <c r="G61" t="n">
-        <v>98.36065600000001</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
-        </is>
-      </c>
-      <c r="B62" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="C62" s="1" t="n">
-        <v>46173</v>
-      </c>
-      <c r="D62" t="n">
-        <v>58</v>
-      </c>
-      <c r="E62" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="F62" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="G62" t="n">
-        <v>95.08196700000001</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
-        </is>
-      </c>
-      <c r="B63" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="C63" s="1" t="n">
-        <v>46173</v>
-      </c>
-      <c r="D63" t="n">
-        <v>58</v>
-      </c>
-      <c r="E63" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="F63" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="G63" t="n">
-        <v>95.08196700000001</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
-        </is>
-      </c>
-      <c r="B64" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="C64" s="1" t="n">
-        <v>46173</v>
-      </c>
-      <c r="D64" t="n">
-        <v>58</v>
-      </c>
-      <c r="E64" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F64" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="G64" t="n">
-        <v>95.08196700000001</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
-        </is>
-      </c>
-      <c r="B65" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="C65" s="1" t="n">
-        <v>46173</v>
-      </c>
-      <c r="D65" t="n">
-        <v>58</v>
-      </c>
-      <c r="E65" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="F65" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="G65" t="n">
         <v>95.08196700000001</v>
       </c>
     </row>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
         <v>121801</v>
       </c>
       <c r="F2" t="n">
-        <v>175335</v>
+        <v>173885</v>
       </c>
       <c r="G2" t="n">
         <v>100</v>
@@ -501,7 +501,7 @@
         <v>117.110001</v>
       </c>
       <c r="F3" t="n">
-        <v>173.740005</v>
+        <v>170.550003</v>
       </c>
       <c r="G3" t="n">
         <v>100</v>
@@ -526,7 +526,7 @@
         <v>141.800003</v>
       </c>
       <c r="F4" t="n">
-        <v>107.169998</v>
+        <v>105.099998</v>
       </c>
       <c r="G4" t="n">
         <v>100</v>
@@ -551,7 +551,7 @@
         <v>250.350006</v>
       </c>
       <c r="F5" t="n">
-        <v>428.609985</v>
+        <v>421.559998</v>
       </c>
       <c r="G5" t="n">
         <v>100</v>
@@ -576,7 +576,7 @@
         <v>5.0804</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1259</v>
+        <v>5.099</v>
       </c>
       <c r="G6" t="n">
         <v>100</v>
@@ -601,7 +601,7 @@
         <v>6.0387</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8325</v>
+        <v>5.8475</v>
       </c>
       <c r="G7" t="n">
         <v>100</v>
@@ -626,7 +626,7 @@
         <v>4395.259766</v>
       </c>
       <c r="F8" t="n">
-        <v>7428.779785</v>
+        <v>7316.149902</v>
       </c>
       <c r="G8" t="n">
         <v>100</v>
@@ -651,7 +651,7 @@
         <v>14672.679688</v>
       </c>
       <c r="F9" t="n">
-        <v>24932.080078</v>
+        <v>24442.939453</v>
       </c>
       <c r="G9" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
         <v>34935.46875</v>
       </c>
       <c r="F10" t="n">
-        <v>52210.078125</v>
+        <v>51594.140625</v>
       </c>
       <c r="G10" t="n">
         <v>100</v>
@@ -701,7 +701,7 @@
         <v>1812.599976</v>
       </c>
       <c r="F11" t="n">
-        <v>4092.399902</v>
+        <v>4136.799805</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
@@ -726,7 +726,7 @@
         <v>73.949997</v>
       </c>
       <c r="F12" t="n">
-        <v>82.660004</v>
+        <v>83.41999800000001</v>
       </c>
       <c r="G12" t="n">
         <v>100</v>
@@ -751,7 +751,7 @@
         <v>76.33000199999999</v>
       </c>
       <c r="F13" t="n">
-        <v>87.91999800000001</v>
+        <v>89.889999</v>
       </c>
       <c r="G13" t="n">
         <v>100</v>
@@ -776,7 +776,7 @@
         <v>1414.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1207.75</v>
+        <v>1193.25</v>
       </c>
       <c r="G14" t="n">
         <v>100</v>
@@ -801,7 +801,7 @@
         <v>547</v>
       </c>
       <c r="F15" t="n">
-        <v>478.5</v>
+        <v>473.5</v>
       </c>
       <c r="G15" t="n">
         <v>100</v>
@@ -826,7 +826,7 @@
         <v>-2.479454</v>
       </c>
       <c r="F16" t="n">
-        <v>1.924731</v>
+        <v>1.081826</v>
       </c>
       <c r="G16" t="n">
         <v>98.36065600000001</v>
@@ -851,7 +851,7 @@
         <v>-2.58731</v>
       </c>
       <c r="F17" t="n">
-        <v>2.774329</v>
+        <v>0.887311</v>
       </c>
       <c r="G17" t="n">
         <v>98.36065600000001</v>
@@ -876,7 +876,7 @@
         <v>-3.857547</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.750144</v>
+        <v>-2.667165</v>
       </c>
       <c r="G18" t="n">
         <v>98.36065600000001</v>
@@ -901,7 +901,7 @@
         <v>1.457956</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.615978</v>
+        <v>-3.234247</v>
       </c>
       <c r="G19" t="n">
         <v>98.36065600000001</v>
@@ -926,7 +926,7 @@
         <v>2.017557</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.078532</v>
+        <v>-1.597654</v>
       </c>
       <c r="G20" t="n">
         <v>98.36065600000001</v>
@@ -951,7 +951,7 @@
         <v>1.212177</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.430755</v>
+        <v>-1.177257</v>
       </c>
       <c r="G21" t="n">
         <v>98.36065600000001</v>
@@ -976,7 +976,7 @@
         <v>2.899042</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.941148</v>
+        <v>-2.443008</v>
       </c>
       <c r="G22" t="n">
         <v>98.36065600000001</v>
@@ -1001,7 +1001,7 @@
         <v>3.997638</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.889198</v>
+        <v>-6.755169</v>
       </c>
       <c r="G23" t="n">
         <v>98.36065600000001</v>
@@ -1026,7 +1026,7 @@
         <v>1.217278</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.208568</v>
+        <v>-1.385837</v>
       </c>
       <c r="G24" t="n">
         <v>98.36065600000001</v>
@@ -1051,7 +1051,7 @@
         <v>0.132408</v>
       </c>
       <c r="F25" t="n">
-        <v>1.727609</v>
+        <v>2.831289</v>
       </c>
       <c r="G25" t="n">
         <v>98.36065600000001</v>
@@ -1076,7 +1076,7 @@
         <v>-7.369841</v>
       </c>
       <c r="F26" t="n">
-        <v>18.935257</v>
+        <v>20.028774</v>
       </c>
       <c r="G26" t="n">
         <v>98.36065600000001</v>
@@ -1101,7 +1101,7 @@
         <v>-4.375742</v>
       </c>
       <c r="F27" t="n">
-        <v>20.570489</v>
+        <v>23.272081</v>
       </c>
       <c r="G27" t="n">
         <v>98.36065600000001</v>
@@ -1126,7 +1126,7 @@
         <v>-8.199329000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>8.148645999999999</v>
+        <v>6.850235</v>
       </c>
       <c r="G28" t="n">
         <v>98.36065600000001</v>
@@ -1151,7 +1151,7 @@
         <v>-2.3766</v>
       </c>
       <c r="F29" t="n">
-        <v>15.92974</v>
+        <v>14.718353</v>
       </c>
       <c r="G29" t="n">
         <v>98.36065600000001</v>
@@ -1210,32 +1210,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca</t>
+          <t>bcb_sgs_cdi</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D32" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E32" t="n">
-        <v>0.96</v>
+        <v>0.016137</v>
       </c>
       <c r="F32" t="n">
-        <v>0.16</v>
+        <v>0.052531</v>
       </c>
       <c r="G32" t="n">
-        <v>98.36065600000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m</t>
+          <t>bcb_sgs_ipca</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
@@ -1248,10 +1248,10 @@
         <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>0.78</v>
+        <v>0.96</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.5</v>
+        <v>0.16</v>
       </c>
       <c r="G33" t="n">
         <v>98.36065600000001</v>
@@ -1260,7 +1260,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc</t>
+          <t>bcb_sgs_igp_m</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1273,10 +1273,10 @@
         <v>60</v>
       </c>
       <c r="E34" t="n">
-        <v>1.02</v>
+        <v>0.78</v>
       </c>
       <c r="F34" t="n">
-        <v>0.14</v>
+        <v>-0.5</v>
       </c>
       <c r="G34" t="n">
         <v>98.36065600000001</v>
@@ -1285,232 +1285,232 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br</t>
+          <t>bcb_sgs_inpc</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D35" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E35" t="n">
-        <v>99.83978</v>
+        <v>1.02</v>
       </c>
       <c r="F35" t="n">
-        <v>109.52993</v>
+        <v>0.14</v>
       </c>
       <c r="G35" t="n">
-        <v>96.721311</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_venda_usd</t>
+          <t>bcb_sgs_ibc_br_sa</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D36" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E36" t="n">
-        <v>5.1216</v>
+        <v>96.31464</v>
       </c>
       <c r="F36" t="n">
-        <v>5.1177</v>
+        <v>111.03587</v>
       </c>
       <c r="G36" t="n">
-        <v>100</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_compra_usd</t>
+          <t>bcb_sgs_ibc_br</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D37" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E37" t="n">
-        <v>5.121</v>
+        <v>99.83978</v>
       </c>
       <c r="F37" t="n">
-        <v>5.1171</v>
+        <v>109.52993</v>
       </c>
       <c r="G37" t="n">
-        <v>100</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D38" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E38" t="n">
-        <v>4271865</v>
+        <v>5.1216</v>
       </c>
       <c r="F38" t="n">
-        <v>7299615</v>
+        <v>5.1217</v>
       </c>
       <c r="G38" t="n">
-        <v>96.721311</v>
+        <v>100</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D39" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E39" t="n">
-        <v>1833179</v>
+        <v>5.121</v>
       </c>
       <c r="F39" t="n">
-        <v>2704550</v>
+        <v>5.1211</v>
       </c>
       <c r="G39" t="n">
-        <v>96.721311</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D40" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E40" t="n">
-        <v>2.36</v>
+        <v>4271865</v>
       </c>
       <c r="F40" t="n">
-        <v>4.74</v>
+        <v>7355800</v>
       </c>
       <c r="G40" t="n">
-        <v>96.721311</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D41" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E41" t="n">
-        <v>1.58</v>
+        <v>1833179</v>
       </c>
       <c r="F41" t="n">
-        <v>3.24</v>
+        <v>2749001</v>
       </c>
       <c r="G41" t="n">
-        <v>96.721311</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D42" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E42" t="n">
-        <v>2.94</v>
+        <v>2438686</v>
       </c>
       <c r="F42" t="n">
-        <v>5.62</v>
+        <v>4606799</v>
       </c>
       <c r="G42" t="n">
-        <v>96.721311</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D43" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E43" t="n">
-        <v>20.26</v>
+        <v>2.36</v>
       </c>
       <c r="F43" t="n">
-        <v>33.42</v>
+        <v>4.68</v>
       </c>
       <c r="G43" t="n">
-        <v>96.721311</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
@@ -1523,10 +1523,10 @@
         <v>60</v>
       </c>
       <c r="E44" t="n">
-        <v>355671</v>
+        <v>2.94</v>
       </c>
       <c r="F44" t="n">
-        <v>367558</v>
+        <v>5.57</v>
       </c>
       <c r="G44" t="n">
         <v>98.36065600000001</v>
@@ -1535,48 +1535,48 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D45" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.512311</v>
+        <v>20.26</v>
       </c>
       <c r="F45" t="n">
-        <v>-3.915762</v>
+        <v>33.44</v>
       </c>
       <c r="G45" t="n">
-        <v>95.08196700000001</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D46" t="n">
         <v>60</v>
       </c>
       <c r="E46" t="n">
-        <v>0.423696</v>
+        <v>355671</v>
       </c>
       <c r="F46" t="n">
-        <v>-1.137812</v>
+        <v>367558</v>
       </c>
       <c r="G46" t="n">
         <v>98.36065600000001</v>
@@ -1585,32 +1585,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D47" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E47" t="n">
-        <v>0.423745</v>
+        <v>0.79016</v>
       </c>
       <c r="F47" t="n">
-        <v>-1.137944</v>
+        <v>0.07079299999999999</v>
       </c>
       <c r="G47" t="n">
-        <v>98.36065600000001</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
@@ -1623,10 +1623,10 @@
         <v>58</v>
       </c>
       <c r="E48" t="n">
-        <v>1.736829</v>
+        <v>-0.512311</v>
       </c>
       <c r="F48" t="n">
-        <v>0.565068</v>
+        <v>-3.915762</v>
       </c>
       <c r="G48" t="n">
         <v>95.08196700000001</v>
@@ -1635,276 +1635,376 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D49" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E49" t="n">
-        <v>0.972464</v>
+        <v>0.423696</v>
       </c>
       <c r="F49" t="n">
-        <v>0.742264</v>
+        <v>-1.060542</v>
       </c>
       <c r="G49" t="n">
-        <v>95.08196700000001</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D50" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E50" t="n">
-        <v>4.139781</v>
+        <v>0.423745</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.964334</v>
+        <v>-1.060665</v>
       </c>
       <c r="G50" t="n">
-        <v>96.721311</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
-        <v>44742</v>
+        <v>44439</v>
       </c>
       <c r="C51" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D51" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E51" t="n">
-        <v>11.88673</v>
+        <v>1.736829</v>
       </c>
       <c r="F51" t="n">
-        <v>4.641328</v>
+        <v>0.714468</v>
       </c>
       <c r="G51" t="n">
-        <v>80.32786900000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
-        <v>44742</v>
+        <v>44439</v>
       </c>
       <c r="C52" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D52" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E52" t="n">
-        <v>10.700862</v>
+        <v>0.972464</v>
       </c>
       <c r="F52" t="n">
-        <v>3.177699</v>
+        <v>1.515494</v>
       </c>
       <c r="G52" t="n">
-        <v>80.32786900000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
-        <v>44742</v>
+        <v>44439</v>
       </c>
       <c r="C53" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D53" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E53" t="n">
-        <v>11.919595</v>
+        <v>2.311409</v>
       </c>
       <c r="F53" t="n">
-        <v>4.327084</v>
+        <v>0.242446</v>
       </c>
       <c r="G53" t="n">
-        <v>80.32786900000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D54" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E54" t="n">
-        <v>1</v>
+        <v>4.139781</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>-0.964334</v>
       </c>
       <c r="G54" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>44439</v>
+        <v>44742</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D55" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E55" t="n">
-        <v>0.003276</v>
+        <v>11.88673</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.000497</v>
+        <v>4.641328</v>
       </c>
       <c r="G55" t="n">
-        <v>98.36065600000001</v>
+        <v>80.32786900000001</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>44439</v>
+        <v>44742</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D56" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E56" t="n">
-        <v>0.01</v>
+        <v>10.700862</v>
       </c>
       <c r="F56" t="n">
-        <v>0.11</v>
+        <v>3.177699</v>
       </c>
       <c r="G56" t="n">
-        <v>95.08196700000001</v>
+        <v>80.32786900000001</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>44439</v>
+        <v>44742</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D57" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.02</v>
+        <v>11.919595</v>
       </c>
       <c r="F57" t="n">
-        <v>0.09</v>
+        <v>4.327084</v>
       </c>
       <c r="G57" t="n">
-        <v>95.08196700000001</v>
+        <v>80.32786900000001</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D58" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E58" t="n">
-        <v>0.02</v>
+        <v>1</v>
       </c>
       <c r="F58" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>95.08196700000001</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>bcb_sgs_dif_selic_over</t>
+        </is>
+      </c>
+      <c r="B59" s="1" t="n">
+        <v>44439</v>
+      </c>
+      <c r="C59" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="D59" t="n">
+        <v>60</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.003276</v>
+      </c>
+      <c r="F59" t="n">
+        <v>-0.000497</v>
+      </c>
+      <c r="G59" t="n">
+        <v>98.36065600000001</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_cdi</t>
+        </is>
+      </c>
+      <c r="B60" s="1" t="n">
+        <v>44439</v>
+      </c>
+      <c r="C60" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="D60" t="n">
+        <v>60</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.003276</v>
+      </c>
+      <c r="F60" t="n">
+        <v>-0.000497</v>
+      </c>
+      <c r="G60" t="n">
+        <v>98.36065600000001</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
+        </is>
+      </c>
+      <c r="B61" s="1" t="n">
+        <v>44439</v>
+      </c>
+      <c r="C61" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="D61" t="n">
+        <v>59</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F61" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="G61" t="n">
+        <v>96.721311</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
+        </is>
+      </c>
+      <c r="B62" s="1" t="n">
+        <v>44439</v>
+      </c>
+      <c r="C62" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="D62" t="n">
+        <v>59</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F62" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G62" t="n">
+        <v>96.721311</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
           <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
-      <c r="B59" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="C59" s="1" t="n">
-        <v>46173</v>
-      </c>
-      <c r="D59" t="n">
-        <v>58</v>
-      </c>
-      <c r="E59" t="n">
+      <c r="B63" s="1" t="n">
+        <v>44439</v>
+      </c>
+      <c r="C63" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="D63" t="n">
+        <v>59</v>
+      </c>
+      <c r="E63" t="n">
         <v>0.66</v>
       </c>
-      <c r="F59" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="G59" t="n">
-        <v>95.08196700000001</v>
+      <c r="F63" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="G63" t="n">
+        <v>96.721311</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
         <v>121801</v>
       </c>
       <c r="F2" t="n">
-        <v>173885</v>
+        <v>177159</v>
       </c>
       <c r="G2" t="n">
         <v>100</v>
@@ -501,7 +501,7 @@
         <v>117.110001</v>
       </c>
       <c r="F3" t="n">
-        <v>170.550003</v>
+        <v>174.309998</v>
       </c>
       <c r="G3" t="n">
         <v>100</v>
@@ -526,7 +526,7 @@
         <v>141.800003</v>
       </c>
       <c r="F4" t="n">
-        <v>105.099998</v>
+        <v>107.360001</v>
       </c>
       <c r="G4" t="n">
         <v>100</v>
@@ -551,7 +551,7 @@
         <v>250.350006</v>
       </c>
       <c r="F5" t="n">
-        <v>421.559998</v>
+        <v>425.369995</v>
       </c>
       <c r="G5" t="n">
         <v>100</v>
@@ -564,22 +564,22 @@
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D6" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E6" t="n">
-        <v>5.0804</v>
+        <v>5.1829</v>
       </c>
       <c r="F6" t="n">
-        <v>5.099</v>
+        <v>5.0716</v>
       </c>
       <c r="G6" t="n">
-        <v>100</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="7">
@@ -589,22 +589,22 @@
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D7" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E7" t="n">
-        <v>6.0387</v>
+        <v>6.1119</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8475</v>
+        <v>5.8255</v>
       </c>
       <c r="G7" t="n">
-        <v>100</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="8">
@@ -614,22 +614,22 @@
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C8" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D8" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E8" t="n">
-        <v>4395.259766</v>
+        <v>4522.680176</v>
       </c>
       <c r="F8" t="n">
-        <v>7316.149902</v>
+        <v>7437.629883</v>
       </c>
       <c r="G8" t="n">
-        <v>100</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="9">
@@ -639,22 +639,22 @@
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C9" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D9" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E9" t="n">
-        <v>14672.679688</v>
+        <v>15259.240234</v>
       </c>
       <c r="F9" t="n">
-        <v>24442.939453</v>
+        <v>25122.179688</v>
       </c>
       <c r="G9" t="n">
-        <v>100</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="10">
@@ -664,22 +664,22 @@
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D10" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E10" t="n">
-        <v>34935.46875</v>
+        <v>35360.730469</v>
       </c>
       <c r="F10" t="n">
-        <v>51594.140625</v>
+        <v>52208.058594</v>
       </c>
       <c r="G10" t="n">
-        <v>100</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="11">
@@ -689,22 +689,22 @@
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D11" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E11" t="n">
-        <v>1812.599976</v>
+        <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4136.799805</v>
+        <v>4109.799805</v>
       </c>
       <c r="G11" t="n">
-        <v>100</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="12">
@@ -714,22 +714,22 @@
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D12" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E12" t="n">
-        <v>73.949997</v>
+        <v>68.5</v>
       </c>
       <c r="F12" t="n">
-        <v>83.41999800000001</v>
+        <v>84.839996</v>
       </c>
       <c r="G12" t="n">
-        <v>100</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="13">
@@ -739,22 +739,22 @@
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E13" t="n">
-        <v>76.33000199999999</v>
+        <v>72.989998</v>
       </c>
       <c r="F13" t="n">
-        <v>89.889999</v>
+        <v>90.25</v>
       </c>
       <c r="G13" t="n">
-        <v>100</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="14">
@@ -764,22 +764,22 @@
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C14" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E14" t="n">
-        <v>1414.75</v>
+        <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1193.25</v>
+        <v>1188.5</v>
       </c>
       <c r="G14" t="n">
-        <v>100</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="15">
@@ -789,22 +789,22 @@
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C15" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D15" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E15" t="n">
-        <v>547</v>
+        <v>534</v>
       </c>
       <c r="F15" t="n">
-        <v>473.5</v>
+        <v>466.25</v>
       </c>
       <c r="G15" t="n">
-        <v>100</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="16">
@@ -826,7 +826,7 @@
         <v>-2.479454</v>
       </c>
       <c r="F16" t="n">
-        <v>1.081826</v>
+        <v>2.985049</v>
       </c>
       <c r="G16" t="n">
         <v>98.36065600000001</v>
@@ -851,7 +851,7 @@
         <v>-2.58731</v>
       </c>
       <c r="F17" t="n">
-        <v>0.887311</v>
+        <v>3.111502</v>
       </c>
       <c r="G17" t="n">
         <v>98.36065600000001</v>
@@ -876,7 +876,7 @@
         <v>-3.857547</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.667165</v>
+        <v>-0.574183</v>
       </c>
       <c r="G18" t="n">
         <v>98.36065600000001</v>
@@ -901,7 +901,7 @@
         <v>1.457956</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.234247</v>
+        <v>-2.359692</v>
       </c>
       <c r="G19" t="n">
         <v>98.36065600000001</v>
@@ -914,22 +914,22 @@
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C20" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D20" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E20" t="n">
-        <v>2.017557</v>
+        <v>4.464682</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.597654</v>
+        <v>-2.12643</v>
       </c>
       <c r="G20" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="21">
@@ -939,22 +939,22 @@
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C21" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D21" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E21" t="n">
-        <v>1.212177</v>
+        <v>2.725834</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.177257</v>
+        <v>-1.549054</v>
       </c>
       <c r="G21" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="22">
@@ -964,22 +964,22 @@
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C22" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D22" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E22" t="n">
-        <v>2.899042</v>
+        <v>-4.756917</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.443008</v>
+        <v>-0.823137</v>
       </c>
       <c r="G22" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="23">
@@ -989,22 +989,22 @@
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C23" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D23" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E23" t="n">
-        <v>3.997638</v>
+        <v>-5.312585</v>
       </c>
       <c r="F23" t="n">
-        <v>-6.755169</v>
+        <v>-4.164006</v>
       </c>
       <c r="G23" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="24">
@@ -1014,22 +1014,22 @@
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C24" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D24" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E24" t="n">
-        <v>1.217278</v>
+        <v>-4.289528</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.385837</v>
+        <v>-0.212428</v>
       </c>
       <c r="G24" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="25">
@@ -1039,22 +1039,22 @@
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C25" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D25" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E25" t="n">
-        <v>0.132408</v>
+        <v>-3.289254</v>
       </c>
       <c r="F25" t="n">
-        <v>2.831289</v>
+        <v>2.160131</v>
       </c>
       <c r="G25" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="26">
@@ -1064,22 +1064,22 @@
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C26" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D26" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E26" t="n">
-        <v>-7.369841</v>
+        <v>9.532845</v>
       </c>
       <c r="F26" t="n">
-        <v>20.028774</v>
+        <v>22.071937</v>
       </c>
       <c r="G26" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="27">
@@ -1089,22 +1089,22 @@
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D27" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E27" t="n">
-        <v>-4.375742</v>
+        <v>7.576379</v>
       </c>
       <c r="F27" t="n">
-        <v>23.272081</v>
+        <v>23.765774</v>
       </c>
       <c r="G27" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="28">
@@ -1114,22 +1114,22 @@
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C28" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D28" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E28" t="n">
-        <v>-8.199329000000001</v>
+        <v>-3.291627</v>
       </c>
       <c r="F28" t="n">
-        <v>6.850235</v>
+        <v>6.424894</v>
       </c>
       <c r="G28" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="29">
@@ -1139,22 +1139,22 @@
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C29" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D29" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E29" t="n">
-        <v>-2.3766</v>
+        <v>0.514981</v>
       </c>
       <c r="F29" t="n">
-        <v>14.718353</v>
+        <v>12.961841</v>
       </c>
       <c r="G29" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="30">
@@ -1189,22 +1189,22 @@
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C31" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D31" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>0.016137</v>
+        <v>0.019413</v>
       </c>
       <c r="F31" t="n">
         <v>0.052531</v>
       </c>
       <c r="G31" t="n">
-        <v>100</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="32">
@@ -1214,22 +1214,22 @@
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C32" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D32" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E32" t="n">
-        <v>0.016137</v>
+        <v>0.019413</v>
       </c>
       <c r="F32" t="n">
         <v>0.052531</v>
       </c>
       <c r="G32" t="n">
-        <v>100</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="33">
@@ -1267,19 +1267,19 @@
         <v>44408</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D34" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E34" t="n">
         <v>0.78</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.5</v>
+        <v>-1.16</v>
       </c>
       <c r="G34" t="n">
-        <v>98.36065600000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35">
@@ -1310,107 +1310,107 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br_sa</t>
+          <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D36" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E36" t="n">
-        <v>96.31464</v>
+        <v>5.1433</v>
       </c>
       <c r="F36" t="n">
-        <v>111.03587</v>
+        <v>5.0739</v>
       </c>
       <c r="G36" t="n">
-        <v>96.721311</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br</t>
+          <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D37" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E37" t="n">
-        <v>99.83978</v>
+        <v>5.1427</v>
       </c>
       <c r="F37" t="n">
-        <v>109.52993</v>
+        <v>5.0733</v>
       </c>
       <c r="G37" t="n">
-        <v>96.721311</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_venda_usd</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D38" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E38" t="n">
-        <v>5.1216</v>
+        <v>4271865</v>
       </c>
       <c r="F38" t="n">
-        <v>5.1217</v>
+        <v>7355800</v>
       </c>
       <c r="G38" t="n">
-        <v>100</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_compra_usd</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D39" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E39" t="n">
-        <v>5.121</v>
+        <v>1833179</v>
       </c>
       <c r="F39" t="n">
-        <v>5.1211</v>
+        <v>2749001</v>
       </c>
       <c r="G39" t="n">
-        <v>100</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
@@ -1423,10 +1423,10 @@
         <v>60</v>
       </c>
       <c r="E40" t="n">
-        <v>4271865</v>
+        <v>2438686</v>
       </c>
       <c r="F40" t="n">
-        <v>7355800</v>
+        <v>4606799</v>
       </c>
       <c r="G40" t="n">
         <v>98.36065600000001</v>
@@ -1435,7 +1435,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
@@ -1448,10 +1448,10 @@
         <v>60</v>
       </c>
       <c r="E41" t="n">
-        <v>1833179</v>
+        <v>2.36</v>
       </c>
       <c r="F41" t="n">
-        <v>2749001</v>
+        <v>4.68</v>
       </c>
       <c r="G41" t="n">
         <v>98.36065600000001</v>
@@ -1460,7 +1460,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
@@ -1473,10 +1473,10 @@
         <v>60</v>
       </c>
       <c r="E42" t="n">
-        <v>2438686</v>
+        <v>1.58</v>
       </c>
       <c r="F42" t="n">
-        <v>4606799</v>
+        <v>3.19</v>
       </c>
       <c r="G42" t="n">
         <v>98.36065600000001</v>
@@ -1485,7 +1485,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
@@ -1498,10 +1498,10 @@
         <v>60</v>
       </c>
       <c r="E43" t="n">
-        <v>2.36</v>
+        <v>2.94</v>
       </c>
       <c r="F43" t="n">
-        <v>4.68</v>
+        <v>5.57</v>
       </c>
       <c r="G43" t="n">
         <v>98.36065600000001</v>
@@ -1510,7 +1510,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
@@ -1523,10 +1523,10 @@
         <v>60</v>
       </c>
       <c r="E44" t="n">
-        <v>2.94</v>
+        <v>20.26</v>
       </c>
       <c r="F44" t="n">
-        <v>5.57</v>
+        <v>33.44</v>
       </c>
       <c r="G44" t="n">
         <v>98.36065600000001</v>
@@ -1535,7 +1535,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
@@ -1548,10 +1548,10 @@
         <v>60</v>
       </c>
       <c r="E45" t="n">
-        <v>20.26</v>
+        <v>355671</v>
       </c>
       <c r="F45" t="n">
-        <v>33.44</v>
+        <v>367558</v>
       </c>
       <c r="G45" t="n">
         <v>98.36065600000001</v>
@@ -1560,132 +1560,132 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>44408</v>
+        <v>44469</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D46" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E46" t="n">
-        <v>355671</v>
+        <v>5.757004</v>
       </c>
       <c r="F46" t="n">
-        <v>367558</v>
+        <v>-1.983928</v>
       </c>
       <c r="G46" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D47" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E47" t="n">
-        <v>0.79016</v>
+        <v>5.757676</v>
       </c>
       <c r="F47" t="n">
-        <v>0.07079299999999999</v>
+        <v>-1.984158</v>
       </c>
       <c r="G47" t="n">
-        <v>95.08196700000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D48" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.512311</v>
+        <v>1.736829</v>
       </c>
       <c r="F48" t="n">
-        <v>-3.915762</v>
+        <v>0.714468</v>
       </c>
       <c r="G48" t="n">
-        <v>95.08196700000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D49" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E49" t="n">
-        <v>0.423696</v>
+        <v>0.972464</v>
       </c>
       <c r="F49" t="n">
-        <v>-1.060542</v>
+        <v>1.515494</v>
       </c>
       <c r="G49" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D50" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E50" t="n">
-        <v>0.423745</v>
+        <v>2.311409</v>
       </c>
       <c r="F50" t="n">
-        <v>-1.060665</v>
+        <v>0.242446</v>
       </c>
       <c r="G50" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
@@ -1698,10 +1698,10 @@
         <v>59</v>
       </c>
       <c r="E51" t="n">
-        <v>1.736829</v>
+        <v>4.139781</v>
       </c>
       <c r="F51" t="n">
-        <v>0.714468</v>
+        <v>-0.964334</v>
       </c>
       <c r="G51" t="n">
         <v>96.721311</v>
@@ -1710,232 +1710,232 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
-        <v>44439</v>
+        <v>44742</v>
       </c>
       <c r="C52" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D52" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E52" t="n">
-        <v>0.972464</v>
+        <v>11.88673</v>
       </c>
       <c r="F52" t="n">
-        <v>1.515494</v>
+        <v>4.641328</v>
       </c>
       <c r="G52" t="n">
-        <v>96.721311</v>
+        <v>80.32786900000001</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
-        <v>44439</v>
+        <v>44742</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D53" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="E53" t="n">
-        <v>2.311409</v>
+        <v>10.700862</v>
       </c>
       <c r="F53" t="n">
-        <v>0.242446</v>
+        <v>2.772183</v>
       </c>
       <c r="G53" t="n">
-        <v>96.721311</v>
+        <v>81.967213</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>44439</v>
+        <v>44742</v>
       </c>
       <c r="C54" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D54" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E54" t="n">
-        <v>4.139781</v>
+        <v>11.919595</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.964334</v>
+        <v>4.327084</v>
       </c>
       <c r="G54" t="n">
-        <v>96.721311</v>
+        <v>80.32786900000001</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>44742</v>
+        <v>44439</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D55" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E55" t="n">
-        <v>11.88673</v>
+        <v>1</v>
       </c>
       <c r="F55" t="n">
-        <v>4.641328</v>
+        <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>80.32786900000001</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>44742</v>
+        <v>44469</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D56" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E56" t="n">
-        <v>10.700862</v>
+        <v>0.001591</v>
       </c>
       <c r="F56" t="n">
-        <v>3.177699</v>
+        <v>-0.000497</v>
       </c>
       <c r="G56" t="n">
-        <v>80.32786900000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>44742</v>
+        <v>44469</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D57" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E57" t="n">
-        <v>11.919595</v>
+        <v>0.001591</v>
       </c>
       <c r="F57" t="n">
-        <v>4.327084</v>
+        <v>-0.000497</v>
       </c>
       <c r="G57" t="n">
-        <v>80.32786900000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D58" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E58" t="n">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="G58" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D59" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E59" t="n">
-        <v>0.003276</v>
+        <v>-0.02</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.000497</v>
+        <v>-0.06</v>
       </c>
       <c r="G59" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D60" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E60" t="n">
-        <v>0.003276</v>
+        <v>0.02</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.000497</v>
+        <v>-0.05</v>
       </c>
       <c r="G60" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
@@ -1948,62 +1948,12 @@
         <v>59</v>
       </c>
       <c r="E61" t="n">
-        <v>0.01</v>
+        <v>0.66</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.06</v>
+        <v>0.22</v>
       </c>
       <c r="G61" t="n">
-        <v>96.721311</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
-        </is>
-      </c>
-      <c r="B62" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="C62" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="D62" t="n">
-        <v>59</v>
-      </c>
-      <c r="E62" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F62" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="G62" t="n">
-        <v>96.721311</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
-        </is>
-      </c>
-      <c r="B63" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="C63" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="D63" t="n">
-        <v>59</v>
-      </c>
-      <c r="E63" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="F63" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="G63" t="n">
         <v>96.721311</v>
       </c>
     </row>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,22 +464,22 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C2" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D2" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E2" t="n">
-        <v>121801</v>
+        <v>118781</v>
       </c>
       <c r="F2" t="n">
-        <v>177159</v>
+        <v>177999</v>
       </c>
       <c r="G2" t="n">
-        <v>100</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="3">
@@ -489,22 +489,22 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D3" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E3" t="n">
-        <v>117.110001</v>
+        <v>114.080002</v>
       </c>
       <c r="F3" t="n">
-        <v>174.309998</v>
+        <v>175.020004</v>
       </c>
       <c r="G3" t="n">
-        <v>100</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="4">
@@ -514,22 +514,22 @@
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D4" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E4" t="n">
-        <v>141.800003</v>
+        <v>136.330002</v>
       </c>
       <c r="F4" t="n">
-        <v>107.360001</v>
+        <v>107.25</v>
       </c>
       <c r="G4" t="n">
-        <v>100</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="5">
@@ -539,22 +539,22 @@
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D5" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E5" t="n">
-        <v>250.350006</v>
+        <v>254</v>
       </c>
       <c r="F5" t="n">
-        <v>425.369995</v>
+        <v>428.390015</v>
       </c>
       <c r="G5" t="n">
-        <v>100</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="6">
@@ -567,19 +567,19 @@
         <v>44439</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D6" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E6" t="n">
         <v>5.1829</v>
       </c>
       <c r="F6" t="n">
-        <v>5.0716</v>
+        <v>5.0747</v>
       </c>
       <c r="G6" t="n">
-        <v>98.36065600000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7">
@@ -601,7 +601,7 @@
         <v>6.1119</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8255</v>
+        <v>5.8536</v>
       </c>
       <c r="G7" t="n">
         <v>98.36065600000001</v>
@@ -626,7 +626,7 @@
         <v>4522.680176</v>
       </c>
       <c r="F8" t="n">
-        <v>7437.629883</v>
+        <v>7489.720215</v>
       </c>
       <c r="G8" t="n">
         <v>98.36065600000001</v>
@@ -651,7 +651,7 @@
         <v>15259.240234</v>
       </c>
       <c r="F9" t="n">
-        <v>25122.179688</v>
+        <v>25373.849609</v>
       </c>
       <c r="G9" t="n">
         <v>98.36065600000001</v>
@@ -676,7 +676,7 @@
         <v>35360.730469</v>
       </c>
       <c r="F10" t="n">
-        <v>52208.058594</v>
+        <v>52485.03125</v>
       </c>
       <c r="G10" t="n">
         <v>98.36065600000001</v>
@@ -701,7 +701,7 @@
         <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4109.799805</v>
+        <v>4049.100098</v>
       </c>
       <c r="G11" t="n">
         <v>98.36065600000001</v>
@@ -726,7 +726,7 @@
         <v>68.5</v>
       </c>
       <c r="F12" t="n">
-        <v>84.839996</v>
+        <v>84.66999800000001</v>
       </c>
       <c r="G12" t="n">
         <v>98.36065600000001</v>
@@ -751,7 +751,7 @@
         <v>72.989998</v>
       </c>
       <c r="F13" t="n">
-        <v>90.25</v>
+        <v>90.120003</v>
       </c>
       <c r="G13" t="n">
         <v>98.36065600000001</v>
@@ -776,7 +776,7 @@
         <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1188.5</v>
+        <v>1172</v>
       </c>
       <c r="G14" t="n">
         <v>98.36065600000001</v>
@@ -801,7 +801,7 @@
         <v>534</v>
       </c>
       <c r="F15" t="n">
-        <v>466.25</v>
+        <v>440.75</v>
       </c>
       <c r="G15" t="n">
         <v>98.36065600000001</v>
@@ -814,22 +814,22 @@
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D16" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.479454</v>
+        <v>-6.568391</v>
       </c>
       <c r="F16" t="n">
-        <v>2.985049</v>
+        <v>3.473353</v>
       </c>
       <c r="G16" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="17">
@@ -839,22 +839,22 @@
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C17" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D17" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.58731</v>
+        <v>-6.653229</v>
       </c>
       <c r="F17" t="n">
-        <v>3.111502</v>
+        <v>3.5315</v>
       </c>
       <c r="G17" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="18">
@@ -864,22 +864,22 @@
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C18" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.857547</v>
+        <v>-6.550283</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.574183</v>
+        <v>-0.676054</v>
       </c>
       <c r="G18" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="19">
@@ -889,22 +889,22 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C19" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D19" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E19" t="n">
-        <v>1.457956</v>
+        <v>0.393701</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.359692</v>
+        <v>-1.666471</v>
       </c>
       <c r="G19" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="20">
@@ -917,19 +917,19 @@
         <v>44469</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D20" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E20" t="n">
         <v>4.464682</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.12643</v>
+        <v>-0.06696100000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>96.721311</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="21">
@@ -951,7 +951,7 @@
         <v>2.725834</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.549054</v>
+        <v>-1.074164</v>
       </c>
       <c r="G21" t="n">
         <v>96.721311</v>
@@ -976,7 +976,7 @@
         <v>-4.756917</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.823137</v>
+        <v>-0.12854</v>
       </c>
       <c r="G22" t="n">
         <v>96.721311</v>
@@ -1001,7 +1001,7 @@
         <v>-5.312585</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.164006</v>
+        <v>-3.203937</v>
       </c>
       <c r="G23" t="n">
         <v>96.721311</v>
@@ -1026,7 +1026,7 @@
         <v>-4.289528</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.212428</v>
+        <v>0.316962</v>
       </c>
       <c r="G24" t="n">
         <v>96.721311</v>
@@ -1051,7 +1051,7 @@
         <v>-3.289254</v>
       </c>
       <c r="F25" t="n">
-        <v>2.160131</v>
+        <v>0.651276</v>
       </c>
       <c r="G25" t="n">
         <v>96.721311</v>
@@ -1076,7 +1076,7 @@
         <v>9.532845</v>
       </c>
       <c r="F26" t="n">
-        <v>22.071937</v>
+        <v>21.827335</v>
       </c>
       <c r="G26" t="n">
         <v>96.721311</v>
@@ -1101,7 +1101,7 @@
         <v>7.576379</v>
       </c>
       <c r="F27" t="n">
-        <v>23.765774</v>
+        <v>23.5875</v>
       </c>
       <c r="G27" t="n">
         <v>96.721311</v>
@@ -1126,7 +1126,7 @@
         <v>-3.291627</v>
       </c>
       <c r="F28" t="n">
-        <v>6.424894</v>
+        <v>4.947392</v>
       </c>
       <c r="G28" t="n">
         <v>96.721311</v>
@@ -1151,7 +1151,7 @@
         <v>0.514981</v>
       </c>
       <c r="F29" t="n">
-        <v>12.961841</v>
+        <v>6.783767</v>
       </c>
       <c r="G29" t="n">
         <v>96.721311</v>
@@ -1164,16 +1164,16 @@
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D30" t="n">
         <v>61</v>
       </c>
       <c r="E30" t="n">
-        <v>4.25</v>
+        <v>5.25</v>
       </c>
       <c r="F30" t="n">
         <v>14.25</v>
@@ -1239,22 +1239,22 @@
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C33" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D33" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E33" t="n">
-        <v>0.96</v>
+        <v>0.87</v>
       </c>
       <c r="F33" t="n">
         <v>0.16</v>
       </c>
       <c r="G33" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="34">
@@ -1264,22 +1264,22 @@
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C34" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D34" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E34" t="n">
-        <v>0.78</v>
+        <v>0.66</v>
       </c>
       <c r="F34" t="n">
         <v>-1.16</v>
       </c>
       <c r="G34" t="n">
-        <v>100</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="35">
@@ -1289,94 +1289,94 @@
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C35" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D35" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E35" t="n">
-        <v>1.02</v>
+        <v>0.88</v>
       </c>
       <c r="F35" t="n">
         <v>0.14</v>
       </c>
       <c r="G35" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_venda_usd</t>
+          <t>bcb_sgs_ibc_br_sa</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D36" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E36" t="n">
-        <v>5.1433</v>
+        <v>97.07568000000001</v>
       </c>
       <c r="F36" t="n">
-        <v>5.0739</v>
+        <v>111.03587</v>
       </c>
       <c r="G36" t="n">
-        <v>98.36065600000001</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_compra_usd</t>
+          <t>bcb_sgs_ibc_br</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D37" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E37" t="n">
-        <v>5.1427</v>
+        <v>99.32829</v>
       </c>
       <c r="F37" t="n">
-        <v>5.0733</v>
+        <v>109.52993</v>
       </c>
       <c r="G37" t="n">
-        <v>98.36065600000001</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D38" t="n">
         <v>60</v>
       </c>
       <c r="E38" t="n">
-        <v>4271865</v>
+        <v>5.1433</v>
       </c>
       <c r="F38" t="n">
-        <v>7355800</v>
+        <v>5.0773</v>
       </c>
       <c r="G38" t="n">
         <v>98.36065600000001</v>
@@ -1385,23 +1385,23 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D39" t="n">
         <v>60</v>
       </c>
       <c r="E39" t="n">
-        <v>1833179</v>
+        <v>5.1427</v>
       </c>
       <c r="F39" t="n">
-        <v>2749001</v>
+        <v>5.0767</v>
       </c>
       <c r="G39" t="n">
         <v>98.36065600000001</v>
@@ -1410,173 +1410,173 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C40" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D40" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E40" t="n">
-        <v>2438686</v>
+        <v>4346060</v>
       </c>
       <c r="F40" t="n">
-        <v>4606799</v>
+        <v>7355800</v>
       </c>
       <c r="G40" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C41" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D41" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E41" t="n">
-        <v>2.36</v>
+        <v>1851006</v>
       </c>
       <c r="F41" t="n">
-        <v>4.68</v>
+        <v>2749001</v>
       </c>
       <c r="G41" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C42" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D42" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E42" t="n">
-        <v>1.58</v>
+        <v>2495054</v>
       </c>
       <c r="F42" t="n">
-        <v>3.19</v>
+        <v>4606799</v>
       </c>
       <c r="G42" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C43" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D43" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E43" t="n">
-        <v>2.94</v>
+        <v>2.37</v>
       </c>
       <c r="F43" t="n">
-        <v>5.57</v>
+        <v>4.68</v>
       </c>
       <c r="G43" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C44" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D44" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E44" t="n">
-        <v>20.26</v>
+        <v>1.56</v>
       </c>
       <c r="F44" t="n">
-        <v>33.44</v>
+        <v>3.19</v>
       </c>
       <c r="G44" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C45" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D45" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E45" t="n">
-        <v>355671</v>
+        <v>2.96</v>
       </c>
       <c r="F45" t="n">
-        <v>367558</v>
+        <v>5.57</v>
       </c>
       <c r="G45" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D46" t="n">
         <v>59</v>
       </c>
       <c r="E46" t="n">
-        <v>5.757004</v>
+        <v>20.92</v>
       </c>
       <c r="F46" t="n">
-        <v>-1.983928</v>
+        <v>33.44</v>
       </c>
       <c r="G46" t="n">
         <v>96.721311</v>
@@ -1585,23 +1585,23 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D47" t="n">
         <v>59</v>
       </c>
       <c r="E47" t="n">
-        <v>5.757676</v>
+        <v>370395</v>
       </c>
       <c r="F47" t="n">
-        <v>-1.984158</v>
+        <v>367558</v>
       </c>
       <c r="G47" t="n">
         <v>96.721311</v>
@@ -1610,73 +1610,73 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="D48" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E48" t="n">
-        <v>1.736829</v>
+        <v>-0.119484</v>
       </c>
       <c r="F48" t="n">
-        <v>0.714468</v>
+        <v>0.07079299999999999</v>
       </c>
       <c r="G48" t="n">
-        <v>96.721311</v>
+        <v>93.442623</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="D49" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E49" t="n">
-        <v>0.972464</v>
+        <v>-2.094902</v>
       </c>
       <c r="F49" t="n">
-        <v>1.515494</v>
+        <v>-3.915762</v>
       </c>
       <c r="G49" t="n">
-        <v>96.721311</v>
+        <v>93.442623</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D50" t="n">
         <v>59</v>
       </c>
       <c r="E50" t="n">
-        <v>2.311409</v>
+        <v>5.757004</v>
       </c>
       <c r="F50" t="n">
-        <v>0.242446</v>
+        <v>-1.918247</v>
       </c>
       <c r="G50" t="n">
         <v>96.721311</v>
@@ -1685,23 +1685,23 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D51" t="n">
         <v>59</v>
       </c>
       <c r="E51" t="n">
-        <v>4.139781</v>
+        <v>5.757676</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.964334</v>
+        <v>-1.91847</v>
       </c>
       <c r="G51" t="n">
         <v>96.721311</v>
@@ -1710,223 +1710,223 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
-        <v>44742</v>
+        <v>44469</v>
       </c>
       <c r="C52" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D52" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E52" t="n">
-        <v>11.88673</v>
+        <v>2.185796</v>
       </c>
       <c r="F52" t="n">
-        <v>4.641328</v>
+        <v>0.714468</v>
       </c>
       <c r="G52" t="n">
-        <v>80.32786900000001</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
-        <v>44742</v>
+        <v>44469</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D53" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E53" t="n">
-        <v>10.700862</v>
+        <v>2.329166</v>
       </c>
       <c r="F53" t="n">
-        <v>2.772183</v>
+        <v>1.515494</v>
       </c>
       <c r="G53" t="n">
-        <v>81.967213</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>44742</v>
+        <v>44469</v>
       </c>
       <c r="C54" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D54" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E54" t="n">
-        <v>11.919595</v>
+        <v>2.079394</v>
       </c>
       <c r="F54" t="n">
-        <v>4.327084</v>
+        <v>0.242446</v>
       </c>
       <c r="G54" t="n">
-        <v>80.32786900000001</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D55" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E55" t="n">
-        <v>1</v>
+        <v>-0.407403</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>-0.964334</v>
       </c>
       <c r="G55" t="n">
-        <v>98.36065600000001</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>44469</v>
+        <v>44773</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D56" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="E56" t="n">
-        <v>0.001591</v>
+        <v>10.069235</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.000497</v>
+        <v>4.641328</v>
       </c>
       <c r="G56" t="n">
-        <v>96.721311</v>
+        <v>78.688525</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>44469</v>
+        <v>44773</v>
       </c>
       <c r="C57" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D57" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E57" t="n">
-        <v>0.001591</v>
+        <v>10.074751</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.000497</v>
+        <v>2.772183</v>
       </c>
       <c r="G57" t="n">
-        <v>96.721311</v>
+        <v>80.32786900000001</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>44439</v>
+        <v>44773</v>
       </c>
       <c r="C58" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D58" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="E58" t="n">
-        <v>0.01</v>
+        <v>10.124804</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.06</v>
+        <v>4.327084</v>
       </c>
       <c r="G58" t="n">
-        <v>96.721311</v>
+        <v>78.688525</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="D59" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.02</v>
+        <v>1</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.06</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>96.721311</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D60" t="n">
         <v>59</v>
       </c>
       <c r="E60" t="n">
-        <v>0.02</v>
+        <v>0.001591</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.05</v>
+        <v>-0.000497</v>
       </c>
       <c r="G60" t="n">
         <v>96.721311</v>
@@ -1935,26 +1935,126 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>bcb_sgs_dif_cdi</t>
+        </is>
+      </c>
+      <c r="B61" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="C61" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="D61" t="n">
+        <v>59</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.001591</v>
+      </c>
+      <c r="F61" t="n">
+        <v>-0.000497</v>
+      </c>
+      <c r="G61" t="n">
+        <v>96.721311</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
+        </is>
+      </c>
+      <c r="B62" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="C62" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="D62" t="n">
+        <v>58</v>
+      </c>
+      <c r="E62" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="F62" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="G62" t="n">
+        <v>95.08196700000001</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
+        </is>
+      </c>
+      <c r="B63" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="C63" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="D63" t="n">
+        <v>58</v>
+      </c>
+      <c r="E63" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="F63" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="G63" t="n">
+        <v>95.08196700000001</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
+        </is>
+      </c>
+      <c r="B64" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="C64" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="D64" t="n">
+        <v>58</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F64" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G64" t="n">
+        <v>95.08196700000001</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
           <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
-      <c r="B61" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="C61" s="1" t="n">
+      <c r="B65" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="C65" s="1" t="n">
         <v>46203</v>
       </c>
-      <c r="D61" t="n">
-        <v>59</v>
-      </c>
-      <c r="E61" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="F61" t="n">
+      <c r="D65" t="n">
+        <v>58</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F65" t="n">
         <v>0.22</v>
       </c>
-      <c r="G61" t="n">
-        <v>96.721311</v>
+      <c r="G65" t="n">
+        <v>95.08196700000001</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -701,7 +701,7 @@
         <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4049.100098</v>
+        <v>4107</v>
       </c>
       <c r="G11" t="n">
         <v>98.36065600000001</v>
@@ -776,7 +776,7 @@
         <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1172</v>
+        <v>1187.5</v>
       </c>
       <c r="G14" t="n">
         <v>98.36065600000001</v>
@@ -801,7 +801,7 @@
         <v>534</v>
       </c>
       <c r="F15" t="n">
-        <v>440.75</v>
+        <v>464</v>
       </c>
       <c r="G15" t="n">
         <v>98.36065600000001</v>
@@ -1051,7 +1051,7 @@
         <v>-3.289254</v>
       </c>
       <c r="F25" t="n">
-        <v>0.651276</v>
+        <v>2.090534</v>
       </c>
       <c r="G25" t="n">
         <v>96.721311</v>
@@ -1126,7 +1126,7 @@
         <v>-3.291627</v>
       </c>
       <c r="F28" t="n">
-        <v>4.947392</v>
+        <v>6.335348</v>
       </c>
       <c r="G28" t="n">
         <v>96.721311</v>
@@ -1151,7 +1151,7 @@
         <v>0.514981</v>
       </c>
       <c r="F29" t="n">
-        <v>6.783767</v>
+        <v>12.416717</v>
       </c>
       <c r="G29" t="n">
         <v>96.721311</v>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -576,7 +576,7 @@
         <v>5.1829</v>
       </c>
       <c r="F6" t="n">
-        <v>5.0747</v>
+        <v>5.0598</v>
       </c>
       <c r="G6" t="n">
         <v>100</v>
@@ -592,19 +592,19 @@
         <v>44439</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D7" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E7" t="n">
         <v>6.1119</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8536</v>
+        <v>5.8308</v>
       </c>
       <c r="G7" t="n">
-        <v>98.36065600000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8">
@@ -692,19 +692,19 @@
         <v>44439</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D11" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E11" t="n">
         <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4107</v>
+        <v>4101.899902</v>
       </c>
       <c r="G11" t="n">
-        <v>98.36065600000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
@@ -717,19 +717,19 @@
         <v>44439</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E12" t="n">
         <v>68.5</v>
       </c>
       <c r="F12" t="n">
-        <v>84.66999800000001</v>
+        <v>78.849998</v>
       </c>
       <c r="G12" t="n">
-        <v>98.36065600000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -742,19 +742,19 @@
         <v>44439</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E13" t="n">
         <v>72.989998</v>
       </c>
       <c r="F13" t="n">
-        <v>90.120003</v>
+        <v>82.839996</v>
       </c>
       <c r="G13" t="n">
-        <v>98.36065600000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -767,19 +767,19 @@
         <v>44439</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E14" t="n">
         <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1187.5</v>
+        <v>1179.75</v>
       </c>
       <c r="G14" t="n">
-        <v>98.36065600000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -792,19 +792,19 @@
         <v>44439</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D15" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E15" t="n">
         <v>534</v>
       </c>
       <c r="F15" t="n">
-        <v>464</v>
+        <v>461.5</v>
       </c>
       <c r="G15" t="n">
-        <v>98.36065600000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16">
@@ -926,7 +926,7 @@
         <v>4.464682</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.06696100000000001</v>
+        <v>-0.360372</v>
       </c>
       <c r="G20" t="n">
         <v>98.36065600000001</v>
@@ -942,19 +942,19 @@
         <v>44469</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D21" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E21" t="n">
         <v>2.725834</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.074164</v>
+        <v>-0.293313</v>
       </c>
       <c r="G21" t="n">
-        <v>96.721311</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="22">
@@ -1042,19 +1042,19 @@
         <v>44469</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D25" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E25" t="n">
         <v>-3.289254</v>
       </c>
       <c r="F25" t="n">
-        <v>2.090534</v>
+        <v>1.303989</v>
       </c>
       <c r="G25" t="n">
-        <v>96.721311</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="26">
@@ -1067,19 +1067,19 @@
         <v>44469</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D26" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E26" t="n">
         <v>9.532845</v>
       </c>
       <c r="F26" t="n">
-        <v>21.827335</v>
+        <v>-6.873745</v>
       </c>
       <c r="G26" t="n">
-        <v>96.721311</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="27">
@@ -1092,19 +1092,19 @@
         <v>44469</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D27" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E27" t="n">
         <v>7.576379</v>
       </c>
       <c r="F27" t="n">
-        <v>23.5875</v>
+        <v>-8.078125</v>
       </c>
       <c r="G27" t="n">
-        <v>96.721311</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="28">
@@ -1117,19 +1117,19 @@
         <v>44469</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D28" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E28" t="n">
         <v>-3.291627</v>
       </c>
       <c r="F28" t="n">
-        <v>6.335348</v>
+        <v>0.661263</v>
       </c>
       <c r="G28" t="n">
-        <v>96.721311</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="29">
@@ -1142,19 +1142,19 @@
         <v>44469</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D29" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E29" t="n">
         <v>0.514981</v>
       </c>
       <c r="F29" t="n">
-        <v>12.416717</v>
+        <v>4.707884</v>
       </c>
       <c r="G29" t="n">
-        <v>96.721311</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="30">
@@ -1198,7 +1198,7 @@
         <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>0.019413</v>
+        <v>0.019569</v>
       </c>
       <c r="F31" t="n">
         <v>0.052531</v>
@@ -1223,7 +1223,7 @@
         <v>60</v>
       </c>
       <c r="E32" t="n">
-        <v>0.019413</v>
+        <v>0.019569</v>
       </c>
       <c r="F32" t="n">
         <v>0.052531</v>
@@ -1435,7 +1435,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
@@ -1448,10 +1448,10 @@
         <v>59</v>
       </c>
       <c r="E41" t="n">
-        <v>1851006</v>
+        <v>2495054</v>
       </c>
       <c r="F41" t="n">
-        <v>2749001</v>
+        <v>4606799</v>
       </c>
       <c r="G41" t="n">
         <v>96.721311</v>
@@ -1460,7 +1460,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
@@ -1473,10 +1473,10 @@
         <v>59</v>
       </c>
       <c r="E42" t="n">
-        <v>2495054</v>
+        <v>2.37</v>
       </c>
       <c r="F42" t="n">
-        <v>4606799</v>
+        <v>4.68</v>
       </c>
       <c r="G42" t="n">
         <v>96.721311</v>
@@ -1485,7 +1485,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
@@ -1498,10 +1498,10 @@
         <v>59</v>
       </c>
       <c r="E43" t="n">
-        <v>2.37</v>
+        <v>1.56</v>
       </c>
       <c r="F43" t="n">
-        <v>4.68</v>
+        <v>3.19</v>
       </c>
       <c r="G43" t="n">
         <v>96.721311</v>
@@ -1510,7 +1510,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
@@ -1523,10 +1523,10 @@
         <v>59</v>
       </c>
       <c r="E44" t="n">
-        <v>1.56</v>
+        <v>2.96</v>
       </c>
       <c r="F44" t="n">
-        <v>3.19</v>
+        <v>5.57</v>
       </c>
       <c r="G44" t="n">
         <v>96.721311</v>
@@ -1535,7 +1535,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
@@ -1548,10 +1548,10 @@
         <v>59</v>
       </c>
       <c r="E45" t="n">
-        <v>2.96</v>
+        <v>20.92</v>
       </c>
       <c r="F45" t="n">
-        <v>5.57</v>
+        <v>33.44</v>
       </c>
       <c r="G45" t="n">
         <v>96.721311</v>
@@ -1560,7 +1560,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
@@ -1573,10 +1573,10 @@
         <v>59</v>
       </c>
       <c r="E46" t="n">
-        <v>20.92</v>
+        <v>370395</v>
       </c>
       <c r="F46" t="n">
-        <v>33.44</v>
+        <v>367558</v>
       </c>
       <c r="G46" t="n">
         <v>96.721311</v>
@@ -1585,32 +1585,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="D47" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E47" t="n">
-        <v>370395</v>
+        <v>-0.119484</v>
       </c>
       <c r="F47" t="n">
-        <v>367558</v>
+        <v>0.07079299999999999</v>
       </c>
       <c r="G47" t="n">
-        <v>96.721311</v>
+        <v>93.442623</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
@@ -1623,10 +1623,10 @@
         <v>57</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.119484</v>
+        <v>-2.094902</v>
       </c>
       <c r="F48" t="n">
-        <v>0.07079299999999999</v>
+        <v>-3.915762</v>
       </c>
       <c r="G48" t="n">
         <v>93.442623</v>
@@ -1635,32 +1635,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D49" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E49" t="n">
-        <v>-2.094902</v>
+        <v>5.757004</v>
       </c>
       <c r="F49" t="n">
-        <v>-3.915762</v>
+        <v>-1.918247</v>
       </c>
       <c r="G49" t="n">
-        <v>93.442623</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
@@ -1673,10 +1673,10 @@
         <v>59</v>
       </c>
       <c r="E50" t="n">
-        <v>5.757004</v>
+        <v>5.757676</v>
       </c>
       <c r="F50" t="n">
-        <v>-1.918247</v>
+        <v>-1.91847</v>
       </c>
       <c r="G50" t="n">
         <v>96.721311</v>
@@ -1685,32 +1685,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D51" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E51" t="n">
-        <v>5.757676</v>
+        <v>2.185796</v>
       </c>
       <c r="F51" t="n">
-        <v>-1.91847</v>
+        <v>0.714468</v>
       </c>
       <c r="G51" t="n">
-        <v>96.721311</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
@@ -1723,10 +1723,10 @@
         <v>58</v>
       </c>
       <c r="E52" t="n">
-        <v>2.185796</v>
+        <v>2.079394</v>
       </c>
       <c r="F52" t="n">
-        <v>0.714468</v>
+        <v>0.242446</v>
       </c>
       <c r="G52" t="n">
         <v>95.08196700000001</v>
@@ -1735,7 +1735,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
@@ -1748,10 +1748,10 @@
         <v>58</v>
       </c>
       <c r="E53" t="n">
-        <v>2.329166</v>
+        <v>-0.407403</v>
       </c>
       <c r="F53" t="n">
-        <v>1.515494</v>
+        <v>-0.964334</v>
       </c>
       <c r="G53" t="n">
         <v>95.08196700000001</v>
@@ -1760,57 +1760,57 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>44469</v>
+        <v>44773</v>
       </c>
       <c r="C54" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D54" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="E54" t="n">
-        <v>2.079394</v>
+        <v>10.069235</v>
       </c>
       <c r="F54" t="n">
-        <v>0.242446</v>
+        <v>4.641328</v>
       </c>
       <c r="G54" t="n">
-        <v>95.08196700000001</v>
+        <v>78.688525</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>44469</v>
+        <v>44773</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D55" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.407403</v>
+        <v>10.074751</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.964334</v>
+        <v>2.772183</v>
       </c>
       <c r="G55" t="n">
-        <v>95.08196700000001</v>
+        <v>80.32786900000001</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
@@ -1823,10 +1823,10 @@
         <v>48</v>
       </c>
       <c r="E56" t="n">
-        <v>10.069235</v>
+        <v>10.124804</v>
       </c>
       <c r="F56" t="n">
-        <v>4.641328</v>
+        <v>4.327084</v>
       </c>
       <c r="G56" t="n">
         <v>78.688525</v>
@@ -1835,132 +1835,132 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>44773</v>
+        <v>44469</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D57" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E57" t="n">
-        <v>10.074751</v>
+        <v>1</v>
       </c>
       <c r="F57" t="n">
-        <v>2.772183</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>80.32786900000001</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>44773</v>
+        <v>44469</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D58" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="E58" t="n">
-        <v>10.124804</v>
+        <v>0.001435</v>
       </c>
       <c r="F58" t="n">
-        <v>4.327084</v>
+        <v>-0.000497</v>
       </c>
       <c r="G58" t="n">
-        <v>78.688525</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D59" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E59" t="n">
-        <v>1</v>
+        <v>0.001435</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>-0.000497</v>
       </c>
       <c r="G59" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D60" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E60" t="n">
-        <v>0.001591</v>
+        <v>-0.03</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.000497</v>
+        <v>-0.06</v>
       </c>
       <c r="G60" t="n">
-        <v>96.721311</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D61" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E61" t="n">
-        <v>0.001591</v>
+        <v>-0.13</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.000497</v>
+        <v>-0.06</v>
       </c>
       <c r="G61" t="n">
-        <v>96.721311</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
@@ -1973,10 +1973,10 @@
         <v>58</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.03</v>
+        <v>0.05</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="G62" t="n">
         <v>95.08196700000001</v>
@@ -1985,7 +1985,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
@@ -1998,62 +1998,12 @@
         <v>58</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.13</v>
+        <v>0.5</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.06</v>
+        <v>0.22</v>
       </c>
       <c r="G63" t="n">
-        <v>95.08196700000001</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
-        </is>
-      </c>
-      <c r="B64" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="C64" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="D64" t="n">
-        <v>58</v>
-      </c>
-      <c r="E64" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F64" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="G64" t="n">
-        <v>95.08196700000001</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
-        </is>
-      </c>
-      <c r="B65" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="C65" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="D65" t="n">
-        <v>58</v>
-      </c>
-      <c r="E65" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F65" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="G65" t="n">
         <v>95.08196700000001</v>
       </c>
     </row>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,19 +467,19 @@
         <v>44439</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E2" t="n">
         <v>118781</v>
       </c>
       <c r="F2" t="n">
-        <v>177999</v>
+        <v>178000</v>
       </c>
       <c r="G2" t="n">
-        <v>98.36065600000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3">
@@ -576,7 +576,7 @@
         <v>5.1829</v>
       </c>
       <c r="F6" t="n">
-        <v>5.0598</v>
+        <v>5.0743</v>
       </c>
       <c r="G6" t="n">
         <v>100</v>
@@ -601,7 +601,7 @@
         <v>6.1119</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8308</v>
+        <v>5.8596</v>
       </c>
       <c r="G7" t="n">
         <v>100</v>
@@ -617,19 +617,19 @@
         <v>44439</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D8" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E8" t="n">
         <v>4522.680176</v>
       </c>
       <c r="F8" t="n">
-        <v>7489.720215</v>
+        <v>7600.5</v>
       </c>
       <c r="G8" t="n">
-        <v>98.36065600000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9">
@@ -638,23 +638,15 @@
           <t>yahoo_nasdaq</t>
         </is>
       </c>
-      <c r="B9" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="C9" s="1" t="n">
-        <v>46234</v>
-      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>60</v>
-      </c>
-      <c r="E9" t="n">
-        <v>15259.240234</v>
-      </c>
-      <c r="F9" t="n">
-        <v>25373.849609</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
-        <v>98.36065600000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -667,19 +659,19 @@
         <v>44439</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D10" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E10" t="n">
         <v>35360.730469</v>
       </c>
       <c r="F10" t="n">
-        <v>52485.03125</v>
+        <v>53178.410156</v>
       </c>
       <c r="G10" t="n">
-        <v>98.36065600000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11">
@@ -701,7 +693,7 @@
         <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4101.899902</v>
+        <v>4133.799805</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
@@ -726,7 +718,7 @@
         <v>68.5</v>
       </c>
       <c r="F12" t="n">
-        <v>78.849998</v>
+        <v>77.480003</v>
       </c>
       <c r="G12" t="n">
         <v>100</v>
@@ -751,7 +743,7 @@
         <v>72.989998</v>
       </c>
       <c r="F13" t="n">
-        <v>82.839996</v>
+        <v>81.370003</v>
       </c>
       <c r="G13" t="n">
         <v>100</v>
@@ -776,7 +768,7 @@
         <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1179.75</v>
+        <v>1182.25</v>
       </c>
       <c r="G14" t="n">
         <v>100</v>
@@ -801,7 +793,7 @@
         <v>534</v>
       </c>
       <c r="F15" t="n">
-        <v>461.5</v>
+        <v>469.25</v>
       </c>
       <c r="G15" t="n">
         <v>100</v>
@@ -817,19 +809,19 @@
         <v>44469</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D16" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E16" t="n">
         <v>-6.568391</v>
       </c>
       <c r="F16" t="n">
-        <v>3.473353</v>
+        <v>0.000562</v>
       </c>
       <c r="G16" t="n">
-        <v>96.721311</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="17">
@@ -926,7 +918,7 @@
         <v>4.464682</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.360372</v>
+        <v>-0.074839</v>
       </c>
       <c r="G20" t="n">
         <v>98.36065600000001</v>
@@ -951,7 +943,7 @@
         <v>2.725834</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.293313</v>
+        <v>0.199168</v>
       </c>
       <c r="G21" t="n">
         <v>98.36065600000001</v>
@@ -967,19 +959,19 @@
         <v>44469</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D22" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E22" t="n">
         <v>-4.756917</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.12854</v>
+        <v>1.479091</v>
       </c>
       <c r="G22" t="n">
-        <v>96.721311</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="23">
@@ -988,23 +980,15 @@
           <t>yahoo_ret_nasdaq</t>
         </is>
       </c>
-      <c r="B23" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="C23" s="1" t="n">
-        <v>46234</v>
-      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="n">
-        <v>59</v>
-      </c>
-      <c r="E23" t="n">
-        <v>-5.312585</v>
-      </c>
-      <c r="F23" t="n">
-        <v>-3.203937</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
-        <v>96.721311</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1017,19 +1001,19 @@
         <v>44469</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D24" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E24" t="n">
         <v>-4.289528</v>
       </c>
       <c r="F24" t="n">
-        <v>0.316962</v>
+        <v>1.321098</v>
       </c>
       <c r="G24" t="n">
-        <v>96.721311</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="25">
@@ -1051,7 +1035,7 @@
         <v>-3.289254</v>
       </c>
       <c r="F25" t="n">
-        <v>1.303989</v>
+        <v>2.091816</v>
       </c>
       <c r="G25" t="n">
         <v>98.36065600000001</v>
@@ -1076,7 +1060,7 @@
         <v>9.532845</v>
       </c>
       <c r="F26" t="n">
-        <v>-6.873745</v>
+        <v>-8.491785999999999</v>
       </c>
       <c r="G26" t="n">
         <v>98.36065600000001</v>
@@ -1101,7 +1085,7 @@
         <v>7.576379</v>
       </c>
       <c r="F27" t="n">
-        <v>-8.078125</v>
+        <v>-9.709275999999999</v>
       </c>
       <c r="G27" t="n">
         <v>98.36065600000001</v>
@@ -1126,7 +1110,7 @@
         <v>-3.291627</v>
       </c>
       <c r="F28" t="n">
-        <v>0.661263</v>
+        <v>0.874573</v>
       </c>
       <c r="G28" t="n">
         <v>98.36065600000001</v>
@@ -1151,7 +1135,7 @@
         <v>0.514981</v>
       </c>
       <c r="F29" t="n">
-        <v>4.707884</v>
+        <v>6.466251</v>
       </c>
       <c r="G29" t="n">
         <v>98.36065600000001</v>
@@ -1192,19 +1176,19 @@
         <v>44439</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D31" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E31" t="n">
-        <v>0.019569</v>
+        <v>0.01974</v>
       </c>
       <c r="F31" t="n">
         <v>0.052531</v>
       </c>
       <c r="G31" t="n">
-        <v>98.36065600000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32">
@@ -1217,19 +1201,19 @@
         <v>44439</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D32" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E32" t="n">
-        <v>0.019569</v>
+        <v>0.01974</v>
       </c>
       <c r="F32" t="n">
         <v>0.052531</v>
       </c>
       <c r="G32" t="n">
-        <v>98.36065600000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33">
@@ -1310,7 +1294,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br_sa</t>
+          <t>bcb_sgs_ibc_br</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
@@ -1323,10 +1307,10 @@
         <v>58</v>
       </c>
       <c r="E36" t="n">
-        <v>97.07568000000001</v>
+        <v>99.32829</v>
       </c>
       <c r="F36" t="n">
-        <v>111.03587</v>
+        <v>109.52993</v>
       </c>
       <c r="G36" t="n">
         <v>95.08196700000001</v>
@@ -1335,82 +1319,82 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br</t>
+          <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46173</v>
+        <v>46265</v>
       </c>
       <c r="D37" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E37" t="n">
-        <v>99.32829</v>
+        <v>5.1433</v>
       </c>
       <c r="F37" t="n">
-        <v>109.52993</v>
+        <v>5.0723</v>
       </c>
       <c r="G37" t="n">
-        <v>95.08196700000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_venda_usd</t>
+          <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D38" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E38" t="n">
-        <v>5.1433</v>
+        <v>5.1427</v>
       </c>
       <c r="F38" t="n">
-        <v>5.0773</v>
+        <v>5.0717</v>
       </c>
       <c r="G38" t="n">
-        <v>98.36065600000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_compra_usd</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D39" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E39" t="n">
-        <v>5.1427</v>
+        <v>4346060</v>
       </c>
       <c r="F39" t="n">
-        <v>5.0767</v>
+        <v>7355800</v>
       </c>
       <c r="G39" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
@@ -1423,10 +1407,10 @@
         <v>59</v>
       </c>
       <c r="E40" t="n">
-        <v>4346060</v>
+        <v>2495054</v>
       </c>
       <c r="F40" t="n">
-        <v>7355800</v>
+        <v>4606799</v>
       </c>
       <c r="G40" t="n">
         <v>96.721311</v>
@@ -1435,7 +1419,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
@@ -1448,10 +1432,10 @@
         <v>59</v>
       </c>
       <c r="E41" t="n">
-        <v>2495054</v>
+        <v>2.37</v>
       </c>
       <c r="F41" t="n">
-        <v>4606799</v>
+        <v>4.68</v>
       </c>
       <c r="G41" t="n">
         <v>96.721311</v>
@@ -1460,7 +1444,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
@@ -1473,10 +1457,10 @@
         <v>59</v>
       </c>
       <c r="E42" t="n">
-        <v>2.37</v>
+        <v>1.56</v>
       </c>
       <c r="F42" t="n">
-        <v>4.68</v>
+        <v>3.19</v>
       </c>
       <c r="G42" t="n">
         <v>96.721311</v>
@@ -1485,7 +1469,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
@@ -1498,10 +1482,10 @@
         <v>59</v>
       </c>
       <c r="E43" t="n">
-        <v>1.56</v>
+        <v>2.96</v>
       </c>
       <c r="F43" t="n">
-        <v>3.19</v>
+        <v>5.57</v>
       </c>
       <c r="G43" t="n">
         <v>96.721311</v>
@@ -1510,7 +1494,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
@@ -1523,10 +1507,10 @@
         <v>59</v>
       </c>
       <c r="E44" t="n">
-        <v>2.96</v>
+        <v>20.92</v>
       </c>
       <c r="F44" t="n">
-        <v>5.57</v>
+        <v>33.44</v>
       </c>
       <c r="G44" t="n">
         <v>96.721311</v>
@@ -1535,232 +1519,232 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D45" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E45" t="n">
-        <v>20.92</v>
+        <v>370395</v>
       </c>
       <c r="F45" t="n">
-        <v>33.44</v>
+        <v>369742</v>
       </c>
       <c r="G45" t="n">
-        <v>96.721311</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="D46" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E46" t="n">
-        <v>370395</v>
+        <v>-2.094902</v>
       </c>
       <c r="F46" t="n">
-        <v>367558</v>
+        <v>-3.915762</v>
       </c>
       <c r="G46" t="n">
-        <v>96.721311</v>
+        <v>93.442623</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46173</v>
+        <v>46265</v>
       </c>
       <c r="D47" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.119484</v>
+        <v>5.757004</v>
       </c>
       <c r="F47" t="n">
-        <v>0.07079299999999999</v>
+        <v>-0.098478</v>
       </c>
       <c r="G47" t="n">
-        <v>93.442623</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>46173</v>
+        <v>46265</v>
       </c>
       <c r="D48" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E48" t="n">
-        <v>-2.094902</v>
+        <v>5.757676</v>
       </c>
       <c r="F48" t="n">
-        <v>-3.915762</v>
+        <v>-0.09848899999999999</v>
       </c>
       <c r="G48" t="n">
-        <v>93.442623</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D49" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E49" t="n">
-        <v>5.757004</v>
+        <v>2.185796</v>
       </c>
       <c r="F49" t="n">
-        <v>-1.918247</v>
+        <v>0.714468</v>
       </c>
       <c r="G49" t="n">
-        <v>96.721311</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D50" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E50" t="n">
-        <v>5.757676</v>
+        <v>2.079394</v>
       </c>
       <c r="F50" t="n">
-        <v>-1.91847</v>
+        <v>0.242446</v>
       </c>
       <c r="G50" t="n">
-        <v>96.721311</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D51" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E51" t="n">
-        <v>2.185796</v>
+        <v>-0.407403</v>
       </c>
       <c r="F51" t="n">
-        <v>0.714468</v>
+        <v>0.5941920000000001</v>
       </c>
       <c r="G51" t="n">
-        <v>95.08196700000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
-        <v>44469</v>
+        <v>44773</v>
       </c>
       <c r="C52" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D52" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="E52" t="n">
-        <v>2.079394</v>
+        <v>10.069235</v>
       </c>
       <c r="F52" t="n">
-        <v>0.242446</v>
+        <v>4.641328</v>
       </c>
       <c r="G52" t="n">
-        <v>95.08196700000001</v>
+        <v>78.688525</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
-        <v>44469</v>
+        <v>44773</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D53" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.407403</v>
+        <v>10.074751</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.964334</v>
+        <v>2.772183</v>
       </c>
       <c r="G53" t="n">
-        <v>95.08196700000001</v>
+        <v>80.32786900000001</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
@@ -1773,10 +1757,10 @@
         <v>48</v>
       </c>
       <c r="E54" t="n">
-        <v>10.069235</v>
+        <v>10.124804</v>
       </c>
       <c r="F54" t="n">
-        <v>4.641328</v>
+        <v>4.327084</v>
       </c>
       <c r="G54" t="n">
         <v>78.688525</v>
@@ -1785,57 +1769,57 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>44773</v>
+        <v>44469</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D55" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E55" t="n">
-        <v>10.074751</v>
+        <v>1</v>
       </c>
       <c r="F55" t="n">
-        <v>2.772183</v>
+        <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>80.32786900000001</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>44773</v>
+        <v>44469</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="D56" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="E56" t="n">
-        <v>10.124804</v>
+        <v>0.001263</v>
       </c>
       <c r="F56" t="n">
-        <v>4.327084</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>78.688525</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
@@ -1848,7 +1832,7 @@
         <v>60</v>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>0.001263</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -1860,57 +1844,57 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D58" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E58" t="n">
-        <v>0.001435</v>
+        <v>-0.03</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.000497</v>
+        <v>-0.06</v>
       </c>
       <c r="G58" t="n">
-        <v>96.721311</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D59" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E59" t="n">
-        <v>0.001435</v>
+        <v>-0.13</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.000497</v>
+        <v>-0.06</v>
       </c>
       <c r="G59" t="n">
-        <v>96.721311</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
@@ -1923,10 +1907,10 @@
         <v>58</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.03</v>
+        <v>0.05</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="G60" t="n">
         <v>95.08196700000001</v>
@@ -1935,7 +1919,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
@@ -1948,62 +1932,12 @@
         <v>58</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.13</v>
+        <v>0.5</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.06</v>
+        <v>0.22</v>
       </c>
       <c r="G61" t="n">
-        <v>95.08196700000001</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
-        </is>
-      </c>
-      <c r="B62" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="C62" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="D62" t="n">
-        <v>58</v>
-      </c>
-      <c r="E62" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F62" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="G62" t="n">
-        <v>95.08196700000001</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
-        </is>
-      </c>
-      <c r="B63" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="C63" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="D63" t="n">
-        <v>58</v>
-      </c>
-      <c r="E63" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F63" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="G63" t="n">
         <v>95.08196700000001</v>
       </c>
     </row>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
         <v>118781</v>
       </c>
       <c r="F2" t="n">
-        <v>178000</v>
+        <v>177895</v>
       </c>
       <c r="G2" t="n">
         <v>100</v>
@@ -492,19 +492,19 @@
         <v>44439</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D3" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E3" t="n">
         <v>114.080002</v>
       </c>
       <c r="F3" t="n">
-        <v>175.020004</v>
+        <v>174.899994</v>
       </c>
       <c r="G3" t="n">
-        <v>98.36065600000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4">
@@ -517,19 +517,19 @@
         <v>44439</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D4" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E4" t="n">
         <v>136.330002</v>
       </c>
       <c r="F4" t="n">
-        <v>107.25</v>
+        <v>108.379997</v>
       </c>
       <c r="G4" t="n">
-        <v>98.36065600000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5">
@@ -542,19 +542,19 @@
         <v>44439</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D5" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E5" t="n">
         <v>254</v>
       </c>
       <c r="F5" t="n">
-        <v>428.390015</v>
+        <v>435.829987</v>
       </c>
       <c r="G5" t="n">
-        <v>98.36065600000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         <v>5.1829</v>
       </c>
       <c r="F6" t="n">
-        <v>5.0743</v>
+        <v>5.1397</v>
       </c>
       <c r="G6" t="n">
         <v>100</v>
@@ -601,7 +601,7 @@
         <v>6.1119</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8596</v>
+        <v>5.9358</v>
       </c>
       <c r="G7" t="n">
         <v>100</v>
@@ -626,7 +626,7 @@
         <v>4522.680176</v>
       </c>
       <c r="F8" t="n">
-        <v>7600.5</v>
+        <v>7736.52002</v>
       </c>
       <c r="G8" t="n">
         <v>100</v>
@@ -638,15 +638,23 @@
           <t>yahoo_nasdaq</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
+      <c r="B9" s="1" t="n">
+        <v>44439</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>46265</v>
+      </c>
       <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+        <v>61</v>
+      </c>
+      <c r="E9" t="n">
+        <v>15259.240234</v>
+      </c>
+      <c r="F9" t="n">
+        <v>26584.990234</v>
+      </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10">
@@ -668,7 +676,7 @@
         <v>35360.730469</v>
       </c>
       <c r="F10" t="n">
-        <v>53178.410156</v>
+        <v>54085.878906</v>
       </c>
       <c r="G10" t="n">
         <v>100</v>
@@ -693,7 +701,7 @@
         <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4133.799805</v>
+        <v>4246.5</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
@@ -718,7 +726,7 @@
         <v>68.5</v>
       </c>
       <c r="F12" t="n">
-        <v>77.480003</v>
+        <v>76.19000200000001</v>
       </c>
       <c r="G12" t="n">
         <v>100</v>
@@ -743,7 +751,7 @@
         <v>72.989998</v>
       </c>
       <c r="F13" t="n">
-        <v>81.370003</v>
+        <v>80.279999</v>
       </c>
       <c r="G13" t="n">
         <v>100</v>
@@ -768,7 +776,7 @@
         <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1182.25</v>
+        <v>1167.75</v>
       </c>
       <c r="G14" t="n">
         <v>100</v>
@@ -793,7 +801,7 @@
         <v>534</v>
       </c>
       <c r="F15" t="n">
-        <v>469.25</v>
+        <v>459.25</v>
       </c>
       <c r="G15" t="n">
         <v>100</v>
@@ -818,7 +826,7 @@
         <v>-6.568391</v>
       </c>
       <c r="F16" t="n">
-        <v>0.000562</v>
+        <v>-0.058427</v>
       </c>
       <c r="G16" t="n">
         <v>98.36065600000001</v>
@@ -834,19 +842,19 @@
         <v>44469</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D17" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E17" t="n">
         <v>-6.653229</v>
       </c>
       <c r="F17" t="n">
-        <v>3.5315</v>
+        <v>-0.06857000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>96.721311</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="18">
@@ -859,19 +867,19 @@
         <v>44469</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E18" t="n">
         <v>-6.550283</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.676054</v>
+        <v>1.05361</v>
       </c>
       <c r="G18" t="n">
-        <v>96.721311</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="19">
@@ -884,19 +892,19 @@
         <v>44469</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D19" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E19" t="n">
         <v>0.393701</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.666471</v>
+        <v>1.736729</v>
       </c>
       <c r="G19" t="n">
-        <v>96.721311</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="20">
@@ -918,7 +926,7 @@
         <v>4.464682</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.074839</v>
+        <v>1.213047</v>
       </c>
       <c r="G20" t="n">
         <v>98.36065600000001</v>
@@ -943,7 +951,7 @@
         <v>2.725834</v>
       </c>
       <c r="F21" t="n">
-        <v>0.199168</v>
+        <v>1.502188</v>
       </c>
       <c r="G21" t="n">
         <v>98.36065600000001</v>
@@ -968,7 +976,7 @@
         <v>-4.756917</v>
       </c>
       <c r="F22" t="n">
-        <v>1.479091</v>
+        <v>3.295181</v>
       </c>
       <c r="G22" t="n">
         <v>98.36065600000001</v>
@@ -980,15 +988,23 @@
           <t>yahoo_ret_nasdaq</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
+      <c r="B23" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="C23" s="1" t="n">
+        <v>46265</v>
+      </c>
       <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-5.312585</v>
+      </c>
+      <c r="F23" t="n">
+        <v>4.773184</v>
+      </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="24">
@@ -1010,7 +1026,7 @@
         <v>-4.289528</v>
       </c>
       <c r="F24" t="n">
-        <v>1.321098</v>
+        <v>3.050103</v>
       </c>
       <c r="G24" t="n">
         <v>98.36065600000001</v>
@@ -1035,7 +1051,7 @@
         <v>-3.289254</v>
       </c>
       <c r="F25" t="n">
-        <v>2.091816</v>
+        <v>4.875155</v>
       </c>
       <c r="G25" t="n">
         <v>98.36065600000001</v>
@@ -1060,7 +1076,7 @@
         <v>9.532845</v>
       </c>
       <c r="F26" t="n">
-        <v>-8.491785999999999</v>
+        <v>-10.015349</v>
       </c>
       <c r="G26" t="n">
         <v>98.36065600000001</v>
@@ -1085,7 +1101,7 @@
         <v>7.576379</v>
       </c>
       <c r="F27" t="n">
-        <v>-9.709275999999999</v>
+        <v>-10.918779</v>
       </c>
       <c r="G27" t="n">
         <v>98.36065600000001</v>
@@ -1110,7 +1126,7 @@
         <v>-3.291627</v>
       </c>
       <c r="F28" t="n">
-        <v>0.874573</v>
+        <v>-0.362628</v>
       </c>
       <c r="G28" t="n">
         <v>98.36065600000001</v>
@@ -1135,7 +1151,7 @@
         <v>0.514981</v>
       </c>
       <c r="F29" t="n">
-        <v>6.466251</v>
+        <v>4.197391</v>
       </c>
       <c r="G29" t="n">
         <v>98.36065600000001</v>
@@ -1182,7 +1198,7 @@
         <v>61</v>
       </c>
       <c r="E31" t="n">
-        <v>0.01974</v>
+        <v>0.01993</v>
       </c>
       <c r="F31" t="n">
         <v>0.052531</v>
@@ -1207,7 +1223,7 @@
         <v>61</v>
       </c>
       <c r="E32" t="n">
-        <v>0.01974</v>
+        <v>0.01993</v>
       </c>
       <c r="F32" t="n">
         <v>0.052531</v>
@@ -1294,7 +1310,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br</t>
+          <t>bcb_sgs_ibc_br_sa</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
@@ -1307,10 +1323,10 @@
         <v>58</v>
       </c>
       <c r="E36" t="n">
-        <v>99.32829</v>
+        <v>97.07568000000001</v>
       </c>
       <c r="F36" t="n">
-        <v>109.52993</v>
+        <v>111.03587</v>
       </c>
       <c r="G36" t="n">
         <v>95.08196700000001</v>
@@ -1319,32 +1335,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_venda_usd</t>
+          <t>bcb_sgs_ibc_br</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46265</v>
+        <v>46173</v>
       </c>
       <c r="D37" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E37" t="n">
-        <v>5.1433</v>
+        <v>99.32829</v>
       </c>
       <c r="F37" t="n">
-        <v>5.0723</v>
+        <v>109.52993</v>
       </c>
       <c r="G37" t="n">
-        <v>100</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_compra_usd</t>
+          <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
@@ -1357,10 +1373,10 @@
         <v>61</v>
       </c>
       <c r="E38" t="n">
-        <v>5.1427</v>
+        <v>5.1433</v>
       </c>
       <c r="F38" t="n">
-        <v>5.0717</v>
+        <v>5.1053</v>
       </c>
       <c r="G38" t="n">
         <v>100</v>
@@ -1394,7 +1410,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
@@ -1407,10 +1423,10 @@
         <v>59</v>
       </c>
       <c r="E40" t="n">
-        <v>2495054</v>
+        <v>1851006</v>
       </c>
       <c r="F40" t="n">
-        <v>4606799</v>
+        <v>2749001</v>
       </c>
       <c r="G40" t="n">
         <v>96.721311</v>
@@ -1419,7 +1435,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
@@ -1432,10 +1448,10 @@
         <v>59</v>
       </c>
       <c r="E41" t="n">
-        <v>2.37</v>
+        <v>2495054</v>
       </c>
       <c r="F41" t="n">
-        <v>4.68</v>
+        <v>4606799</v>
       </c>
       <c r="G41" t="n">
         <v>96.721311</v>
@@ -1444,7 +1460,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
@@ -1457,10 +1473,10 @@
         <v>59</v>
       </c>
       <c r="E42" t="n">
-        <v>1.56</v>
+        <v>2.37</v>
       </c>
       <c r="F42" t="n">
-        <v>3.19</v>
+        <v>4.68</v>
       </c>
       <c r="G42" t="n">
         <v>96.721311</v>
@@ -1469,7 +1485,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
@@ -1482,10 +1498,10 @@
         <v>59</v>
       </c>
       <c r="E43" t="n">
-        <v>2.96</v>
+        <v>1.56</v>
       </c>
       <c r="F43" t="n">
-        <v>5.57</v>
+        <v>3.19</v>
       </c>
       <c r="G43" t="n">
         <v>96.721311</v>
@@ -1494,7 +1510,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
@@ -1507,10 +1523,10 @@
         <v>59</v>
       </c>
       <c r="E44" t="n">
-        <v>20.92</v>
+        <v>2.96</v>
       </c>
       <c r="F44" t="n">
-        <v>33.44</v>
+        <v>5.57</v>
       </c>
       <c r="G44" t="n">
         <v>96.721311</v>
@@ -1519,132 +1535,132 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D45" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E45" t="n">
-        <v>370395</v>
+        <v>20.92</v>
       </c>
       <c r="F45" t="n">
-        <v>369742</v>
+        <v>33.44</v>
       </c>
       <c r="G45" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D46" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E46" t="n">
-        <v>-2.094902</v>
+        <v>370395</v>
       </c>
       <c r="F46" t="n">
-        <v>-3.915762</v>
+        <v>369742</v>
       </c>
       <c r="G46" t="n">
-        <v>93.442623</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46265</v>
+        <v>46173</v>
       </c>
       <c r="D47" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E47" t="n">
-        <v>5.757004</v>
+        <v>-0.119484</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.098478</v>
+        <v>0.07079299999999999</v>
       </c>
       <c r="G47" t="n">
-        <v>98.36065600000001</v>
+        <v>93.442623</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>46265</v>
+        <v>46173</v>
       </c>
       <c r="D48" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E48" t="n">
-        <v>5.757676</v>
+        <v>-2.094902</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.09848899999999999</v>
+        <v>-3.915762</v>
       </c>
       <c r="G48" t="n">
-        <v>98.36065600000001</v>
+        <v>93.442623</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="D49" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E49" t="n">
-        <v>2.185796</v>
+        <v>5.757004</v>
       </c>
       <c r="F49" t="n">
-        <v>0.714468</v>
+        <v>0.551474</v>
       </c>
       <c r="G49" t="n">
-        <v>95.08196700000001</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
@@ -1657,10 +1673,10 @@
         <v>58</v>
       </c>
       <c r="E50" t="n">
-        <v>2.079394</v>
+        <v>2.185796</v>
       </c>
       <c r="F50" t="n">
-        <v>0.242446</v>
+        <v>0.714468</v>
       </c>
       <c r="G50" t="n">
         <v>95.08196700000001</v>
@@ -1669,82 +1685,82 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D51" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.407403</v>
+        <v>2.329166</v>
       </c>
       <c r="F51" t="n">
-        <v>0.5941920000000001</v>
+        <v>1.515494</v>
       </c>
       <c r="G51" t="n">
-        <v>96.721311</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
-        <v>44773</v>
+        <v>44469</v>
       </c>
       <c r="C52" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D52" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="E52" t="n">
-        <v>10.069235</v>
+        <v>2.079394</v>
       </c>
       <c r="F52" t="n">
-        <v>4.641328</v>
+        <v>0.242446</v>
       </c>
       <c r="G52" t="n">
-        <v>78.688525</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
-        <v>44773</v>
+        <v>44469</v>
       </c>
       <c r="C53" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D53" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E53" t="n">
-        <v>10.074751</v>
+        <v>-0.407403</v>
       </c>
       <c r="F53" t="n">
-        <v>2.772183</v>
+        <v>0.5941920000000001</v>
       </c>
       <c r="G53" t="n">
-        <v>80.32786900000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
@@ -1757,10 +1773,10 @@
         <v>48</v>
       </c>
       <c r="E54" t="n">
-        <v>10.124804</v>
+        <v>10.069235</v>
       </c>
       <c r="F54" t="n">
-        <v>4.327084</v>
+        <v>4.641328</v>
       </c>
       <c r="G54" t="n">
         <v>78.688525</v>
@@ -1769,57 +1785,57 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>44469</v>
+        <v>44773</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D55" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E55" t="n">
-        <v>1</v>
+        <v>10.074751</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>2.772183</v>
       </c>
       <c r="G55" t="n">
-        <v>98.36065600000001</v>
+        <v>80.32786900000001</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>44469</v>
+        <v>44773</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="D56" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="E56" t="n">
-        <v>0.001263</v>
+        <v>10.124804</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>4.327084</v>
       </c>
       <c r="G56" t="n">
-        <v>98.36065600000001</v>
+        <v>78.688525</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
@@ -1832,7 +1848,7 @@
         <v>60</v>
       </c>
       <c r="E57" t="n">
-        <v>0.001263</v>
+        <v>1</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -1844,57 +1860,57 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="D58" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.03</v>
+        <v>0.001073</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.06</v>
+        <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>95.08196700000001</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="D59" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.13</v>
+        <v>0.001073</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.06</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>95.08196700000001</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
@@ -1907,10 +1923,10 @@
         <v>58</v>
       </c>
       <c r="E60" t="n">
-        <v>0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="G60" t="n">
         <v>95.08196700000001</v>
@@ -1919,7 +1935,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
@@ -1932,12 +1948,62 @@
         <v>58</v>
       </c>
       <c r="E61" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="F61" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="G61" t="n">
+        <v>95.08196700000001</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
+        </is>
+      </c>
+      <c r="B62" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="C62" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="D62" t="n">
+        <v>58</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F62" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G62" t="n">
+        <v>95.08196700000001</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_juros_credito_total</t>
+        </is>
+      </c>
+      <c r="B63" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="C63" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="D63" t="n">
+        <v>58</v>
+      </c>
+      <c r="E63" t="n">
         <v>0.5</v>
       </c>
-      <c r="F61" t="n">
+      <c r="F63" t="n">
         <v>0.22</v>
       </c>
-      <c r="G61" t="n">
+      <c r="G63" t="n">
         <v>95.08196700000001</v>
       </c>
     </row>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
         <v>118781</v>
       </c>
       <c r="F2" t="n">
-        <v>177895</v>
+        <v>177726</v>
       </c>
       <c r="G2" t="n">
         <v>100</v>
@@ -501,7 +501,7 @@
         <v>114.080002</v>
       </c>
       <c r="F3" t="n">
-        <v>174.899994</v>
+        <v>174.699997</v>
       </c>
       <c r="G3" t="n">
         <v>100</v>
@@ -526,7 +526,7 @@
         <v>136.330002</v>
       </c>
       <c r="F4" t="n">
-        <v>108.379997</v>
+        <v>107.790001</v>
       </c>
       <c r="G4" t="n">
         <v>100</v>
@@ -551,7 +551,7 @@
         <v>254</v>
       </c>
       <c r="F5" t="n">
-        <v>435.829987</v>
+        <v>446.51001</v>
       </c>
       <c r="G5" t="n">
         <v>100</v>
@@ -576,7 +576,7 @@
         <v>5.1829</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1397</v>
+        <v>5.1165</v>
       </c>
       <c r="G6" t="n">
         <v>100</v>
@@ -601,7 +601,7 @@
         <v>6.1119</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9358</v>
+        <v>5.9151</v>
       </c>
       <c r="G7" t="n">
         <v>100</v>
@@ -626,7 +626,7 @@
         <v>4522.680176</v>
       </c>
       <c r="F8" t="n">
-        <v>7736.52002</v>
+        <v>7723.549805</v>
       </c>
       <c r="G8" t="n">
         <v>100</v>
@@ -651,7 +651,7 @@
         <v>15259.240234</v>
       </c>
       <c r="F9" t="n">
-        <v>26584.990234</v>
+        <v>26363.439453</v>
       </c>
       <c r="G9" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
         <v>35360.730469</v>
       </c>
       <c r="F10" t="n">
-        <v>54085.878906</v>
+        <v>54349.121094</v>
       </c>
       <c r="G10" t="n">
         <v>100</v>
@@ -701,7 +701,7 @@
         <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4246.5</v>
+        <v>4312.799805</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
@@ -726,7 +726,7 @@
         <v>68.5</v>
       </c>
       <c r="F12" t="n">
-        <v>76.19000200000001</v>
+        <v>76.129997</v>
       </c>
       <c r="G12" t="n">
         <v>100</v>
@@ -751,7 +751,7 @@
         <v>72.989998</v>
       </c>
       <c r="F13" t="n">
-        <v>80.279999</v>
+        <v>80.55999799999999</v>
       </c>
       <c r="G13" t="n">
         <v>100</v>
@@ -776,7 +776,7 @@
         <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1167.75</v>
+        <v>1174</v>
       </c>
       <c r="G14" t="n">
         <v>100</v>
@@ -801,7 +801,7 @@
         <v>534</v>
       </c>
       <c r="F15" t="n">
-        <v>459.25</v>
+        <v>460.5</v>
       </c>
       <c r="G15" t="n">
         <v>100</v>
@@ -826,7 +826,7 @@
         <v>-6.568391</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.058427</v>
+        <v>-0.153372</v>
       </c>
       <c r="G16" t="n">
         <v>98.36065600000001</v>
@@ -851,7 +851,7 @@
         <v>-6.653229</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.06857000000000001</v>
+        <v>-0.18284</v>
       </c>
       <c r="G17" t="n">
         <v>98.36065600000001</v>
@@ -876,7 +876,7 @@
         <v>-6.550283</v>
       </c>
       <c r="F18" t="n">
-        <v>1.05361</v>
+        <v>0.503497</v>
       </c>
       <c r="G18" t="n">
         <v>98.36065600000001</v>
@@ -901,7 +901,7 @@
         <v>0.393701</v>
       </c>
       <c r="F19" t="n">
-        <v>1.736729</v>
+        <v>4.229789</v>
       </c>
       <c r="G19" t="n">
         <v>98.36065600000001</v>
@@ -926,7 +926,7 @@
         <v>4.464682</v>
       </c>
       <c r="F20" t="n">
-        <v>1.213047</v>
+        <v>0.756182</v>
       </c>
       <c r="G20" t="n">
         <v>98.36065600000001</v>
@@ -951,7 +951,7 @@
         <v>2.725834</v>
       </c>
       <c r="F21" t="n">
-        <v>1.502188</v>
+        <v>1.148218</v>
       </c>
       <c r="G21" t="n">
         <v>98.36065600000001</v>
@@ -976,7 +976,7 @@
         <v>-4.756917</v>
       </c>
       <c r="F22" t="n">
-        <v>3.295181</v>
+        <v>3.122007</v>
       </c>
       <c r="G22" t="n">
         <v>98.36065600000001</v>
@@ -1001,7 +1001,7 @@
         <v>-5.312585</v>
       </c>
       <c r="F23" t="n">
-        <v>4.773184</v>
+        <v>3.900038</v>
       </c>
       <c r="G23" t="n">
         <v>98.36065600000001</v>
@@ -1026,7 +1026,7 @@
         <v>-4.289528</v>
       </c>
       <c r="F24" t="n">
-        <v>3.050103</v>
+        <v>3.55166</v>
       </c>
       <c r="G24" t="n">
         <v>98.36065600000001</v>
@@ -1051,7 +1051,7 @@
         <v>-3.289254</v>
       </c>
       <c r="F25" t="n">
-        <v>4.875155</v>
+        <v>6.512551</v>
       </c>
       <c r="G25" t="n">
         <v>98.36065600000001</v>
@@ -1076,7 +1076,7 @@
         <v>9.532845</v>
       </c>
       <c r="F26" t="n">
-        <v>-10.015349</v>
+        <v>-10.086218</v>
       </c>
       <c r="G26" t="n">
         <v>98.36065600000001</v>
@@ -1101,7 +1101,7 @@
         <v>7.576379</v>
       </c>
       <c r="F27" t="n">
-        <v>-10.918779</v>
+        <v>-10.608084</v>
       </c>
       <c r="G27" t="n">
         <v>98.36065600000001</v>
@@ -1126,7 +1126,7 @@
         <v>-3.291627</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.362628</v>
+        <v>0.170648</v>
       </c>
       <c r="G28" t="n">
         <v>98.36065600000001</v>
@@ -1151,7 +1151,7 @@
         <v>0.514981</v>
       </c>
       <c r="F29" t="n">
-        <v>4.197391</v>
+        <v>4.480998</v>
       </c>
       <c r="G29" t="n">
         <v>98.36065600000001</v>
@@ -1160,7 +1160,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_meta</t>
+          <t>bcb_sgs_selic_over</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
@@ -1173,10 +1173,10 @@
         <v>61</v>
       </c>
       <c r="E30" t="n">
-        <v>5.25</v>
+        <v>0.01993</v>
       </c>
       <c r="F30" t="n">
-        <v>14.25</v>
+        <v>0.052531</v>
       </c>
       <c r="G30" t="n">
         <v>100</v>
@@ -1185,7 +1185,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_over</t>
+          <t>bcb_sgs_cdi</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1210,182 +1210,182 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bcb_sgs_cdi</t>
+          <t>bcb_sgs_ipca</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="D32" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E32" t="n">
-        <v>0.01993</v>
+        <v>0.87</v>
       </c>
       <c r="F32" t="n">
-        <v>0.052531</v>
+        <v>0.16</v>
       </c>
       <c r="G32" t="n">
-        <v>100</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca</t>
+          <t>bcb_sgs_igp_m</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D33" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>0.87</v>
+        <v>0.66</v>
       </c>
       <c r="F33" t="n">
-        <v>0.16</v>
+        <v>-1.16</v>
       </c>
       <c r="G33" t="n">
-        <v>96.721311</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m</t>
+          <t>bcb_sgs_ibc_br_sa</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D34" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E34" t="n">
-        <v>0.66</v>
+        <v>97.07568000000001</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.16</v>
+        <v>111.03587</v>
       </c>
       <c r="G34" t="n">
-        <v>98.36065600000001</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc</t>
+          <t>bcb_sgs_ibc_br</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="D35" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E35" t="n">
-        <v>0.88</v>
+        <v>99.32829</v>
       </c>
       <c r="F35" t="n">
-        <v>0.14</v>
+        <v>109.52993</v>
       </c>
       <c r="G35" t="n">
-        <v>96.721311</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br_sa</t>
+          <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>46173</v>
+        <v>46265</v>
       </c>
       <c r="D36" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E36" t="n">
-        <v>97.07568000000001</v>
+        <v>5.1433</v>
       </c>
       <c r="F36" t="n">
-        <v>111.03587</v>
+        <v>5.1154</v>
       </c>
       <c r="G36" t="n">
-        <v>95.08196700000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br</t>
+          <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46173</v>
+        <v>46265</v>
       </c>
       <c r="D37" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E37" t="n">
-        <v>99.32829</v>
+        <v>5.1427</v>
       </c>
       <c r="F37" t="n">
-        <v>109.52993</v>
+        <v>5.1148</v>
       </c>
       <c r="G37" t="n">
-        <v>95.08196700000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_venda_usd</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="D38" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E38" t="n">
-        <v>5.1433</v>
+        <v>4346060</v>
       </c>
       <c r="F38" t="n">
-        <v>5.1053</v>
+        <v>7355800</v>
       </c>
       <c r="G38" t="n">
-        <v>100</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
@@ -1398,10 +1398,10 @@
         <v>59</v>
       </c>
       <c r="E39" t="n">
-        <v>4346060</v>
+        <v>2495054</v>
       </c>
       <c r="F39" t="n">
-        <v>7355800</v>
+        <v>4606799</v>
       </c>
       <c r="G39" t="n">
         <v>96.721311</v>
@@ -1410,7 +1410,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
@@ -1423,10 +1423,10 @@
         <v>59</v>
       </c>
       <c r="E40" t="n">
-        <v>1851006</v>
+        <v>2.37</v>
       </c>
       <c r="F40" t="n">
-        <v>2749001</v>
+        <v>4.68</v>
       </c>
       <c r="G40" t="n">
         <v>96.721311</v>
@@ -1435,7 +1435,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
@@ -1448,10 +1448,10 @@
         <v>59</v>
       </c>
       <c r="E41" t="n">
-        <v>2495054</v>
+        <v>1.56</v>
       </c>
       <c r="F41" t="n">
-        <v>4606799</v>
+        <v>3.19</v>
       </c>
       <c r="G41" t="n">
         <v>96.721311</v>
@@ -1460,7 +1460,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
@@ -1473,10 +1473,10 @@
         <v>59</v>
       </c>
       <c r="E42" t="n">
-        <v>2.37</v>
+        <v>2.96</v>
       </c>
       <c r="F42" t="n">
-        <v>4.68</v>
+        <v>5.57</v>
       </c>
       <c r="G42" t="n">
         <v>96.721311</v>
@@ -1485,7 +1485,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
@@ -1498,10 +1498,10 @@
         <v>59</v>
       </c>
       <c r="E43" t="n">
-        <v>1.56</v>
+        <v>20.92</v>
       </c>
       <c r="F43" t="n">
-        <v>3.19</v>
+        <v>33.44</v>
       </c>
       <c r="G43" t="n">
         <v>96.721311</v>
@@ -1510,157 +1510,157 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D44" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E44" t="n">
-        <v>2.96</v>
+        <v>370395</v>
       </c>
       <c r="F44" t="n">
-        <v>5.57</v>
+        <v>369742</v>
       </c>
       <c r="G44" t="n">
-        <v>96.721311</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="D45" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E45" t="n">
-        <v>20.92</v>
+        <v>-0.119484</v>
       </c>
       <c r="F45" t="n">
-        <v>33.44</v>
+        <v>0.07079299999999999</v>
       </c>
       <c r="G45" t="n">
-        <v>96.721311</v>
+        <v>93.442623</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D46" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E46" t="n">
-        <v>370395</v>
+        <v>-2.094902</v>
       </c>
       <c r="F46" t="n">
-        <v>369742</v>
+        <v>-3.915762</v>
       </c>
       <c r="G46" t="n">
-        <v>98.36065600000001</v>
+        <v>93.442623</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46173</v>
+        <v>46265</v>
       </c>
       <c r="D47" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.119484</v>
+        <v>5.757004</v>
       </c>
       <c r="F47" t="n">
-        <v>0.07079299999999999</v>
+        <v>0.750399</v>
       </c>
       <c r="G47" t="n">
-        <v>93.442623</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>46173</v>
+        <v>46265</v>
       </c>
       <c r="D48" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E48" t="n">
-        <v>-2.094902</v>
+        <v>5.757676</v>
       </c>
       <c r="F48" t="n">
-        <v>-3.915762</v>
+        <v>0.750488</v>
       </c>
       <c r="G48" t="n">
-        <v>93.442623</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="D49" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E49" t="n">
-        <v>5.757004</v>
+        <v>2.185796</v>
       </c>
       <c r="F49" t="n">
-        <v>0.551474</v>
+        <v>0.714468</v>
       </c>
       <c r="G49" t="n">
-        <v>98.36065600000001</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
@@ -1673,10 +1673,10 @@
         <v>58</v>
       </c>
       <c r="E50" t="n">
-        <v>2.185796</v>
+        <v>2.079394</v>
       </c>
       <c r="F50" t="n">
-        <v>0.714468</v>
+        <v>0.242446</v>
       </c>
       <c r="G50" t="n">
         <v>95.08196700000001</v>
@@ -1685,325 +1685,225 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D51" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E51" t="n">
-        <v>2.329166</v>
+        <v>-0.407403</v>
       </c>
       <c r="F51" t="n">
-        <v>1.515494</v>
+        <v>0.5941920000000001</v>
       </c>
       <c r="G51" t="n">
-        <v>95.08196700000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
-        <v>44469</v>
+        <v>44773</v>
       </c>
       <c r="C52" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D52" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="E52" t="n">
-        <v>2.079394</v>
+        <v>10.069235</v>
       </c>
       <c r="F52" t="n">
-        <v>0.242446</v>
+        <v>4.641328</v>
       </c>
       <c r="G52" t="n">
-        <v>95.08196700000001</v>
+        <v>78.688525</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
-        <v>44469</v>
+        <v>44773</v>
       </c>
       <c r="C53" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D53" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.407403</v>
+        <v>10.074751</v>
       </c>
       <c r="F53" t="n">
-        <v>0.5941920000000001</v>
+        <v>2.772183</v>
       </c>
       <c r="G53" t="n">
-        <v>96.721311</v>
+        <v>80.32786900000001</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>44773</v>
+        <v>44469</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="D54" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="E54" t="n">
-        <v>10.069235</v>
+        <v>0.001073</v>
       </c>
       <c r="F54" t="n">
-        <v>4.641328</v>
+        <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>78.688525</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>44773</v>
+        <v>44469</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D55" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E55" t="n">
-        <v>10.074751</v>
+        <v>0.001073</v>
       </c>
       <c r="F55" t="n">
-        <v>2.772183</v>
+        <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>80.32786900000001</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>44773</v>
+        <v>44469</v>
       </c>
       <c r="C56" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D56" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="E56" t="n">
-        <v>10.124804</v>
+        <v>-0.03</v>
       </c>
       <c r="F56" t="n">
-        <v>4.327084</v>
+        <v>-0.06</v>
       </c>
       <c r="G56" t="n">
-        <v>78.688525</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="D57" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>-0.13</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="G57" t="n">
-        <v>98.36065600000001</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="D58" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E58" t="n">
-        <v>0.001073</v>
+        <v>0.05</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="G58" t="n">
-        <v>98.36065600000001</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="D59" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E59" t="n">
-        <v>0.001073</v>
+        <v>0.5</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="G59" t="n">
-        <v>98.36065600000001</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
-        </is>
-      </c>
-      <c r="B60" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="C60" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="D60" t="n">
-        <v>58</v>
-      </c>
-      <c r="E60" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="F60" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="G60" t="n">
-        <v>95.08196700000001</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
-        </is>
-      </c>
-      <c r="B61" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="C61" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="D61" t="n">
-        <v>58</v>
-      </c>
-      <c r="E61" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="F61" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="G61" t="n">
-        <v>95.08196700000001</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
-        </is>
-      </c>
-      <c r="B62" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="C62" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="D62" t="n">
-        <v>58</v>
-      </c>
-      <c r="E62" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F62" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="G62" t="n">
-        <v>95.08196700000001</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
-        </is>
-      </c>
-      <c r="B63" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="C63" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="D63" t="n">
-        <v>58</v>
-      </c>
-      <c r="E63" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F63" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="G63" t="n">
         <v>95.08196700000001</v>
       </c>
     </row>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
         <v>118781</v>
       </c>
       <c r="F2" t="n">
-        <v>177726</v>
+        <v>175546</v>
       </c>
       <c r="G2" t="n">
         <v>100</v>
@@ -501,7 +501,7 @@
         <v>114.080002</v>
       </c>
       <c r="F3" t="n">
-        <v>174.699997</v>
+        <v>172.039993</v>
       </c>
       <c r="G3" t="n">
         <v>100</v>
@@ -526,7 +526,7 @@
         <v>136.330002</v>
       </c>
       <c r="F4" t="n">
-        <v>107.790001</v>
+        <v>105.910004</v>
       </c>
       <c r="G4" t="n">
         <v>100</v>
@@ -551,7 +551,7 @@
         <v>254</v>
       </c>
       <c r="F5" t="n">
-        <v>446.51001</v>
+        <v>443.950012</v>
       </c>
       <c r="G5" t="n">
         <v>100</v>
@@ -576,7 +576,7 @@
         <v>5.1829</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1165</v>
+        <v>5.1014</v>
       </c>
       <c r="G6" t="n">
         <v>100</v>
@@ -601,7 +601,7 @@
         <v>6.1119</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9151</v>
+        <v>5.8811</v>
       </c>
       <c r="G7" t="n">
         <v>100</v>
@@ -626,7 +626,7 @@
         <v>4522.680176</v>
       </c>
       <c r="F8" t="n">
-        <v>7723.549805</v>
+        <v>7709.959961</v>
       </c>
       <c r="G8" t="n">
         <v>100</v>
@@ -651,7 +651,7 @@
         <v>15259.240234</v>
       </c>
       <c r="F9" t="n">
-        <v>26363.439453</v>
+        <v>26348.349609</v>
       </c>
       <c r="G9" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
         <v>35360.730469</v>
       </c>
       <c r="F10" t="n">
-        <v>54349.121094</v>
+        <v>53885.101562</v>
       </c>
       <c r="G10" t="n">
         <v>100</v>
@@ -701,7 +701,7 @@
         <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4312.799805</v>
+        <v>4375.799805</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
@@ -726,7 +726,7 @@
         <v>68.5</v>
       </c>
       <c r="F12" t="n">
-        <v>76.129997</v>
+        <v>76.879997</v>
       </c>
       <c r="G12" t="n">
         <v>100</v>
@@ -751,7 +751,7 @@
         <v>72.989998</v>
       </c>
       <c r="F13" t="n">
-        <v>80.55999799999999</v>
+        <v>81.839996</v>
       </c>
       <c r="G13" t="n">
         <v>100</v>
@@ -776,7 +776,7 @@
         <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1174</v>
+        <v>1182.25</v>
       </c>
       <c r="G14" t="n">
         <v>100</v>
@@ -801,7 +801,7 @@
         <v>534</v>
       </c>
       <c r="F15" t="n">
-        <v>460.5</v>
+        <v>465.25</v>
       </c>
       <c r="G15" t="n">
         <v>100</v>
@@ -826,7 +826,7 @@
         <v>-6.568391</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.153372</v>
+        <v>-1.378098</v>
       </c>
       <c r="G16" t="n">
         <v>98.36065600000001</v>
@@ -851,7 +851,7 @@
         <v>-6.653229</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.18284</v>
+        <v>-1.702669</v>
       </c>
       <c r="G17" t="n">
         <v>98.36065600000001</v>
@@ -876,7 +876,7 @@
         <v>-6.550283</v>
       </c>
       <c r="F18" t="n">
-        <v>0.503497</v>
+        <v>-1.249414</v>
       </c>
       <c r="G18" t="n">
         <v>98.36065600000001</v>
@@ -901,7 +901,7 @@
         <v>0.393701</v>
       </c>
       <c r="F19" t="n">
-        <v>4.229789</v>
+        <v>3.632204</v>
       </c>
       <c r="G19" t="n">
         <v>98.36065600000001</v>
@@ -926,7 +926,7 @@
         <v>4.464682</v>
       </c>
       <c r="F20" t="n">
-        <v>0.756182</v>
+        <v>0.458827</v>
       </c>
       <c r="G20" t="n">
         <v>98.36065600000001</v>
@@ -951,7 +951,7 @@
         <v>2.725834</v>
       </c>
       <c r="F21" t="n">
-        <v>1.148218</v>
+        <v>0.566819</v>
       </c>
       <c r="G21" t="n">
         <v>98.36065600000001</v>
@@ -976,7 +976,7 @@
         <v>-4.756917</v>
       </c>
       <c r="F22" t="n">
-        <v>3.122007</v>
+        <v>2.94056</v>
       </c>
       <c r="G22" t="n">
         <v>98.36065600000001</v>
@@ -1001,7 +1001,7 @@
         <v>-5.312585</v>
       </c>
       <c r="F23" t="n">
-        <v>3.900038</v>
+        <v>3.840568</v>
       </c>
       <c r="G23" t="n">
         <v>98.36065600000001</v>
@@ -1026,7 +1026,7 @@
         <v>-4.289528</v>
       </c>
       <c r="F24" t="n">
-        <v>3.55166</v>
+        <v>2.667561</v>
       </c>
       <c r="G24" t="n">
         <v>98.36065600000001</v>
@@ -1051,7 +1051,7 @@
         <v>-3.289254</v>
       </c>
       <c r="F25" t="n">
-        <v>6.512551</v>
+        <v>8.068452000000001</v>
       </c>
       <c r="G25" t="n">
         <v>98.36065600000001</v>
@@ -1076,7 +1076,7 @@
         <v>9.532845</v>
       </c>
       <c r="F26" t="n">
-        <v>-10.086218</v>
+        <v>-9.200426</v>
       </c>
       <c r="G26" t="n">
         <v>98.36065600000001</v>
@@ -1101,7 +1101,7 @@
         <v>7.576379</v>
       </c>
       <c r="F27" t="n">
-        <v>-10.608084</v>
+        <v>-9.187756</v>
       </c>
       <c r="G27" t="n">
         <v>98.36065600000001</v>
@@ -1126,7 +1126,7 @@
         <v>-3.291627</v>
       </c>
       <c r="F28" t="n">
-        <v>0.170648</v>
+        <v>0.874573</v>
       </c>
       <c r="G28" t="n">
         <v>98.36065600000001</v>
@@ -1151,7 +1151,7 @@
         <v>0.514981</v>
       </c>
       <c r="F29" t="n">
-        <v>4.480998</v>
+        <v>5.558707</v>
       </c>
       <c r="G29" t="n">
         <v>98.36065600000001</v>
@@ -1160,7 +1160,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_over</t>
+          <t>bcb_sgs_selic_meta</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
@@ -1173,10 +1173,10 @@
         <v>61</v>
       </c>
       <c r="E30" t="n">
-        <v>0.01993</v>
+        <v>5.25</v>
       </c>
       <c r="F30" t="n">
-        <v>0.052531</v>
+        <v>14</v>
       </c>
       <c r="G30" t="n">
         <v>100</v>
@@ -1185,7 +1185,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>bcb_sgs_cdi</t>
+          <t>bcb_sgs_selic_over</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1201,7 +1201,7 @@
         <v>0.01993</v>
       </c>
       <c r="F31" t="n">
-        <v>0.052531</v>
+        <v>0.052313</v>
       </c>
       <c r="G31" t="n">
         <v>100</v>
@@ -1210,207 +1210,207 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca</t>
+          <t>bcb_sgs_cdi</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="D32" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E32" t="n">
-        <v>0.87</v>
+        <v>0.01993</v>
       </c>
       <c r="F32" t="n">
-        <v>0.16</v>
+        <v>0.052531</v>
       </c>
       <c r="G32" t="n">
-        <v>96.721311</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m</t>
+          <t>bcb_sgs_ipca</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D33" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E33" t="n">
-        <v>0.66</v>
+        <v>0.87</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.16</v>
+        <v>0.16</v>
       </c>
       <c r="G33" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br_sa</t>
+          <t>bcb_sgs_igp_m</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D34" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E34" t="n">
-        <v>97.07568000000001</v>
+        <v>0.66</v>
       </c>
       <c r="F34" t="n">
-        <v>111.03587</v>
+        <v>-1.16</v>
       </c>
       <c r="G34" t="n">
-        <v>95.08196700000001</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br</t>
+          <t>bcb_sgs_inpc</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D35" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E35" t="n">
-        <v>99.32829</v>
+        <v>0.88</v>
       </c>
       <c r="F35" t="n">
-        <v>109.52993</v>
+        <v>0.14</v>
       </c>
       <c r="G35" t="n">
-        <v>95.08196700000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_venda_usd</t>
+          <t>bcb_sgs_ibc_br_sa</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>46265</v>
+        <v>46173</v>
       </c>
       <c r="D36" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E36" t="n">
-        <v>5.1433</v>
+        <v>97.07568000000001</v>
       </c>
       <c r="F36" t="n">
-        <v>5.1154</v>
+        <v>111.03587</v>
       </c>
       <c r="G36" t="n">
-        <v>100</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_compra_usd</t>
+          <t>bcb_sgs_ibc_br</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46265</v>
+        <v>46173</v>
       </c>
       <c r="D37" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E37" t="n">
-        <v>5.1427</v>
+        <v>99.32829</v>
       </c>
       <c r="F37" t="n">
-        <v>5.1148</v>
+        <v>109.52993</v>
       </c>
       <c r="G37" t="n">
-        <v>100</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="D38" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E38" t="n">
-        <v>4346060</v>
+        <v>5.1433</v>
       </c>
       <c r="F38" t="n">
-        <v>7355800</v>
+        <v>5.1017</v>
       </c>
       <c r="G38" t="n">
-        <v>96.721311</v>
+        <v>100</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="D39" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E39" t="n">
-        <v>2495054</v>
+        <v>5.1427</v>
       </c>
       <c r="F39" t="n">
-        <v>4606799</v>
+        <v>5.1011</v>
       </c>
       <c r="G39" t="n">
-        <v>96.721311</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
@@ -1423,10 +1423,10 @@
         <v>59</v>
       </c>
       <c r="E40" t="n">
-        <v>2.37</v>
+        <v>4346060</v>
       </c>
       <c r="F40" t="n">
-        <v>4.68</v>
+        <v>7355800</v>
       </c>
       <c r="G40" t="n">
         <v>96.721311</v>
@@ -1435,7 +1435,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
@@ -1448,10 +1448,10 @@
         <v>59</v>
       </c>
       <c r="E41" t="n">
-        <v>1.56</v>
+        <v>1851006</v>
       </c>
       <c r="F41" t="n">
-        <v>3.19</v>
+        <v>2749001</v>
       </c>
       <c r="G41" t="n">
         <v>96.721311</v>
@@ -1460,7 +1460,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
@@ -1473,10 +1473,10 @@
         <v>59</v>
       </c>
       <c r="E42" t="n">
-        <v>2.96</v>
+        <v>2495054</v>
       </c>
       <c r="F42" t="n">
-        <v>5.57</v>
+        <v>4606799</v>
       </c>
       <c r="G42" t="n">
         <v>96.721311</v>
@@ -1485,7 +1485,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
@@ -1498,10 +1498,10 @@
         <v>59</v>
       </c>
       <c r="E43" t="n">
-        <v>20.92</v>
+        <v>2.37</v>
       </c>
       <c r="F43" t="n">
-        <v>33.44</v>
+        <v>4.68</v>
       </c>
       <c r="G43" t="n">
         <v>96.721311</v>
@@ -1510,98 +1510,98 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D44" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E44" t="n">
-        <v>370395</v>
+        <v>1.56</v>
       </c>
       <c r="F44" t="n">
-        <v>369742</v>
+        <v>3.19</v>
       </c>
       <c r="G44" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D45" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.119484</v>
+        <v>2.96</v>
       </c>
       <c r="F45" t="n">
-        <v>0.07079299999999999</v>
+        <v>5.57</v>
       </c>
       <c r="G45" t="n">
-        <v>93.442623</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D46" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E46" t="n">
-        <v>-2.094902</v>
+        <v>20.92</v>
       </c>
       <c r="F46" t="n">
-        <v>-3.915762</v>
+        <v>33.44</v>
       </c>
       <c r="G46" t="n">
-        <v>93.442623</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D47" t="n">
         <v>60</v>
       </c>
       <c r="E47" t="n">
-        <v>5.757004</v>
+        <v>370395</v>
       </c>
       <c r="F47" t="n">
-        <v>0.750399</v>
+        <v>369742</v>
       </c>
       <c r="G47" t="n">
         <v>98.36065600000001</v>
@@ -1610,300 +1610,450 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>46265</v>
+        <v>46173</v>
       </c>
       <c r="D48" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E48" t="n">
-        <v>5.757676</v>
+        <v>-0.119484</v>
       </c>
       <c r="F48" t="n">
-        <v>0.750488</v>
+        <v>0.07079299999999999</v>
       </c>
       <c r="G48" t="n">
-        <v>98.36065600000001</v>
+        <v>93.442623</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="D49" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E49" t="n">
-        <v>2.185796</v>
+        <v>-2.094902</v>
       </c>
       <c r="F49" t="n">
-        <v>0.714468</v>
+        <v>-3.915762</v>
       </c>
       <c r="G49" t="n">
-        <v>95.08196700000001</v>
+        <v>93.442623</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="D50" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E50" t="n">
-        <v>2.079394</v>
+        <v>5.757004</v>
       </c>
       <c r="F50" t="n">
-        <v>0.242446</v>
+        <v>0.48057</v>
       </c>
       <c r="G50" t="n">
-        <v>95.08196700000001</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D51" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.407403</v>
+        <v>5.757676</v>
       </c>
       <c r="F51" t="n">
-        <v>0.5941920000000001</v>
+        <v>0.480627</v>
       </c>
       <c r="G51" t="n">
-        <v>96.721311</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
-        <v>44773</v>
+        <v>44469</v>
       </c>
       <c r="C52" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D52" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="E52" t="n">
-        <v>10.069235</v>
+        <v>2.185796</v>
       </c>
       <c r="F52" t="n">
-        <v>4.641328</v>
+        <v>0.714468</v>
       </c>
       <c r="G52" t="n">
-        <v>78.688525</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
-        <v>44773</v>
+        <v>44469</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D53" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E53" t="n">
-        <v>10.074751</v>
+        <v>2.329166</v>
       </c>
       <c r="F53" t="n">
-        <v>2.772183</v>
+        <v>1.515494</v>
       </c>
       <c r="G53" t="n">
-        <v>80.32786900000001</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="D54" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E54" t="n">
-        <v>0.001073</v>
+        <v>2.079394</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>0.242446</v>
       </c>
       <c r="G54" t="n">
-        <v>98.36065600000001</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D55" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E55" t="n">
-        <v>0.001073</v>
+        <v>-0.407403</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>0.5941920000000001</v>
       </c>
       <c r="G55" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>44469</v>
+        <v>44773</v>
       </c>
       <c r="C56" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D56" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.03</v>
+        <v>10.069235</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.06</v>
+        <v>4.641328</v>
       </c>
       <c r="G56" t="n">
-        <v>95.08196700000001</v>
+        <v>78.688525</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>44469</v>
+        <v>44773</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D57" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.13</v>
+        <v>10.074751</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.06</v>
+        <v>2.772183</v>
       </c>
       <c r="G57" t="n">
-        <v>95.08196700000001</v>
+        <v>80.32786900000001</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>44469</v>
+        <v>44773</v>
       </c>
       <c r="C58" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D58" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="E58" t="n">
-        <v>0.05</v>
+        <v>10.124804</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.05</v>
+        <v>4.327084</v>
       </c>
       <c r="G58" t="n">
-        <v>95.08196700000001</v>
+        <v>78.688525</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>bcb_sgs_dif_selic_meta</t>
+        </is>
+      </c>
+      <c r="B59" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="C59" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D59" t="n">
+        <v>60</v>
+      </c>
+      <c r="E59" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="G59" t="n">
+        <v>98.36065600000001</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_selic_over</t>
+        </is>
+      </c>
+      <c r="B60" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="C60" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D60" t="n">
+        <v>60</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.001073</v>
+      </c>
+      <c r="F60" t="n">
+        <v>-0.000218</v>
+      </c>
+      <c r="G60" t="n">
+        <v>98.36065600000001</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_cdi</t>
+        </is>
+      </c>
+      <c r="B61" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="C61" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D61" t="n">
+        <v>60</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.001073</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" t="n">
+        <v>98.36065600000001</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
+        </is>
+      </c>
+      <c r="B62" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="C62" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="D62" t="n">
+        <v>58</v>
+      </c>
+      <c r="E62" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="F62" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="G62" t="n">
+        <v>95.08196700000001</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
+        </is>
+      </c>
+      <c r="B63" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="C63" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="D63" t="n">
+        <v>58</v>
+      </c>
+      <c r="E63" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="F63" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="G63" t="n">
+        <v>95.08196700000001</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
+        </is>
+      </c>
+      <c r="B64" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="C64" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="D64" t="n">
+        <v>58</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F64" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G64" t="n">
+        <v>95.08196700000001</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
           <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
-      <c r="B59" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="C59" s="1" t="n">
+      <c r="B65" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="C65" s="1" t="n">
         <v>46203</v>
       </c>
-      <c r="D59" t="n">
+      <c r="D65" t="n">
         <v>58</v>
       </c>
-      <c r="E59" t="n">
+      <c r="E65" t="n">
         <v>0.5</v>
       </c>
-      <c r="F59" t="n">
+      <c r="F65" t="n">
         <v>0.22</v>
       </c>
-      <c r="G59" t="n">
+      <c r="G65" t="n">
         <v>95.08196700000001</v>
       </c>
     </row>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -476,7 +476,7 @@
         <v>118781</v>
       </c>
       <c r="F2" t="n">
-        <v>175546</v>
+        <v>172513</v>
       </c>
       <c r="G2" t="n">
         <v>100</v>
@@ -501,7 +501,7 @@
         <v>114.080002</v>
       </c>
       <c r="F3" t="n">
-        <v>172.039993</v>
+        <v>169.369995</v>
       </c>
       <c r="G3" t="n">
         <v>100</v>
@@ -526,7 +526,7 @@
         <v>136.330002</v>
       </c>
       <c r="F4" t="n">
-        <v>105.910004</v>
+        <v>104.699997</v>
       </c>
       <c r="G4" t="n">
         <v>100</v>
@@ -551,7 +551,7 @@
         <v>254</v>
       </c>
       <c r="F5" t="n">
-        <v>443.950012</v>
+        <v>444.350006</v>
       </c>
       <c r="G5" t="n">
         <v>100</v>
@@ -576,7 +576,7 @@
         <v>5.1829</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1014</v>
+        <v>5.0842</v>
       </c>
       <c r="G6" t="n">
         <v>100</v>
@@ -601,7 +601,7 @@
         <v>6.1119</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8811</v>
+        <v>5.8734</v>
       </c>
       <c r="G7" t="n">
         <v>100</v>
@@ -626,7 +626,7 @@
         <v>4522.680176</v>
       </c>
       <c r="F8" t="n">
-        <v>7709.959961</v>
+        <v>7757.640137</v>
       </c>
       <c r="G8" t="n">
         <v>100</v>
@@ -651,7 +651,7 @@
         <v>15259.240234</v>
       </c>
       <c r="F9" t="n">
-        <v>26348.349609</v>
+        <v>26690.619141</v>
       </c>
       <c r="G9" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
         <v>35360.730469</v>
       </c>
       <c r="F10" t="n">
-        <v>53885.101562</v>
+        <v>54036.929688</v>
       </c>
       <c r="G10" t="n">
         <v>100</v>
@@ -701,7 +701,7 @@
         <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4375.799805</v>
+        <v>4340.700195</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
@@ -726,7 +726,7 @@
         <v>68.5</v>
       </c>
       <c r="F12" t="n">
-        <v>76.879997</v>
+        <v>78.18000000000001</v>
       </c>
       <c r="G12" t="n">
         <v>100</v>
@@ -751,7 +751,7 @@
         <v>72.989998</v>
       </c>
       <c r="F13" t="n">
-        <v>81.839996</v>
+        <v>83.550003</v>
       </c>
       <c r="G13" t="n">
         <v>100</v>
@@ -776,7 +776,7 @@
         <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1182.25</v>
+        <v>1156.5</v>
       </c>
       <c r="G14" t="n">
         <v>100</v>
@@ -801,7 +801,7 @@
         <v>534</v>
       </c>
       <c r="F15" t="n">
-        <v>465.25</v>
+        <v>439</v>
       </c>
       <c r="G15" t="n">
         <v>100</v>
@@ -826,7 +826,7 @@
         <v>-6.568391</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.378098</v>
+        <v>-3.08204</v>
       </c>
       <c r="G16" t="n">
         <v>98.36065600000001</v>
@@ -851,7 +851,7 @@
         <v>-6.653229</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.702669</v>
+        <v>-3.228208</v>
       </c>
       <c r="G17" t="n">
         <v>98.36065600000001</v>
@@ -876,7 +876,7 @@
         <v>-6.550283</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.249414</v>
+        <v>-2.377625</v>
       </c>
       <c r="G18" t="n">
         <v>98.36065600000001</v>
@@ -901,7 +901,7 @@
         <v>0.393701</v>
       </c>
       <c r="F19" t="n">
-        <v>3.632204</v>
+        <v>3.725575</v>
       </c>
       <c r="G19" t="n">
         <v>98.36065600000001</v>
@@ -926,7 +926,7 @@
         <v>4.464682</v>
       </c>
       <c r="F20" t="n">
-        <v>0.458827</v>
+        <v>0.120118</v>
       </c>
       <c r="G20" t="n">
         <v>98.36065600000001</v>
@@ -951,7 +951,7 @@
         <v>2.725834</v>
       </c>
       <c r="F21" t="n">
-        <v>0.566819</v>
+        <v>0.43515</v>
       </c>
       <c r="G21" t="n">
         <v>98.36065600000001</v>
@@ -976,7 +976,7 @@
         <v>-4.756917</v>
       </c>
       <c r="F22" t="n">
-        <v>2.94056</v>
+        <v>3.577169</v>
       </c>
       <c r="G22" t="n">
         <v>98.36065600000001</v>
@@ -1001,7 +1001,7 @@
         <v>-5.312585</v>
       </c>
       <c r="F23" t="n">
-        <v>3.840568</v>
+        <v>5.189475</v>
       </c>
       <c r="G23" t="n">
         <v>98.36065600000001</v>
@@ -1026,7 +1026,7 @@
         <v>-4.289528</v>
       </c>
       <c r="F24" t="n">
-        <v>2.667561</v>
+        <v>2.95684</v>
       </c>
       <c r="G24" t="n">
         <v>98.36065600000001</v>
@@ -1051,7 +1051,7 @@
         <v>-3.289254</v>
       </c>
       <c r="F25" t="n">
-        <v>8.068452000000001</v>
+        <v>7.201603</v>
       </c>
       <c r="G25" t="n">
         <v>98.36065600000001</v>
@@ -1076,7 +1076,7 @@
         <v>9.532845</v>
       </c>
       <c r="F26" t="n">
-        <v>-9.200426</v>
+        <v>-7.66505</v>
       </c>
       <c r="G26" t="n">
         <v>98.36065600000001</v>
@@ -1101,7 +1101,7 @@
         <v>7.576379</v>
       </c>
       <c r="F27" t="n">
-        <v>-9.187756</v>
+        <v>-7.290279</v>
       </c>
       <c r="G27" t="n">
         <v>98.36065600000001</v>
@@ -1126,7 +1126,7 @@
         <v>-3.291627</v>
       </c>
       <c r="F28" t="n">
-        <v>0.874573</v>
+        <v>-1.322526</v>
       </c>
       <c r="G28" t="n">
         <v>98.36065600000001</v>
@@ -1151,7 +1151,7 @@
         <v>0.514981</v>
       </c>
       <c r="F29" t="n">
-        <v>5.558707</v>
+        <v>-0.39705</v>
       </c>
       <c r="G29" t="n">
         <v>98.36065600000001</v>
@@ -1201,7 +1201,7 @@
         <v>0.01993</v>
       </c>
       <c r="F31" t="n">
-        <v>0.052313</v>
+        <v>0.052183</v>
       </c>
       <c r="G31" t="n">
         <v>100</v>
@@ -1226,7 +1226,7 @@
         <v>0.01993</v>
       </c>
       <c r="F32" t="n">
-        <v>0.052531</v>
+        <v>0.052313</v>
       </c>
       <c r="G32" t="n">
         <v>100</v>
@@ -1376,7 +1376,7 @@
         <v>5.1433</v>
       </c>
       <c r="F38" t="n">
-        <v>5.1017</v>
+        <v>5.0908</v>
       </c>
       <c r="G38" t="n">
         <v>100</v>
@@ -1401,7 +1401,7 @@
         <v>5.1427</v>
       </c>
       <c r="F39" t="n">
-        <v>5.1011</v>
+        <v>5.0902</v>
       </c>
       <c r="G39" t="n">
         <v>100</v>
@@ -1676,7 +1676,7 @@
         <v>5.757004</v>
       </c>
       <c r="F50" t="n">
-        <v>0.48057</v>
+        <v>0.265889</v>
       </c>
       <c r="G50" t="n">
         <v>98.36065600000001</v>
@@ -1701,7 +1701,7 @@
         <v>5.757676</v>
       </c>
       <c r="F51" t="n">
-        <v>0.480627</v>
+        <v>0.265921</v>
       </c>
       <c r="G51" t="n">
         <v>98.36065600000001</v>
@@ -1926,7 +1926,7 @@
         <v>0.001073</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.000218</v>
+        <v>-0.000348</v>
       </c>
       <c r="G60" t="n">
         <v>98.36065600000001</v>
@@ -1951,7 +1951,7 @@
         <v>0.001073</v>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>-0.000218</v>
       </c>
       <c r="G61" t="n">
         <v>98.36065600000001</v>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -701,7 +701,7 @@
         <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4340.700195</v>
+        <v>4399.700195</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
@@ -776,7 +776,7 @@
         <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1156.5</v>
+        <v>1176.25</v>
       </c>
       <c r="G14" t="n">
         <v>100</v>
@@ -801,7 +801,7 @@
         <v>534</v>
       </c>
       <c r="F15" t="n">
-        <v>439</v>
+        <v>461.5</v>
       </c>
       <c r="G15" t="n">
         <v>100</v>
@@ -1051,7 +1051,7 @@
         <v>-3.289254</v>
       </c>
       <c r="F25" t="n">
-        <v>7.201603</v>
+        <v>8.658716</v>
       </c>
       <c r="G25" t="n">
         <v>98.36065600000001</v>
@@ -1126,7 +1126,7 @@
         <v>-3.291627</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.322526</v>
+        <v>0.362628</v>
       </c>
       <c r="G28" t="n">
         <v>98.36065600000001</v>
@@ -1151,7 +1151,7 @@
         <v>0.514981</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.39705</v>
+        <v>4.707884</v>
       </c>
       <c r="G29" t="n">
         <v>98.36065600000001</v>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -576,7 +576,7 @@
         <v>5.1829</v>
       </c>
       <c r="F6" t="n">
-        <v>5.0842</v>
+        <v>5.0848</v>
       </c>
       <c r="G6" t="n">
         <v>100</v>
@@ -601,7 +601,7 @@
         <v>6.1119</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8734</v>
+        <v>5.8753</v>
       </c>
       <c r="G7" t="n">
         <v>100</v>
@@ -701,7 +701,7 @@
         <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4399.700195</v>
+        <v>4395.700195</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
@@ -726,7 +726,7 @@
         <v>68.5</v>
       </c>
       <c r="F12" t="n">
-        <v>78.18000000000001</v>
+        <v>79.5</v>
       </c>
       <c r="G12" t="n">
         <v>100</v>
@@ -751,7 +751,7 @@
         <v>72.989998</v>
       </c>
       <c r="F13" t="n">
-        <v>83.550003</v>
+        <v>84.949997</v>
       </c>
       <c r="G13" t="n">
         <v>100</v>
@@ -776,7 +776,7 @@
         <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1176.25</v>
+        <v>1183.25</v>
       </c>
       <c r="G14" t="n">
         <v>100</v>
@@ -801,7 +801,7 @@
         <v>534</v>
       </c>
       <c r="F15" t="n">
-        <v>461.5</v>
+        <v>463.75</v>
       </c>
       <c r="G15" t="n">
         <v>100</v>
@@ -926,7 +926,7 @@
         <v>4.464682</v>
       </c>
       <c r="F20" t="n">
-        <v>0.120118</v>
+        <v>0.13193</v>
       </c>
       <c r="G20" t="n">
         <v>98.36065600000001</v>
@@ -951,7 +951,7 @@
         <v>2.725834</v>
       </c>
       <c r="F21" t="n">
-        <v>0.43515</v>
+        <v>0.467635</v>
       </c>
       <c r="G21" t="n">
         <v>98.36065600000001</v>
@@ -1051,7 +1051,7 @@
         <v>-3.289254</v>
       </c>
       <c r="F25" t="n">
-        <v>8.658716</v>
+        <v>8.559929</v>
       </c>
       <c r="G25" t="n">
         <v>98.36065600000001</v>
@@ -1076,7 +1076,7 @@
         <v>9.532845</v>
       </c>
       <c r="F26" t="n">
-        <v>-7.66505</v>
+        <v>-6.106057</v>
       </c>
       <c r="G26" t="n">
         <v>98.36065600000001</v>
@@ -1101,7 +1101,7 @@
         <v>7.576379</v>
       </c>
       <c r="F27" t="n">
-        <v>-7.290279</v>
+        <v>-5.736802</v>
       </c>
       <c r="G27" t="n">
         <v>98.36065600000001</v>
@@ -1126,7 +1126,7 @@
         <v>-3.291627</v>
       </c>
       <c r="F28" t="n">
-        <v>0.362628</v>
+        <v>0.959898</v>
       </c>
       <c r="G28" t="n">
         <v>98.36065600000001</v>
@@ -1151,7 +1151,7 @@
         <v>0.514981</v>
       </c>
       <c r="F29" t="n">
-        <v>4.707884</v>
+        <v>5.218378</v>
       </c>
       <c r="G29" t="n">
         <v>98.36065600000001</v>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -476,7 +476,7 @@
         <v>118781</v>
       </c>
       <c r="F2" t="n">
-        <v>172513</v>
+        <v>172180</v>
       </c>
       <c r="G2" t="n">
         <v>100</v>
@@ -501,7 +501,7 @@
         <v>114.080002</v>
       </c>
       <c r="F3" t="n">
-        <v>169.369995</v>
+        <v>169.270004</v>
       </c>
       <c r="G3" t="n">
         <v>100</v>
@@ -526,7 +526,7 @@
         <v>136.330002</v>
       </c>
       <c r="F4" t="n">
-        <v>104.699997</v>
+        <v>103.519997</v>
       </c>
       <c r="G4" t="n">
         <v>100</v>
@@ -551,7 +551,7 @@
         <v>254</v>
       </c>
       <c r="F5" t="n">
-        <v>444.350006</v>
+        <v>446.850006</v>
       </c>
       <c r="G5" t="n">
         <v>100</v>
@@ -576,7 +576,7 @@
         <v>5.1829</v>
       </c>
       <c r="F6" t="n">
-        <v>5.0848</v>
+        <v>5.1133</v>
       </c>
       <c r="G6" t="n">
         <v>100</v>
@@ -601,7 +601,7 @@
         <v>6.1119</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8753</v>
+        <v>5.8987</v>
       </c>
       <c r="G7" t="n">
         <v>100</v>
@@ -626,7 +626,7 @@
         <v>4522.680176</v>
       </c>
       <c r="F8" t="n">
-        <v>7757.640137</v>
+        <v>7753.109863</v>
       </c>
       <c r="G8" t="n">
         <v>100</v>
@@ -651,7 +651,7 @@
         <v>15259.240234</v>
       </c>
       <c r="F9" t="n">
-        <v>26690.619141</v>
+        <v>26605.359375</v>
       </c>
       <c r="G9" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
         <v>35360.730469</v>
       </c>
       <c r="F10" t="n">
-        <v>54036.929688</v>
+        <v>53975.980469</v>
       </c>
       <c r="G10" t="n">
         <v>100</v>
@@ -701,7 +701,7 @@
         <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4395.700195</v>
+        <v>4436.600098</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
@@ -726,7 +726,7 @@
         <v>68.5</v>
       </c>
       <c r="F12" t="n">
-        <v>79.5</v>
+        <v>83.68000000000001</v>
       </c>
       <c r="G12" t="n">
         <v>100</v>
@@ -751,7 +751,7 @@
         <v>72.989998</v>
       </c>
       <c r="F13" t="n">
-        <v>84.949997</v>
+        <v>89.19000200000001</v>
       </c>
       <c r="G13" t="n">
         <v>100</v>
@@ -776,7 +776,7 @@
         <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1183.25</v>
+        <v>1180.75</v>
       </c>
       <c r="G14" t="n">
         <v>100</v>
@@ -826,7 +826,7 @@
         <v>-6.568391</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.08204</v>
+        <v>-3.269119</v>
       </c>
       <c r="G16" t="n">
         <v>98.36065600000001</v>
@@ -851,7 +851,7 @@
         <v>-6.653229</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.228208</v>
+        <v>-3.285339</v>
       </c>
       <c r="G17" t="n">
         <v>98.36065600000001</v>
@@ -876,7 +876,7 @@
         <v>-6.550283</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.377625</v>
+        <v>-3.477859</v>
       </c>
       <c r="G18" t="n">
         <v>98.36065600000001</v>
@@ -901,7 +901,7 @@
         <v>0.393701</v>
       </c>
       <c r="F19" t="n">
-        <v>3.725575</v>
+        <v>4.309155</v>
       </c>
       <c r="G19" t="n">
         <v>98.36065600000001</v>
@@ -926,7 +926,7 @@
         <v>4.464682</v>
       </c>
       <c r="F20" t="n">
-        <v>0.13193</v>
+        <v>0.6931659999999999</v>
       </c>
       <c r="G20" t="n">
         <v>98.36065600000001</v>
@@ -951,7 +951,7 @@
         <v>2.725834</v>
       </c>
       <c r="F21" t="n">
-        <v>0.467635</v>
+        <v>0.867781</v>
       </c>
       <c r="G21" t="n">
         <v>98.36065600000001</v>
@@ -976,7 +976,7 @@
         <v>-4.756917</v>
       </c>
       <c r="F22" t="n">
-        <v>3.577169</v>
+        <v>3.516682</v>
       </c>
       <c r="G22" t="n">
         <v>98.36065600000001</v>
@@ -1001,7 +1001,7 @@
         <v>-5.312585</v>
       </c>
       <c r="F23" t="n">
-        <v>5.189475</v>
+        <v>4.85346</v>
       </c>
       <c r="G23" t="n">
         <v>98.36065600000001</v>
@@ -1026,7 +1026,7 @@
         <v>-4.289528</v>
       </c>
       <c r="F24" t="n">
-        <v>2.95684</v>
+        <v>2.840713</v>
       </c>
       <c r="G24" t="n">
         <v>98.36065600000001</v>
@@ -1051,7 +1051,7 @@
         <v>-3.289254</v>
       </c>
       <c r="F25" t="n">
-        <v>8.559929</v>
+        <v>9.570028000000001</v>
       </c>
       <c r="G25" t="n">
         <v>98.36065600000001</v>
@@ -1076,7 +1076,7 @@
         <v>9.532845</v>
       </c>
       <c r="F26" t="n">
-        <v>-6.106057</v>
+        <v>-1.169243</v>
       </c>
       <c r="G26" t="n">
         <v>98.36065600000001</v>
@@ -1101,7 +1101,7 @@
         <v>7.576379</v>
       </c>
       <c r="F27" t="n">
-        <v>-5.736802</v>
+        <v>-1.031958</v>
       </c>
       <c r="G27" t="n">
         <v>98.36065600000001</v>
@@ -1126,7 +1126,7 @@
         <v>-3.291627</v>
       </c>
       <c r="F28" t="n">
-        <v>0.959898</v>
+        <v>0.746587</v>
       </c>
       <c r="G28" t="n">
         <v>98.36065600000001</v>
@@ -1201,7 +1201,7 @@
         <v>0.01993</v>
       </c>
       <c r="F31" t="n">
-        <v>0.052183</v>
+        <v>0.052095</v>
       </c>
       <c r="G31" t="n">
         <v>100</v>
@@ -1226,7 +1226,7 @@
         <v>0.01993</v>
       </c>
       <c r="F32" t="n">
-        <v>0.052313</v>
+        <v>0.052183</v>
       </c>
       <c r="G32" t="n">
         <v>100</v>
@@ -1376,7 +1376,7 @@
         <v>5.1433</v>
       </c>
       <c r="F38" t="n">
-        <v>5.0908</v>
+        <v>5.0963</v>
       </c>
       <c r="G38" t="n">
         <v>100</v>
@@ -1401,7 +1401,7 @@
         <v>5.1427</v>
       </c>
       <c r="F39" t="n">
-        <v>5.0902</v>
+        <v>5.0957</v>
       </c>
       <c r="G39" t="n">
         <v>100</v>
@@ -1676,7 +1676,7 @@
         <v>5.757004</v>
       </c>
       <c r="F50" t="n">
-        <v>0.265889</v>
+        <v>0.374215</v>
       </c>
       <c r="G50" t="n">
         <v>98.36065600000001</v>
@@ -1701,7 +1701,7 @@
         <v>5.757676</v>
       </c>
       <c r="F51" t="n">
-        <v>0.265921</v>
+        <v>0.374259</v>
       </c>
       <c r="G51" t="n">
         <v>98.36065600000001</v>
@@ -1926,7 +1926,7 @@
         <v>0.001073</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.000348</v>
+        <v>-0.000436</v>
       </c>
       <c r="G60" t="n">
         <v>98.36065600000001</v>
@@ -1951,7 +1951,7 @@
         <v>0.001073</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.000218</v>
+        <v>-0.000348</v>
       </c>
       <c r="G61" t="n">
         <v>98.36065600000001</v>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
         <v>118781</v>
       </c>
       <c r="F2" t="n">
-        <v>172180</v>
+        <v>167875</v>
       </c>
       <c r="G2" t="n">
         <v>100</v>
@@ -576,7 +576,7 @@
         <v>5.1829</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1133</v>
+        <v>5.1716</v>
       </c>
       <c r="G6" t="n">
         <v>100</v>
@@ -601,7 +601,7 @@
         <v>6.1119</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8987</v>
+        <v>5.9654</v>
       </c>
       <c r="G7" t="n">
         <v>100</v>
@@ -626,7 +626,7 @@
         <v>4522.680176</v>
       </c>
       <c r="F8" t="n">
-        <v>7753.109863</v>
+        <v>7728.200195</v>
       </c>
       <c r="G8" t="n">
         <v>100</v>
@@ -651,7 +651,7 @@
         <v>15259.240234</v>
       </c>
       <c r="F9" t="n">
-        <v>26605.359375</v>
+        <v>26445.449219</v>
       </c>
       <c r="G9" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
         <v>35360.730469</v>
       </c>
       <c r="F10" t="n">
-        <v>53975.980469</v>
+        <v>53791.851562</v>
       </c>
       <c r="G10" t="n">
         <v>100</v>
@@ -701,7 +701,7 @@
         <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4436.600098</v>
+        <v>4469</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
@@ -726,7 +726,7 @@
         <v>68.5</v>
       </c>
       <c r="F12" t="n">
-        <v>83.68000000000001</v>
+        <v>83.519997</v>
       </c>
       <c r="G12" t="n">
         <v>100</v>
@@ -751,7 +751,7 @@
         <v>72.989998</v>
       </c>
       <c r="F13" t="n">
-        <v>89.19000200000001</v>
+        <v>89.220001</v>
       </c>
       <c r="G13" t="n">
         <v>100</v>
@@ -776,7 +776,7 @@
         <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1180.75</v>
+        <v>1175.25</v>
       </c>
       <c r="G14" t="n">
         <v>100</v>
@@ -801,7 +801,7 @@
         <v>534</v>
       </c>
       <c r="F15" t="n">
-        <v>463.75</v>
+        <v>465.75</v>
       </c>
       <c r="G15" t="n">
         <v>100</v>
@@ -826,7 +826,7 @@
         <v>-6.568391</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.269119</v>
+        <v>-5.687672</v>
       </c>
       <c r="G16" t="n">
         <v>98.36065600000001</v>
@@ -926,7 +926,7 @@
         <v>4.464682</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6931659999999999</v>
+        <v>1.841233</v>
       </c>
       <c r="G20" t="n">
         <v>98.36065600000001</v>
@@ -951,7 +951,7 @@
         <v>2.725834</v>
       </c>
       <c r="F21" t="n">
-        <v>0.867781</v>
+        <v>2.00835</v>
       </c>
       <c r="G21" t="n">
         <v>98.36065600000001</v>
@@ -976,7 +976,7 @@
         <v>-4.756917</v>
       </c>
       <c r="F22" t="n">
-        <v>3.516682</v>
+        <v>3.184097</v>
       </c>
       <c r="G22" t="n">
         <v>98.36065600000001</v>
@@ -1001,7 +1001,7 @@
         <v>-5.312585</v>
       </c>
       <c r="F23" t="n">
-        <v>4.85346</v>
+        <v>4.223244</v>
       </c>
       <c r="G23" t="n">
         <v>98.36065600000001</v>
@@ -1026,7 +1026,7 @@
         <v>-4.289528</v>
       </c>
       <c r="F24" t="n">
-        <v>2.840713</v>
+        <v>2.489891</v>
       </c>
       <c r="G24" t="n">
         <v>98.36065600000001</v>
@@ -1051,7 +1051,7 @@
         <v>-3.289254</v>
       </c>
       <c r="F25" t="n">
-        <v>9.570028000000001</v>
+        <v>10.370203</v>
       </c>
       <c r="G25" t="n">
         <v>98.36065600000001</v>
@@ -1076,7 +1076,7 @@
         <v>9.532845</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.169243</v>
+        <v>-1.358216</v>
       </c>
       <c r="G26" t="n">
         <v>98.36065600000001</v>
@@ -1101,7 +1101,7 @@
         <v>7.576379</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.031958</v>
+        <v>-0.9986699999999999</v>
       </c>
       <c r="G27" t="n">
         <v>98.36065600000001</v>
@@ -1126,7 +1126,7 @@
         <v>-3.291627</v>
       </c>
       <c r="F28" t="n">
-        <v>0.746587</v>
+        <v>0.277304</v>
       </c>
       <c r="G28" t="n">
         <v>98.36065600000001</v>
@@ -1151,7 +1151,7 @@
         <v>0.514981</v>
       </c>
       <c r="F29" t="n">
-        <v>5.218378</v>
+        <v>5.67215</v>
       </c>
       <c r="G29" t="n">
         <v>98.36065600000001</v>
@@ -1160,7 +1160,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_meta</t>
+          <t>bcb_sgs_selic_over</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
@@ -1173,10 +1173,10 @@
         <v>61</v>
       </c>
       <c r="E30" t="n">
-        <v>5.25</v>
+        <v>0.01993</v>
       </c>
       <c r="F30" t="n">
-        <v>14</v>
+        <v>0.052033</v>
       </c>
       <c r="G30" t="n">
         <v>100</v>
@@ -1185,7 +1185,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_over</t>
+          <t>bcb_sgs_cdi</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1210,57 +1210,57 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bcb_sgs_cdi</t>
+          <t>bcb_sgs_ipca</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D32" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E32" t="n">
-        <v>0.01993</v>
+        <v>0.87</v>
       </c>
       <c r="F32" t="n">
-        <v>0.052183</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G32" t="n">
-        <v>100</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca</t>
+          <t>bcb_sgs_igp_m</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D33" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>0.87</v>
+        <v>0.66</v>
       </c>
       <c r="F33" t="n">
-        <v>0.16</v>
+        <v>-1.16</v>
       </c>
       <c r="G33" t="n">
-        <v>96.721311</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m</t>
+          <t>bcb_sgs_inpc</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1273,10 +1273,10 @@
         <v>60</v>
       </c>
       <c r="E34" t="n">
-        <v>0.66</v>
+        <v>0.88</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.16</v>
+        <v>-0.01</v>
       </c>
       <c r="G34" t="n">
         <v>98.36065600000001</v>
@@ -1285,32 +1285,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc</t>
+          <t>bcb_sgs_ibc_br_sa</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="D35" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E35" t="n">
-        <v>0.88</v>
+        <v>97.07568000000001</v>
       </c>
       <c r="F35" t="n">
-        <v>0.14</v>
+        <v>111.03587</v>
       </c>
       <c r="G35" t="n">
-        <v>96.721311</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br_sa</t>
+          <t>bcb_sgs_ibc_br</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
@@ -1323,10 +1323,10 @@
         <v>58</v>
       </c>
       <c r="E36" t="n">
-        <v>97.07568000000001</v>
+        <v>99.32829</v>
       </c>
       <c r="F36" t="n">
-        <v>111.03587</v>
+        <v>109.52993</v>
       </c>
       <c r="G36" t="n">
         <v>95.08196700000001</v>
@@ -1335,32 +1335,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br</t>
+          <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46173</v>
+        <v>46265</v>
       </c>
       <c r="D37" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E37" t="n">
-        <v>99.32829</v>
+        <v>5.1433</v>
       </c>
       <c r="F37" t="n">
-        <v>109.52993</v>
+        <v>5.1285</v>
       </c>
       <c r="G37" t="n">
-        <v>95.08196700000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_venda_usd</t>
+          <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
@@ -1373,10 +1373,10 @@
         <v>61</v>
       </c>
       <c r="E38" t="n">
-        <v>5.1433</v>
+        <v>5.1427</v>
       </c>
       <c r="F38" t="n">
-        <v>5.0963</v>
+        <v>5.1279</v>
       </c>
       <c r="G38" t="n">
         <v>100</v>
@@ -1385,32 +1385,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_compra_usd</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="D39" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E39" t="n">
-        <v>5.1427</v>
+        <v>4346060</v>
       </c>
       <c r="F39" t="n">
-        <v>5.0957</v>
+        <v>7355800</v>
       </c>
       <c r="G39" t="n">
-        <v>100</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
@@ -1423,10 +1423,10 @@
         <v>59</v>
       </c>
       <c r="E40" t="n">
-        <v>4346060</v>
+        <v>1851006</v>
       </c>
       <c r="F40" t="n">
-        <v>7355800</v>
+        <v>2749001</v>
       </c>
       <c r="G40" t="n">
         <v>96.721311</v>
@@ -1435,7 +1435,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
@@ -1448,10 +1448,10 @@
         <v>59</v>
       </c>
       <c r="E41" t="n">
-        <v>1851006</v>
+        <v>2495054</v>
       </c>
       <c r="F41" t="n">
-        <v>2749001</v>
+        <v>4606799</v>
       </c>
       <c r="G41" t="n">
         <v>96.721311</v>
@@ -1460,7 +1460,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
@@ -1473,10 +1473,10 @@
         <v>59</v>
       </c>
       <c r="E42" t="n">
-        <v>2495054</v>
+        <v>2.37</v>
       </c>
       <c r="F42" t="n">
-        <v>4606799</v>
+        <v>4.68</v>
       </c>
       <c r="G42" t="n">
         <v>96.721311</v>
@@ -1485,7 +1485,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
@@ -1498,10 +1498,10 @@
         <v>59</v>
       </c>
       <c r="E43" t="n">
-        <v>2.37</v>
+        <v>1.56</v>
       </c>
       <c r="F43" t="n">
-        <v>4.68</v>
+        <v>3.19</v>
       </c>
       <c r="G43" t="n">
         <v>96.721311</v>
@@ -1510,7 +1510,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
@@ -1523,10 +1523,10 @@
         <v>59</v>
       </c>
       <c r="E44" t="n">
-        <v>1.56</v>
+        <v>2.96</v>
       </c>
       <c r="F44" t="n">
-        <v>3.19</v>
+        <v>5.57</v>
       </c>
       <c r="G44" t="n">
         <v>96.721311</v>
@@ -1535,7 +1535,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
@@ -1548,10 +1548,10 @@
         <v>59</v>
       </c>
       <c r="E45" t="n">
-        <v>2.96</v>
+        <v>20.92</v>
       </c>
       <c r="F45" t="n">
-        <v>5.57</v>
+        <v>33.44</v>
       </c>
       <c r="G45" t="n">
         <v>96.721311</v>
@@ -1560,57 +1560,57 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D46" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E46" t="n">
-        <v>20.92</v>
+        <v>370395</v>
       </c>
       <c r="F46" t="n">
-        <v>33.44</v>
+        <v>369742</v>
       </c>
       <c r="G46" t="n">
-        <v>96.721311</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="D47" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E47" t="n">
-        <v>370395</v>
+        <v>-0.119484</v>
       </c>
       <c r="F47" t="n">
-        <v>369742</v>
+        <v>0.07079299999999999</v>
       </c>
       <c r="G47" t="n">
-        <v>98.36065600000001</v>
+        <v>93.442623</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
@@ -1623,10 +1623,10 @@
         <v>57</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.119484</v>
+        <v>-2.094902</v>
       </c>
       <c r="F48" t="n">
-        <v>0.07079299999999999</v>
+        <v>-3.915762</v>
       </c>
       <c r="G48" t="n">
         <v>93.442623</v>
@@ -1635,32 +1635,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46173</v>
+        <v>46265</v>
       </c>
       <c r="D49" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E49" t="n">
-        <v>-2.094902</v>
+        <v>5.757004</v>
       </c>
       <c r="F49" t="n">
-        <v>-3.915762</v>
+        <v>1.00841</v>
       </c>
       <c r="G49" t="n">
-        <v>93.442623</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
@@ -1673,10 +1673,10 @@
         <v>60</v>
       </c>
       <c r="E50" t="n">
-        <v>5.757004</v>
+        <v>5.757676</v>
       </c>
       <c r="F50" t="n">
-        <v>0.374215</v>
+        <v>1.008529</v>
       </c>
       <c r="G50" t="n">
         <v>98.36065600000001</v>
@@ -1685,32 +1685,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="D51" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E51" t="n">
-        <v>5.757676</v>
+        <v>2.185796</v>
       </c>
       <c r="F51" t="n">
-        <v>0.374259</v>
+        <v>0.714468</v>
       </c>
       <c r="G51" t="n">
-        <v>98.36065600000001</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
@@ -1723,10 +1723,10 @@
         <v>58</v>
       </c>
       <c r="E52" t="n">
-        <v>2.185796</v>
+        <v>2.329166</v>
       </c>
       <c r="F52" t="n">
-        <v>0.714468</v>
+        <v>1.515494</v>
       </c>
       <c r="G52" t="n">
         <v>95.08196700000001</v>
@@ -1735,7 +1735,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
@@ -1748,10 +1748,10 @@
         <v>58</v>
       </c>
       <c r="E53" t="n">
-        <v>2.329166</v>
+        <v>2.079394</v>
       </c>
       <c r="F53" t="n">
-        <v>1.515494</v>
+        <v>0.242446</v>
       </c>
       <c r="G53" t="n">
         <v>95.08196700000001</v>
@@ -1760,82 +1760,82 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D54" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E54" t="n">
-        <v>2.079394</v>
+        <v>-0.407403</v>
       </c>
       <c r="F54" t="n">
-        <v>0.242446</v>
+        <v>0.5941920000000001</v>
       </c>
       <c r="G54" t="n">
-        <v>95.08196700000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>44469</v>
+        <v>44773</v>
       </c>
       <c r="C55" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D55" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.407403</v>
+        <v>10.069235</v>
       </c>
       <c r="F55" t="n">
-        <v>0.5941920000000001</v>
+        <v>4.443025</v>
       </c>
       <c r="G55" t="n">
-        <v>96.721311</v>
+        <v>80.32786900000001</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
         <v>44773</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D56" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E56" t="n">
-        <v>10.069235</v>
+        <v>10.074751</v>
       </c>
       <c r="F56" t="n">
-        <v>4.641328</v>
+        <v>2.772183</v>
       </c>
       <c r="G56" t="n">
-        <v>78.688525</v>
+        <v>80.32786900000001</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
@@ -1848,10 +1848,10 @@
         <v>49</v>
       </c>
       <c r="E57" t="n">
-        <v>10.074751</v>
+        <v>10.124804</v>
       </c>
       <c r="F57" t="n">
-        <v>2.772183</v>
+        <v>4.098046</v>
       </c>
       <c r="G57" t="n">
         <v>80.32786900000001</v>
@@ -1860,32 +1860,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>44773</v>
+        <v>44469</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="D58" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="E58" t="n">
-        <v>10.124804</v>
+        <v>0.001073</v>
       </c>
       <c r="F58" t="n">
-        <v>4.327084</v>
+        <v>-0.000498</v>
       </c>
       <c r="G58" t="n">
-        <v>78.688525</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
@@ -1898,10 +1898,10 @@
         <v>60</v>
       </c>
       <c r="E59" t="n">
-        <v>1</v>
+        <v>0.001073</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.25</v>
+        <v>-0.000436</v>
       </c>
       <c r="G59" t="n">
         <v>98.36065600000001</v>
@@ -1910,57 +1910,57 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="D60" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E60" t="n">
-        <v>0.001073</v>
+        <v>-0.03</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.000436</v>
+        <v>-0.06</v>
       </c>
       <c r="G60" t="n">
-        <v>98.36065600000001</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="D61" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E61" t="n">
-        <v>0.001073</v>
+        <v>-0.13</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.000348</v>
+        <v>-0.06</v>
       </c>
       <c r="G61" t="n">
-        <v>98.36065600000001</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
@@ -1973,10 +1973,10 @@
         <v>58</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.03</v>
+        <v>0.05</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="G62" t="n">
         <v>95.08196700000001</v>
@@ -1985,7 +1985,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
@@ -1998,62 +1998,12 @@
         <v>58</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.13</v>
+        <v>0.5</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.06</v>
+        <v>0.22</v>
       </c>
       <c r="G63" t="n">
-        <v>95.08196700000001</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
-        </is>
-      </c>
-      <c r="B64" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="C64" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="D64" t="n">
-        <v>58</v>
-      </c>
-      <c r="E64" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F64" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="G64" t="n">
-        <v>95.08196700000001</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
-        </is>
-      </c>
-      <c r="B65" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="C65" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="D65" t="n">
-        <v>58</v>
-      </c>
-      <c r="E65" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F65" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="G65" t="n">
         <v>95.08196700000001</v>
       </c>
     </row>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
         <v>118781</v>
       </c>
       <c r="F2" t="n">
-        <v>167875</v>
+        <v>167491</v>
       </c>
       <c r="G2" t="n">
         <v>100</v>
@@ -501,7 +501,7 @@
         <v>114.080002</v>
       </c>
       <c r="F3" t="n">
-        <v>169.270004</v>
+        <v>165.050003</v>
       </c>
       <c r="G3" t="n">
         <v>100</v>
@@ -526,7 +526,7 @@
         <v>136.330002</v>
       </c>
       <c r="F4" t="n">
-        <v>103.519997</v>
+        <v>101.199997</v>
       </c>
       <c r="G4" t="n">
         <v>100</v>
@@ -551,7 +551,7 @@
         <v>254</v>
       </c>
       <c r="F5" t="n">
-        <v>446.850006</v>
+        <v>450.350006</v>
       </c>
       <c r="G5" t="n">
         <v>100</v>
@@ -576,7 +576,7 @@
         <v>5.1829</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1716</v>
+        <v>5.1612</v>
       </c>
       <c r="G6" t="n">
         <v>100</v>
@@ -601,7 +601,7 @@
         <v>6.1119</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9654</v>
+        <v>5.9514</v>
       </c>
       <c r="G7" t="n">
         <v>100</v>
@@ -626,7 +626,7 @@
         <v>4522.680176</v>
       </c>
       <c r="F8" t="n">
-        <v>7728.200195</v>
+        <v>7748.5</v>
       </c>
       <c r="G8" t="n">
         <v>100</v>
@@ -651,7 +651,7 @@
         <v>15259.240234</v>
       </c>
       <c r="F9" t="n">
-        <v>26445.449219</v>
+        <v>26588.490234</v>
       </c>
       <c r="G9" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
         <v>35360.730469</v>
       </c>
       <c r="F10" t="n">
-        <v>53791.851562</v>
+        <v>53770.269531</v>
       </c>
       <c r="G10" t="n">
         <v>100</v>
@@ -701,7 +701,7 @@
         <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4469</v>
+        <v>4450.399902</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
@@ -726,7 +726,7 @@
         <v>68.5</v>
       </c>
       <c r="F12" t="n">
-        <v>83.519997</v>
+        <v>81.459999</v>
       </c>
       <c r="G12" t="n">
         <v>100</v>
@@ -751,7 +751,7 @@
         <v>72.989998</v>
       </c>
       <c r="F13" t="n">
-        <v>89.220001</v>
+        <v>87.220001</v>
       </c>
       <c r="G13" t="n">
         <v>100</v>
@@ -776,7 +776,7 @@
         <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1175.25</v>
+        <v>1184.5</v>
       </c>
       <c r="G14" t="n">
         <v>100</v>
@@ -801,7 +801,7 @@
         <v>534</v>
       </c>
       <c r="F15" t="n">
-        <v>465.75</v>
+        <v>478.25</v>
       </c>
       <c r="G15" t="n">
         <v>100</v>
@@ -826,7 +826,7 @@
         <v>-6.568391</v>
       </c>
       <c r="F16" t="n">
-        <v>-5.687672</v>
+        <v>-5.903404</v>
       </c>
       <c r="G16" t="n">
         <v>98.36065600000001</v>
@@ -851,7 +851,7 @@
         <v>-6.653229</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.285339</v>
+        <v>-5.696492</v>
       </c>
       <c r="G17" t="n">
         <v>98.36065600000001</v>
@@ -876,7 +876,7 @@
         <v>-6.550283</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.477859</v>
+        <v>-5.641028</v>
       </c>
       <c r="G18" t="n">
         <v>98.36065600000001</v>
@@ -901,7 +901,7 @@
         <v>0.393701</v>
       </c>
       <c r="F19" t="n">
-        <v>4.309155</v>
+        <v>5.126168</v>
       </c>
       <c r="G19" t="n">
         <v>98.36065600000001</v>
@@ -926,7 +926,7 @@
         <v>4.464682</v>
       </c>
       <c r="F20" t="n">
-        <v>1.841233</v>
+        <v>1.636436</v>
       </c>
       <c r="G20" t="n">
         <v>98.36065600000001</v>
@@ -951,7 +951,7 @@
         <v>2.725834</v>
       </c>
       <c r="F21" t="n">
-        <v>2.00835</v>
+        <v>1.768943</v>
       </c>
       <c r="G21" t="n">
         <v>98.36065600000001</v>
@@ -976,7 +976,7 @@
         <v>-4.756917</v>
       </c>
       <c r="F22" t="n">
-        <v>3.184097</v>
+        <v>3.455133</v>
       </c>
       <c r="G22" t="n">
         <v>98.36065600000001</v>
@@ -1001,7 +1001,7 @@
         <v>-5.312585</v>
       </c>
       <c r="F23" t="n">
-        <v>4.223244</v>
+        <v>4.786978</v>
       </c>
       <c r="G23" t="n">
         <v>98.36065600000001</v>
@@ -1026,7 +1026,7 @@
         <v>-4.289528</v>
       </c>
       <c r="F24" t="n">
-        <v>2.489891</v>
+        <v>2.448771</v>
       </c>
       <c r="G24" t="n">
         <v>98.36065600000001</v>
@@ -1051,7 +1051,7 @@
         <v>-3.289254</v>
       </c>
       <c r="F25" t="n">
-        <v>10.370203</v>
+        <v>9.910838999999999</v>
       </c>
       <c r="G25" t="n">
         <v>98.36065600000001</v>
@@ -1076,7 +1076,7 @@
         <v>9.532845</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.358216</v>
+        <v>-3.791188</v>
       </c>
       <c r="G26" t="n">
         <v>98.36065600000001</v>
@@ -1101,7 +1101,7 @@
         <v>7.576379</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.9986699999999999</v>
+        <v>-3.217933</v>
       </c>
       <c r="G27" t="n">
         <v>98.36065600000001</v>
@@ -1126,7 +1126,7 @@
         <v>-3.291627</v>
       </c>
       <c r="F28" t="n">
-        <v>0.277304</v>
+        <v>1.066553</v>
       </c>
       <c r="G28" t="n">
         <v>98.36065600000001</v>
@@ -1151,7 +1151,7 @@
         <v>0.514981</v>
       </c>
       <c r="F29" t="n">
-        <v>5.67215</v>
+        <v>8.508224999999999</v>
       </c>
       <c r="G29" t="n">
         <v>98.36065600000001</v>
@@ -1160,7 +1160,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_over</t>
+          <t>bcb_sgs_selic_meta</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
@@ -1173,10 +1173,10 @@
         <v>61</v>
       </c>
       <c r="E30" t="n">
-        <v>0.01993</v>
+        <v>5.25</v>
       </c>
       <c r="F30" t="n">
-        <v>0.052033</v>
+        <v>14</v>
       </c>
       <c r="G30" t="n">
         <v>100</v>
@@ -1185,7 +1185,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>bcb_sgs_cdi</t>
+          <t>bcb_sgs_selic_over</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1201,7 +1201,7 @@
         <v>0.01993</v>
       </c>
       <c r="F31" t="n">
-        <v>0.052095</v>
+        <v>0.051987</v>
       </c>
       <c r="G31" t="n">
         <v>100</v>
@@ -1351,7 +1351,7 @@
         <v>5.1433</v>
       </c>
       <c r="F37" t="n">
-        <v>5.1285</v>
+        <v>5.1639</v>
       </c>
       <c r="G37" t="n">
         <v>100</v>
@@ -1376,7 +1376,7 @@
         <v>5.1427</v>
       </c>
       <c r="F38" t="n">
-        <v>5.1279</v>
+        <v>5.1632</v>
       </c>
       <c r="G38" t="n">
         <v>100</v>
@@ -1485,98 +1485,98 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D43" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E43" t="n">
-        <v>1.56</v>
+        <v>370395</v>
       </c>
       <c r="F43" t="n">
-        <v>3.19</v>
+        <v>369742</v>
       </c>
       <c r="G43" t="n">
-        <v>96.721311</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="D44" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E44" t="n">
-        <v>2.96</v>
+        <v>-0.119484</v>
       </c>
       <c r="F44" t="n">
-        <v>5.57</v>
+        <v>0.07079299999999999</v>
       </c>
       <c r="G44" t="n">
-        <v>96.721311</v>
+        <v>93.442623</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="D45" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E45" t="n">
-        <v>20.92</v>
+        <v>-2.094902</v>
       </c>
       <c r="F45" t="n">
-        <v>33.44</v>
+        <v>-3.915762</v>
       </c>
       <c r="G45" t="n">
-        <v>96.721311</v>
+        <v>93.442623</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D46" t="n">
         <v>60</v>
       </c>
       <c r="E46" t="n">
-        <v>370395</v>
+        <v>5.757004</v>
       </c>
       <c r="F46" t="n">
-        <v>369742</v>
+        <v>1.705631</v>
       </c>
       <c r="G46" t="n">
         <v>98.36065600000001</v>
@@ -1585,425 +1585,275 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46173</v>
+        <v>46265</v>
       </c>
       <c r="D47" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.119484</v>
+        <v>5.757676</v>
       </c>
       <c r="F47" t="n">
-        <v>0.07079299999999999</v>
+        <v>1.703863</v>
       </c>
       <c r="G47" t="n">
-        <v>93.442623</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D48" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E48" t="n">
-        <v>-2.094902</v>
+        <v>2.185796</v>
       </c>
       <c r="F48" t="n">
-        <v>-3.915762</v>
+        <v>0.714468</v>
       </c>
       <c r="G48" t="n">
-        <v>93.442623</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="D49" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E49" t="n">
-        <v>5.757004</v>
+        <v>2.329166</v>
       </c>
       <c r="F49" t="n">
-        <v>1.00841</v>
+        <v>1.515494</v>
       </c>
       <c r="G49" t="n">
-        <v>98.36065600000001</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="D50" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E50" t="n">
-        <v>5.757676</v>
+        <v>2.079394</v>
       </c>
       <c r="F50" t="n">
-        <v>1.008529</v>
+        <v>0.242446</v>
       </c>
       <c r="G50" t="n">
-        <v>98.36065600000001</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D51" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E51" t="n">
-        <v>2.185796</v>
+        <v>-0.407403</v>
       </c>
       <c r="F51" t="n">
-        <v>0.714468</v>
+        <v>0.5941920000000001</v>
       </c>
       <c r="G51" t="n">
-        <v>95.08196700000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
-        <v>44469</v>
+        <v>44773</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D52" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E52" t="n">
-        <v>2.329166</v>
+        <v>10.069235</v>
       </c>
       <c r="F52" t="n">
-        <v>1.515494</v>
+        <v>4.443025</v>
       </c>
       <c r="G52" t="n">
-        <v>95.08196700000001</v>
+        <v>80.32786900000001</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
-        <v>44469</v>
+        <v>44773</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D53" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E53" t="n">
-        <v>2.079394</v>
+        <v>10.074751</v>
       </c>
       <c r="F53" t="n">
-        <v>0.242446</v>
+        <v>2.772183</v>
       </c>
       <c r="G53" t="n">
-        <v>95.08196700000001</v>
+        <v>80.32786900000001</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>44469</v>
+        <v>44773</v>
       </c>
       <c r="C54" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D54" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.407403</v>
+        <v>10.124804</v>
       </c>
       <c r="F54" t="n">
-        <v>0.5941920000000001</v>
+        <v>4.098046</v>
       </c>
       <c r="G54" t="n">
-        <v>96.721311</v>
+        <v>80.32786900000001</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>44773</v>
+        <v>44469</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D55" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E55" t="n">
-        <v>10.069235</v>
+        <v>1</v>
       </c>
       <c r="F55" t="n">
-        <v>4.443025</v>
+        <v>-0.25</v>
       </c>
       <c r="G55" t="n">
-        <v>80.32786900000001</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>44773</v>
+        <v>44469</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D56" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E56" t="n">
-        <v>10.074751</v>
+        <v>0.001073</v>
       </c>
       <c r="F56" t="n">
-        <v>2.772183</v>
+        <v>-0.000544</v>
       </c>
       <c r="G56" t="n">
-        <v>80.32786900000001</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>44773</v>
+        <v>44469</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D57" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E57" t="n">
-        <v>10.124804</v>
+        <v>-0.03</v>
       </c>
       <c r="F57" t="n">
-        <v>4.098046</v>
+        <v>-0.06</v>
       </c>
       <c r="G57" t="n">
-        <v>80.32786900000001</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>bcb_sgs_dif_selic_over</t>
-        </is>
-      </c>
-      <c r="B58" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="C58" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D58" t="n">
-        <v>60</v>
-      </c>
-      <c r="E58" t="n">
-        <v>0.001073</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-0.000498</v>
-      </c>
-      <c r="G58" t="n">
-        <v>98.36065600000001</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>bcb_sgs_dif_cdi</t>
-        </is>
-      </c>
-      <c r="B59" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="C59" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="D59" t="n">
-        <v>60</v>
-      </c>
-      <c r="E59" t="n">
-        <v>0.001073</v>
-      </c>
-      <c r="F59" t="n">
-        <v>-0.000436</v>
-      </c>
-      <c r="G59" t="n">
-        <v>98.36065600000001</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
-        </is>
-      </c>
-      <c r="B60" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="C60" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="D60" t="n">
-        <v>58</v>
-      </c>
-      <c r="E60" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="F60" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="G60" t="n">
-        <v>95.08196700000001</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
-        </is>
-      </c>
-      <c r="B61" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="C61" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="D61" t="n">
-        <v>58</v>
-      </c>
-      <c r="E61" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="F61" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="G61" t="n">
-        <v>95.08196700000001</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
-        </is>
-      </c>
-      <c r="B62" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="C62" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="D62" t="n">
-        <v>58</v>
-      </c>
-      <c r="E62" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F62" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="G62" t="n">
-        <v>95.08196700000001</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
-        </is>
-      </c>
-      <c r="B63" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="C63" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="D63" t="n">
-        <v>58</v>
-      </c>
-      <c r="E63" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F63" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="G63" t="n">
         <v>95.08196700000001</v>
       </c>
     </row>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
         <v>118781</v>
       </c>
       <c r="F2" t="n">
-        <v>167491</v>
+        <v>167101</v>
       </c>
       <c r="G2" t="n">
         <v>100</v>
@@ -501,7 +501,7 @@
         <v>114.080002</v>
       </c>
       <c r="F3" t="n">
-        <v>165.050003</v>
+        <v>164.669998</v>
       </c>
       <c r="G3" t="n">
         <v>100</v>
@@ -526,7 +526,7 @@
         <v>136.330002</v>
       </c>
       <c r="F4" t="n">
-        <v>101.199997</v>
+        <v>100.769997</v>
       </c>
       <c r="G4" t="n">
         <v>100</v>
@@ -551,7 +551,7 @@
         <v>254</v>
       </c>
       <c r="F5" t="n">
-        <v>450.350006</v>
+        <v>452.440002</v>
       </c>
       <c r="G5" t="n">
         <v>100</v>
@@ -576,7 +576,7 @@
         <v>5.1829</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1612</v>
+        <v>5.189</v>
       </c>
       <c r="G6" t="n">
         <v>100</v>
@@ -601,7 +601,7 @@
         <v>6.1119</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9514</v>
+        <v>5.9962</v>
       </c>
       <c r="G7" t="n">
         <v>100</v>
@@ -626,7 +626,7 @@
         <v>4522.680176</v>
       </c>
       <c r="F8" t="n">
-        <v>7748.5</v>
+        <v>7798.990234</v>
       </c>
       <c r="G8" t="n">
         <v>100</v>
@@ -651,7 +651,7 @@
         <v>15259.240234</v>
       </c>
       <c r="F9" t="n">
-        <v>26588.490234</v>
+        <v>26803.029297</v>
       </c>
       <c r="G9" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
         <v>35360.730469</v>
       </c>
       <c r="F10" t="n">
-        <v>53770.269531</v>
+        <v>53839.988281</v>
       </c>
       <c r="G10" t="n">
         <v>100</v>
@@ -701,7 +701,7 @@
         <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4450.399902</v>
+        <v>4407.899902</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
@@ -726,7 +726,7 @@
         <v>68.5</v>
       </c>
       <c r="F12" t="n">
-        <v>81.459999</v>
+        <v>81.699997</v>
       </c>
       <c r="G12" t="n">
         <v>100</v>
@@ -751,7 +751,7 @@
         <v>72.989998</v>
       </c>
       <c r="F13" t="n">
-        <v>87.220001</v>
+        <v>87.160004</v>
       </c>
       <c r="G13" t="n">
         <v>100</v>
@@ -776,7 +776,7 @@
         <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1184.5</v>
+        <v>1186.5</v>
       </c>
       <c r="G14" t="n">
         <v>100</v>
@@ -801,7 +801,7 @@
         <v>534</v>
       </c>
       <c r="F15" t="n">
-        <v>478.25</v>
+        <v>476</v>
       </c>
       <c r="G15" t="n">
         <v>100</v>
@@ -826,7 +826,7 @@
         <v>-6.568391</v>
       </c>
       <c r="F16" t="n">
-        <v>-5.903404</v>
+        <v>-6.122506</v>
       </c>
       <c r="G16" t="n">
         <v>98.36065600000001</v>
@@ -851,7 +851,7 @@
         <v>-6.653229</v>
       </c>
       <c r="F17" t="n">
-        <v>-5.696492</v>
+        <v>-5.913613</v>
       </c>
       <c r="G17" t="n">
         <v>98.36065600000001</v>
@@ -876,7 +876,7 @@
         <v>-6.550283</v>
       </c>
       <c r="F18" t="n">
-        <v>-5.641028</v>
+        <v>-6.041961</v>
       </c>
       <c r="G18" t="n">
         <v>98.36065600000001</v>
@@ -901,7 +901,7 @@
         <v>0.393701</v>
       </c>
       <c r="F19" t="n">
-        <v>5.126168</v>
+        <v>5.61404</v>
       </c>
       <c r="G19" t="n">
         <v>98.36065600000001</v>
@@ -926,7 +926,7 @@
         <v>4.464682</v>
       </c>
       <c r="F20" t="n">
-        <v>1.636436</v>
+        <v>2.183886</v>
       </c>
       <c r="G20" t="n">
         <v>98.36065600000001</v>
@@ -951,7 +951,7 @@
         <v>2.725834</v>
       </c>
       <c r="F21" t="n">
-        <v>1.768943</v>
+        <v>2.535028</v>
       </c>
       <c r="G21" t="n">
         <v>98.36065600000001</v>
@@ -976,7 +976,7 @@
         <v>-4.756917</v>
       </c>
       <c r="F22" t="n">
-        <v>3.455133</v>
+        <v>4.858542</v>
       </c>
       <c r="G22" t="n">
         <v>98.36065600000001</v>
@@ -1001,7 +1001,7 @@
         <v>-5.312585</v>
       </c>
       <c r="F23" t="n">
-        <v>4.786978</v>
+        <v>5.632491</v>
       </c>
       <c r="G23" t="n">
         <v>98.36065600000001</v>
@@ -1026,7 +1026,7 @@
         <v>-4.289528</v>
       </c>
       <c r="F24" t="n">
-        <v>2.448771</v>
+        <v>3.12582</v>
       </c>
       <c r="G24" t="n">
         <v>98.36065600000001</v>
@@ -1051,7 +1051,7 @@
         <v>-3.289254</v>
       </c>
       <c r="F25" t="n">
-        <v>9.910838999999999</v>
+        <v>8.861223000000001</v>
       </c>
       <c r="G25" t="n">
         <v>98.36065600000001</v>
@@ -1076,7 +1076,7 @@
         <v>9.532845</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.791188</v>
+        <v>-3.507737</v>
       </c>
       <c r="G26" t="n">
         <v>98.36065600000001</v>
@@ -1101,7 +1101,7 @@
         <v>7.576379</v>
       </c>
       <c r="F27" t="n">
-        <v>-3.217933</v>
+        <v>-3.284508</v>
       </c>
       <c r="G27" t="n">
         <v>98.36065600000001</v>
@@ -1126,7 +1126,7 @@
         <v>-3.291627</v>
       </c>
       <c r="F28" t="n">
-        <v>1.066553</v>
+        <v>1.237201</v>
       </c>
       <c r="G28" t="n">
         <v>98.36065600000001</v>
@@ -1151,7 +1151,7 @@
         <v>0.514981</v>
       </c>
       <c r="F29" t="n">
-        <v>8.508224999999999</v>
+        <v>7.997731</v>
       </c>
       <c r="G29" t="n">
         <v>98.36065600000001</v>
@@ -1201,7 +1201,7 @@
         <v>0.01993</v>
       </c>
       <c r="F31" t="n">
-        <v>0.051987</v>
+        <v>0.05195</v>
       </c>
       <c r="G31" t="n">
         <v>100</v>
@@ -1210,32 +1210,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca</t>
+          <t>bcb_sgs_cdi</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D32" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E32" t="n">
-        <v>0.87</v>
+        <v>0.01993</v>
       </c>
       <c r="F32" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.051987</v>
       </c>
       <c r="G32" t="n">
-        <v>98.36065600000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m</t>
+          <t>bcb_sgs_ipca</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
@@ -1248,10 +1248,10 @@
         <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>0.66</v>
+        <v>0.87</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.16</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G33" t="n">
         <v>98.36065600000001</v>
@@ -1260,7 +1260,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc</t>
+          <t>bcb_sgs_igp_m</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1273,10 +1273,10 @@
         <v>60</v>
       </c>
       <c r="E34" t="n">
-        <v>0.88</v>
+        <v>0.66</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.01</v>
+        <v>-1.16</v>
       </c>
       <c r="G34" t="n">
         <v>98.36065600000001</v>
@@ -1285,32 +1285,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br_sa</t>
+          <t>bcb_sgs_inpc</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="D35" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E35" t="n">
-        <v>97.07568000000001</v>
+        <v>0.88</v>
       </c>
       <c r="F35" t="n">
-        <v>111.03587</v>
+        <v>-0.01</v>
       </c>
       <c r="G35" t="n">
-        <v>95.08196700000001</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br</t>
+          <t>bcb_sgs_ibc_br_sa</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
@@ -1323,10 +1323,10 @@
         <v>58</v>
       </c>
       <c r="E36" t="n">
-        <v>99.32829</v>
+        <v>97.07568000000001</v>
       </c>
       <c r="F36" t="n">
-        <v>109.52993</v>
+        <v>111.03587</v>
       </c>
       <c r="G36" t="n">
         <v>95.08196700000001</v>
@@ -1335,32 +1335,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_venda_usd</t>
+          <t>bcb_sgs_ibc_br</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46265</v>
+        <v>46173</v>
       </c>
       <c r="D37" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E37" t="n">
-        <v>5.1433</v>
+        <v>99.32829</v>
       </c>
       <c r="F37" t="n">
-        <v>5.1639</v>
+        <v>109.52993</v>
       </c>
       <c r="G37" t="n">
-        <v>100</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_compra_usd</t>
+          <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
@@ -1373,10 +1373,10 @@
         <v>61</v>
       </c>
       <c r="E38" t="n">
-        <v>5.1427</v>
+        <v>5.1433</v>
       </c>
       <c r="F38" t="n">
-        <v>5.1632</v>
+        <v>5.1859</v>
       </c>
       <c r="G38" t="n">
         <v>100</v>
@@ -1385,32 +1385,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="D39" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E39" t="n">
-        <v>4346060</v>
+        <v>5.1427</v>
       </c>
       <c r="F39" t="n">
-        <v>7355800</v>
+        <v>5.1853</v>
       </c>
       <c r="G39" t="n">
-        <v>96.721311</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
@@ -1423,10 +1423,10 @@
         <v>59</v>
       </c>
       <c r="E40" t="n">
-        <v>1851006</v>
+        <v>4346060</v>
       </c>
       <c r="F40" t="n">
-        <v>2749001</v>
+        <v>7355800</v>
       </c>
       <c r="G40" t="n">
         <v>96.721311</v>
@@ -1435,7 +1435,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
@@ -1448,10 +1448,10 @@
         <v>59</v>
       </c>
       <c r="E41" t="n">
-        <v>2495054</v>
+        <v>1851006</v>
       </c>
       <c r="F41" t="n">
-        <v>4606799</v>
+        <v>2749001</v>
       </c>
       <c r="G41" t="n">
         <v>96.721311</v>
@@ -1460,7 +1460,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
@@ -1473,10 +1473,10 @@
         <v>59</v>
       </c>
       <c r="E42" t="n">
-        <v>2.37</v>
+        <v>2495054</v>
       </c>
       <c r="F42" t="n">
-        <v>4.68</v>
+        <v>4606799</v>
       </c>
       <c r="G42" t="n">
         <v>96.721311</v>
@@ -1485,123 +1485,123 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D43" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E43" t="n">
-        <v>370395</v>
+        <v>2.37</v>
       </c>
       <c r="F43" t="n">
-        <v>369742</v>
+        <v>4.68</v>
       </c>
       <c r="G43" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D44" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.119484</v>
+        <v>1.56</v>
       </c>
       <c r="F44" t="n">
-        <v>0.07079299999999999</v>
+        <v>3.19</v>
       </c>
       <c r="G44" t="n">
-        <v>93.442623</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D45" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E45" t="n">
-        <v>-2.094902</v>
+        <v>2.96</v>
       </c>
       <c r="F45" t="n">
-        <v>-3.915762</v>
+        <v>5.57</v>
       </c>
       <c r="G45" t="n">
-        <v>93.442623</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="D46" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E46" t="n">
-        <v>5.757004</v>
+        <v>20.92</v>
       </c>
       <c r="F46" t="n">
-        <v>1.705631</v>
+        <v>33.44</v>
       </c>
       <c r="G46" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D47" t="n">
         <v>60</v>
       </c>
       <c r="E47" t="n">
-        <v>5.757676</v>
+        <v>370395</v>
       </c>
       <c r="F47" t="n">
-        <v>1.703863</v>
+        <v>369742</v>
       </c>
       <c r="G47" t="n">
         <v>98.36065600000001</v>
@@ -1610,250 +1610,450 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="D48" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E48" t="n">
-        <v>2.185796</v>
+        <v>-0.119484</v>
       </c>
       <c r="F48" t="n">
-        <v>0.714468</v>
+        <v>0.07079299999999999</v>
       </c>
       <c r="G48" t="n">
-        <v>95.08196700000001</v>
+        <v>93.442623</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="D49" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E49" t="n">
-        <v>2.329166</v>
+        <v>-2.094902</v>
       </c>
       <c r="F49" t="n">
-        <v>1.515494</v>
+        <v>-3.915762</v>
       </c>
       <c r="G49" t="n">
-        <v>95.08196700000001</v>
+        <v>93.442623</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="D50" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E50" t="n">
-        <v>2.079394</v>
+        <v>5.757004</v>
       </c>
       <c r="F50" t="n">
-        <v>0.242446</v>
+        <v>2.138932</v>
       </c>
       <c r="G50" t="n">
-        <v>95.08196700000001</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D51" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.407403</v>
+        <v>5.757676</v>
       </c>
       <c r="F51" t="n">
-        <v>0.5941920000000001</v>
+        <v>2.139185</v>
       </c>
       <c r="G51" t="n">
-        <v>96.721311</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
-        <v>44773</v>
+        <v>44469</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D52" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E52" t="n">
-        <v>10.069235</v>
+        <v>2.185796</v>
       </c>
       <c r="F52" t="n">
-        <v>4.443025</v>
+        <v>0.714468</v>
       </c>
       <c r="G52" t="n">
-        <v>80.32786900000001</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
-        <v>44773</v>
+        <v>44469</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D53" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E53" t="n">
-        <v>10.074751</v>
+        <v>2.329166</v>
       </c>
       <c r="F53" t="n">
-        <v>2.772183</v>
+        <v>1.515494</v>
       </c>
       <c r="G53" t="n">
-        <v>80.32786900000001</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>44773</v>
+        <v>44469</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D54" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E54" t="n">
-        <v>10.124804</v>
+        <v>2.079394</v>
       </c>
       <c r="F54" t="n">
-        <v>4.098046</v>
+        <v>0.242446</v>
       </c>
       <c r="G54" t="n">
-        <v>80.32786900000001</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D55" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E55" t="n">
-        <v>1</v>
+        <v>-0.407403</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.25</v>
+        <v>0.5941920000000001</v>
       </c>
       <c r="G55" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>44469</v>
+        <v>44773</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D56" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E56" t="n">
-        <v>0.001073</v>
+        <v>10.069235</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.000544</v>
+        <v>4.443025</v>
       </c>
       <c r="G56" t="n">
-        <v>98.36065600000001</v>
+        <v>80.32786900000001</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>bcb_sgs_igp_m_acum_12m</t>
+        </is>
+      </c>
+      <c r="B57" s="1" t="n">
+        <v>44773</v>
+      </c>
+      <c r="C57" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="D57" t="n">
+        <v>49</v>
+      </c>
+      <c r="E57" t="n">
+        <v>10.074751</v>
+      </c>
+      <c r="F57" t="n">
+        <v>2.772183</v>
+      </c>
+      <c r="G57" t="n">
+        <v>80.32786900000001</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>bcb_sgs_inpc_acum_12m</t>
+        </is>
+      </c>
+      <c r="B58" s="1" t="n">
+        <v>44773</v>
+      </c>
+      <c r="C58" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="D58" t="n">
+        <v>49</v>
+      </c>
+      <c r="E58" t="n">
+        <v>10.124804</v>
+      </c>
+      <c r="F58" t="n">
+        <v>4.098046</v>
+      </c>
+      <c r="G58" t="n">
+        <v>80.32786900000001</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_selic_meta</t>
+        </is>
+      </c>
+      <c r="B59" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="C59" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D59" t="n">
+        <v>60</v>
+      </c>
+      <c r="E59" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="G59" t="n">
+        <v>98.36065600000001</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_selic_over</t>
+        </is>
+      </c>
+      <c r="B60" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="C60" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D60" t="n">
+        <v>60</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.001073</v>
+      </c>
+      <c r="F60" t="n">
+        <v>-0.000581</v>
+      </c>
+      <c r="G60" t="n">
+        <v>98.36065600000001</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_cdi</t>
+        </is>
+      </c>
+      <c r="B61" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="C61" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D61" t="n">
+        <v>60</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.001073</v>
+      </c>
+      <c r="F61" t="n">
+        <v>-0.000544</v>
+      </c>
+      <c r="G61" t="n">
+        <v>98.36065600000001</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
           <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
-      <c r="B57" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="C57" s="1" t="n">
+      <c r="B62" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="C62" s="1" t="n">
         <v>46203</v>
       </c>
-      <c r="D57" t="n">
+      <c r="D62" t="n">
         <v>58</v>
       </c>
-      <c r="E57" t="n">
+      <c r="E62" t="n">
         <v>-0.03</v>
       </c>
-      <c r="F57" t="n">
+      <c r="F62" t="n">
         <v>-0.06</v>
       </c>
-      <c r="G57" t="n">
+      <c r="G62" t="n">
+        <v>95.08196700000001</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
+        </is>
+      </c>
+      <c r="B63" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="C63" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="D63" t="n">
+        <v>58</v>
+      </c>
+      <c r="E63" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="F63" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="G63" t="n">
+        <v>95.08196700000001</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
+        </is>
+      </c>
+      <c r="B64" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="C64" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="D64" t="n">
+        <v>58</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F64" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G64" t="n">
+        <v>95.08196700000001</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_juros_credito_total</t>
+        </is>
+      </c>
+      <c r="B65" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="C65" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="D65" t="n">
+        <v>58</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="G65" t="n">
         <v>95.08196700000001</v>
       </c>
     </row>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -476,7 +476,7 @@
         <v>118781</v>
       </c>
       <c r="F2" t="n">
-        <v>167101</v>
+        <v>166934</v>
       </c>
       <c r="G2" t="n">
         <v>100</v>
@@ -501,7 +501,7 @@
         <v>114.080002</v>
       </c>
       <c r="F3" t="n">
-        <v>164.669998</v>
+        <v>164.149994</v>
       </c>
       <c r="G3" t="n">
         <v>100</v>
@@ -526,7 +526,7 @@
         <v>136.330002</v>
       </c>
       <c r="F4" t="n">
-        <v>100.769997</v>
+        <v>100.970001</v>
       </c>
       <c r="G4" t="n">
         <v>100</v>
@@ -551,7 +551,7 @@
         <v>254</v>
       </c>
       <c r="F5" t="n">
-        <v>452.440002</v>
+        <v>457</v>
       </c>
       <c r="G5" t="n">
         <v>100</v>
@@ -576,7 +576,7 @@
         <v>5.1829</v>
       </c>
       <c r="F6" t="n">
-        <v>5.189</v>
+        <v>5.2132</v>
       </c>
       <c r="G6" t="n">
         <v>100</v>
@@ -601,7 +601,7 @@
         <v>6.1119</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9962</v>
+        <v>6.0459</v>
       </c>
       <c r="G7" t="n">
         <v>100</v>
@@ -626,7 +626,7 @@
         <v>4522.680176</v>
       </c>
       <c r="F8" t="n">
-        <v>7798.990234</v>
+        <v>7785.759766</v>
       </c>
       <c r="G8" t="n">
         <v>100</v>
@@ -651,7 +651,7 @@
         <v>15259.240234</v>
       </c>
       <c r="F9" t="n">
-        <v>26803.029297</v>
+        <v>26729.160156</v>
       </c>
       <c r="G9" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
         <v>35360.730469</v>
       </c>
       <c r="F10" t="n">
-        <v>53839.988281</v>
+        <v>53732.410156</v>
       </c>
       <c r="G10" t="n">
         <v>100</v>
@@ -701,7 +701,7 @@
         <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4407.899902</v>
+        <v>4380.399902</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
@@ -726,7 +726,7 @@
         <v>68.5</v>
       </c>
       <c r="F12" t="n">
-        <v>81.699997</v>
+        <v>82.400002</v>
       </c>
       <c r="G12" t="n">
         <v>100</v>
@@ -751,7 +751,7 @@
         <v>72.989998</v>
       </c>
       <c r="F13" t="n">
-        <v>87.160004</v>
+        <v>88.519997</v>
       </c>
       <c r="G13" t="n">
         <v>100</v>
@@ -776,7 +776,7 @@
         <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1186.5</v>
+        <v>1173.75</v>
       </c>
       <c r="G14" t="n">
         <v>100</v>
@@ -801,7 +801,7 @@
         <v>534</v>
       </c>
       <c r="F15" t="n">
-        <v>476</v>
+        <v>459</v>
       </c>
       <c r="G15" t="n">
         <v>100</v>
@@ -826,7 +826,7 @@
         <v>-6.568391</v>
       </c>
       <c r="F16" t="n">
-        <v>-6.122506</v>
+        <v>-5.771651</v>
       </c>
       <c r="G16" t="n">
         <v>98.36065600000001</v>
@@ -851,7 +851,7 @@
         <v>-6.653229</v>
       </c>
       <c r="F17" t="n">
-        <v>-5.913613</v>
+        <v>-6.210725</v>
       </c>
       <c r="G17" t="n">
         <v>98.36065600000001</v>
@@ -876,7 +876,7 @@
         <v>-6.550283</v>
       </c>
       <c r="F18" t="n">
-        <v>-6.041961</v>
+        <v>-5.855477</v>
       </c>
       <c r="G18" t="n">
         <v>98.36065600000001</v>
@@ -901,7 +901,7 @@
         <v>0.393701</v>
       </c>
       <c r="F19" t="n">
-        <v>5.61404</v>
+        <v>6.67849</v>
       </c>
       <c r="G19" t="n">
         <v>98.36065600000001</v>
@@ -926,7 +926,7 @@
         <v>4.464682</v>
       </c>
       <c r="F20" t="n">
-        <v>2.183886</v>
+        <v>2.660442</v>
       </c>
       <c r="G20" t="n">
         <v>98.36065600000001</v>
@@ -951,7 +951,7 @@
         <v>2.725834</v>
       </c>
       <c r="F21" t="n">
-        <v>2.535028</v>
+        <v>3.384894</v>
       </c>
       <c r="G21" t="n">
         <v>98.36065600000001</v>
@@ -976,7 +976,7 @@
         <v>-4.756917</v>
       </c>
       <c r="F22" t="n">
-        <v>4.858542</v>
+        <v>4.680656</v>
       </c>
       <c r="G22" t="n">
         <v>98.36065600000001</v>
@@ -1001,7 +1001,7 @@
         <v>-5.312585</v>
       </c>
       <c r="F23" t="n">
-        <v>5.632491</v>
+        <v>6.39666</v>
       </c>
       <c r="G23" t="n">
         <v>98.36065600000001</v>
@@ -1026,7 +1026,7 @@
         <v>-4.289528</v>
       </c>
       <c r="F24" t="n">
-        <v>3.12582</v>
+        <v>2.919763</v>
       </c>
       <c r="G24" t="n">
         <v>98.36065600000001</v>
@@ -1051,7 +1051,7 @@
         <v>-3.289254</v>
       </c>
       <c r="F25" t="n">
-        <v>8.861223000000001</v>
+        <v>8.18206</v>
       </c>
       <c r="G25" t="n">
         <v>98.36065600000001</v>
@@ -1076,7 +1076,7 @@
         <v>9.532845</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.507737</v>
+        <v>-2.680993</v>
       </c>
       <c r="G26" t="n">
         <v>98.36065600000001</v>
@@ -1101,7 +1101,7 @@
         <v>7.576379</v>
       </c>
       <c r="F27" t="n">
-        <v>-3.284508</v>
+        <v>-1.775417</v>
       </c>
       <c r="G27" t="n">
         <v>98.36065600000001</v>
@@ -1126,7 +1126,7 @@
         <v>-3.291627</v>
       </c>
       <c r="F28" t="n">
-        <v>1.237201</v>
+        <v>0.149317</v>
       </c>
       <c r="G28" t="n">
         <v>98.36065600000001</v>
@@ -1151,7 +1151,7 @@
         <v>0.514981</v>
       </c>
       <c r="F29" t="n">
-        <v>7.997731</v>
+        <v>4.140669</v>
       </c>
       <c r="G29" t="n">
         <v>98.36065600000001</v>
@@ -1201,7 +1201,7 @@
         <v>0.01993</v>
       </c>
       <c r="F31" t="n">
-        <v>0.05195</v>
+        <v>0.051921</v>
       </c>
       <c r="G31" t="n">
         <v>100</v>
@@ -1226,7 +1226,7 @@
         <v>0.01993</v>
       </c>
       <c r="F32" t="n">
-        <v>0.051987</v>
+        <v>0.05195</v>
       </c>
       <c r="G32" t="n">
         <v>100</v>
@@ -1376,7 +1376,7 @@
         <v>5.1433</v>
       </c>
       <c r="F38" t="n">
-        <v>5.1859</v>
+        <v>5.2236</v>
       </c>
       <c r="G38" t="n">
         <v>100</v>
@@ -1401,7 +1401,7 @@
         <v>5.1427</v>
       </c>
       <c r="F39" t="n">
-        <v>5.1853</v>
+        <v>5.223</v>
       </c>
       <c r="G39" t="n">
         <v>100</v>
@@ -1676,7 +1676,7 @@
         <v>5.757004</v>
       </c>
       <c r="F50" t="n">
-        <v>2.138932</v>
+        <v>2.881453</v>
       </c>
       <c r="G50" t="n">
         <v>98.36065600000001</v>
@@ -1701,7 +1701,7 @@
         <v>5.757676</v>
       </c>
       <c r="F51" t="n">
-        <v>2.139185</v>
+        <v>2.881793</v>
       </c>
       <c r="G51" t="n">
         <v>98.36065600000001</v>
@@ -1926,7 +1926,7 @@
         <v>0.001073</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.000581</v>
+        <v>-0.00061</v>
       </c>
       <c r="G60" t="n">
         <v>98.36065600000001</v>
@@ -1951,7 +1951,7 @@
         <v>0.001073</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.000544</v>
+        <v>-0.000581</v>
       </c>
       <c r="G61" t="n">
         <v>98.36065600000001</v>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -501,7 +501,7 @@
         <v>114.080002</v>
       </c>
       <c r="F3" t="n">
-        <v>164.149994</v>
+        <v>163.899994</v>
       </c>
       <c r="G3" t="n">
         <v>100</v>
@@ -526,7 +526,7 @@
         <v>136.330002</v>
       </c>
       <c r="F4" t="n">
-        <v>100.970001</v>
+        <v>100.120003</v>
       </c>
       <c r="G4" t="n">
         <v>100</v>
@@ -551,7 +551,7 @@
         <v>254</v>
       </c>
       <c r="F5" t="n">
-        <v>457</v>
+        <v>458.100006</v>
       </c>
       <c r="G5" t="n">
         <v>100</v>
@@ -701,7 +701,7 @@
         <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4380.399902</v>
+        <v>4437.299805</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
@@ -776,7 +776,7 @@
         <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1173.75</v>
+        <v>1192.5</v>
       </c>
       <c r="G14" t="n">
         <v>100</v>
@@ -801,7 +801,7 @@
         <v>534</v>
       </c>
       <c r="F15" t="n">
-        <v>459</v>
+        <v>483.25</v>
       </c>
       <c r="G15" t="n">
         <v>100</v>
@@ -826,7 +826,7 @@
         <v>-6.568391</v>
       </c>
       <c r="F16" t="n">
-        <v>-5.771651</v>
+        <v>-6.216327</v>
       </c>
       <c r="G16" t="n">
         <v>98.36065600000001</v>
@@ -851,7 +851,7 @@
         <v>-6.653229</v>
       </c>
       <c r="F17" t="n">
-        <v>-6.210725</v>
+        <v>-6.353565</v>
       </c>
       <c r="G17" t="n">
         <v>98.36065600000001</v>
@@ -876,7 +876,7 @@
         <v>-6.550283</v>
       </c>
       <c r="F18" t="n">
-        <v>-5.855477</v>
+        <v>-6.648016</v>
       </c>
       <c r="G18" t="n">
         <v>98.36065600000001</v>
@@ -901,7 +901,7 @@
         <v>0.393701</v>
       </c>
       <c r="F19" t="n">
-        <v>6.67849</v>
+        <v>6.935267</v>
       </c>
       <c r="G19" t="n">
         <v>98.36065600000001</v>
@@ -976,7 +976,7 @@
         <v>-4.756917</v>
       </c>
       <c r="F22" t="n">
-        <v>4.680656</v>
+        <v>3.952612</v>
       </c>
       <c r="G22" t="n">
         <v>98.36065600000001</v>
@@ -1001,7 +1001,7 @@
         <v>-5.312585</v>
       </c>
       <c r="F23" t="n">
-        <v>6.39666</v>
+        <v>5.341367</v>
       </c>
       <c r="G23" t="n">
         <v>98.36065600000001</v>
@@ -1026,7 +1026,7 @@
         <v>-4.289528</v>
       </c>
       <c r="F24" t="n">
-        <v>2.919763</v>
+        <v>2.376637</v>
       </c>
       <c r="G24" t="n">
         <v>98.36065600000001</v>
@@ -1051,7 +1051,7 @@
         <v>-3.289254</v>
       </c>
       <c r="F25" t="n">
-        <v>8.18206</v>
+        <v>9.587308</v>
       </c>
       <c r="G25" t="n">
         <v>98.36065600000001</v>
@@ -1126,7 +1126,7 @@
         <v>-3.291627</v>
       </c>
       <c r="F28" t="n">
-        <v>0.149317</v>
+        <v>1.749147</v>
       </c>
       <c r="G28" t="n">
         <v>98.36065600000001</v>
@@ -1151,7 +1151,7 @@
         <v>0.514981</v>
       </c>
       <c r="F29" t="n">
-        <v>4.140669</v>
+        <v>9.642655</v>
       </c>
       <c r="G29" t="n">
         <v>98.36065600000001</v>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -576,7 +576,7 @@
         <v>5.1829</v>
       </c>
       <c r="F6" t="n">
-        <v>5.2132</v>
+        <v>5.2265</v>
       </c>
       <c r="G6" t="n">
         <v>100</v>
@@ -601,7 +601,7 @@
         <v>6.1119</v>
       </c>
       <c r="F7" t="n">
-        <v>6.0459</v>
+        <v>6.0614</v>
       </c>
       <c r="G7" t="n">
         <v>100</v>
@@ -701,7 +701,7 @@
         <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4437.299805</v>
+        <v>4452.100098</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
@@ -726,7 +726,7 @@
         <v>68.5</v>
       </c>
       <c r="F12" t="n">
-        <v>82.400002</v>
+        <v>83.050003</v>
       </c>
       <c r="G12" t="n">
         <v>100</v>
@@ -751,7 +751,7 @@
         <v>72.989998</v>
       </c>
       <c r="F13" t="n">
-        <v>88.519997</v>
+        <v>89.480003</v>
       </c>
       <c r="G13" t="n">
         <v>100</v>
@@ -776,7 +776,7 @@
         <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1192.5</v>
+        <v>1198.75</v>
       </c>
       <c r="G14" t="n">
         <v>100</v>
@@ -801,7 +801,7 @@
         <v>534</v>
       </c>
       <c r="F15" t="n">
-        <v>483.25</v>
+        <v>486</v>
       </c>
       <c r="G15" t="n">
         <v>100</v>
@@ -926,7 +926,7 @@
         <v>4.464682</v>
       </c>
       <c r="F20" t="n">
-        <v>2.660442</v>
+        <v>2.922349</v>
       </c>
       <c r="G20" t="n">
         <v>98.36065600000001</v>
@@ -951,7 +951,7 @@
         <v>2.725834</v>
       </c>
       <c r="F21" t="n">
-        <v>3.384894</v>
+        <v>3.649946</v>
       </c>
       <c r="G21" t="n">
         <v>98.36065600000001</v>
@@ -1051,7 +1051,7 @@
         <v>-3.289254</v>
       </c>
       <c r="F25" t="n">
-        <v>9.587308</v>
+        <v>9.952828999999999</v>
       </c>
       <c r="G25" t="n">
         <v>98.36065600000001</v>
@@ -1076,7 +1076,7 @@
         <v>9.532845</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.680993</v>
+        <v>-1.913305</v>
       </c>
       <c r="G26" t="n">
         <v>98.36065600000001</v>
@@ -1101,7 +1101,7 @@
         <v>7.576379</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.775417</v>
+        <v>-0.710164</v>
       </c>
       <c r="G27" t="n">
         <v>98.36065600000001</v>
@@ -1126,7 +1126,7 @@
         <v>-3.291627</v>
       </c>
       <c r="F28" t="n">
-        <v>1.749147</v>
+        <v>2.282423</v>
       </c>
       <c r="G28" t="n">
         <v>98.36065600000001</v>
@@ -1151,7 +1151,7 @@
         <v>0.514981</v>
       </c>
       <c r="F29" t="n">
-        <v>9.642655</v>
+        <v>10.266591</v>
       </c>
       <c r="G29" t="n">
         <v>98.36065600000001</v>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -576,7 +576,7 @@
         <v>5.1829</v>
       </c>
       <c r="F6" t="n">
-        <v>5.2265</v>
+        <v>5.2</v>
       </c>
       <c r="G6" t="n">
         <v>100</v>
@@ -601,7 +601,7 @@
         <v>6.1119</v>
       </c>
       <c r="F7" t="n">
-        <v>6.0614</v>
+        <v>6.0196</v>
       </c>
       <c r="G7" t="n">
         <v>100</v>
@@ -701,7 +701,7 @@
         <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4452.100098</v>
+        <v>4451.399902</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
@@ -726,7 +726,7 @@
         <v>68.5</v>
       </c>
       <c r="F12" t="n">
-        <v>83.050003</v>
+        <v>84.370003</v>
       </c>
       <c r="G12" t="n">
         <v>100</v>
@@ -751,7 +751,7 @@
         <v>72.989998</v>
       </c>
       <c r="F13" t="n">
-        <v>89.480003</v>
+        <v>91.129997</v>
       </c>
       <c r="G13" t="n">
         <v>100</v>
@@ -776,7 +776,7 @@
         <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1198.75</v>
+        <v>1225</v>
       </c>
       <c r="G14" t="n">
         <v>100</v>
@@ -801,7 +801,7 @@
         <v>534</v>
       </c>
       <c r="F15" t="n">
-        <v>486</v>
+        <v>492.75</v>
       </c>
       <c r="G15" t="n">
         <v>100</v>
@@ -826,7 +826,7 @@
         <v>-6.568391</v>
       </c>
       <c r="F16" t="n">
-        <v>-6.216327</v>
+        <v>-5.771651</v>
       </c>
       <c r="G16" t="n">
         <v>98.36065600000001</v>
@@ -926,7 +926,7 @@
         <v>4.464682</v>
       </c>
       <c r="F20" t="n">
-        <v>2.922349</v>
+        <v>2.400496</v>
       </c>
       <c r="G20" t="n">
         <v>98.36065600000001</v>
@@ -951,7 +951,7 @@
         <v>2.725834</v>
       </c>
       <c r="F21" t="n">
-        <v>3.649946</v>
+        <v>2.935165</v>
       </c>
       <c r="G21" t="n">
         <v>98.36065600000001</v>
@@ -976,7 +976,7 @@
         <v>-4.756917</v>
       </c>
       <c r="F22" t="n">
-        <v>3.952612</v>
+        <v>4.680656</v>
       </c>
       <c r="G22" t="n">
         <v>98.36065600000001</v>
@@ -1001,7 +1001,7 @@
         <v>-5.312585</v>
       </c>
       <c r="F23" t="n">
-        <v>5.341367</v>
+        <v>6.39666</v>
       </c>
       <c r="G23" t="n">
         <v>98.36065600000001</v>
@@ -1051,7 +1051,7 @@
         <v>-3.289254</v>
       </c>
       <c r="F25" t="n">
-        <v>9.952828999999999</v>
+        <v>9.935536000000001</v>
       </c>
       <c r="G25" t="n">
         <v>98.36065600000001</v>
@@ -1076,7 +1076,7 @@
         <v>9.532845</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.913305</v>
+        <v>-0.354311</v>
       </c>
       <c r="G26" t="n">
         <v>98.36065600000001</v>
@@ -1101,7 +1101,7 @@
         <v>7.576379</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.710164</v>
+        <v>1.120722</v>
       </c>
       <c r="G27" t="n">
         <v>98.36065600000001</v>
@@ -1126,7 +1126,7 @@
         <v>-3.291627</v>
       </c>
       <c r="F28" t="n">
-        <v>2.282423</v>
+        <v>4.522184</v>
       </c>
       <c r="G28" t="n">
         <v>98.36065600000001</v>
@@ -1151,7 +1151,7 @@
         <v>0.514981</v>
       </c>
       <c r="F29" t="n">
-        <v>10.266591</v>
+        <v>11.798071</v>
       </c>
       <c r="G29" t="n">
         <v>98.36065600000001</v>
@@ -1201,7 +1201,7 @@
         <v>0.01993</v>
       </c>
       <c r="F31" t="n">
-        <v>0.051921</v>
+        <v>0.051898</v>
       </c>
       <c r="G31" t="n">
         <v>100</v>
@@ -1226,7 +1226,7 @@
         <v>0.01993</v>
       </c>
       <c r="F32" t="n">
-        <v>0.05195</v>
+        <v>0.051921</v>
       </c>
       <c r="G32" t="n">
         <v>100</v>
@@ -1317,19 +1317,19 @@
         <v>44439</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D36" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E36" t="n">
-        <v>97.07568000000001</v>
+        <v>97.01608</v>
       </c>
       <c r="F36" t="n">
-        <v>111.03587</v>
+        <v>110.22154</v>
       </c>
       <c r="G36" t="n">
-        <v>95.08196700000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="37">
@@ -1342,19 +1342,19 @@
         <v>44439</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D37" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E37" t="n">
-        <v>99.32829</v>
+        <v>99.19190999999999</v>
       </c>
       <c r="F37" t="n">
-        <v>109.52993</v>
+        <v>109.89427</v>
       </c>
       <c r="G37" t="n">
-        <v>95.08196700000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="38">
@@ -1376,7 +1376,7 @@
         <v>5.1433</v>
       </c>
       <c r="F38" t="n">
-        <v>5.2236</v>
+        <v>5.2014</v>
       </c>
       <c r="G38" t="n">
         <v>100</v>
@@ -1401,7 +1401,7 @@
         <v>5.1427</v>
       </c>
       <c r="F39" t="n">
-        <v>5.223</v>
+        <v>5.2008</v>
       </c>
       <c r="G39" t="n">
         <v>100</v>
@@ -1617,19 +1617,19 @@
         <v>44469</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D48" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.119484</v>
+        <v>-0.064886</v>
       </c>
       <c r="F48" t="n">
-        <v>0.07079299999999999</v>
+        <v>-0.6395690000000001</v>
       </c>
       <c r="G48" t="n">
-        <v>93.442623</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="49">
@@ -1642,19 +1642,19 @@
         <v>44469</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="D49" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E49" t="n">
-        <v>-2.094902</v>
+        <v>-2.103216</v>
       </c>
       <c r="F49" t="n">
-        <v>-3.915762</v>
+        <v>0.332557</v>
       </c>
       <c r="G49" t="n">
-        <v>93.442623</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="50">
@@ -1676,7 +1676,7 @@
         <v>5.757004</v>
       </c>
       <c r="F50" t="n">
-        <v>2.881453</v>
+        <v>2.444212</v>
       </c>
       <c r="G50" t="n">
         <v>98.36065600000001</v>
@@ -1701,7 +1701,7 @@
         <v>5.757676</v>
       </c>
       <c r="F51" t="n">
-        <v>2.881793</v>
+        <v>2.444501</v>
       </c>
       <c r="G51" t="n">
         <v>98.36065600000001</v>
@@ -1926,7 +1926,7 @@
         <v>0.001073</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.00061</v>
+        <v>-0.000633</v>
       </c>
       <c r="G60" t="n">
         <v>98.36065600000001</v>
@@ -1951,7 +1951,7 @@
         <v>0.001073</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.000581</v>
+        <v>-0.00061</v>
       </c>
       <c r="G61" t="n">
         <v>98.36065600000001</v>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -476,7 +476,7 @@
         <v>118781</v>
       </c>
       <c r="F2" t="n">
-        <v>166934</v>
+        <v>166335</v>
       </c>
       <c r="G2" t="n">
         <v>100</v>
@@ -501,7 +501,7 @@
         <v>114.080002</v>
       </c>
       <c r="F3" t="n">
-        <v>163.899994</v>
+        <v>163.800003</v>
       </c>
       <c r="G3" t="n">
         <v>100</v>
@@ -526,7 +526,7 @@
         <v>136.330002</v>
       </c>
       <c r="F4" t="n">
-        <v>100.120003</v>
+        <v>100</v>
       </c>
       <c r="G4" t="n">
         <v>100</v>
@@ -551,7 +551,7 @@
         <v>254</v>
       </c>
       <c r="F5" t="n">
-        <v>458.100006</v>
+        <v>453.890015</v>
       </c>
       <c r="G5" t="n">
         <v>100</v>
@@ -576,7 +576,7 @@
         <v>5.1829</v>
       </c>
       <c r="F6" t="n">
-        <v>5.2</v>
+        <v>5.2196</v>
       </c>
       <c r="G6" t="n">
         <v>100</v>
@@ -601,7 +601,7 @@
         <v>6.1119</v>
       </c>
       <c r="F7" t="n">
-        <v>6.0196</v>
+        <v>6.0607</v>
       </c>
       <c r="G7" t="n">
         <v>100</v>
@@ -626,7 +626,7 @@
         <v>4522.680176</v>
       </c>
       <c r="F8" t="n">
-        <v>7785.759766</v>
+        <v>7691.759766</v>
       </c>
       <c r="G8" t="n">
         <v>100</v>
@@ -651,7 +651,7 @@
         <v>15259.240234</v>
       </c>
       <c r="F9" t="n">
-        <v>26729.160156</v>
+        <v>26289.710938</v>
       </c>
       <c r="G9" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
         <v>35360.730469</v>
       </c>
       <c r="F10" t="n">
-        <v>53732.410156</v>
+        <v>53343.398438</v>
       </c>
       <c r="G10" t="n">
         <v>100</v>
@@ -701,7 +701,7 @@
         <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4451.399902</v>
+        <v>4422.299805</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
@@ -726,7 +726,7 @@
         <v>68.5</v>
       </c>
       <c r="F12" t="n">
-        <v>84.370003</v>
+        <v>85.019997</v>
       </c>
       <c r="G12" t="n">
         <v>100</v>
@@ -751,7 +751,7 @@
         <v>72.989998</v>
       </c>
       <c r="F13" t="n">
-        <v>91.129997</v>
+        <v>92.010002</v>
       </c>
       <c r="G13" t="n">
         <v>100</v>
@@ -776,7 +776,7 @@
         <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1225</v>
+        <v>1227.25</v>
       </c>
       <c r="G14" t="n">
         <v>100</v>
@@ -801,7 +801,7 @@
         <v>534</v>
       </c>
       <c r="F15" t="n">
-        <v>492.75</v>
+        <v>490.25</v>
       </c>
       <c r="G15" t="n">
         <v>100</v>
@@ -826,7 +826,7 @@
         <v>-6.568391</v>
       </c>
       <c r="F16" t="n">
-        <v>-5.771651</v>
+        <v>-6.109766</v>
       </c>
       <c r="G16" t="n">
         <v>98.36065600000001</v>
@@ -851,7 +851,7 @@
         <v>-6.653229</v>
       </c>
       <c r="F17" t="n">
-        <v>-6.353565</v>
+        <v>-6.410696</v>
       </c>
       <c r="G17" t="n">
         <v>98.36065600000001</v>
@@ -876,7 +876,7 @@
         <v>-6.550283</v>
       </c>
       <c r="F18" t="n">
-        <v>-6.648016</v>
+        <v>-6.759907</v>
       </c>
       <c r="G18" t="n">
         <v>98.36065600000001</v>
@@ -901,7 +901,7 @@
         <v>0.393701</v>
       </c>
       <c r="F19" t="n">
-        <v>6.935267</v>
+        <v>5.95252</v>
       </c>
       <c r="G19" t="n">
         <v>98.36065600000001</v>
@@ -926,7 +926,7 @@
         <v>4.464682</v>
       </c>
       <c r="F20" t="n">
-        <v>2.400496</v>
+        <v>2.786475</v>
       </c>
       <c r="G20" t="n">
         <v>98.36065600000001</v>
@@ -951,7 +951,7 @@
         <v>2.725834</v>
       </c>
       <c r="F21" t="n">
-        <v>2.935165</v>
+        <v>3.637976</v>
       </c>
       <c r="G21" t="n">
         <v>98.36065600000001</v>
@@ -976,7 +976,7 @@
         <v>-4.756917</v>
       </c>
       <c r="F22" t="n">
-        <v>4.680656</v>
+        <v>3.416813</v>
       </c>
       <c r="G22" t="n">
         <v>98.36065600000001</v>
@@ -1001,7 +1001,7 @@
         <v>-5.312585</v>
       </c>
       <c r="F23" t="n">
-        <v>6.39666</v>
+        <v>4.647412</v>
       </c>
       <c r="G23" t="n">
         <v>98.36065600000001</v>
@@ -1026,7 +1026,7 @@
         <v>-4.289528</v>
       </c>
       <c r="F24" t="n">
-        <v>2.376637</v>
+        <v>2.174645</v>
       </c>
       <c r="G24" t="n">
         <v>98.36065600000001</v>
@@ -1051,7 +1051,7 @@
         <v>-3.289254</v>
       </c>
       <c r="F25" t="n">
-        <v>9.935536000000001</v>
+        <v>9.216856</v>
       </c>
       <c r="G25" t="n">
         <v>98.36065600000001</v>
@@ -1076,7 +1076,7 @@
         <v>9.532845</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.354311</v>
+        <v>0.413368</v>
       </c>
       <c r="G26" t="n">
         <v>98.36065600000001</v>
@@ -1101,7 +1101,7 @@
         <v>7.576379</v>
       </c>
       <c r="F27" t="n">
-        <v>1.120722</v>
+        <v>2.097203</v>
       </c>
       <c r="G27" t="n">
         <v>98.36065600000001</v>
@@ -1126,7 +1126,7 @@
         <v>-3.291627</v>
       </c>
       <c r="F28" t="n">
-        <v>4.522184</v>
+        <v>4.714164</v>
       </c>
       <c r="G28" t="n">
         <v>98.36065600000001</v>
@@ -1151,7 +1151,7 @@
         <v>0.514981</v>
       </c>
       <c r="F29" t="n">
-        <v>11.798071</v>
+        <v>11.230856</v>
       </c>
       <c r="G29" t="n">
         <v>98.36065600000001</v>
@@ -1201,7 +1201,7 @@
         <v>0.01993</v>
       </c>
       <c r="F31" t="n">
-        <v>0.051898</v>
+        <v>0.051878</v>
       </c>
       <c r="G31" t="n">
         <v>100</v>
@@ -1226,7 +1226,7 @@
         <v>0.01993</v>
       </c>
       <c r="F32" t="n">
-        <v>0.051921</v>
+        <v>0.051898</v>
       </c>
       <c r="G32" t="n">
         <v>100</v>
@@ -1376,7 +1376,7 @@
         <v>5.1433</v>
       </c>
       <c r="F38" t="n">
-        <v>5.2014</v>
+        <v>5.2043</v>
       </c>
       <c r="G38" t="n">
         <v>100</v>
@@ -1401,7 +1401,7 @@
         <v>5.1427</v>
       </c>
       <c r="F39" t="n">
-        <v>5.2008</v>
+        <v>5.2037</v>
       </c>
       <c r="G39" t="n">
         <v>100</v>
@@ -1676,7 +1676,7 @@
         <v>5.757004</v>
       </c>
       <c r="F50" t="n">
-        <v>2.444212</v>
+        <v>2.501329</v>
       </c>
       <c r="G50" t="n">
         <v>98.36065600000001</v>
@@ -1701,7 +1701,7 @@
         <v>5.757676</v>
       </c>
       <c r="F51" t="n">
-        <v>2.444501</v>
+        <v>2.501625</v>
       </c>
       <c r="G51" t="n">
         <v>98.36065600000001</v>
@@ -1926,7 +1926,7 @@
         <v>0.001073</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.000633</v>
+        <v>-0.000653</v>
       </c>
       <c r="G60" t="n">
         <v>98.36065600000001</v>
@@ -1951,7 +1951,7 @@
         <v>0.001073</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.00061</v>
+        <v>-0.000633</v>
       </c>
       <c r="G61" t="n">
         <v>98.36065600000001</v>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -476,7 +476,7 @@
         <v>118781</v>
       </c>
       <c r="F2" t="n">
-        <v>166335</v>
+        <v>167830</v>
       </c>
       <c r="G2" t="n">
         <v>100</v>
@@ -501,7 +501,7 @@
         <v>114.080002</v>
       </c>
       <c r="F3" t="n">
-        <v>163.800003</v>
+        <v>163.550003</v>
       </c>
       <c r="G3" t="n">
         <v>100</v>
@@ -526,7 +526,7 @@
         <v>136.330002</v>
       </c>
       <c r="F4" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G4" t="n">
         <v>100</v>
@@ -551,7 +551,7 @@
         <v>254</v>
       </c>
       <c r="F5" t="n">
-        <v>453.890015</v>
+        <v>453.25</v>
       </c>
       <c r="G5" t="n">
         <v>100</v>
@@ -576,7 +576,7 @@
         <v>5.1829</v>
       </c>
       <c r="F6" t="n">
-        <v>5.2196</v>
+        <v>5.1681</v>
       </c>
       <c r="G6" t="n">
         <v>100</v>
@@ -601,7 +601,7 @@
         <v>6.1119</v>
       </c>
       <c r="F7" t="n">
-        <v>6.0607</v>
+        <v>6.0502</v>
       </c>
       <c r="G7" t="n">
         <v>100</v>
@@ -626,7 +626,7 @@
         <v>4522.680176</v>
       </c>
       <c r="F8" t="n">
-        <v>7691.759766</v>
+        <v>7707.97998</v>
       </c>
       <c r="G8" t="n">
         <v>100</v>
@@ -651,7 +651,7 @@
         <v>15259.240234</v>
       </c>
       <c r="F9" t="n">
-        <v>26289.710938</v>
+        <v>26331.089844</v>
       </c>
       <c r="G9" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
         <v>35360.730469</v>
       </c>
       <c r="F10" t="n">
-        <v>53343.398438</v>
+        <v>53463.050781</v>
       </c>
       <c r="G10" t="n">
         <v>100</v>
@@ -701,7 +701,7 @@
         <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4422.299805</v>
+        <v>4543.5</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
@@ -726,7 +726,7 @@
         <v>68.5</v>
       </c>
       <c r="F12" t="n">
-        <v>85.019997</v>
+        <v>86.589996</v>
       </c>
       <c r="G12" t="n">
         <v>100</v>
@@ -751,7 +751,7 @@
         <v>72.989998</v>
       </c>
       <c r="F13" t="n">
-        <v>92.010002</v>
+        <v>93.849998</v>
       </c>
       <c r="G13" t="n">
         <v>100</v>
@@ -776,7 +776,7 @@
         <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1227.25</v>
+        <v>1241.5</v>
       </c>
       <c r="G14" t="n">
         <v>100</v>
@@ -801,7 +801,7 @@
         <v>534</v>
       </c>
       <c r="F15" t="n">
-        <v>490.25</v>
+        <v>502</v>
       </c>
       <c r="G15" t="n">
         <v>100</v>
@@ -826,7 +826,7 @@
         <v>-6.568391</v>
       </c>
       <c r="F16" t="n">
-        <v>-6.109766</v>
+        <v>-5.712953</v>
       </c>
       <c r="G16" t="n">
         <v>98.36065600000001</v>
@@ -851,7 +851,7 @@
         <v>-6.653229</v>
       </c>
       <c r="F17" t="n">
-        <v>-6.410696</v>
+        <v>-6.553537</v>
       </c>
       <c r="G17" t="n">
         <v>98.36065600000001</v>
@@ -876,7 +876,7 @@
         <v>-6.550283</v>
       </c>
       <c r="F18" t="n">
-        <v>-6.759907</v>
+        <v>-7.692308</v>
       </c>
       <c r="G18" t="n">
         <v>98.36065600000001</v>
@@ -901,7 +901,7 @@
         <v>0.393701</v>
       </c>
       <c r="F19" t="n">
-        <v>5.95252</v>
+        <v>5.80312</v>
       </c>
       <c r="G19" t="n">
         <v>98.36065600000001</v>
@@ -926,7 +926,7 @@
         <v>4.464682</v>
       </c>
       <c r="F20" t="n">
-        <v>2.786475</v>
+        <v>1.77231</v>
       </c>
       <c r="G20" t="n">
         <v>98.36065600000001</v>
@@ -951,7 +951,7 @@
         <v>2.725834</v>
       </c>
       <c r="F21" t="n">
-        <v>3.637976</v>
+        <v>3.458426</v>
       </c>
       <c r="G21" t="n">
         <v>98.36065600000001</v>
@@ -976,7 +976,7 @@
         <v>-4.756917</v>
       </c>
       <c r="F22" t="n">
-        <v>3.416813</v>
+        <v>2.914124</v>
       </c>
       <c r="G22" t="n">
         <v>98.36065600000001</v>
@@ -1001,7 +1001,7 @@
         <v>-5.312585</v>
       </c>
       <c r="F23" t="n">
-        <v>4.647412</v>
+        <v>3.772546</v>
       </c>
       <c r="G23" t="n">
         <v>98.36065600000001</v>
@@ -1026,7 +1026,7 @@
         <v>-4.289528</v>
       </c>
       <c r="F24" t="n">
-        <v>2.174645</v>
+        <v>1.863426</v>
       </c>
       <c r="G24" t="n">
         <v>98.36065600000001</v>
@@ -1051,7 +1051,7 @@
         <v>-3.289254</v>
       </c>
       <c r="F25" t="n">
-        <v>9.216856</v>
+        <v>12.210118</v>
       </c>
       <c r="G25" t="n">
         <v>98.36065600000001</v>
@@ -1076,7 +1076,7 @@
         <v>9.532845</v>
       </c>
       <c r="F26" t="n">
-        <v>0.413368</v>
+        <v>2.267625</v>
       </c>
       <c r="G26" t="n">
         <v>98.36065600000001</v>
@@ -1101,7 +1101,7 @@
         <v>7.576379</v>
       </c>
       <c r="F27" t="n">
-        <v>2.097203</v>
+        <v>4.138921</v>
       </c>
       <c r="G27" t="n">
         <v>98.36065600000001</v>
@@ -1126,7 +1126,7 @@
         <v>-3.291627</v>
       </c>
       <c r="F28" t="n">
-        <v>4.714164</v>
+        <v>5.930034</v>
       </c>
       <c r="G28" t="n">
         <v>98.36065600000001</v>
@@ -1151,7 +1151,7 @@
         <v>0.514981</v>
       </c>
       <c r="F29" t="n">
-        <v>11.230856</v>
+        <v>13.896767</v>
       </c>
       <c r="G29" t="n">
         <v>98.36065600000001</v>
@@ -1201,7 +1201,7 @@
         <v>0.01993</v>
       </c>
       <c r="F31" t="n">
-        <v>0.051878</v>
+        <v>0.051861</v>
       </c>
       <c r="G31" t="n">
         <v>100</v>
@@ -1226,7 +1226,7 @@
         <v>0.01993</v>
       </c>
       <c r="F32" t="n">
-        <v>0.051898</v>
+        <v>0.051878</v>
       </c>
       <c r="G32" t="n">
         <v>100</v>
@@ -1376,7 +1376,7 @@
         <v>5.1433</v>
       </c>
       <c r="F38" t="n">
-        <v>5.2043</v>
+        <v>5.1714</v>
       </c>
       <c r="G38" t="n">
         <v>100</v>
@@ -1401,7 +1401,7 @@
         <v>5.1427</v>
       </c>
       <c r="F39" t="n">
-        <v>5.2037</v>
+        <v>5.1708</v>
       </c>
       <c r="G39" t="n">
         <v>100</v>
@@ -1676,7 +1676,7 @@
         <v>5.757004</v>
       </c>
       <c r="F50" t="n">
-        <v>2.501329</v>
+        <v>1.853347</v>
       </c>
       <c r="G50" t="n">
         <v>98.36065600000001</v>
@@ -1701,7 +1701,7 @@
         <v>5.757676</v>
       </c>
       <c r="F51" t="n">
-        <v>2.501625</v>
+        <v>1.853566</v>
       </c>
       <c r="G51" t="n">
         <v>98.36065600000001</v>
@@ -1926,7 +1926,7 @@
         <v>0.001073</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.000653</v>
+        <v>-0.00067</v>
       </c>
       <c r="G60" t="n">
         <v>98.36065600000001</v>
@@ -1951,7 +1951,7 @@
         <v>0.001073</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.000633</v>
+        <v>-0.000653</v>
       </c>
       <c r="G61" t="n">
         <v>98.36065600000001</v>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -476,7 +476,7 @@
         <v>118781</v>
       </c>
       <c r="F2" t="n">
-        <v>167830</v>
+        <v>167927</v>
       </c>
       <c r="G2" t="n">
         <v>100</v>
@@ -501,7 +501,7 @@
         <v>114.080002</v>
       </c>
       <c r="F3" t="n">
-        <v>163.550003</v>
+        <v>165</v>
       </c>
       <c r="G3" t="n">
         <v>100</v>
@@ -526,7 +526,7 @@
         <v>136.330002</v>
       </c>
       <c r="F4" t="n">
-        <v>99</v>
+        <v>99.94000200000001</v>
       </c>
       <c r="G4" t="n">
         <v>100</v>
@@ -551,7 +551,7 @@
         <v>254</v>
       </c>
       <c r="F5" t="n">
-        <v>453.25</v>
+        <v>450.299988</v>
       </c>
       <c r="G5" t="n">
         <v>100</v>
@@ -576,7 +576,7 @@
         <v>5.1829</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1681</v>
+        <v>5.1931</v>
       </c>
       <c r="G6" t="n">
         <v>100</v>
@@ -601,7 +601,7 @@
         <v>6.1119</v>
       </c>
       <c r="F7" t="n">
-        <v>6.0502</v>
+        <v>6.0795</v>
       </c>
       <c r="G7" t="n">
         <v>100</v>
@@ -626,7 +626,7 @@
         <v>4522.680176</v>
       </c>
       <c r="F8" t="n">
-        <v>7707.97998</v>
+        <v>7641.160156</v>
       </c>
       <c r="G8" t="n">
         <v>100</v>
@@ -651,7 +651,7 @@
         <v>15259.240234</v>
       </c>
       <c r="F9" t="n">
-        <v>26331.089844</v>
+        <v>26067.169922</v>
       </c>
       <c r="G9" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
         <v>35360.730469</v>
       </c>
       <c r="F10" t="n">
-        <v>53463.050781</v>
+        <v>52759.210938</v>
       </c>
       <c r="G10" t="n">
         <v>100</v>
@@ -701,7 +701,7 @@
         <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4543.5</v>
+        <v>4640.700195</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
@@ -726,7 +726,7 @@
         <v>68.5</v>
       </c>
       <c r="F12" t="n">
-        <v>86.589996</v>
+        <v>87.25</v>
       </c>
       <c r="G12" t="n">
         <v>100</v>
@@ -751,7 +751,7 @@
         <v>72.989998</v>
       </c>
       <c r="F13" t="n">
-        <v>93.849998</v>
+        <v>94.05999799999999</v>
       </c>
       <c r="G13" t="n">
         <v>100</v>
@@ -776,7 +776,7 @@
         <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1241.5</v>
+        <v>1231.75</v>
       </c>
       <c r="G14" t="n">
         <v>100</v>
@@ -826,7 +826,7 @@
         <v>-6.568391</v>
       </c>
       <c r="F16" t="n">
-        <v>-5.712953</v>
+        <v>-5.658459</v>
       </c>
       <c r="G16" t="n">
         <v>98.36065600000001</v>
@@ -851,7 +851,7 @@
         <v>-6.653229</v>
       </c>
       <c r="F17" t="n">
-        <v>-6.553537</v>
+        <v>-5.725062</v>
       </c>
       <c r="G17" t="n">
         <v>98.36065600000001</v>
@@ -876,7 +876,7 @@
         <v>-6.550283</v>
       </c>
       <c r="F18" t="n">
-        <v>-7.692308</v>
+        <v>-6.815849</v>
       </c>
       <c r="G18" t="n">
         <v>98.36065600000001</v>
@@ -901,7 +901,7 @@
         <v>0.393701</v>
       </c>
       <c r="F19" t="n">
-        <v>5.80312</v>
+        <v>5.114492</v>
       </c>
       <c r="G19" t="n">
         <v>98.36065600000001</v>
@@ -926,7 +926,7 @@
         <v>4.464682</v>
       </c>
       <c r="F20" t="n">
-        <v>1.77231</v>
+        <v>2.264622</v>
       </c>
       <c r="G20" t="n">
         <v>98.36065600000001</v>
@@ -951,7 +951,7 @@
         <v>2.725834</v>
       </c>
       <c r="F21" t="n">
-        <v>3.458426</v>
+        <v>3.95946</v>
       </c>
       <c r="G21" t="n">
         <v>98.36065600000001</v>
@@ -976,7 +976,7 @@
         <v>-4.756917</v>
       </c>
       <c r="F22" t="n">
-        <v>2.914124</v>
+        <v>2.021971</v>
       </c>
       <c r="G22" t="n">
         <v>98.36065600000001</v>
@@ -1001,7 +1001,7 @@
         <v>-5.312585</v>
       </c>
       <c r="F23" t="n">
-        <v>3.772546</v>
+        <v>2.732421</v>
       </c>
       <c r="G23" t="n">
         <v>98.36065600000001</v>
@@ -1026,7 +1026,7 @@
         <v>-4.289528</v>
       </c>
       <c r="F24" t="n">
-        <v>1.863426</v>
+        <v>0.522396</v>
       </c>
       <c r="G24" t="n">
         <v>98.36065600000001</v>
@@ -1051,7 +1051,7 @@
         <v>-3.289254</v>
       </c>
       <c r="F25" t="n">
-        <v>12.210118</v>
+        <v>14.610656</v>
       </c>
       <c r="G25" t="n">
         <v>98.36065600000001</v>
@@ -1076,7 +1076,7 @@
         <v>9.532845</v>
       </c>
       <c r="F26" t="n">
-        <v>2.267625</v>
+        <v>3.047126</v>
       </c>
       <c r="G26" t="n">
         <v>98.36065600000001</v>
@@ -1101,7 +1101,7 @@
         <v>7.576379</v>
       </c>
       <c r="F27" t="n">
-        <v>4.138921</v>
+        <v>4.371943</v>
       </c>
       <c r="G27" t="n">
         <v>98.36065600000001</v>
@@ -1126,7 +1126,7 @@
         <v>-3.291627</v>
       </c>
       <c r="F28" t="n">
-        <v>5.930034</v>
+        <v>5.098123</v>
       </c>
       <c r="G28" t="n">
         <v>98.36065600000001</v>
@@ -1201,7 +1201,7 @@
         <v>0.01993</v>
       </c>
       <c r="F31" t="n">
-        <v>0.051861</v>
+        <v>0.051847</v>
       </c>
       <c r="G31" t="n">
         <v>100</v>
@@ -1226,7 +1226,7 @@
         <v>0.01993</v>
       </c>
       <c r="F32" t="n">
-        <v>0.051878</v>
+        <v>0.051861</v>
       </c>
       <c r="G32" t="n">
         <v>100</v>
@@ -1376,7 +1376,7 @@
         <v>5.1433</v>
       </c>
       <c r="F38" t="n">
-        <v>5.1714</v>
+        <v>5.1862</v>
       </c>
       <c r="G38" t="n">
         <v>100</v>
@@ -1401,7 +1401,7 @@
         <v>5.1427</v>
       </c>
       <c r="F39" t="n">
-        <v>5.1708</v>
+        <v>5.1856</v>
       </c>
       <c r="G39" t="n">
         <v>100</v>
@@ -1676,7 +1676,7 @@
         <v>5.757004</v>
       </c>
       <c r="F50" t="n">
-        <v>1.853347</v>
+        <v>2.144841</v>
       </c>
       <c r="G50" t="n">
         <v>98.36065600000001</v>
@@ -1701,7 +1701,7 @@
         <v>5.757676</v>
       </c>
       <c r="F51" t="n">
-        <v>1.853566</v>
+        <v>2.145094</v>
       </c>
       <c r="G51" t="n">
         <v>98.36065600000001</v>
@@ -1926,7 +1926,7 @@
         <v>0.001073</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.00067</v>
+        <v>-0.000684</v>
       </c>
       <c r="G60" t="n">
         <v>98.36065600000001</v>
@@ -1951,7 +1951,7 @@
         <v>0.001073</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.000653</v>
+        <v>-0.00067</v>
       </c>
       <c r="G61" t="n">
         <v>98.36065600000001</v>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -476,7 +476,7 @@
         <v>118781</v>
       </c>
       <c r="F2" t="n">
-        <v>167927</v>
+        <v>171031.734375</v>
       </c>
       <c r="G2" t="n">
         <v>100</v>
@@ -526,7 +526,7 @@
         <v>136.330002</v>
       </c>
       <c r="F4" t="n">
-        <v>99.94000200000001</v>
+        <v>99.25</v>
       </c>
       <c r="G4" t="n">
         <v>100</v>
@@ -551,7 +551,7 @@
         <v>254</v>
       </c>
       <c r="F5" t="n">
-        <v>450.299988</v>
+        <v>448</v>
       </c>
       <c r="G5" t="n">
         <v>100</v>
@@ -576,7 +576,7 @@
         <v>5.1829</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1931</v>
+        <v>5.1366</v>
       </c>
       <c r="G6" t="n">
         <v>100</v>
@@ -601,7 +601,7 @@
         <v>6.1119</v>
       </c>
       <c r="F7" t="n">
-        <v>6.0795</v>
+        <v>6</v>
       </c>
       <c r="G7" t="n">
         <v>100</v>
@@ -626,7 +626,7 @@
         <v>4522.680176</v>
       </c>
       <c r="F8" t="n">
-        <v>7641.160156</v>
+        <v>7674.370117</v>
       </c>
       <c r="G8" t="n">
         <v>100</v>
@@ -651,7 +651,7 @@
         <v>15259.240234</v>
       </c>
       <c r="F9" t="n">
-        <v>26067.169922</v>
+        <v>26180.460938</v>
       </c>
       <c r="G9" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
         <v>35360.730469</v>
       </c>
       <c r="F10" t="n">
-        <v>52759.210938</v>
+        <v>53277.011719</v>
       </c>
       <c r="G10" t="n">
         <v>100</v>
@@ -701,7 +701,7 @@
         <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4640.700195</v>
+        <v>4624.100098</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
@@ -726,7 +726,7 @@
         <v>68.5</v>
       </c>
       <c r="F12" t="n">
-        <v>87.25</v>
+        <v>87.05999799999999</v>
       </c>
       <c r="G12" t="n">
         <v>100</v>
@@ -751,7 +751,7 @@
         <v>72.989998</v>
       </c>
       <c r="F13" t="n">
-        <v>94.05999799999999</v>
+        <v>94.389999</v>
       </c>
       <c r="G13" t="n">
         <v>100</v>
@@ -776,7 +776,7 @@
         <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1231.75</v>
+        <v>1225</v>
       </c>
       <c r="G14" t="n">
         <v>100</v>
@@ -801,7 +801,7 @@
         <v>534</v>
       </c>
       <c r="F15" t="n">
-        <v>502</v>
+        <v>483.75</v>
       </c>
       <c r="G15" t="n">
         <v>100</v>
@@ -826,7 +826,7 @@
         <v>-6.568391</v>
       </c>
       <c r="F16" t="n">
-        <v>-5.658459</v>
+        <v>-3.914216</v>
       </c>
       <c r="G16" t="n">
         <v>98.36065600000001</v>
@@ -876,7 +876,7 @@
         <v>-6.550283</v>
       </c>
       <c r="F18" t="n">
-        <v>-6.815849</v>
+        <v>-7.459207</v>
       </c>
       <c r="G18" t="n">
         <v>98.36065600000001</v>
@@ -901,7 +901,7 @@
         <v>0.393701</v>
       </c>
       <c r="F19" t="n">
-        <v>5.114492</v>
+        <v>4.577601</v>
       </c>
       <c r="G19" t="n">
         <v>98.36065600000001</v>
@@ -926,7 +926,7 @@
         <v>4.464682</v>
       </c>
       <c r="F20" t="n">
-        <v>2.264622</v>
+        <v>1.152002</v>
       </c>
       <c r="G20" t="n">
         <v>98.36065600000001</v>
@@ -951,7 +951,7 @@
         <v>2.725834</v>
       </c>
       <c r="F21" t="n">
-        <v>3.95946</v>
+        <v>2.600007</v>
       </c>
       <c r="G21" t="n">
         <v>98.36065600000001</v>
@@ -976,7 +976,7 @@
         <v>-4.756917</v>
       </c>
       <c r="F22" t="n">
-        <v>2.021971</v>
+        <v>2.465378</v>
       </c>
       <c r="G22" t="n">
         <v>98.36065600000001</v>
@@ -1001,7 +1001,7 @@
         <v>-5.312585</v>
       </c>
       <c r="F23" t="n">
-        <v>2.732421</v>
+        <v>3.178908</v>
       </c>
       <c r="G23" t="n">
         <v>98.36065600000001</v>
@@ -1026,7 +1026,7 @@
         <v>-4.289528</v>
       </c>
       <c r="F24" t="n">
-        <v>0.522396</v>
+        <v>1.508964</v>
       </c>
       <c r="G24" t="n">
         <v>98.36065600000001</v>
@@ -1051,7 +1051,7 @@
         <v>-3.289254</v>
       </c>
       <c r="F25" t="n">
-        <v>14.610656</v>
+        <v>14.200686</v>
       </c>
       <c r="G25" t="n">
         <v>98.36065600000001</v>
@@ -1076,7 +1076,7 @@
         <v>9.532845</v>
       </c>
       <c r="F26" t="n">
-        <v>3.047126</v>
+        <v>2.822723</v>
       </c>
       <c r="G26" t="n">
         <v>98.36065600000001</v>
@@ -1101,7 +1101,7 @@
         <v>7.576379</v>
       </c>
       <c r="F27" t="n">
-        <v>4.371943</v>
+        <v>4.738123</v>
       </c>
       <c r="G27" t="n">
         <v>98.36065600000001</v>
@@ -1126,7 +1126,7 @@
         <v>-3.291627</v>
       </c>
       <c r="F28" t="n">
-        <v>5.098123</v>
+        <v>4.522184</v>
       </c>
       <c r="G28" t="n">
         <v>98.36065600000001</v>
@@ -1151,7 +1151,7 @@
         <v>0.514981</v>
       </c>
       <c r="F29" t="n">
-        <v>13.896767</v>
+        <v>9.756098</v>
       </c>
       <c r="G29" t="n">
         <v>98.36065600000001</v>
@@ -1201,7 +1201,7 @@
         <v>0.01993</v>
       </c>
       <c r="F31" t="n">
-        <v>0.051847</v>
+        <v>0.051834</v>
       </c>
       <c r="G31" t="n">
         <v>100</v>
@@ -1226,7 +1226,7 @@
         <v>0.01993</v>
       </c>
       <c r="F32" t="n">
-        <v>0.051861</v>
+        <v>0.051847</v>
       </c>
       <c r="G32" t="n">
         <v>100</v>
@@ -1376,7 +1376,7 @@
         <v>5.1433</v>
       </c>
       <c r="F38" t="n">
-        <v>5.1862</v>
+        <v>5.1625</v>
       </c>
       <c r="G38" t="n">
         <v>100</v>
@@ -1401,7 +1401,7 @@
         <v>5.1427</v>
       </c>
       <c r="F39" t="n">
-        <v>5.1856</v>
+        <v>5.1619</v>
       </c>
       <c r="G39" t="n">
         <v>100</v>
@@ -1676,7 +1676,7 @@
         <v>5.757004</v>
       </c>
       <c r="F50" t="n">
-        <v>2.144841</v>
+        <v>1.678057</v>
       </c>
       <c r="G50" t="n">
         <v>98.36065600000001</v>
@@ -1701,7 +1701,7 @@
         <v>5.757676</v>
       </c>
       <c r="F51" t="n">
-        <v>2.145094</v>
+        <v>1.678256</v>
       </c>
       <c r="G51" t="n">
         <v>98.36065600000001</v>
@@ -1926,7 +1926,7 @@
         <v>0.001073</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.000684</v>
+        <v>-0.000697</v>
       </c>
       <c r="G60" t="n">
         <v>98.36065600000001</v>
@@ -1951,7 +1951,7 @@
         <v>0.001073</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.00067</v>
+        <v>-0.000684</v>
       </c>
       <c r="G61" t="n">
         <v>98.36065600000001</v>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -501,7 +501,7 @@
         <v>114.080002</v>
       </c>
       <c r="F3" t="n">
-        <v>165</v>
+        <v>168.330002</v>
       </c>
       <c r="G3" t="n">
         <v>100</v>
@@ -526,7 +526,7 @@
         <v>136.330002</v>
       </c>
       <c r="F4" t="n">
-        <v>99.25</v>
+        <v>102.25</v>
       </c>
       <c r="G4" t="n">
         <v>100</v>
@@ -551,7 +551,7 @@
         <v>254</v>
       </c>
       <c r="F5" t="n">
-        <v>448</v>
+        <v>445.850006</v>
       </c>
       <c r="G5" t="n">
         <v>100</v>
@@ -701,7 +701,7 @@
         <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4624.100098</v>
+        <v>4680.600098</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
@@ -714,22 +714,22 @@
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>44439</v>
+        <v>46265</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D12" t="n">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>68.5</v>
+        <v>87.05999799999999</v>
       </c>
       <c r="F12" t="n">
         <v>87.05999799999999</v>
       </c>
       <c r="G12" t="n">
-        <v>100</v>
+        <v>1.639344</v>
       </c>
     </row>
     <row r="13">
@@ -776,7 +776,7 @@
         <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1225</v>
+        <v>1239.5</v>
       </c>
       <c r="G14" t="n">
         <v>100</v>
@@ -801,7 +801,7 @@
         <v>534</v>
       </c>
       <c r="F15" t="n">
-        <v>483.75</v>
+        <v>508.5</v>
       </c>
       <c r="G15" t="n">
         <v>100</v>
@@ -851,7 +851,7 @@
         <v>-6.653229</v>
       </c>
       <c r="F17" t="n">
-        <v>-5.725062</v>
+        <v>-3.822422</v>
       </c>
       <c r="G17" t="n">
         <v>98.36065600000001</v>
@@ -876,7 +876,7 @@
         <v>-6.550283</v>
       </c>
       <c r="F18" t="n">
-        <v>-7.459207</v>
+        <v>-4.662005</v>
       </c>
       <c r="G18" t="n">
         <v>98.36065600000001</v>
@@ -901,7 +901,7 @@
         <v>0.393701</v>
       </c>
       <c r="F19" t="n">
-        <v>4.577601</v>
+        <v>4.075723</v>
       </c>
       <c r="G19" t="n">
         <v>98.36065600000001</v>
@@ -1051,7 +1051,7 @@
         <v>-3.289254</v>
       </c>
       <c r="F25" t="n">
-        <v>14.200686</v>
+        <v>15.596058</v>
       </c>
       <c r="G25" t="n">
         <v>98.36065600000001</v>
@@ -1063,23 +1063,15 @@
           <t>yahoo_ret_petroleo_wti</t>
         </is>
       </c>
-      <c r="B26" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="C26" s="1" t="n">
-        <v>46265</v>
-      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="n">
-        <v>60</v>
-      </c>
-      <c r="E26" t="n">
-        <v>9.532845</v>
-      </c>
-      <c r="F26" t="n">
-        <v>2.822723</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
-        <v>98.36065600000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1126,7 +1118,7 @@
         <v>-3.291627</v>
       </c>
       <c r="F28" t="n">
-        <v>4.522184</v>
+        <v>5.759386</v>
       </c>
       <c r="G28" t="n">
         <v>98.36065600000001</v>
@@ -1151,7 +1143,7 @@
         <v>0.514981</v>
       </c>
       <c r="F29" t="n">
-        <v>9.756098</v>
+        <v>15.371526</v>
       </c>
       <c r="G29" t="n">
         <v>98.36065600000001</v>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -476,7 +476,7 @@
         <v>118781</v>
       </c>
       <c r="F2" t="n">
-        <v>171031.734375</v>
+        <v>170448.875</v>
       </c>
       <c r="G2" t="n">
         <v>100</v>
@@ -601,7 +601,7 @@
         <v>6.1119</v>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>5.9925</v>
       </c>
       <c r="G7" t="n">
         <v>100</v>
@@ -701,7 +701,7 @@
         <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4680.600098</v>
+        <v>4700.799805</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
@@ -714,22 +714,22 @@
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>46265</v>
+        <v>44439</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="E12" t="n">
-        <v>87.05999799999999</v>
+        <v>68.5</v>
       </c>
       <c r="F12" t="n">
-        <v>87.05999799999999</v>
+        <v>85.040001</v>
       </c>
       <c r="G12" t="n">
-        <v>1.639344</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -751,7 +751,7 @@
         <v>72.989998</v>
       </c>
       <c r="F13" t="n">
-        <v>94.389999</v>
+        <v>92.779999</v>
       </c>
       <c r="G13" t="n">
         <v>100</v>
@@ -776,7 +776,7 @@
         <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1239.5</v>
+        <v>1237.25</v>
       </c>
       <c r="G14" t="n">
         <v>100</v>
@@ -801,7 +801,7 @@
         <v>534</v>
       </c>
       <c r="F15" t="n">
-        <v>508.5</v>
+        <v>522.5</v>
       </c>
       <c r="G15" t="n">
         <v>100</v>
@@ -826,7 +826,7 @@
         <v>-6.568391</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.914216</v>
+        <v>-4.241667</v>
       </c>
       <c r="G16" t="n">
         <v>98.36065600000001</v>
@@ -951,7 +951,7 @@
         <v>2.725834</v>
       </c>
       <c r="F21" t="n">
-        <v>2.600007</v>
+        <v>2.471754</v>
       </c>
       <c r="G21" t="n">
         <v>98.36065600000001</v>
@@ -1051,7 +1051,7 @@
         <v>-3.289254</v>
       </c>
       <c r="F25" t="n">
-        <v>15.596058</v>
+        <v>16.094927</v>
       </c>
       <c r="G25" t="n">
         <v>98.36065600000001</v>
@@ -1063,15 +1063,23 @@
           <t>yahoo_ret_petroleo_wti</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
+      <c r="B26" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="C26" s="1" t="n">
+        <v>46265</v>
+      </c>
       <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="E26" t="n">
+        <v>9.532845</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.436994</v>
+      </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="27">
@@ -1093,7 +1101,7 @@
         <v>7.576379</v>
       </c>
       <c r="F27" t="n">
-        <v>4.738123</v>
+        <v>2.951616</v>
       </c>
       <c r="G27" t="n">
         <v>98.36065600000001</v>
@@ -1118,7 +1126,7 @@
         <v>-3.291627</v>
       </c>
       <c r="F28" t="n">
-        <v>5.759386</v>
+        <v>5.567406</v>
       </c>
       <c r="G28" t="n">
         <v>98.36065600000001</v>
@@ -1143,7 +1151,7 @@
         <v>0.514981</v>
       </c>
       <c r="F29" t="n">
-        <v>15.371526</v>
+        <v>18.54793</v>
       </c>
       <c r="G29" t="n">
         <v>98.36065600000001</v>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
         <v>118781</v>
       </c>
       <c r="F2" t="n">
-        <v>170448.875</v>
+        <v>171907</v>
       </c>
       <c r="G2" t="n">
         <v>100</v>
@@ -576,7 +576,7 @@
         <v>5.1829</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1366</v>
+        <v>5.154</v>
       </c>
       <c r="G6" t="n">
         <v>100</v>
@@ -601,7 +601,7 @@
         <v>6.1119</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9925</v>
+        <v>6.0109</v>
       </c>
       <c r="G7" t="n">
         <v>100</v>
@@ -626,7 +626,7 @@
         <v>4522.680176</v>
       </c>
       <c r="F8" t="n">
-        <v>7674.370117</v>
+        <v>7652.859863</v>
       </c>
       <c r="G8" t="n">
         <v>100</v>
@@ -651,7 +651,7 @@
         <v>15259.240234</v>
       </c>
       <c r="F9" t="n">
-        <v>26180.460938</v>
+        <v>25980.189453</v>
       </c>
       <c r="G9" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
         <v>35360.730469</v>
       </c>
       <c r="F10" t="n">
-        <v>53277.011719</v>
+        <v>53417.160156</v>
       </c>
       <c r="G10" t="n">
         <v>100</v>
@@ -701,7 +701,7 @@
         <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4700.799805</v>
+        <v>4693.100098</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
@@ -726,7 +726,7 @@
         <v>68.5</v>
       </c>
       <c r="F12" t="n">
-        <v>85.040001</v>
+        <v>82.540001</v>
       </c>
       <c r="G12" t="n">
         <v>100</v>
@@ -751,7 +751,7 @@
         <v>72.989998</v>
       </c>
       <c r="F13" t="n">
-        <v>92.779999</v>
+        <v>88.019997</v>
       </c>
       <c r="G13" t="n">
         <v>100</v>
@@ -776,7 +776,7 @@
         <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1237.25</v>
+        <v>1218.25</v>
       </c>
       <c r="G14" t="n">
         <v>100</v>
@@ -801,7 +801,7 @@
         <v>534</v>
       </c>
       <c r="F15" t="n">
-        <v>522.5</v>
+        <v>514.25</v>
       </c>
       <c r="G15" t="n">
         <v>100</v>
@@ -826,7 +826,7 @@
         <v>-6.568391</v>
       </c>
       <c r="F16" t="n">
-        <v>-4.241667</v>
+        <v>-3.422491</v>
       </c>
       <c r="G16" t="n">
         <v>98.36065600000001</v>
@@ -926,7 +926,7 @@
         <v>4.464682</v>
       </c>
       <c r="F20" t="n">
-        <v>1.152002</v>
+        <v>1.494646</v>
       </c>
       <c r="G20" t="n">
         <v>98.36065600000001</v>
@@ -951,7 +951,7 @@
         <v>2.725834</v>
       </c>
       <c r="F21" t="n">
-        <v>2.471754</v>
+        <v>2.786397</v>
       </c>
       <c r="G21" t="n">
         <v>98.36065600000001</v>
@@ -976,7 +976,7 @@
         <v>-4.756917</v>
       </c>
       <c r="F22" t="n">
-        <v>2.465378</v>
+        <v>2.178181</v>
       </c>
       <c r="G22" t="n">
         <v>98.36065600000001</v>
@@ -1001,7 +1001,7 @@
         <v>-5.312585</v>
       </c>
       <c r="F23" t="n">
-        <v>3.178908</v>
+        <v>2.389625</v>
       </c>
       <c r="G23" t="n">
         <v>98.36065600000001</v>
@@ -1026,7 +1026,7 @@
         <v>-4.289528</v>
       </c>
       <c r="F24" t="n">
-        <v>1.508964</v>
+        <v>1.77599</v>
       </c>
       <c r="G24" t="n">
         <v>98.36065600000001</v>
@@ -1051,7 +1051,7 @@
         <v>-3.289254</v>
       </c>
       <c r="F25" t="n">
-        <v>16.094927</v>
+        <v>15.904769</v>
       </c>
       <c r="G25" t="n">
         <v>98.36065600000001</v>
@@ -1076,7 +1076,7 @@
         <v>9.532845</v>
       </c>
       <c r="F26" t="n">
-        <v>0.436994</v>
+        <v>-2.515646</v>
       </c>
       <c r="G26" t="n">
         <v>98.36065600000001</v>
@@ -1101,7 +1101,7 @@
         <v>7.576379</v>
       </c>
       <c r="F27" t="n">
-        <v>2.951616</v>
+        <v>-2.330233</v>
       </c>
       <c r="G27" t="n">
         <v>98.36065600000001</v>
@@ -1126,7 +1126,7 @@
         <v>-3.291627</v>
       </c>
       <c r="F28" t="n">
-        <v>5.567406</v>
+        <v>3.946246</v>
       </c>
       <c r="G28" t="n">
         <v>98.36065600000001</v>
@@ -1151,7 +1151,7 @@
         <v>0.514981</v>
       </c>
       <c r="F29" t="n">
-        <v>18.54793</v>
+        <v>16.67612</v>
       </c>
       <c r="G29" t="n">
         <v>98.36065600000001</v>
@@ -1185,7 +1185,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_over</t>
+          <t>bcb_sgs_cdi</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1210,32 +1210,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bcb_sgs_cdi</t>
+          <t>bcb_sgs_ipca</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D32" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E32" t="n">
-        <v>0.01993</v>
+        <v>0.87</v>
       </c>
       <c r="F32" t="n">
-        <v>0.051847</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G32" t="n">
-        <v>100</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca</t>
+          <t>bcb_sgs_igp_m</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
@@ -1248,10 +1248,10 @@
         <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>0.87</v>
+        <v>0.66</v>
       </c>
       <c r="F33" t="n">
-        <v>0.07000000000000001</v>
+        <v>-1.16</v>
       </c>
       <c r="G33" t="n">
         <v>98.36065600000001</v>
@@ -1260,7 +1260,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m</t>
+          <t>bcb_sgs_inpc</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1273,10 +1273,10 @@
         <v>60</v>
       </c>
       <c r="E34" t="n">
-        <v>0.66</v>
+        <v>0.88</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.16</v>
+        <v>-0.01</v>
       </c>
       <c r="G34" t="n">
         <v>98.36065600000001</v>
@@ -1285,32 +1285,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc</t>
+          <t>bcb_sgs_ibc_br_sa</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D35" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E35" t="n">
-        <v>0.88</v>
+        <v>97.01608</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.01</v>
+        <v>110.22154</v>
       </c>
       <c r="G35" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br_sa</t>
+          <t>bcb_sgs_ibc_br</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
@@ -1323,10 +1323,10 @@
         <v>59</v>
       </c>
       <c r="E36" t="n">
-        <v>97.01608</v>
+        <v>99.19190999999999</v>
       </c>
       <c r="F36" t="n">
-        <v>110.22154</v>
+        <v>109.89427</v>
       </c>
       <c r="G36" t="n">
         <v>96.721311</v>
@@ -1335,32 +1335,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br</t>
+          <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="D37" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E37" t="n">
-        <v>99.19190999999999</v>
+        <v>5.1433</v>
       </c>
       <c r="F37" t="n">
-        <v>109.89427</v>
+        <v>5.1512</v>
       </c>
       <c r="G37" t="n">
-        <v>96.721311</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_venda_usd</t>
+          <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
@@ -1373,10 +1373,10 @@
         <v>61</v>
       </c>
       <c r="E38" t="n">
-        <v>5.1433</v>
+        <v>5.1427</v>
       </c>
       <c r="F38" t="n">
-        <v>5.1625</v>
+        <v>5.1506</v>
       </c>
       <c r="G38" t="n">
         <v>100</v>
@@ -1385,32 +1385,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_compra_usd</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="D39" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E39" t="n">
-        <v>5.1427</v>
+        <v>4346060</v>
       </c>
       <c r="F39" t="n">
-        <v>5.1619</v>
+        <v>7355800</v>
       </c>
       <c r="G39" t="n">
-        <v>100</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
@@ -1423,10 +1423,10 @@
         <v>59</v>
       </c>
       <c r="E40" t="n">
-        <v>4346060</v>
+        <v>1851006</v>
       </c>
       <c r="F40" t="n">
-        <v>7355800</v>
+        <v>2749001</v>
       </c>
       <c r="G40" t="n">
         <v>96.721311</v>
@@ -1435,7 +1435,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
@@ -1448,10 +1448,10 @@
         <v>59</v>
       </c>
       <c r="E41" t="n">
-        <v>1851006</v>
+        <v>2495054</v>
       </c>
       <c r="F41" t="n">
-        <v>2749001</v>
+        <v>4606799</v>
       </c>
       <c r="G41" t="n">
         <v>96.721311</v>
@@ -1460,7 +1460,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
@@ -1473,10 +1473,10 @@
         <v>59</v>
       </c>
       <c r="E42" t="n">
-        <v>2495054</v>
+        <v>2.37</v>
       </c>
       <c r="F42" t="n">
-        <v>4606799</v>
+        <v>4.68</v>
       </c>
       <c r="G42" t="n">
         <v>96.721311</v>
@@ -1485,7 +1485,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
@@ -1498,10 +1498,10 @@
         <v>59</v>
       </c>
       <c r="E43" t="n">
-        <v>2.37</v>
+        <v>1.56</v>
       </c>
       <c r="F43" t="n">
-        <v>4.68</v>
+        <v>3.19</v>
       </c>
       <c r="G43" t="n">
         <v>96.721311</v>
@@ -1510,7 +1510,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
@@ -1523,10 +1523,10 @@
         <v>59</v>
       </c>
       <c r="E44" t="n">
-        <v>1.56</v>
+        <v>2.96</v>
       </c>
       <c r="F44" t="n">
-        <v>3.19</v>
+        <v>5.57</v>
       </c>
       <c r="G44" t="n">
         <v>96.721311</v>
@@ -1535,7 +1535,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
@@ -1548,10 +1548,10 @@
         <v>59</v>
       </c>
       <c r="E45" t="n">
-        <v>2.96</v>
+        <v>20.92</v>
       </c>
       <c r="F45" t="n">
-        <v>5.57</v>
+        <v>33.44</v>
       </c>
       <c r="G45" t="n">
         <v>96.721311</v>
@@ -1560,57 +1560,57 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D46" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E46" t="n">
-        <v>20.92</v>
+        <v>370395</v>
       </c>
       <c r="F46" t="n">
-        <v>33.44</v>
+        <v>369742</v>
       </c>
       <c r="G46" t="n">
-        <v>96.721311</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D47" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E47" t="n">
-        <v>370395</v>
+        <v>-0.064886</v>
       </c>
       <c r="F47" t="n">
-        <v>369742</v>
+        <v>-0.6395690000000001</v>
       </c>
       <c r="G47" t="n">
-        <v>98.36065600000001</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
@@ -1623,10 +1623,10 @@
         <v>58</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.064886</v>
+        <v>-2.103216</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.6395690000000001</v>
+        <v>0.332557</v>
       </c>
       <c r="G48" t="n">
         <v>95.08196700000001</v>
@@ -1635,32 +1635,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="D49" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E49" t="n">
-        <v>-2.103216</v>
+        <v>5.757004</v>
       </c>
       <c r="F49" t="n">
-        <v>0.332557</v>
+        <v>1.455498</v>
       </c>
       <c r="G49" t="n">
-        <v>95.08196700000001</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
@@ -1673,10 +1673,10 @@
         <v>60</v>
       </c>
       <c r="E50" t="n">
-        <v>5.757004</v>
+        <v>5.757676</v>
       </c>
       <c r="F50" t="n">
-        <v>1.678057</v>
+        <v>1.45567</v>
       </c>
       <c r="G50" t="n">
         <v>98.36065600000001</v>
@@ -1685,32 +1685,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="D51" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E51" t="n">
-        <v>5.757676</v>
+        <v>2.185796</v>
       </c>
       <c r="F51" t="n">
-        <v>1.678256</v>
+        <v>0.714468</v>
       </c>
       <c r="G51" t="n">
-        <v>98.36065600000001</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
@@ -1723,10 +1723,10 @@
         <v>58</v>
       </c>
       <c r="E52" t="n">
-        <v>2.185796</v>
+        <v>2.329166</v>
       </c>
       <c r="F52" t="n">
-        <v>0.714468</v>
+        <v>1.515494</v>
       </c>
       <c r="G52" t="n">
         <v>95.08196700000001</v>
@@ -1735,7 +1735,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
@@ -1748,10 +1748,10 @@
         <v>58</v>
       </c>
       <c r="E53" t="n">
-        <v>2.329166</v>
+        <v>2.079394</v>
       </c>
       <c r="F53" t="n">
-        <v>1.515494</v>
+        <v>0.242446</v>
       </c>
       <c r="G53" t="n">
         <v>95.08196700000001</v>
@@ -1760,57 +1760,57 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D54" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E54" t="n">
-        <v>2.079394</v>
+        <v>-0.407403</v>
       </c>
       <c r="F54" t="n">
-        <v>0.242446</v>
+        <v>0.5941920000000001</v>
       </c>
       <c r="G54" t="n">
-        <v>95.08196700000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>44469</v>
+        <v>44773</v>
       </c>
       <c r="C55" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D55" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.407403</v>
+        <v>10.069235</v>
       </c>
       <c r="F55" t="n">
-        <v>0.5941920000000001</v>
+        <v>4.443025</v>
       </c>
       <c r="G55" t="n">
-        <v>96.721311</v>
+        <v>80.32786900000001</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
@@ -1823,10 +1823,10 @@
         <v>49</v>
       </c>
       <c r="E56" t="n">
-        <v>10.069235</v>
+        <v>10.074751</v>
       </c>
       <c r="F56" t="n">
-        <v>4.443025</v>
+        <v>2.772183</v>
       </c>
       <c r="G56" t="n">
         <v>80.32786900000001</v>
@@ -1835,7 +1835,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
@@ -1848,10 +1848,10 @@
         <v>49</v>
       </c>
       <c r="E57" t="n">
-        <v>10.074751</v>
+        <v>10.124804</v>
       </c>
       <c r="F57" t="n">
-        <v>2.772183</v>
+        <v>4.098046</v>
       </c>
       <c r="G57" t="n">
         <v>80.32786900000001</v>
@@ -1860,32 +1860,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>44773</v>
+        <v>44469</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D58" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E58" t="n">
-        <v>10.124804</v>
+        <v>1</v>
       </c>
       <c r="F58" t="n">
-        <v>4.098046</v>
+        <v>-0.25</v>
       </c>
       <c r="G58" t="n">
-        <v>80.32786900000001</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
@@ -1898,10 +1898,10 @@
         <v>60</v>
       </c>
       <c r="E59" t="n">
-        <v>1</v>
+        <v>0.001073</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.25</v>
+        <v>-0.000697</v>
       </c>
       <c r="G59" t="n">
         <v>98.36065600000001</v>
@@ -1910,57 +1910,57 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="D60" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E60" t="n">
-        <v>0.001073</v>
+        <v>-0.03</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.000697</v>
+        <v>-0.06</v>
       </c>
       <c r="G60" t="n">
-        <v>98.36065600000001</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="D61" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E61" t="n">
-        <v>0.001073</v>
+        <v>-0.13</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.000684</v>
+        <v>-0.06</v>
       </c>
       <c r="G61" t="n">
-        <v>98.36065600000001</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
@@ -1973,10 +1973,10 @@
         <v>58</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.03</v>
+        <v>0.05</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="G62" t="n">
         <v>95.08196700000001</v>
@@ -1985,7 +1985,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
@@ -1998,62 +1998,12 @@
         <v>58</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.13</v>
+        <v>0.5</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.06</v>
+        <v>0.22</v>
       </c>
       <c r="G63" t="n">
-        <v>95.08196700000001</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
-        </is>
-      </c>
-      <c r="B64" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="C64" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="D64" t="n">
-        <v>58</v>
-      </c>
-      <c r="E64" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F64" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="G64" t="n">
-        <v>95.08196700000001</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
-        </is>
-      </c>
-      <c r="B65" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="C65" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="D65" t="n">
-        <v>58</v>
-      </c>
-      <c r="E65" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F65" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="G65" t="n">
         <v>95.08196700000001</v>
       </c>
     </row>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
         <v>118781</v>
       </c>
       <c r="F2" t="n">
-        <v>171907</v>
+        <v>174577</v>
       </c>
       <c r="G2" t="n">
         <v>100</v>
@@ -501,7 +501,7 @@
         <v>114.080002</v>
       </c>
       <c r="F3" t="n">
-        <v>168.330002</v>
+        <v>169.009995</v>
       </c>
       <c r="G3" t="n">
         <v>100</v>
@@ -526,7 +526,7 @@
         <v>136.330002</v>
       </c>
       <c r="F4" t="n">
-        <v>102.25</v>
+        <v>102.639999</v>
       </c>
       <c r="G4" t="n">
         <v>100</v>
@@ -551,7 +551,7 @@
         <v>254</v>
       </c>
       <c r="F5" t="n">
-        <v>445.850006</v>
+        <v>444.700012</v>
       </c>
       <c r="G5" t="n">
         <v>100</v>
@@ -576,7 +576,7 @@
         <v>5.1829</v>
       </c>
       <c r="F6" t="n">
-        <v>5.154</v>
+        <v>5.148</v>
       </c>
       <c r="G6" t="n">
         <v>100</v>
@@ -601,7 +601,7 @@
         <v>6.1119</v>
       </c>
       <c r="F7" t="n">
-        <v>6.0109</v>
+        <v>6.0044</v>
       </c>
       <c r="G7" t="n">
         <v>100</v>
@@ -626,7 +626,7 @@
         <v>4522.680176</v>
       </c>
       <c r="F8" t="n">
-        <v>7652.859863</v>
+        <v>7677.279785</v>
       </c>
       <c r="G8" t="n">
         <v>100</v>
@@ -651,7 +651,7 @@
         <v>15259.240234</v>
       </c>
       <c r="F9" t="n">
-        <v>25980.189453</v>
+        <v>26151.300781</v>
       </c>
       <c r="G9" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
         <v>35360.730469</v>
       </c>
       <c r="F10" t="n">
-        <v>53417.160156</v>
+        <v>53577.398438</v>
       </c>
       <c r="G10" t="n">
         <v>100</v>
@@ -701,7 +701,7 @@
         <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4693.100098</v>
+        <v>4670.700195</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
@@ -726,7 +726,7 @@
         <v>68.5</v>
       </c>
       <c r="F12" t="n">
-        <v>82.540001</v>
+        <v>80.139999</v>
       </c>
       <c r="G12" t="n">
         <v>100</v>
@@ -751,7 +751,7 @@
         <v>72.989998</v>
       </c>
       <c r="F13" t="n">
-        <v>88.019997</v>
+        <v>84.910004</v>
       </c>
       <c r="G13" t="n">
         <v>100</v>
@@ -776,7 +776,7 @@
         <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1218.25</v>
+        <v>1240.75</v>
       </c>
       <c r="G14" t="n">
         <v>100</v>
@@ -801,7 +801,7 @@
         <v>534</v>
       </c>
       <c r="F15" t="n">
-        <v>514.25</v>
+        <v>528</v>
       </c>
       <c r="G15" t="n">
         <v>100</v>
@@ -826,7 +826,7 @@
         <v>-6.568391</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.422491</v>
+        <v>-1.922483</v>
       </c>
       <c r="G16" t="n">
         <v>98.36065600000001</v>
@@ -851,7 +851,7 @@
         <v>-6.653229</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.822422</v>
+        <v>-3.433899</v>
       </c>
       <c r="G17" t="n">
         <v>98.36065600000001</v>
@@ -876,7 +876,7 @@
         <v>-6.550283</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.662005</v>
+        <v>-4.298369</v>
       </c>
       <c r="G18" t="n">
         <v>98.36065600000001</v>
@@ -901,7 +901,7 @@
         <v>0.393701</v>
       </c>
       <c r="F19" t="n">
-        <v>4.075723</v>
+        <v>3.807278</v>
       </c>
       <c r="G19" t="n">
         <v>98.36065600000001</v>
@@ -926,7 +926,7 @@
         <v>4.464682</v>
       </c>
       <c r="F20" t="n">
-        <v>1.494646</v>
+        <v>1.37649</v>
       </c>
       <c r="G20" t="n">
         <v>98.36065600000001</v>
@@ -951,7 +951,7 @@
         <v>2.725834</v>
       </c>
       <c r="F21" t="n">
-        <v>2.786397</v>
+        <v>2.675243</v>
       </c>
       <c r="G21" t="n">
         <v>98.36065600000001</v>
@@ -976,7 +976,7 @@
         <v>-4.756917</v>
       </c>
       <c r="F22" t="n">
-        <v>2.178181</v>
+        <v>2.504227</v>
       </c>
       <c r="G22" t="n">
         <v>98.36065600000001</v>
@@ -1001,7 +1001,7 @@
         <v>-5.312585</v>
       </c>
       <c r="F23" t="n">
-        <v>2.389625</v>
+        <v>3.063986</v>
       </c>
       <c r="G23" t="n">
         <v>98.36065600000001</v>
@@ -1026,7 +1026,7 @@
         <v>-4.289528</v>
       </c>
       <c r="F24" t="n">
-        <v>1.77599</v>
+        <v>2.081293</v>
       </c>
       <c r="G24" t="n">
         <v>98.36065600000001</v>
@@ -1051,7 +1051,7 @@
         <v>-3.289254</v>
       </c>
       <c r="F25" t="n">
-        <v>15.904769</v>
+        <v>15.351562</v>
       </c>
       <c r="G25" t="n">
         <v>98.36065600000001</v>
@@ -1076,7 +1076,7 @@
         <v>9.532845</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.515646</v>
+        <v>-5.350182</v>
       </c>
       <c r="G26" t="n">
         <v>98.36065600000001</v>
@@ -1101,7 +1101,7 @@
         <v>7.576379</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.330233</v>
+        <v>-5.781179</v>
       </c>
       <c r="G27" t="n">
         <v>98.36065600000001</v>
@@ -1126,7 +1126,7 @@
         <v>-3.291627</v>
       </c>
       <c r="F28" t="n">
-        <v>3.946246</v>
+        <v>5.866041</v>
       </c>
       <c r="G28" t="n">
         <v>98.36065600000001</v>
@@ -1151,7 +1151,7 @@
         <v>0.514981</v>
       </c>
       <c r="F29" t="n">
-        <v>16.67612</v>
+        <v>19.795803</v>
       </c>
       <c r="G29" t="n">
         <v>98.36065600000001</v>
@@ -1185,7 +1185,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>bcb_sgs_cdi</t>
+          <t>bcb_sgs_selic_over</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1201,7 +1201,7 @@
         <v>0.01993</v>
       </c>
       <c r="F31" t="n">
-        <v>0.051834</v>
+        <v>0.051814</v>
       </c>
       <c r="G31" t="n">
         <v>100</v>
@@ -1210,32 +1210,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca</t>
+          <t>bcb_sgs_cdi</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D32" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E32" t="n">
-        <v>0.87</v>
+        <v>0.01993</v>
       </c>
       <c r="F32" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.051823</v>
       </c>
       <c r="G32" t="n">
-        <v>98.36065600000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m</t>
+          <t>bcb_sgs_ipca</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
@@ -1248,10 +1248,10 @@
         <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>0.66</v>
+        <v>0.87</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.16</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G33" t="n">
         <v>98.36065600000001</v>
@@ -1260,7 +1260,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc</t>
+          <t>bcb_sgs_igp_m</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1273,10 +1273,10 @@
         <v>60</v>
       </c>
       <c r="E34" t="n">
-        <v>0.88</v>
+        <v>0.66</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.01</v>
+        <v>-1.16</v>
       </c>
       <c r="G34" t="n">
         <v>98.36065600000001</v>
@@ -1285,32 +1285,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br_sa</t>
+          <t>bcb_sgs_inpc</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D35" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E35" t="n">
-        <v>97.01608</v>
+        <v>0.88</v>
       </c>
       <c r="F35" t="n">
-        <v>110.22154</v>
+        <v>-0.01</v>
       </c>
       <c r="G35" t="n">
-        <v>96.721311</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br</t>
+          <t>bcb_sgs_ibc_br_sa</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
@@ -1323,10 +1323,10 @@
         <v>59</v>
       </c>
       <c r="E36" t="n">
-        <v>99.19190999999999</v>
+        <v>97.01608</v>
       </c>
       <c r="F36" t="n">
-        <v>109.89427</v>
+        <v>110.22154</v>
       </c>
       <c r="G36" t="n">
         <v>96.721311</v>
@@ -1335,32 +1335,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_venda_usd</t>
+          <t>bcb_sgs_ibc_br</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="D37" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E37" t="n">
-        <v>5.1433</v>
+        <v>99.19190999999999</v>
       </c>
       <c r="F37" t="n">
-        <v>5.1512</v>
+        <v>109.89427</v>
       </c>
       <c r="G37" t="n">
-        <v>100</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_compra_usd</t>
+          <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
@@ -1373,10 +1373,10 @@
         <v>61</v>
       </c>
       <c r="E38" t="n">
-        <v>5.1427</v>
+        <v>5.1433</v>
       </c>
       <c r="F38" t="n">
-        <v>5.1506</v>
+        <v>5.149</v>
       </c>
       <c r="G38" t="n">
         <v>100</v>
@@ -1385,32 +1385,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="D39" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E39" t="n">
-        <v>4346060</v>
+        <v>5.1427</v>
       </c>
       <c r="F39" t="n">
-        <v>7355800</v>
+        <v>5.1484</v>
       </c>
       <c r="G39" t="n">
-        <v>96.721311</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
@@ -1423,10 +1423,10 @@
         <v>59</v>
       </c>
       <c r="E40" t="n">
-        <v>1851006</v>
+        <v>4346060</v>
       </c>
       <c r="F40" t="n">
-        <v>2749001</v>
+        <v>7355800</v>
       </c>
       <c r="G40" t="n">
         <v>96.721311</v>
@@ -1435,7 +1435,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
@@ -1448,10 +1448,10 @@
         <v>59</v>
       </c>
       <c r="E41" t="n">
-        <v>2495054</v>
+        <v>1851006</v>
       </c>
       <c r="F41" t="n">
-        <v>4606799</v>
+        <v>2749001</v>
       </c>
       <c r="G41" t="n">
         <v>96.721311</v>
@@ -1460,7 +1460,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
@@ -1473,10 +1473,10 @@
         <v>59</v>
       </c>
       <c r="E42" t="n">
-        <v>2.37</v>
+        <v>2495054</v>
       </c>
       <c r="F42" t="n">
-        <v>4.68</v>
+        <v>4606799</v>
       </c>
       <c r="G42" t="n">
         <v>96.721311</v>
@@ -1485,7 +1485,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
@@ -1498,10 +1498,10 @@
         <v>59</v>
       </c>
       <c r="E43" t="n">
-        <v>1.56</v>
+        <v>2.37</v>
       </c>
       <c r="F43" t="n">
-        <v>3.19</v>
+        <v>4.68</v>
       </c>
       <c r="G43" t="n">
         <v>96.721311</v>
@@ -1510,7 +1510,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
@@ -1523,10 +1523,10 @@
         <v>59</v>
       </c>
       <c r="E44" t="n">
-        <v>2.96</v>
+        <v>1.56</v>
       </c>
       <c r="F44" t="n">
-        <v>5.57</v>
+        <v>3.19</v>
       </c>
       <c r="G44" t="n">
         <v>96.721311</v>
@@ -1535,7 +1535,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
@@ -1548,10 +1548,10 @@
         <v>59</v>
       </c>
       <c r="E45" t="n">
-        <v>20.92</v>
+        <v>2.96</v>
       </c>
       <c r="F45" t="n">
-        <v>33.44</v>
+        <v>5.57</v>
       </c>
       <c r="G45" t="n">
         <v>96.721311</v>
@@ -1560,57 +1560,57 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D46" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E46" t="n">
-        <v>370395</v>
+        <v>20.92</v>
       </c>
       <c r="F46" t="n">
-        <v>369742</v>
+        <v>33.44</v>
       </c>
       <c r="G46" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D47" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.064886</v>
+        <v>370395</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.6395690000000001</v>
+        <v>369742</v>
       </c>
       <c r="G47" t="n">
-        <v>95.08196700000001</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
@@ -1623,10 +1623,10 @@
         <v>58</v>
       </c>
       <c r="E48" t="n">
-        <v>-2.103216</v>
+        <v>-0.064886</v>
       </c>
       <c r="F48" t="n">
-        <v>0.332557</v>
+        <v>-0.6395690000000001</v>
       </c>
       <c r="G48" t="n">
         <v>95.08196700000001</v>
@@ -1635,32 +1635,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="D49" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E49" t="n">
-        <v>5.757004</v>
+        <v>-2.103216</v>
       </c>
       <c r="F49" t="n">
-        <v>1.455498</v>
+        <v>0.332557</v>
       </c>
       <c r="G49" t="n">
-        <v>98.36065600000001</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
@@ -1673,10 +1673,10 @@
         <v>60</v>
       </c>
       <c r="E50" t="n">
-        <v>5.757676</v>
+        <v>5.757004</v>
       </c>
       <c r="F50" t="n">
-        <v>1.45567</v>
+        <v>1.412168</v>
       </c>
       <c r="G50" t="n">
         <v>98.36065600000001</v>
@@ -1685,32 +1685,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="D51" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E51" t="n">
-        <v>2.185796</v>
+        <v>5.757676</v>
       </c>
       <c r="F51" t="n">
-        <v>0.714468</v>
+        <v>1.412335</v>
       </c>
       <c r="G51" t="n">
-        <v>95.08196700000001</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
@@ -1723,10 +1723,10 @@
         <v>58</v>
       </c>
       <c r="E52" t="n">
-        <v>2.329166</v>
+        <v>2.185796</v>
       </c>
       <c r="F52" t="n">
-        <v>1.515494</v>
+        <v>0.714468</v>
       </c>
       <c r="G52" t="n">
         <v>95.08196700000001</v>
@@ -1735,7 +1735,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
@@ -1748,10 +1748,10 @@
         <v>58</v>
       </c>
       <c r="E53" t="n">
-        <v>2.079394</v>
+        <v>2.329166</v>
       </c>
       <c r="F53" t="n">
-        <v>0.242446</v>
+        <v>1.515494</v>
       </c>
       <c r="G53" t="n">
         <v>95.08196700000001</v>
@@ -1760,57 +1760,57 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D54" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.407403</v>
+        <v>2.079394</v>
       </c>
       <c r="F54" t="n">
-        <v>0.5941920000000001</v>
+        <v>0.242446</v>
       </c>
       <c r="G54" t="n">
-        <v>96.721311</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>44773</v>
+        <v>44469</v>
       </c>
       <c r="C55" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D55" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E55" t="n">
-        <v>10.069235</v>
+        <v>-0.407403</v>
       </c>
       <c r="F55" t="n">
-        <v>4.443025</v>
+        <v>0.5941920000000001</v>
       </c>
       <c r="G55" t="n">
-        <v>80.32786900000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
@@ -1823,10 +1823,10 @@
         <v>49</v>
       </c>
       <c r="E56" t="n">
-        <v>10.074751</v>
+        <v>10.069235</v>
       </c>
       <c r="F56" t="n">
-        <v>2.772183</v>
+        <v>4.443025</v>
       </c>
       <c r="G56" t="n">
         <v>80.32786900000001</v>
@@ -1835,7 +1835,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
@@ -1848,10 +1848,10 @@
         <v>49</v>
       </c>
       <c r="E57" t="n">
-        <v>10.124804</v>
+        <v>10.074751</v>
       </c>
       <c r="F57" t="n">
-        <v>4.098046</v>
+        <v>2.772183</v>
       </c>
       <c r="G57" t="n">
         <v>80.32786900000001</v>
@@ -1860,32 +1860,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>44469</v>
+        <v>44773</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D58" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E58" t="n">
-        <v>1</v>
+        <v>10.124804</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.25</v>
+        <v>4.098046</v>
       </c>
       <c r="G58" t="n">
-        <v>98.36065600000001</v>
+        <v>80.32786900000001</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
@@ -1898,10 +1898,10 @@
         <v>60</v>
       </c>
       <c r="E59" t="n">
-        <v>0.001073</v>
+        <v>1</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.000697</v>
+        <v>-0.25</v>
       </c>
       <c r="G59" t="n">
         <v>98.36065600000001</v>
@@ -1910,57 +1910,57 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="D60" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.03</v>
+        <v>0.001073</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.06</v>
+        <v>-0.000717</v>
       </c>
       <c r="G60" t="n">
-        <v>95.08196700000001</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="D61" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.13</v>
+        <v>0.001073</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.06</v>
+        <v>-0.000708</v>
       </c>
       <c r="G61" t="n">
-        <v>95.08196700000001</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
@@ -1973,10 +1973,10 @@
         <v>58</v>
       </c>
       <c r="E62" t="n">
-        <v>0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="G62" t="n">
         <v>95.08196700000001</v>
@@ -1985,7 +1985,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
@@ -1998,12 +1998,62 @@
         <v>58</v>
       </c>
       <c r="E63" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="F63" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="G63" t="n">
+        <v>95.08196700000001</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
+        </is>
+      </c>
+      <c r="B64" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="C64" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="D64" t="n">
+        <v>58</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F64" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G64" t="n">
+        <v>95.08196700000001</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_juros_credito_total</t>
+        </is>
+      </c>
+      <c r="B65" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="C65" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="D65" t="n">
+        <v>58</v>
+      </c>
+      <c r="E65" t="n">
         <v>0.5</v>
       </c>
-      <c r="F63" t="n">
+      <c r="F65" t="n">
         <v>0.22</v>
       </c>
-      <c r="G63" t="n">
+      <c r="G65" t="n">
         <v>95.08196700000001</v>
       </c>
     </row>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -476,7 +476,7 @@
         <v>118781</v>
       </c>
       <c r="F2" t="n">
-        <v>174577</v>
+        <v>175329.453125</v>
       </c>
       <c r="G2" t="n">
         <v>100</v>
@@ -501,7 +501,7 @@
         <v>114.080002</v>
       </c>
       <c r="F3" t="n">
-        <v>169.009995</v>
+        <v>172.399994</v>
       </c>
       <c r="G3" t="n">
         <v>100</v>
@@ -526,7 +526,7 @@
         <v>136.330002</v>
       </c>
       <c r="F4" t="n">
-        <v>102.639999</v>
+        <v>105.360001</v>
       </c>
       <c r="G4" t="n">
         <v>100</v>
@@ -551,7 +551,7 @@
         <v>254</v>
       </c>
       <c r="F5" t="n">
-        <v>444.700012</v>
+        <v>450.690002</v>
       </c>
       <c r="G5" t="n">
         <v>100</v>
@@ -576,7 +576,7 @@
         <v>5.1829</v>
       </c>
       <c r="F6" t="n">
-        <v>5.148</v>
+        <v>5.1611</v>
       </c>
       <c r="G6" t="n">
         <v>100</v>
@@ -601,7 +601,7 @@
         <v>6.1119</v>
       </c>
       <c r="F7" t="n">
-        <v>6.0044</v>
+        <v>6.013</v>
       </c>
       <c r="G7" t="n">
         <v>100</v>
@@ -626,7 +626,7 @@
         <v>4522.680176</v>
       </c>
       <c r="F8" t="n">
-        <v>7677.279785</v>
+        <v>7730.990234</v>
       </c>
       <c r="G8" t="n">
         <v>100</v>
@@ -651,7 +651,7 @@
         <v>15259.240234</v>
       </c>
       <c r="F9" t="n">
-        <v>26151.300781</v>
+        <v>26541.351562</v>
       </c>
       <c r="G9" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
         <v>35360.730469</v>
       </c>
       <c r="F10" t="n">
-        <v>53577.398438</v>
+        <v>53569.441406</v>
       </c>
       <c r="G10" t="n">
         <v>100</v>
@@ -701,7 +701,7 @@
         <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4670.700195</v>
+        <v>4660.600098</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
@@ -726,7 +726,7 @@
         <v>68.5</v>
       </c>
       <c r="F12" t="n">
-        <v>80.139999</v>
+        <v>83.639999</v>
       </c>
       <c r="G12" t="n">
         <v>100</v>
@@ -751,7 +751,7 @@
         <v>72.989998</v>
       </c>
       <c r="F13" t="n">
-        <v>84.910004</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="G13" t="n">
         <v>100</v>
@@ -776,7 +776,7 @@
         <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1240.75</v>
+        <v>1263.5</v>
       </c>
       <c r="G14" t="n">
         <v>100</v>
@@ -801,7 +801,7 @@
         <v>534</v>
       </c>
       <c r="F15" t="n">
-        <v>528</v>
+        <v>531.5</v>
       </c>
       <c r="G15" t="n">
         <v>100</v>
@@ -826,7 +826,7 @@
         <v>-6.568391</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.922483</v>
+        <v>-1.499754</v>
       </c>
       <c r="G16" t="n">
         <v>98.36065600000001</v>
@@ -851,7 +851,7 @@
         <v>-6.653229</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.433899</v>
+        <v>-1.496978</v>
       </c>
       <c r="G17" t="n">
         <v>98.36065600000001</v>
@@ -876,7 +876,7 @@
         <v>-6.550283</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.298369</v>
+        <v>-1.762237</v>
       </c>
       <c r="G18" t="n">
         <v>98.36065600000001</v>
@@ -901,7 +901,7 @@
         <v>0.393701</v>
       </c>
       <c r="F19" t="n">
-        <v>3.807278</v>
+        <v>5.205534</v>
       </c>
       <c r="G19" t="n">
         <v>98.36065600000001</v>
@@ -926,7 +926,7 @@
         <v>4.464682</v>
       </c>
       <c r="F20" t="n">
-        <v>1.37649</v>
+        <v>1.634464</v>
       </c>
       <c r="G20" t="n">
         <v>98.36065600000001</v>
@@ -951,7 +951,7 @@
         <v>2.725834</v>
       </c>
       <c r="F21" t="n">
-        <v>2.675243</v>
+        <v>2.822307</v>
       </c>
       <c r="G21" t="n">
         <v>98.36065600000001</v>
@@ -976,7 +976,7 @@
         <v>-4.756917</v>
       </c>
       <c r="F22" t="n">
-        <v>2.504227</v>
+        <v>3.221349</v>
       </c>
       <c r="G22" t="n">
         <v>98.36065600000001</v>
@@ -1001,7 +1001,7 @@
         <v>-5.312585</v>
       </c>
       <c r="F23" t="n">
-        <v>3.063986</v>
+        <v>4.601202</v>
       </c>
       <c r="G23" t="n">
         <v>98.36065600000001</v>
@@ -1026,7 +1026,7 @@
         <v>-4.289528</v>
       </c>
       <c r="F24" t="n">
-        <v>2.081293</v>
+        <v>2.066132</v>
       </c>
       <c r="G24" t="n">
         <v>98.36065600000001</v>
@@ -1051,7 +1051,7 @@
         <v>-3.289254</v>
       </c>
       <c r="F25" t="n">
-        <v>15.351562</v>
+        <v>15.102121</v>
       </c>
       <c r="G25" t="n">
         <v>98.36065600000001</v>
@@ -1076,7 +1076,7 @@
         <v>9.532845</v>
       </c>
       <c r="F26" t="n">
-        <v>-5.350182</v>
+        <v>-1.216486</v>
       </c>
       <c r="G26" t="n">
         <v>98.36065600000001</v>
@@ -1101,7 +1101,7 @@
         <v>7.576379</v>
       </c>
       <c r="F27" t="n">
-        <v>-5.781179</v>
+        <v>-1.719932</v>
       </c>
       <c r="G27" t="n">
         <v>98.36065600000001</v>
@@ -1126,7 +1126,7 @@
         <v>-3.291627</v>
       </c>
       <c r="F28" t="n">
-        <v>5.866041</v>
+        <v>7.807167</v>
       </c>
       <c r="G28" t="n">
         <v>98.36065600000001</v>
@@ -1151,7 +1151,7 @@
         <v>0.514981</v>
       </c>
       <c r="F29" t="n">
-        <v>19.795803</v>
+        <v>20.589904</v>
       </c>
       <c r="G29" t="n">
         <v>98.36065600000001</v>
@@ -1201,7 +1201,7 @@
         <v>0.01993</v>
       </c>
       <c r="F31" t="n">
-        <v>0.051814</v>
+        <v>0.051805</v>
       </c>
       <c r="G31" t="n">
         <v>100</v>
@@ -1226,7 +1226,7 @@
         <v>0.01993</v>
       </c>
       <c r="F32" t="n">
-        <v>0.051823</v>
+        <v>0.051805</v>
       </c>
       <c r="G32" t="n">
         <v>100</v>
@@ -1376,7 +1376,7 @@
         <v>5.1433</v>
       </c>
       <c r="F38" t="n">
-        <v>5.149</v>
+        <v>5.1642</v>
       </c>
       <c r="G38" t="n">
         <v>100</v>
@@ -1401,7 +1401,7 @@
         <v>5.1427</v>
       </c>
       <c r="F39" t="n">
-        <v>5.1484</v>
+        <v>5.1637</v>
       </c>
       <c r="G39" t="n">
         <v>100</v>
@@ -1676,7 +1676,7 @@
         <v>5.757004</v>
       </c>
       <c r="F50" t="n">
-        <v>1.412168</v>
+        <v>1.71154</v>
       </c>
       <c r="G50" t="n">
         <v>98.36065600000001</v>
@@ -1701,7 +1701,7 @@
         <v>5.757676</v>
       </c>
       <c r="F51" t="n">
-        <v>1.412335</v>
+        <v>1.713712</v>
       </c>
       <c r="G51" t="n">
         <v>98.36065600000001</v>
@@ -1926,7 +1926,7 @@
         <v>0.001073</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.000717</v>
+        <v>-0.000726</v>
       </c>
       <c r="G60" t="n">
         <v>98.36065600000001</v>
@@ -1951,7 +1951,7 @@
         <v>0.001073</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.000708</v>
+        <v>-0.000726</v>
       </c>
       <c r="G61" t="n">
         <v>98.36065600000001</v>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -476,7 +476,7 @@
         <v>118781</v>
       </c>
       <c r="F2" t="n">
-        <v>175329.453125</v>
+        <v>175664.625</v>
       </c>
       <c r="G2" t="n">
         <v>100</v>
@@ -501,7 +501,7 @@
         <v>114.080002</v>
       </c>
       <c r="F3" t="n">
-        <v>172.399994</v>
+        <v>172.720001</v>
       </c>
       <c r="G3" t="n">
         <v>100</v>
@@ -526,7 +526,7 @@
         <v>136.330002</v>
       </c>
       <c r="F4" t="n">
-        <v>105.360001</v>
+        <v>104.580002</v>
       </c>
       <c r="G4" t="n">
         <v>100</v>
@@ -551,7 +551,7 @@
         <v>254</v>
       </c>
       <c r="F5" t="n">
-        <v>450.690002</v>
+        <v>452.049988</v>
       </c>
       <c r="G5" t="n">
         <v>100</v>
@@ -576,7 +576,7 @@
         <v>5.1829</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1611</v>
+        <v>5.1925</v>
       </c>
       <c r="G6" t="n">
         <v>100</v>
@@ -601,7 +601,7 @@
         <v>6.1119</v>
       </c>
       <c r="F7" t="n">
-        <v>6.013</v>
+        <v>6.0137</v>
       </c>
       <c r="G7" t="n">
         <v>100</v>
@@ -626,7 +626,7 @@
         <v>4522.680176</v>
       </c>
       <c r="F8" t="n">
-        <v>7730.990234</v>
+        <v>7711.759766</v>
       </c>
       <c r="G8" t="n">
         <v>100</v>
@@ -651,7 +651,7 @@
         <v>15259.240234</v>
       </c>
       <c r="F9" t="n">
-        <v>26541.351562</v>
+        <v>26402.423828</v>
       </c>
       <c r="G9" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
         <v>35360.730469</v>
       </c>
       <c r="F10" t="n">
-        <v>53569.441406</v>
+        <v>53559.988281</v>
       </c>
       <c r="G10" t="n">
         <v>100</v>
@@ -701,7 +701,7 @@
         <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4660.600098</v>
+        <v>4505.799805</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
@@ -726,7 +726,7 @@
         <v>68.5</v>
       </c>
       <c r="F12" t="n">
-        <v>83.639999</v>
+        <v>83.400002</v>
       </c>
       <c r="G12" t="n">
         <v>100</v>
@@ -751,7 +751,7 @@
         <v>72.989998</v>
       </c>
       <c r="F13" t="n">
-        <v>88.56999999999999</v>
+        <v>88.230003</v>
       </c>
       <c r="G13" t="n">
         <v>100</v>
@@ -776,7 +776,7 @@
         <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1263.5</v>
+        <v>1287.75</v>
       </c>
       <c r="G14" t="n">
         <v>100</v>
@@ -801,7 +801,7 @@
         <v>534</v>
       </c>
       <c r="F15" t="n">
-        <v>531.5</v>
+        <v>536.25</v>
       </c>
       <c r="G15" t="n">
         <v>100</v>
@@ -826,7 +826,7 @@
         <v>-6.568391</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.499754</v>
+        <v>-1.311454</v>
       </c>
       <c r="G16" t="n">
         <v>98.36065600000001</v>
@@ -851,7 +851,7 @@
         <v>-6.653229</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.496978</v>
+        <v>-1.314137</v>
       </c>
       <c r="G17" t="n">
         <v>98.36065600000001</v>
@@ -876,7 +876,7 @@
         <v>-6.550283</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.762237</v>
+        <v>-2.489509</v>
       </c>
       <c r="G18" t="n">
         <v>98.36065600000001</v>
@@ -901,7 +901,7 @@
         <v>0.393701</v>
       </c>
       <c r="F19" t="n">
-        <v>5.205534</v>
+        <v>5.522998</v>
       </c>
       <c r="G19" t="n">
         <v>98.36065600000001</v>
@@ -926,7 +926,7 @@
         <v>4.464682</v>
       </c>
       <c r="F20" t="n">
-        <v>1.634464</v>
+        <v>2.252809</v>
       </c>
       <c r="G20" t="n">
         <v>98.36065600000001</v>
@@ -951,7 +951,7 @@
         <v>2.725834</v>
       </c>
       <c r="F21" t="n">
-        <v>2.822307</v>
+        <v>2.834277</v>
       </c>
       <c r="G21" t="n">
         <v>98.36065600000001</v>
@@ -976,7 +976,7 @@
         <v>-4.756917</v>
       </c>
       <c r="F22" t="n">
-        <v>3.221349</v>
+        <v>2.964591</v>
       </c>
       <c r="G22" t="n">
         <v>98.36065600000001</v>
@@ -1001,7 +1001,7 @@
         <v>-5.312585</v>
       </c>
       <c r="F23" t="n">
-        <v>4.601202</v>
+        <v>4.053678</v>
       </c>
       <c r="G23" t="n">
         <v>98.36065600000001</v>
@@ -1026,7 +1026,7 @@
         <v>-4.289528</v>
       </c>
       <c r="F24" t="n">
-        <v>2.066132</v>
+        <v>2.048121</v>
       </c>
       <c r="G24" t="n">
         <v>98.36065600000001</v>
@@ -1051,7 +1051,7 @@
         <v>-3.289254</v>
       </c>
       <c r="F25" t="n">
-        <v>15.102121</v>
+        <v>11.279042</v>
       </c>
       <c r="G25" t="n">
         <v>98.36065600000001</v>
@@ -1076,7 +1076,7 @@
         <v>9.532845</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.216486</v>
+        <v>-1.499937</v>
       </c>
       <c r="G26" t="n">
         <v>98.36065600000001</v>
@@ -1101,7 +1101,7 @@
         <v>7.576379</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.719932</v>
+        <v>-2.097203</v>
       </c>
       <c r="G27" t="n">
         <v>98.36065600000001</v>
@@ -1126,7 +1126,7 @@
         <v>-3.291627</v>
       </c>
       <c r="F28" t="n">
-        <v>7.807167</v>
+        <v>9.87628</v>
       </c>
       <c r="G28" t="n">
         <v>98.36065600000001</v>
@@ -1151,7 +1151,7 @@
         <v>0.514981</v>
       </c>
       <c r="F29" t="n">
-        <v>20.589904</v>
+        <v>21.667612</v>
       </c>
       <c r="G29" t="n">
         <v>98.36065600000001</v>
@@ -1201,7 +1201,7 @@
         <v>0.01993</v>
       </c>
       <c r="F31" t="n">
-        <v>0.051805</v>
+        <v>0.051798</v>
       </c>
       <c r="G31" t="n">
         <v>100</v>
@@ -1226,7 +1226,7 @@
         <v>0.01993</v>
       </c>
       <c r="F32" t="n">
-        <v>0.051805</v>
+        <v>0.051798</v>
       </c>
       <c r="G32" t="n">
         <v>100</v>
@@ -1267,19 +1267,19 @@
         <v>44439</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D34" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E34" t="n">
         <v>0.66</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.16</v>
+        <v>-0.22</v>
       </c>
       <c r="G34" t="n">
-        <v>98.36065600000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35">
@@ -1376,7 +1376,7 @@
         <v>5.1433</v>
       </c>
       <c r="F38" t="n">
-        <v>5.1642</v>
+        <v>5.2005</v>
       </c>
       <c r="G38" t="n">
         <v>100</v>
@@ -1401,7 +1401,7 @@
         <v>5.1427</v>
       </c>
       <c r="F39" t="n">
-        <v>5.1637</v>
+        <v>5.1999</v>
       </c>
       <c r="G39" t="n">
         <v>100</v>
@@ -1417,19 +1417,19 @@
         <v>44439</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D40" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E40" t="n">
         <v>4346060</v>
       </c>
       <c r="F40" t="n">
-        <v>7355800</v>
+        <v>7372243</v>
       </c>
       <c r="G40" t="n">
-        <v>96.721311</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="41">
@@ -1442,19 +1442,19 @@
         <v>44439</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D41" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E41" t="n">
         <v>1851006</v>
       </c>
       <c r="F41" t="n">
-        <v>2749001</v>
+        <v>2731513</v>
       </c>
       <c r="G41" t="n">
-        <v>96.721311</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="42">
@@ -1467,19 +1467,19 @@
         <v>44439</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D42" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E42" t="n">
         <v>2495054</v>
       </c>
       <c r="F42" t="n">
-        <v>4606799</v>
+        <v>4640730</v>
       </c>
       <c r="G42" t="n">
-        <v>96.721311</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="43">
@@ -1492,19 +1492,19 @@
         <v>44439</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D43" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E43" t="n">
         <v>2.37</v>
       </c>
       <c r="F43" t="n">
-        <v>4.68</v>
+        <v>4.88</v>
       </c>
       <c r="G43" t="n">
-        <v>96.721311</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="44">
@@ -1517,19 +1517,19 @@
         <v>44439</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D44" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E44" t="n">
         <v>1.56</v>
       </c>
       <c r="F44" t="n">
-        <v>3.19</v>
+        <v>3.31</v>
       </c>
       <c r="G44" t="n">
-        <v>96.721311</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="45">
@@ -1542,19 +1542,19 @@
         <v>44439</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D45" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E45" t="n">
         <v>2.96</v>
       </c>
       <c r="F45" t="n">
-        <v>5.57</v>
+        <v>5.81</v>
       </c>
       <c r="G45" t="n">
-        <v>96.721311</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="46">
@@ -1567,19 +1567,19 @@
         <v>44439</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D46" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E46" t="n">
         <v>20.92</v>
       </c>
       <c r="F46" t="n">
-        <v>33.44</v>
+        <v>32.08</v>
       </c>
       <c r="G46" t="n">
-        <v>96.721311</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="47">
@@ -1676,7 +1676,7 @@
         <v>5.757004</v>
       </c>
       <c r="F50" t="n">
-        <v>1.71154</v>
+        <v>2.426487</v>
       </c>
       <c r="G50" t="n">
         <v>98.36065600000001</v>
@@ -1701,7 +1701,7 @@
         <v>5.757676</v>
       </c>
       <c r="F51" t="n">
-        <v>1.713712</v>
+        <v>2.426773</v>
       </c>
       <c r="G51" t="n">
         <v>98.36065600000001</v>
@@ -1717,19 +1717,19 @@
         <v>44469</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D52" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E52" t="n">
         <v>2.185796</v>
       </c>
       <c r="F52" t="n">
-        <v>0.714468</v>
+        <v>0.257708</v>
       </c>
       <c r="G52" t="n">
-        <v>95.08196700000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="53">
@@ -1742,19 +1742,19 @@
         <v>44469</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D53" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E53" t="n">
         <v>2.329166</v>
       </c>
       <c r="F53" t="n">
-        <v>1.515494</v>
+        <v>-0.694824</v>
       </c>
       <c r="G53" t="n">
-        <v>95.08196700000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="54">
@@ -1767,19 +1767,19 @@
         <v>44469</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D54" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E54" t="n">
         <v>2.079394</v>
       </c>
       <c r="F54" t="n">
-        <v>0.242446</v>
+        <v>0.826955</v>
       </c>
       <c r="G54" t="n">
-        <v>95.08196700000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="55">
@@ -1842,19 +1842,19 @@
         <v>44773</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D57" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E57" t="n">
         <v>10.074751</v>
       </c>
       <c r="F57" t="n">
-        <v>2.772183</v>
+        <v>2.178243</v>
       </c>
       <c r="G57" t="n">
-        <v>80.32786900000001</v>
+        <v>81.967213</v>
       </c>
     </row>
     <row r="58">
@@ -1926,7 +1926,7 @@
         <v>0.001073</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.000726</v>
+        <v>-0.000733</v>
       </c>
       <c r="G60" t="n">
         <v>98.36065600000001</v>
@@ -1951,7 +1951,7 @@
         <v>0.001073</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.000726</v>
+        <v>-0.000733</v>
       </c>
       <c r="G61" t="n">
         <v>98.36065600000001</v>
@@ -1967,19 +1967,19 @@
         <v>44469</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D62" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E62" t="n">
         <v>-0.03</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.06</v>
+        <v>0.3</v>
       </c>
       <c r="G62" t="n">
-        <v>95.08196700000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="63">
@@ -1992,19 +1992,19 @@
         <v>44469</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D63" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E63" t="n">
         <v>-0.13</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.06</v>
+        <v>0.13</v>
       </c>
       <c r="G63" t="n">
-        <v>95.08196700000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="64">
@@ -2017,19 +2017,19 @@
         <v>44469</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D64" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E64" t="n">
         <v>0.05</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.05</v>
+        <v>0.39</v>
       </c>
       <c r="G64" t="n">
-        <v>95.08196700000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="65">
@@ -2042,19 +2042,19 @@
         <v>44469</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D65" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E65" t="n">
         <v>0.5</v>
       </c>
       <c r="F65" t="n">
-        <v>0.22</v>
+        <v>-1.25</v>
       </c>
       <c r="G65" t="n">
-        <v>95.08196700000001</v>
+        <v>96.721311</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
         <v>118781</v>
       </c>
       <c r="F2" t="n">
-        <v>175664.625</v>
+        <v>175135</v>
       </c>
       <c r="G2" t="n">
         <v>100</v>
@@ -501,7 +501,7 @@
         <v>114.080002</v>
       </c>
       <c r="F3" t="n">
-        <v>172.720001</v>
+        <v>172.399994</v>
       </c>
       <c r="G3" t="n">
         <v>100</v>
@@ -526,7 +526,7 @@
         <v>136.330002</v>
       </c>
       <c r="F4" t="n">
-        <v>104.580002</v>
+        <v>105.169998</v>
       </c>
       <c r="G4" t="n">
         <v>100</v>
@@ -551,7 +551,7 @@
         <v>254</v>
       </c>
       <c r="F5" t="n">
-        <v>452.049988</v>
+        <v>450</v>
       </c>
       <c r="G5" t="n">
         <v>100</v>
@@ -576,7 +576,7 @@
         <v>5.1829</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1925</v>
+        <v>5.2054</v>
       </c>
       <c r="G6" t="n">
         <v>100</v>
@@ -601,7 +601,7 @@
         <v>6.1119</v>
       </c>
       <c r="F7" t="n">
-        <v>6.0137</v>
+        <v>6.0054</v>
       </c>
       <c r="G7" t="n">
         <v>100</v>
@@ -626,7 +626,7 @@
         <v>4522.680176</v>
       </c>
       <c r="F8" t="n">
-        <v>7711.759766</v>
+        <v>7730.990234</v>
       </c>
       <c r="G8" t="n">
         <v>100</v>
@@ -651,7 +651,7 @@
         <v>15259.240234</v>
       </c>
       <c r="F9" t="n">
-        <v>26402.423828</v>
+        <v>26541.349609</v>
       </c>
       <c r="G9" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
         <v>35360.730469</v>
       </c>
       <c r="F10" t="n">
-        <v>53559.988281</v>
+        <v>53569.441406</v>
       </c>
       <c r="G10" t="n">
         <v>100</v>
@@ -701,7 +701,7 @@
         <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4505.799805</v>
+        <v>4609.700195</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
@@ -726,7 +726,7 @@
         <v>68.5</v>
       </c>
       <c r="F12" t="n">
-        <v>83.400002</v>
+        <v>83.529999</v>
       </c>
       <c r="G12" t="n">
         <v>100</v>
@@ -751,7 +751,7 @@
         <v>72.989998</v>
       </c>
       <c r="F13" t="n">
-        <v>88.230003</v>
+        <v>89.699997</v>
       </c>
       <c r="G13" t="n">
         <v>100</v>
@@ -776,7 +776,7 @@
         <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1287.75</v>
+        <v>1256.5</v>
       </c>
       <c r="G14" t="n">
         <v>100</v>
@@ -801,7 +801,7 @@
         <v>534</v>
       </c>
       <c r="F15" t="n">
-        <v>536.25</v>
+        <v>510.25</v>
       </c>
       <c r="G15" t="n">
         <v>100</v>
@@ -826,7 +826,7 @@
         <v>-6.568391</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.311454</v>
+        <v>-1.608998</v>
       </c>
       <c r="G16" t="n">
         <v>98.36065600000001</v>
@@ -851,7 +851,7 @@
         <v>-6.653229</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.314137</v>
+        <v>-1.496978</v>
       </c>
       <c r="G17" t="n">
         <v>98.36065600000001</v>
@@ -876,7 +876,7 @@
         <v>-6.550283</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.489509</v>
+        <v>-1.939396</v>
       </c>
       <c r="G18" t="n">
         <v>98.36065600000001</v>
@@ -901,7 +901,7 @@
         <v>0.393701</v>
       </c>
       <c r="F19" t="n">
-        <v>5.522998</v>
+        <v>5.044465</v>
       </c>
       <c r="G19" t="n">
         <v>98.36065600000001</v>
@@ -926,7 +926,7 @@
         <v>4.464682</v>
       </c>
       <c r="F20" t="n">
-        <v>2.252809</v>
+        <v>2.506839</v>
       </c>
       <c r="G20" t="n">
         <v>98.36065600000001</v>
@@ -951,7 +951,7 @@
         <v>2.725834</v>
       </c>
       <c r="F21" t="n">
-        <v>2.834277</v>
+        <v>2.69235</v>
       </c>
       <c r="G21" t="n">
         <v>98.36065600000001</v>
@@ -976,7 +976,7 @@
         <v>-4.756917</v>
       </c>
       <c r="F22" t="n">
-        <v>2.964591</v>
+        <v>3.221349</v>
       </c>
       <c r="G22" t="n">
         <v>98.36065600000001</v>
@@ -1001,7 +1001,7 @@
         <v>-5.312585</v>
       </c>
       <c r="F23" t="n">
-        <v>4.053678</v>
+        <v>4.601194</v>
       </c>
       <c r="G23" t="n">
         <v>98.36065600000001</v>
@@ -1026,7 +1026,7 @@
         <v>-4.289528</v>
       </c>
       <c r="F24" t="n">
-        <v>2.048121</v>
+        <v>2.066132</v>
       </c>
       <c r="G24" t="n">
         <v>98.36065600000001</v>
@@ -1051,7 +1051,7 @@
         <v>-3.289254</v>
       </c>
       <c r="F25" t="n">
-        <v>11.279042</v>
+        <v>13.845054</v>
       </c>
       <c r="G25" t="n">
         <v>98.36065600000001</v>
@@ -1076,7 +1076,7 @@
         <v>9.532845</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.499937</v>
+        <v>-1.346403</v>
       </c>
       <c r="G26" t="n">
         <v>98.36065600000001</v>
@@ -1101,7 +1101,7 @@
         <v>7.576379</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.097203</v>
+        <v>-0.466052</v>
       </c>
       <c r="G27" t="n">
         <v>98.36065600000001</v>
@@ -1126,7 +1126,7 @@
         <v>-3.291627</v>
       </c>
       <c r="F28" t="n">
-        <v>9.87628</v>
+        <v>7.209898</v>
       </c>
       <c r="G28" t="n">
         <v>98.36065600000001</v>
@@ -1151,7 +1151,7 @@
         <v>0.514981</v>
       </c>
       <c r="F29" t="n">
-        <v>21.667612</v>
+        <v>15.768576</v>
       </c>
       <c r="G29" t="n">
         <v>98.36065600000001</v>
@@ -1201,7 +1201,7 @@
         <v>0.01993</v>
       </c>
       <c r="F31" t="n">
-        <v>0.051798</v>
+        <v>0.051791</v>
       </c>
       <c r="G31" t="n">
         <v>100</v>
@@ -1560,7 +1560,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
@@ -1573,10 +1573,10 @@
         <v>60</v>
       </c>
       <c r="E46" t="n">
-        <v>20.92</v>
+        <v>370395</v>
       </c>
       <c r="F46" t="n">
-        <v>32.08</v>
+        <v>369742</v>
       </c>
       <c r="G46" t="n">
         <v>98.36065600000001</v>
@@ -1585,32 +1585,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D47" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E47" t="n">
-        <v>370395</v>
+        <v>-0.064886</v>
       </c>
       <c r="F47" t="n">
-        <v>369742</v>
+        <v>-0.6395690000000001</v>
       </c>
       <c r="G47" t="n">
-        <v>98.36065600000001</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
@@ -1623,10 +1623,10 @@
         <v>58</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.064886</v>
+        <v>-2.103216</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.6395690000000001</v>
+        <v>0.332557</v>
       </c>
       <c r="G48" t="n">
         <v>95.08196700000001</v>
@@ -1635,32 +1635,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="D49" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E49" t="n">
-        <v>-2.103216</v>
+        <v>5.757004</v>
       </c>
       <c r="F49" t="n">
-        <v>0.332557</v>
+        <v>2.426487</v>
       </c>
       <c r="G49" t="n">
-        <v>95.08196700000001</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
@@ -1673,10 +1673,10 @@
         <v>60</v>
       </c>
       <c r="E50" t="n">
-        <v>5.757004</v>
+        <v>5.757676</v>
       </c>
       <c r="F50" t="n">
-        <v>2.426487</v>
+        <v>2.426773</v>
       </c>
       <c r="G50" t="n">
         <v>98.36065600000001</v>
@@ -1685,32 +1685,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D51" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E51" t="n">
-        <v>5.757676</v>
+        <v>2.185796</v>
       </c>
       <c r="F51" t="n">
-        <v>2.426773</v>
+        <v>0.257708</v>
       </c>
       <c r="G51" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
@@ -1723,10 +1723,10 @@
         <v>59</v>
       </c>
       <c r="E52" t="n">
-        <v>2.185796</v>
+        <v>2.329166</v>
       </c>
       <c r="F52" t="n">
-        <v>0.257708</v>
+        <v>-0.694824</v>
       </c>
       <c r="G52" t="n">
         <v>96.721311</v>
@@ -1735,7 +1735,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
@@ -1748,10 +1748,10 @@
         <v>59</v>
       </c>
       <c r="E53" t="n">
-        <v>2.329166</v>
+        <v>2.079394</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.694824</v>
+        <v>0.826955</v>
       </c>
       <c r="G53" t="n">
         <v>96.721311</v>
@@ -1760,7 +1760,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
@@ -1773,10 +1773,10 @@
         <v>59</v>
       </c>
       <c r="E54" t="n">
-        <v>2.079394</v>
+        <v>-0.407403</v>
       </c>
       <c r="F54" t="n">
-        <v>0.826955</v>
+        <v>0.5941920000000001</v>
       </c>
       <c r="G54" t="n">
         <v>96.721311</v>
@@ -1785,107 +1785,107 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>44469</v>
+        <v>44773</v>
       </c>
       <c r="C55" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D55" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.407403</v>
+        <v>10.069235</v>
       </c>
       <c r="F55" t="n">
-        <v>0.5941920000000001</v>
+        <v>4.443025</v>
       </c>
       <c r="G55" t="n">
-        <v>96.721311</v>
+        <v>80.32786900000001</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
         <v>44773</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D56" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E56" t="n">
-        <v>10.069235</v>
+        <v>10.074751</v>
       </c>
       <c r="F56" t="n">
-        <v>4.443025</v>
+        <v>2.178243</v>
       </c>
       <c r="G56" t="n">
-        <v>80.32786900000001</v>
+        <v>81.967213</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
         <v>44773</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D57" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E57" t="n">
-        <v>10.074751</v>
+        <v>10.124804</v>
       </c>
       <c r="F57" t="n">
-        <v>2.178243</v>
+        <v>4.098046</v>
       </c>
       <c r="G57" t="n">
-        <v>81.967213</v>
+        <v>80.32786900000001</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>44773</v>
+        <v>44469</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D58" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E58" t="n">
-        <v>10.124804</v>
+        <v>1</v>
       </c>
       <c r="F58" t="n">
-        <v>4.098046</v>
+        <v>-0.25</v>
       </c>
       <c r="G58" t="n">
-        <v>80.32786900000001</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
@@ -1898,10 +1898,10 @@
         <v>60</v>
       </c>
       <c r="E59" t="n">
-        <v>1</v>
+        <v>0.001073</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.25</v>
+        <v>-0.00074</v>
       </c>
       <c r="G59" t="n">
         <v>98.36065600000001</v>
@@ -1910,7 +1910,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
@@ -1935,32 +1935,32 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D61" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E61" t="n">
-        <v>0.001073</v>
+        <v>-0.03</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.000733</v>
+        <v>0.3</v>
       </c>
       <c r="G61" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
@@ -1973,10 +1973,10 @@
         <v>59</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.03</v>
+        <v>-0.13</v>
       </c>
       <c r="F62" t="n">
-        <v>0.3</v>
+        <v>0.13</v>
       </c>
       <c r="G62" t="n">
         <v>96.721311</v>
@@ -1985,7 +1985,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
@@ -1998,62 +1998,12 @@
         <v>59</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.13</v>
+        <v>0.05</v>
       </c>
       <c r="F63" t="n">
-        <v>0.13</v>
+        <v>0.39</v>
       </c>
       <c r="G63" t="n">
-        <v>96.721311</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
-        </is>
-      </c>
-      <c r="B64" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="C64" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="D64" t="n">
-        <v>59</v>
-      </c>
-      <c r="E64" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F64" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="G64" t="n">
-        <v>96.721311</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
-        </is>
-      </c>
-      <c r="B65" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="C65" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="D65" t="n">
-        <v>59</v>
-      </c>
-      <c r="E65" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F65" t="n">
-        <v>-1.25</v>
-      </c>
-      <c r="G65" t="n">
         <v>96.721311</v>
       </c>
     </row>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
         <v>118781</v>
       </c>
       <c r="F2" t="n">
-        <v>175135</v>
+        <v>175665</v>
       </c>
       <c r="G2" t="n">
         <v>100</v>
@@ -576,7 +576,7 @@
         <v>5.1829</v>
       </c>
       <c r="F6" t="n">
-        <v>5.2054</v>
+        <v>5.185</v>
       </c>
       <c r="G6" t="n">
         <v>100</v>
@@ -626,7 +626,7 @@
         <v>4522.680176</v>
       </c>
       <c r="F8" t="n">
-        <v>7730.990234</v>
+        <v>7711.759766</v>
       </c>
       <c r="G8" t="n">
         <v>100</v>
@@ -651,7 +651,7 @@
         <v>15259.240234</v>
       </c>
       <c r="F9" t="n">
-        <v>26541.349609</v>
+        <v>26402.419922</v>
       </c>
       <c r="G9" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
         <v>35360.730469</v>
       </c>
       <c r="F10" t="n">
-        <v>53569.441406</v>
+        <v>53559.988281</v>
       </c>
       <c r="G10" t="n">
         <v>100</v>
@@ -701,7 +701,7 @@
         <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4609.700195</v>
+        <v>4529.899902</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
@@ -726,7 +726,7 @@
         <v>68.5</v>
       </c>
       <c r="F12" t="n">
-        <v>83.529999</v>
+        <v>83.400002</v>
       </c>
       <c r="G12" t="n">
         <v>100</v>
@@ -751,7 +751,7 @@
         <v>72.989998</v>
       </c>
       <c r="F13" t="n">
-        <v>89.699997</v>
+        <v>88.099998</v>
       </c>
       <c r="G13" t="n">
         <v>100</v>
@@ -776,7 +776,7 @@
         <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1256.5</v>
+        <v>1288</v>
       </c>
       <c r="G14" t="n">
         <v>100</v>
@@ -801,7 +801,7 @@
         <v>534</v>
       </c>
       <c r="F15" t="n">
-        <v>510.25</v>
+        <v>536.5</v>
       </c>
       <c r="G15" t="n">
         <v>100</v>
@@ -826,7 +826,7 @@
         <v>-6.568391</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.608998</v>
+        <v>-1.311243</v>
       </c>
       <c r="G16" t="n">
         <v>98.36065600000001</v>
@@ -926,7 +926,7 @@
         <v>4.464682</v>
       </c>
       <c r="F20" t="n">
-        <v>2.506839</v>
+        <v>2.105113</v>
       </c>
       <c r="G20" t="n">
         <v>98.36065600000001</v>
@@ -976,7 +976,7 @@
         <v>-4.756917</v>
       </c>
       <c r="F22" t="n">
-        <v>3.221349</v>
+        <v>2.964591</v>
       </c>
       <c r="G22" t="n">
         <v>98.36065600000001</v>
@@ -1001,7 +1001,7 @@
         <v>-5.312585</v>
       </c>
       <c r="F23" t="n">
-        <v>4.601194</v>
+        <v>4.053663</v>
       </c>
       <c r="G23" t="n">
         <v>98.36065600000001</v>
@@ -1026,7 +1026,7 @@
         <v>-4.289528</v>
       </c>
       <c r="F24" t="n">
-        <v>2.066132</v>
+        <v>2.048121</v>
       </c>
       <c r="G24" t="n">
         <v>98.36065600000001</v>
@@ -1051,7 +1051,7 @@
         <v>-3.289254</v>
       </c>
       <c r="F25" t="n">
-        <v>13.845054</v>
+        <v>11.874239</v>
       </c>
       <c r="G25" t="n">
         <v>98.36065600000001</v>
@@ -1076,7 +1076,7 @@
         <v>9.532845</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.346403</v>
+        <v>-1.499937</v>
       </c>
       <c r="G26" t="n">
         <v>98.36065600000001</v>
@@ -1101,7 +1101,7 @@
         <v>7.576379</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.466052</v>
+        <v>-2.241461</v>
       </c>
       <c r="G27" t="n">
         <v>98.36065600000001</v>
@@ -1126,7 +1126,7 @@
         <v>-3.291627</v>
       </c>
       <c r="F28" t="n">
-        <v>7.209898</v>
+        <v>9.897610999999999</v>
       </c>
       <c r="G28" t="n">
         <v>98.36065600000001</v>
@@ -1151,7 +1151,7 @@
         <v>0.514981</v>
       </c>
       <c r="F29" t="n">
-        <v>15.768576</v>
+        <v>21.724334</v>
       </c>
       <c r="G29" t="n">
         <v>98.36065600000001</v>
@@ -1560,7 +1560,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
@@ -1573,10 +1573,10 @@
         <v>60</v>
       </c>
       <c r="E46" t="n">
-        <v>370395</v>
+        <v>20.92</v>
       </c>
       <c r="F46" t="n">
-        <v>369742</v>
+        <v>32.08</v>
       </c>
       <c r="G46" t="n">
         <v>98.36065600000001</v>
@@ -1585,32 +1585,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D47" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.064886</v>
+        <v>370395</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.6395690000000001</v>
+        <v>369742</v>
       </c>
       <c r="G47" t="n">
-        <v>95.08196700000001</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
@@ -1623,10 +1623,10 @@
         <v>58</v>
       </c>
       <c r="E48" t="n">
-        <v>-2.103216</v>
+        <v>-0.064886</v>
       </c>
       <c r="F48" t="n">
-        <v>0.332557</v>
+        <v>-0.6395690000000001</v>
       </c>
       <c r="G48" t="n">
         <v>95.08196700000001</v>
@@ -1635,32 +1635,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="D49" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E49" t="n">
-        <v>5.757004</v>
+        <v>-2.103216</v>
       </c>
       <c r="F49" t="n">
-        <v>2.426487</v>
+        <v>0.332557</v>
       </c>
       <c r="G49" t="n">
-        <v>98.36065600000001</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
@@ -1673,10 +1673,10 @@
         <v>60</v>
       </c>
       <c r="E50" t="n">
-        <v>5.757676</v>
+        <v>5.757004</v>
       </c>
       <c r="F50" t="n">
-        <v>2.426773</v>
+        <v>2.426487</v>
       </c>
       <c r="G50" t="n">
         <v>98.36065600000001</v>
@@ -1685,32 +1685,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D51" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E51" t="n">
-        <v>2.185796</v>
+        <v>5.757676</v>
       </c>
       <c r="F51" t="n">
-        <v>0.257708</v>
+        <v>2.426773</v>
       </c>
       <c r="G51" t="n">
-        <v>96.721311</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
@@ -1723,10 +1723,10 @@
         <v>59</v>
       </c>
       <c r="E52" t="n">
-        <v>2.329166</v>
+        <v>2.185796</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.694824</v>
+        <v>0.257708</v>
       </c>
       <c r="G52" t="n">
         <v>96.721311</v>
@@ -1735,7 +1735,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
@@ -1748,10 +1748,10 @@
         <v>59</v>
       </c>
       <c r="E53" t="n">
-        <v>2.079394</v>
+        <v>2.329166</v>
       </c>
       <c r="F53" t="n">
-        <v>0.826955</v>
+        <v>-0.694824</v>
       </c>
       <c r="G53" t="n">
         <v>96.721311</v>
@@ -1760,7 +1760,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
@@ -1773,10 +1773,10 @@
         <v>59</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.407403</v>
+        <v>2.079394</v>
       </c>
       <c r="F54" t="n">
-        <v>0.5941920000000001</v>
+        <v>0.826955</v>
       </c>
       <c r="G54" t="n">
         <v>96.721311</v>
@@ -1785,107 +1785,107 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>44773</v>
+        <v>44469</v>
       </c>
       <c r="C55" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D55" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E55" t="n">
-        <v>10.069235</v>
+        <v>-0.407403</v>
       </c>
       <c r="F55" t="n">
-        <v>4.443025</v>
+        <v>0.5941920000000001</v>
       </c>
       <c r="G55" t="n">
-        <v>80.32786900000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
         <v>44773</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D56" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E56" t="n">
-        <v>10.074751</v>
+        <v>10.069235</v>
       </c>
       <c r="F56" t="n">
-        <v>2.178243</v>
+        <v>4.443025</v>
       </c>
       <c r="G56" t="n">
-        <v>81.967213</v>
+        <v>80.32786900000001</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
         <v>44773</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D57" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E57" t="n">
-        <v>10.124804</v>
+        <v>10.074751</v>
       </c>
       <c r="F57" t="n">
-        <v>4.098046</v>
+        <v>2.178243</v>
       </c>
       <c r="G57" t="n">
-        <v>80.32786900000001</v>
+        <v>81.967213</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>44469</v>
+        <v>44773</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D58" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E58" t="n">
-        <v>1</v>
+        <v>10.124804</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.25</v>
+        <v>4.098046</v>
       </c>
       <c r="G58" t="n">
-        <v>98.36065600000001</v>
+        <v>80.32786900000001</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
@@ -1898,10 +1898,10 @@
         <v>60</v>
       </c>
       <c r="E59" t="n">
-        <v>0.001073</v>
+        <v>1</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.00074</v>
+        <v>-0.25</v>
       </c>
       <c r="G59" t="n">
         <v>98.36065600000001</v>
@@ -1910,7 +1910,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
@@ -1926,7 +1926,7 @@
         <v>0.001073</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.000733</v>
+        <v>-0.00074</v>
       </c>
       <c r="G60" t="n">
         <v>98.36065600000001</v>
@@ -1935,32 +1935,32 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D61" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.03</v>
+        <v>0.001073</v>
       </c>
       <c r="F61" t="n">
-        <v>0.3</v>
+        <v>-0.000733</v>
       </c>
       <c r="G61" t="n">
-        <v>96.721311</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
@@ -1973,10 +1973,10 @@
         <v>59</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.13</v>
+        <v>-0.03</v>
       </c>
       <c r="F62" t="n">
-        <v>0.13</v>
+        <v>0.3</v>
       </c>
       <c r="G62" t="n">
         <v>96.721311</v>
@@ -1985,7 +1985,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
@@ -1998,12 +1998,62 @@
         <v>59</v>
       </c>
       <c r="E63" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="G63" t="n">
+        <v>96.721311</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
+        </is>
+      </c>
+      <c r="B64" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="C64" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="D64" t="n">
+        <v>59</v>
+      </c>
+      <c r="E64" t="n">
         <v>0.05</v>
       </c>
-      <c r="F63" t="n">
+      <c r="F64" t="n">
         <v>0.39</v>
       </c>
-      <c r="G63" t="n">
+      <c r="G64" t="n">
+        <v>96.721311</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_juros_credito_total</t>
+        </is>
+      </c>
+      <c r="B65" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="C65" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="D65" t="n">
+        <v>59</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F65" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="G65" t="n">
         <v>96.721311</v>
       </c>
     </row>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
         <v>118781</v>
       </c>
       <c r="F2" t="n">
-        <v>175665</v>
+        <v>177580.765625</v>
       </c>
       <c r="G2" t="n">
         <v>100</v>
@@ -501,7 +501,7 @@
         <v>114.080002</v>
       </c>
       <c r="F3" t="n">
-        <v>172.399994</v>
+        <v>174.800003</v>
       </c>
       <c r="G3" t="n">
         <v>100</v>
@@ -526,7 +526,7 @@
         <v>136.330002</v>
       </c>
       <c r="F4" t="n">
-        <v>105.169998</v>
+        <v>106.550003</v>
       </c>
       <c r="G4" t="n">
         <v>100</v>
@@ -551,7 +551,7 @@
         <v>254</v>
       </c>
       <c r="F5" t="n">
-        <v>450</v>
+        <v>449.230011</v>
       </c>
       <c r="G5" t="n">
         <v>100</v>
@@ -576,7 +576,7 @@
         <v>5.1829</v>
       </c>
       <c r="F6" t="n">
-        <v>5.185</v>
+        <v>5.1834</v>
       </c>
       <c r="G6" t="n">
         <v>100</v>
@@ -601,7 +601,7 @@
         <v>6.1119</v>
       </c>
       <c r="F7" t="n">
-        <v>6.0054</v>
+        <v>6.0184</v>
       </c>
       <c r="G7" t="n">
         <v>100</v>
@@ -626,7 +626,7 @@
         <v>4522.680176</v>
       </c>
       <c r="F8" t="n">
-        <v>7711.759766</v>
+        <v>7672.839844</v>
       </c>
       <c r="G8" t="n">
         <v>100</v>
@@ -651,7 +651,7 @@
         <v>15259.240234</v>
       </c>
       <c r="F9" t="n">
-        <v>26402.419922</v>
+        <v>26289.875</v>
       </c>
       <c r="G9" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
         <v>35360.730469</v>
       </c>
       <c r="F10" t="n">
-        <v>53559.988281</v>
+        <v>53199.460938</v>
       </c>
       <c r="G10" t="n">
         <v>100</v>
@@ -701,7 +701,7 @@
         <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4529.899902</v>
+        <v>4483.399902</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
@@ -726,7 +726,7 @@
         <v>68.5</v>
       </c>
       <c r="F12" t="n">
-        <v>83.400002</v>
+        <v>85.68000000000001</v>
       </c>
       <c r="G12" t="n">
         <v>100</v>
@@ -751,7 +751,7 @@
         <v>72.989998</v>
       </c>
       <c r="F13" t="n">
-        <v>88.099998</v>
+        <v>88.269997</v>
       </c>
       <c r="G13" t="n">
         <v>100</v>
@@ -776,7 +776,7 @@
         <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1288</v>
+        <v>1290</v>
       </c>
       <c r="G14" t="n">
         <v>100</v>
@@ -801,7 +801,7 @@
         <v>534</v>
       </c>
       <c r="F15" t="n">
-        <v>536.5</v>
+        <v>538</v>
       </c>
       <c r="G15" t="n">
         <v>100</v>
@@ -826,7 +826,7 @@
         <v>-6.568391</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.311243</v>
+        <v>-0.234964</v>
       </c>
       <c r="G16" t="n">
         <v>98.36065600000001</v>
@@ -851,7 +851,7 @@
         <v>-6.653229</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.496978</v>
+        <v>-0.125701</v>
       </c>
       <c r="G17" t="n">
         <v>98.36065600000001</v>
@@ -876,7 +876,7 @@
         <v>-6.550283</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.939396</v>
+        <v>-0.652678</v>
       </c>
       <c r="G18" t="n">
         <v>98.36065600000001</v>
@@ -901,7 +901,7 @@
         <v>0.393701</v>
       </c>
       <c r="F19" t="n">
-        <v>5.044465</v>
+        <v>4.864725</v>
       </c>
       <c r="G19" t="n">
         <v>98.36065600000001</v>
@@ -926,7 +926,7 @@
         <v>4.464682</v>
       </c>
       <c r="F20" t="n">
-        <v>2.105113</v>
+        <v>2.073609</v>
       </c>
       <c r="G20" t="n">
         <v>98.36065600000001</v>
@@ -951,7 +951,7 @@
         <v>2.725834</v>
       </c>
       <c r="F21" t="n">
-        <v>2.69235</v>
+        <v>2.91465</v>
       </c>
       <c r="G21" t="n">
         <v>98.36065600000001</v>
@@ -976,7 +976,7 @@
         <v>-4.756917</v>
       </c>
       <c r="F22" t="n">
-        <v>2.964591</v>
+        <v>2.444946</v>
       </c>
       <c r="G22" t="n">
         <v>98.36065600000001</v>
@@ -1001,7 +1001,7 @@
         <v>-5.312585</v>
       </c>
       <c r="F23" t="n">
-        <v>4.053663</v>
+        <v>3.610116</v>
       </c>
       <c r="G23" t="n">
         <v>98.36065600000001</v>
@@ -1026,7 +1026,7 @@
         <v>-4.289528</v>
       </c>
       <c r="F24" t="n">
-        <v>2.048121</v>
+        <v>1.361207</v>
       </c>
       <c r="G24" t="n">
         <v>98.36065600000001</v>
@@ -1051,7 +1051,7 @@
         <v>-3.289254</v>
       </c>
       <c r="F25" t="n">
-        <v>11.874239</v>
+        <v>10.725835</v>
       </c>
       <c r="G25" t="n">
         <v>98.36065600000001</v>
@@ -1076,7 +1076,7 @@
         <v>9.532845</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.499937</v>
+        <v>1.192869</v>
       </c>
       <c r="G26" t="n">
         <v>98.36065600000001</v>
@@ -1101,7 +1101,7 @@
         <v>7.576379</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.241461</v>
+        <v>-2.052825</v>
       </c>
       <c r="G27" t="n">
         <v>98.36065600000001</v>
@@ -1126,7 +1126,7 @@
         <v>-3.291627</v>
       </c>
       <c r="F28" t="n">
-        <v>9.897610999999999</v>
+        <v>10.068259</v>
       </c>
       <c r="G28" t="n">
         <v>98.36065600000001</v>
@@ -1151,7 +1151,7 @@
         <v>0.514981</v>
       </c>
       <c r="F29" t="n">
-        <v>21.724334</v>
+        <v>22.064663</v>
       </c>
       <c r="G29" t="n">
         <v>98.36065600000001</v>
@@ -1226,7 +1226,7 @@
         <v>0.01993</v>
       </c>
       <c r="F32" t="n">
-        <v>0.051798</v>
+        <v>0.051791</v>
       </c>
       <c r="G32" t="n">
         <v>100</v>
@@ -1376,7 +1376,7 @@
         <v>5.1433</v>
       </c>
       <c r="F38" t="n">
-        <v>5.2005</v>
+        <v>5.1816</v>
       </c>
       <c r="G38" t="n">
         <v>100</v>
@@ -1401,7 +1401,7 @@
         <v>5.1427</v>
       </c>
       <c r="F39" t="n">
-        <v>5.1999</v>
+        <v>5.181</v>
       </c>
       <c r="G39" t="n">
         <v>100</v>
@@ -1485,7 +1485,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
@@ -1498,10 +1498,10 @@
         <v>60</v>
       </c>
       <c r="E43" t="n">
-        <v>2.37</v>
+        <v>1.56</v>
       </c>
       <c r="F43" t="n">
-        <v>4.88</v>
+        <v>3.31</v>
       </c>
       <c r="G43" t="n">
         <v>98.36065600000001</v>
@@ -1510,7 +1510,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
@@ -1523,10 +1523,10 @@
         <v>60</v>
       </c>
       <c r="E44" t="n">
-        <v>1.56</v>
+        <v>2.96</v>
       </c>
       <c r="F44" t="n">
-        <v>3.31</v>
+        <v>5.81</v>
       </c>
       <c r="G44" t="n">
         <v>98.36065600000001</v>
@@ -1535,7 +1535,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
@@ -1548,10 +1548,10 @@
         <v>60</v>
       </c>
       <c r="E45" t="n">
-        <v>2.96</v>
+        <v>20.92</v>
       </c>
       <c r="F45" t="n">
-        <v>5.81</v>
+        <v>32.08</v>
       </c>
       <c r="G45" t="n">
         <v>98.36065600000001</v>
@@ -1560,7 +1560,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
@@ -1573,10 +1573,10 @@
         <v>60</v>
       </c>
       <c r="E46" t="n">
-        <v>20.92</v>
+        <v>370395</v>
       </c>
       <c r="F46" t="n">
-        <v>32.08</v>
+        <v>369742</v>
       </c>
       <c r="G46" t="n">
         <v>98.36065600000001</v>
@@ -1585,32 +1585,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D47" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E47" t="n">
-        <v>370395</v>
+        <v>-0.064886</v>
       </c>
       <c r="F47" t="n">
-        <v>369742</v>
+        <v>-0.6395690000000001</v>
       </c>
       <c r="G47" t="n">
-        <v>98.36065600000001</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
@@ -1623,10 +1623,10 @@
         <v>58</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.064886</v>
+        <v>-2.103216</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.6395690000000001</v>
+        <v>0.332557</v>
       </c>
       <c r="G48" t="n">
         <v>95.08196700000001</v>
@@ -1635,32 +1635,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="D49" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E49" t="n">
-        <v>-2.103216</v>
+        <v>5.757004</v>
       </c>
       <c r="F49" t="n">
-        <v>0.332557</v>
+        <v>2.054241</v>
       </c>
       <c r="G49" t="n">
-        <v>95.08196700000001</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
@@ -1673,10 +1673,10 @@
         <v>60</v>
       </c>
       <c r="E50" t="n">
-        <v>5.757004</v>
+        <v>5.757676</v>
       </c>
       <c r="F50" t="n">
-        <v>2.426487</v>
+        <v>2.054484</v>
       </c>
       <c r="G50" t="n">
         <v>98.36065600000001</v>
@@ -1685,32 +1685,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D51" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E51" t="n">
-        <v>5.757676</v>
+        <v>2.185796</v>
       </c>
       <c r="F51" t="n">
-        <v>2.426773</v>
+        <v>0.257708</v>
       </c>
       <c r="G51" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
@@ -1723,10 +1723,10 @@
         <v>59</v>
       </c>
       <c r="E52" t="n">
-        <v>2.185796</v>
+        <v>2.329166</v>
       </c>
       <c r="F52" t="n">
-        <v>0.257708</v>
+        <v>-0.694824</v>
       </c>
       <c r="G52" t="n">
         <v>96.721311</v>
@@ -1735,7 +1735,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
@@ -1748,10 +1748,10 @@
         <v>59</v>
       </c>
       <c r="E53" t="n">
-        <v>2.329166</v>
+        <v>2.079394</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.694824</v>
+        <v>0.826955</v>
       </c>
       <c r="G53" t="n">
         <v>96.721311</v>
@@ -1760,7 +1760,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
@@ -1773,10 +1773,10 @@
         <v>59</v>
       </c>
       <c r="E54" t="n">
-        <v>2.079394</v>
+        <v>-0.407403</v>
       </c>
       <c r="F54" t="n">
-        <v>0.826955</v>
+        <v>0.5941920000000001</v>
       </c>
       <c r="G54" t="n">
         <v>96.721311</v>
@@ -1785,107 +1785,107 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>44469</v>
+        <v>44773</v>
       </c>
       <c r="C55" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D55" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.407403</v>
+        <v>10.069235</v>
       </c>
       <c r="F55" t="n">
-        <v>0.5941920000000001</v>
+        <v>4.443025</v>
       </c>
       <c r="G55" t="n">
-        <v>96.721311</v>
+        <v>80.32786900000001</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
         <v>44773</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D56" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E56" t="n">
-        <v>10.069235</v>
+        <v>10.074751</v>
       </c>
       <c r="F56" t="n">
-        <v>4.443025</v>
+        <v>2.178243</v>
       </c>
       <c r="G56" t="n">
-        <v>80.32786900000001</v>
+        <v>81.967213</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
         <v>44773</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D57" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E57" t="n">
-        <v>10.074751</v>
+        <v>10.124804</v>
       </c>
       <c r="F57" t="n">
-        <v>2.178243</v>
+        <v>4.098046</v>
       </c>
       <c r="G57" t="n">
-        <v>81.967213</v>
+        <v>80.32786900000001</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>44773</v>
+        <v>44469</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D58" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E58" t="n">
-        <v>10.124804</v>
+        <v>1</v>
       </c>
       <c r="F58" t="n">
-        <v>4.098046</v>
+        <v>-0.25</v>
       </c>
       <c r="G58" t="n">
-        <v>80.32786900000001</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
@@ -1898,10 +1898,10 @@
         <v>60</v>
       </c>
       <c r="E59" t="n">
-        <v>1</v>
+        <v>0.001073</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.25</v>
+        <v>-0.00074</v>
       </c>
       <c r="G59" t="n">
         <v>98.36065600000001</v>
@@ -1910,7 +1910,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
@@ -1935,32 +1935,32 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D61" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E61" t="n">
-        <v>0.001073</v>
+        <v>-0.13</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.000733</v>
+        <v>0.13</v>
       </c>
       <c r="G61" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
@@ -1973,10 +1973,10 @@
         <v>59</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.03</v>
+        <v>0.05</v>
       </c>
       <c r="F62" t="n">
-        <v>0.3</v>
+        <v>0.39</v>
       </c>
       <c r="G62" t="n">
         <v>96.721311</v>
@@ -1985,7 +1985,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
@@ -1998,62 +1998,12 @@
         <v>59</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.13</v>
+        <v>0.5</v>
       </c>
       <c r="F63" t="n">
-        <v>0.13</v>
+        <v>-1.25</v>
       </c>
       <c r="G63" t="n">
-        <v>96.721311</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
-        </is>
-      </c>
-      <c r="B64" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="C64" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="D64" t="n">
-        <v>59</v>
-      </c>
-      <c r="E64" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F64" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="G64" t="n">
-        <v>96.721311</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
-        </is>
-      </c>
-      <c r="B65" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="C65" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="D65" t="n">
-        <v>59</v>
-      </c>
-      <c r="E65" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F65" t="n">
-        <v>-1.25</v>
-      </c>
-      <c r="G65" t="n">
         <v>96.721311</v>
       </c>
     </row>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,19 +464,19 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D2" t="n">
         <v>61</v>
       </c>
       <c r="E2" t="n">
-        <v>118781</v>
+        <v>110979</v>
       </c>
       <c r="F2" t="n">
-        <v>177580.765625</v>
+        <v>180393.8125</v>
       </c>
       <c r="G2" t="n">
         <v>100</v>
@@ -489,19 +489,19 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D3" t="n">
         <v>61</v>
       </c>
       <c r="E3" t="n">
-        <v>114.080002</v>
+        <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>174.800003</v>
+        <v>177.610001</v>
       </c>
       <c r="G3" t="n">
         <v>100</v>
@@ -514,19 +514,19 @@
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D4" t="n">
         <v>61</v>
       </c>
       <c r="E4" t="n">
-        <v>136.330002</v>
+        <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>106.550003</v>
+        <v>108.040001</v>
       </c>
       <c r="G4" t="n">
         <v>100</v>
@@ -539,19 +539,19 @@
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D5" t="n">
         <v>61</v>
       </c>
       <c r="E5" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>449.230011</v>
+        <v>444.790009</v>
       </c>
       <c r="G5" t="n">
         <v>100</v>
@@ -564,19 +564,19 @@
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D6" t="n">
         <v>61</v>
       </c>
       <c r="E6" t="n">
-        <v>5.1829</v>
+        <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1834</v>
+        <v>5.1434</v>
       </c>
       <c r="G6" t="n">
         <v>100</v>
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D7" t="n">
         <v>61</v>
       </c>
       <c r="E7" t="n">
-        <v>6.1119</v>
+        <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>6.0184</v>
+        <v>5.9697</v>
       </c>
       <c r="G7" t="n">
         <v>100</v>
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D8" t="n">
         <v>61</v>
       </c>
       <c r="E8" t="n">
-        <v>4522.680176</v>
+        <v>4307.540039</v>
       </c>
       <c r="F8" t="n">
-        <v>7672.839844</v>
+        <v>7659.640137</v>
       </c>
       <c r="G8" t="n">
         <v>100</v>
@@ -639,19 +639,19 @@
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D9" t="n">
         <v>61</v>
       </c>
       <c r="E9" t="n">
-        <v>15259.240234</v>
+        <v>14448.580078</v>
       </c>
       <c r="F9" t="n">
-        <v>26289.875</v>
+        <v>26179.060547</v>
       </c>
       <c r="G9" t="n">
         <v>100</v>
@@ -664,19 +664,19 @@
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D10" t="n">
         <v>61</v>
       </c>
       <c r="E10" t="n">
-        <v>35360.730469</v>
+        <v>33843.921875</v>
       </c>
       <c r="F10" t="n">
-        <v>53199.460938</v>
+        <v>53141.730469</v>
       </c>
       <c r="G10" t="n">
         <v>100</v>
@@ -689,19 +689,19 @@
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D11" t="n">
         <v>61</v>
       </c>
       <c r="E11" t="n">
-        <v>1815</v>
+        <v>1755.300049</v>
       </c>
       <c r="F11" t="n">
-        <v>4483.399902</v>
+        <v>4419.100098</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
@@ -714,19 +714,19 @@
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D12" t="n">
         <v>61</v>
       </c>
       <c r="E12" t="n">
-        <v>68.5</v>
+        <v>75.029999</v>
       </c>
       <c r="F12" t="n">
-        <v>85.68000000000001</v>
+        <v>87.650002</v>
       </c>
       <c r="G12" t="n">
         <v>100</v>
@@ -739,19 +739,19 @@
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D13" t="n">
         <v>61</v>
       </c>
       <c r="E13" t="n">
-        <v>72.989998</v>
+        <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>88.269997</v>
+        <v>92.06999999999999</v>
       </c>
       <c r="G13" t="n">
         <v>100</v>
@@ -764,19 +764,19 @@
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D14" t="n">
         <v>61</v>
       </c>
       <c r="E14" t="n">
-        <v>1298.75</v>
+        <v>1256</v>
       </c>
       <c r="F14" t="n">
-        <v>1290</v>
+        <v>1312</v>
       </c>
       <c r="G14" t="n">
         <v>100</v>
@@ -789,19 +789,19 @@
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D15" t="n">
         <v>61</v>
       </c>
       <c r="E15" t="n">
-        <v>534</v>
+        <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>538</v>
+        <v>542.25</v>
       </c>
       <c r="G15" t="n">
         <v>100</v>
@@ -814,19 +814,19 @@
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D16" t="n">
         <v>60</v>
       </c>
       <c r="E16" t="n">
-        <v>-6.568391</v>
+        <v>-6.738212</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.234964</v>
+        <v>1.676716</v>
       </c>
       <c r="G16" t="n">
         <v>98.36065600000001</v>
@@ -839,19 +839,19 @@
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D17" t="n">
         <v>60</v>
       </c>
       <c r="E17" t="n">
-        <v>-6.653229</v>
+        <v>-6.394964</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.125701</v>
+        <v>2.831171</v>
       </c>
       <c r="G17" t="n">
         <v>98.36065600000001</v>
@@ -864,19 +864,19 @@
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D18" t="n">
         <v>60</v>
       </c>
       <c r="E18" t="n">
-        <v>-6.550283</v>
+        <v>-12.715859</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.652678</v>
+        <v>3.308471</v>
       </c>
       <c r="G18" t="n">
         <v>98.36065600000001</v>
@@ -889,19 +889,19 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D19" t="n">
         <v>60</v>
       </c>
       <c r="E19" t="n">
-        <v>0.393701</v>
+        <v>10.980392</v>
       </c>
       <c r="F19" t="n">
-        <v>4.864725</v>
+        <v>-1.606012</v>
       </c>
       <c r="G19" t="n">
         <v>98.36065600000001</v>
@@ -914,19 +914,19 @@
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D20" t="n">
         <v>60</v>
       </c>
       <c r="E20" t="n">
-        <v>4.464682</v>
+        <v>4.259089</v>
       </c>
       <c r="F20" t="n">
-        <v>2.073609</v>
+        <v>-0.920781</v>
       </c>
       <c r="G20" t="n">
         <v>98.36065600000001</v>
@@ -939,19 +939,19 @@
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D21" t="n">
         <v>60</v>
       </c>
       <c r="E21" t="n">
-        <v>2.725834</v>
+        <v>5.009156</v>
       </c>
       <c r="F21" t="n">
-        <v>2.91465</v>
+        <v>-0.664187</v>
       </c>
       <c r="G21" t="n">
         <v>98.36065600000001</v>
@@ -964,19 +964,19 @@
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D22" t="n">
         <v>60</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.756917</v>
+        <v>6.914384</v>
       </c>
       <c r="F22" t="n">
-        <v>2.444946</v>
+        <v>-0.344776</v>
       </c>
       <c r="G22" t="n">
         <v>98.36065600000001</v>
@@ -989,19 +989,19 @@
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D23" t="n">
         <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.312585</v>
+        <v>7.265832</v>
       </c>
       <c r="F23" t="n">
-        <v>3.610116</v>
+        <v>-0.727431</v>
       </c>
       <c r="G23" t="n">
         <v>98.36065600000001</v>
@@ -1014,19 +1014,19 @@
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D24" t="n">
         <v>60</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.289528</v>
+        <v>5.837493</v>
       </c>
       <c r="F24" t="n">
-        <v>1.361207</v>
+        <v>-0.08304499999999999</v>
       </c>
       <c r="G24" t="n">
         <v>98.36065600000001</v>
@@ -1039,19 +1039,19 @@
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D25" t="n">
         <v>60</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.289254</v>
+        <v>1.578075</v>
       </c>
       <c r="F25" t="n">
-        <v>10.725835</v>
+        <v>-0.270813</v>
       </c>
       <c r="G25" t="n">
         <v>98.36065600000001</v>
@@ -1064,19 +1064,19 @@
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D26" t="n">
         <v>60</v>
       </c>
       <c r="E26" t="n">
-        <v>9.532845</v>
+        <v>11.382115</v>
       </c>
       <c r="F26" t="n">
-        <v>1.192869</v>
+        <v>2.203824</v>
       </c>
       <c r="G26" t="n">
         <v>98.36065600000001</v>
@@ -1089,19 +1089,19 @@
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D27" t="n">
         <v>60</v>
       </c>
       <c r="E27" t="n">
-        <v>7.576379</v>
+        <v>7.463068</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.052825</v>
+        <v>1.746051</v>
       </c>
       <c r="G27" t="n">
         <v>98.36065600000001</v>
@@ -1114,19 +1114,19 @@
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D28" t="n">
         <v>60</v>
       </c>
       <c r="E28" t="n">
-        <v>-3.291627</v>
+        <v>-1.612261</v>
       </c>
       <c r="F28" t="n">
-        <v>10.068259</v>
+        <v>2.881788</v>
       </c>
       <c r="G28" t="n">
         <v>98.36065600000001</v>
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D29" t="n">
         <v>60</v>
       </c>
       <c r="E29" t="n">
-        <v>0.514981</v>
+        <v>5.868654</v>
       </c>
       <c r="F29" t="n">
-        <v>22.064663</v>
+        <v>5.291262</v>
       </c>
       <c r="G29" t="n">
         <v>98.36065600000001</v>
@@ -1164,16 +1164,16 @@
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D30" t="n">
         <v>61</v>
       </c>
       <c r="E30" t="n">
-        <v>5.25</v>
+        <v>6.25</v>
       </c>
       <c r="F30" t="n">
         <v>14</v>
@@ -1189,22 +1189,22 @@
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C31" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D31" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>0.01993</v>
+        <v>0.021003</v>
       </c>
       <c r="F31" t="n">
-        <v>0.051791</v>
+        <v>0.051784</v>
       </c>
       <c r="G31" t="n">
-        <v>100</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="32">
@@ -1214,22 +1214,22 @@
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C32" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D32" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E32" t="n">
-        <v>0.01993</v>
+        <v>0.021003</v>
       </c>
       <c r="F32" t="n">
-        <v>0.051791</v>
+        <v>0.051784</v>
       </c>
       <c r="G32" t="n">
-        <v>100</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="33">
@@ -1239,22 +1239,22 @@
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C33" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D33" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E33" t="n">
-        <v>0.87</v>
+        <v>1.16</v>
       </c>
       <c r="F33" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="G33" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="34">
@@ -1264,22 +1264,22 @@
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C34" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D34" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E34" t="n">
-        <v>0.66</v>
+        <v>-0.64</v>
       </c>
       <c r="F34" t="n">
         <v>-0.22</v>
       </c>
       <c r="G34" t="n">
-        <v>100</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="35">
@@ -1289,22 +1289,22 @@
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C35" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D35" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E35" t="n">
-        <v>0.88</v>
+        <v>1.2</v>
       </c>
       <c r="F35" t="n">
         <v>-0.01</v>
       </c>
       <c r="G35" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="36">
@@ -1314,22 +1314,22 @@
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C36" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D36" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E36" t="n">
-        <v>97.01608</v>
+        <v>96.95313</v>
       </c>
       <c r="F36" t="n">
         <v>110.22154</v>
       </c>
       <c r="G36" t="n">
-        <v>96.721311</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="37">
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C37" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D37" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E37" t="n">
-        <v>99.19190999999999</v>
+        <v>97.10569</v>
       </c>
       <c r="F37" t="n">
         <v>109.89427</v>
       </c>
       <c r="G37" t="n">
-        <v>96.721311</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="38">
@@ -1364,22 +1364,22 @@
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C38" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D38" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E38" t="n">
-        <v>5.1433</v>
+        <v>5.4394</v>
       </c>
       <c r="F38" t="n">
         <v>5.1816</v>
       </c>
       <c r="G38" t="n">
-        <v>100</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="39">
@@ -1389,22 +1389,22 @@
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C39" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D39" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E39" t="n">
-        <v>5.1427</v>
+        <v>5.4388</v>
       </c>
       <c r="F39" t="n">
         <v>5.181</v>
       </c>
       <c r="G39" t="n">
-        <v>100</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="40">
@@ -1414,22 +1414,22 @@
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C40" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D40" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E40" t="n">
-        <v>4346060</v>
+        <v>4441056</v>
       </c>
       <c r="F40" t="n">
         <v>7372243</v>
       </c>
       <c r="G40" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="41">
@@ -1439,22 +1439,22 @@
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C41" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D41" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E41" t="n">
-        <v>1851006</v>
+        <v>1894119</v>
       </c>
       <c r="F41" t="n">
         <v>2731513</v>
       </c>
       <c r="G41" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="42">
@@ -1464,244 +1464,244 @@
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C42" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D42" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E42" t="n">
-        <v>2495054</v>
+        <v>2546936</v>
       </c>
       <c r="F42" t="n">
         <v>4640730</v>
       </c>
       <c r="G42" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C43" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D43" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E43" t="n">
-        <v>1.56</v>
+        <v>2.34</v>
       </c>
       <c r="F43" t="n">
-        <v>3.31</v>
+        <v>4.88</v>
       </c>
       <c r="G43" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C44" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D44" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E44" t="n">
-        <v>2.96</v>
+        <v>1.43</v>
       </c>
       <c r="F44" t="n">
-        <v>5.81</v>
+        <v>3.31</v>
       </c>
       <c r="G44" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C45" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D45" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E45" t="n">
-        <v>20.92</v>
+        <v>3.01</v>
       </c>
       <c r="F45" t="n">
-        <v>32.08</v>
+        <v>5.81</v>
       </c>
       <c r="G45" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C46" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D46" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E46" t="n">
-        <v>370395</v>
+        <v>21.42</v>
       </c>
       <c r="F46" t="n">
-        <v>369742</v>
+        <v>32.08</v>
       </c>
       <c r="G46" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D47" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.064886</v>
+        <v>368886</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.6395690000000001</v>
+        <v>369742</v>
       </c>
       <c r="G47" t="n">
-        <v>95.08196700000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C48" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="D48" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E48" t="n">
-        <v>-2.103216</v>
+        <v>0.541272</v>
       </c>
       <c r="F48" t="n">
-        <v>0.332557</v>
+        <v>-0.6395690000000001</v>
       </c>
       <c r="G48" t="n">
-        <v>95.08196700000001</v>
+        <v>93.442623</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="D49" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E49" t="n">
-        <v>5.757004</v>
+        <v>-0.59426</v>
       </c>
       <c r="F49" t="n">
-        <v>2.054241</v>
+        <v>0.332557</v>
       </c>
       <c r="G49" t="n">
-        <v>98.36065600000001</v>
+        <v>93.442623</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C50" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D50" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E50" t="n">
-        <v>5.757676</v>
+        <v>3.74306</v>
       </c>
       <c r="F50" t="n">
-        <v>2.054484</v>
+        <v>2.054241</v>
       </c>
       <c r="G50" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D51" t="n">
         <v>59</v>
       </c>
       <c r="E51" t="n">
-        <v>2.185796</v>
+        <v>3.743473</v>
       </c>
       <c r="F51" t="n">
-        <v>0.257708</v>
+        <v>2.054484</v>
       </c>
       <c r="G51" t="n">
         <v>96.721311</v>
@@ -1710,148 +1710,148 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C52" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D52" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E52" t="n">
-        <v>2.329166</v>
+        <v>1.596467</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.694824</v>
+        <v>0.257708</v>
       </c>
       <c r="G52" t="n">
-        <v>96.721311</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C53" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D53" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E53" t="n">
-        <v>2.079394</v>
+        <v>0.888065</v>
       </c>
       <c r="F53" t="n">
-        <v>0.826955</v>
+        <v>-0.694824</v>
       </c>
       <c r="G53" t="n">
-        <v>96.721311</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C54" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D54" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.407403</v>
+        <v>2.123375</v>
       </c>
       <c r="F54" t="n">
-        <v>0.5941920000000001</v>
+        <v>0.826955</v>
       </c>
       <c r="G54" t="n">
-        <v>96.721311</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>44773</v>
+        <v>44500</v>
       </c>
       <c r="C55" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D55" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E55" t="n">
-        <v>10.069235</v>
+        <v>-0.259972</v>
       </c>
       <c r="F55" t="n">
-        <v>4.443025</v>
+        <v>0.5941920000000001</v>
       </c>
       <c r="G55" t="n">
-        <v>80.32786900000001</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>44773</v>
+        <v>44804</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D56" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E56" t="n">
-        <v>10.074751</v>
+        <v>8.727061000000001</v>
       </c>
       <c r="F56" t="n">
-        <v>2.178243</v>
+        <v>4.443025</v>
       </c>
       <c r="G56" t="n">
-        <v>81.967213</v>
+        <v>78.688525</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>44773</v>
+        <v>44804</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D57" t="n">
         <v>49</v>
       </c>
       <c r="E57" t="n">
-        <v>10.124804</v>
+        <v>8.58755</v>
       </c>
       <c r="F57" t="n">
-        <v>4.098046</v>
+        <v>2.178243</v>
       </c>
       <c r="G57" t="n">
         <v>80.32786900000001</v>
@@ -1860,48 +1860,48 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>44469</v>
+        <v>44804</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D58" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="E58" t="n">
-        <v>1</v>
+        <v>8.825751</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.25</v>
+        <v>4.098046</v>
       </c>
       <c r="G58" t="n">
-        <v>98.36065600000001</v>
+        <v>78.688525</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D59" t="n">
         <v>60</v>
       </c>
       <c r="E59" t="n">
-        <v>0.001073</v>
+        <v>1.5</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.00074</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
         <v>98.36065600000001</v>
@@ -1910,48 +1910,48 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C60" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D60" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E60" t="n">
-        <v>0.001073</v>
+        <v>0.00324</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.00074</v>
+        <v>-0.0007470000000000001</v>
       </c>
       <c r="G60" t="n">
-        <v>98.36065600000001</v>
+        <v>96.721311</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D61" t="n">
         <v>59</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.13</v>
+        <v>0.00324</v>
       </c>
       <c r="F61" t="n">
-        <v>0.13</v>
+        <v>-0.0007470000000000001</v>
       </c>
       <c r="G61" t="n">
         <v>96.721311</v>
@@ -1960,51 +1960,101 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C62" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D62" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E62" t="n">
-        <v>0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="F62" t="n">
-        <v>0.39</v>
+        <v>0.3</v>
       </c>
       <c r="G62" t="n">
-        <v>96.721311</v>
+        <v>95.08196700000001</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C63" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D63" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E63" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F63" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="G63" t="n">
+        <v>95.08196700000001</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
+        </is>
+      </c>
+      <c r="B64" s="1" t="n">
+        <v>44500</v>
+      </c>
+      <c r="C64" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="D64" t="n">
+        <v>58</v>
+      </c>
+      <c r="E64" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="G64" t="n">
+        <v>95.08196700000001</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_juros_credito_total</t>
+        </is>
+      </c>
+      <c r="B65" s="1" t="n">
+        <v>44500</v>
+      </c>
+      <c r="C65" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="D65" t="n">
+        <v>58</v>
+      </c>
+      <c r="E65" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="F65" t="n">
         <v>-1.25</v>
       </c>
-      <c r="G63" t="n">
-        <v>96.721311</v>
+      <c r="G65" t="n">
+        <v>95.08196700000001</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -476,7 +476,7 @@
         <v>110979</v>
       </c>
       <c r="F2" t="n">
-        <v>180393.8125</v>
+        <v>183242.234375</v>
       </c>
       <c r="G2" t="n">
         <v>100</v>
@@ -501,7 +501,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>177.610001</v>
+        <v>180.369995</v>
       </c>
       <c r="G3" t="n">
         <v>100</v>
@@ -526,7 +526,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>108.040001</v>
+        <v>109.370003</v>
       </c>
       <c r="G4" t="n">
         <v>100</v>
@@ -551,7 +551,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>444.790009</v>
+        <v>442.920013</v>
       </c>
       <c r="G5" t="n">
         <v>100</v>
@@ -576,7 +576,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1434</v>
+        <v>5.1304</v>
       </c>
       <c r="G6" t="n">
         <v>100</v>
@@ -601,7 +601,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9697</v>
+        <v>5.9502</v>
       </c>
       <c r="G7" t="n">
         <v>100</v>
@@ -626,7 +626,7 @@
         <v>4307.540039</v>
       </c>
       <c r="F8" t="n">
-        <v>7659.640137</v>
+        <v>7656.77002</v>
       </c>
       <c r="G8" t="n">
         <v>100</v>
@@ -651,7 +651,7 @@
         <v>14448.580078</v>
       </c>
       <c r="F9" t="n">
-        <v>26179.060547</v>
+        <v>26157.546875</v>
       </c>
       <c r="G9" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
         <v>33843.921875</v>
       </c>
       <c r="F10" t="n">
-        <v>53141.730469</v>
+        <v>53092.410156</v>
       </c>
       <c r="G10" t="n">
         <v>100</v>
@@ -701,7 +701,7 @@
         <v>1755.300049</v>
       </c>
       <c r="F11" t="n">
-        <v>4419.100098</v>
+        <v>4431.299805</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
@@ -726,7 +726,7 @@
         <v>75.029999</v>
       </c>
       <c r="F12" t="n">
-        <v>87.650002</v>
+        <v>89.129997</v>
       </c>
       <c r="G12" t="n">
         <v>100</v>
@@ -751,7 +751,7 @@
         <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>92.06999999999999</v>
+        <v>93.889999</v>
       </c>
       <c r="G13" t="n">
         <v>100</v>
@@ -776,7 +776,7 @@
         <v>1256</v>
       </c>
       <c r="F14" t="n">
-        <v>1312</v>
+        <v>1304</v>
       </c>
       <c r="G14" t="n">
         <v>100</v>
@@ -801,7 +801,7 @@
         <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>542.25</v>
+        <v>541</v>
       </c>
       <c r="G15" t="n">
         <v>100</v>
@@ -826,7 +826,7 @@
         <v>-6.738212</v>
       </c>
       <c r="F16" t="n">
-        <v>1.676716</v>
+        <v>3.282193</v>
       </c>
       <c r="G16" t="n">
         <v>98.36065600000001</v>
@@ -851,7 +851,7 @@
         <v>-6.394964</v>
       </c>
       <c r="F17" t="n">
-        <v>2.831171</v>
+        <v>3.198304</v>
       </c>
       <c r="G17" t="n">
         <v>98.36065600000001</v>
@@ -876,7 +876,7 @@
         <v>-12.715859</v>
       </c>
       <c r="F18" t="n">
-        <v>3.308471</v>
+        <v>3.052865</v>
       </c>
       <c r="G18" t="n">
         <v>98.36065600000001</v>
@@ -901,7 +901,7 @@
         <v>10.980392</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.606012</v>
+        <v>-1.430954</v>
       </c>
       <c r="G19" t="n">
         <v>98.36065600000001</v>
@@ -926,7 +926,7 @@
         <v>4.259089</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.920781</v>
+        <v>-1.171205</v>
       </c>
       <c r="G20" t="n">
         <v>98.36065600000001</v>
@@ -951,7 +951,7 @@
         <v>5.009156</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.664187</v>
+        <v>-0.988663</v>
       </c>
       <c r="G21" t="n">
         <v>98.36065600000001</v>
@@ -976,7 +976,7 @@
         <v>6.914384</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.344776</v>
+        <v>-0.382118</v>
       </c>
       <c r="G22" t="n">
         <v>98.36065600000001</v>
@@ -1001,7 +1001,7 @@
         <v>7.265832</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.727431</v>
+        <v>-0.809012</v>
       </c>
       <c r="G23" t="n">
         <v>98.36065600000001</v>
@@ -1026,7 +1026,7 @@
         <v>5.837493</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.08304499999999999</v>
+        <v>-0.175776</v>
       </c>
       <c r="G24" t="n">
         <v>98.36065600000001</v>
@@ -1051,7 +1051,7 @@
         <v>1.578075</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.270813</v>
+        <v>0.004507</v>
       </c>
       <c r="G25" t="n">
         <v>98.36065600000001</v>
@@ -1076,7 +1076,7 @@
         <v>11.382115</v>
       </c>
       <c r="F26" t="n">
-        <v>2.203824</v>
+        <v>3.929565</v>
       </c>
       <c r="G26" t="n">
         <v>98.36065600000001</v>
@@ -1101,7 +1101,7 @@
         <v>7.463068</v>
       </c>
       <c r="F27" t="n">
-        <v>1.746051</v>
+        <v>3.757323</v>
       </c>
       <c r="G27" t="n">
         <v>98.36065600000001</v>
@@ -1126,7 +1126,7 @@
         <v>-1.612261</v>
       </c>
       <c r="F28" t="n">
-        <v>2.881788</v>
+        <v>2.25446</v>
       </c>
       <c r="G28" t="n">
         <v>98.36065600000001</v>
@@ -1151,7 +1151,7 @@
         <v>5.868654</v>
       </c>
       <c r="F29" t="n">
-        <v>5.291262</v>
+        <v>5.048544</v>
       </c>
       <c r="G29" t="n">
         <v>98.36065600000001</v>
@@ -1192,19 +1192,19 @@
         <v>44469</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D31" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E31" t="n">
-        <v>0.021003</v>
+        <v>0.021057</v>
       </c>
       <c r="F31" t="n">
-        <v>0.051784</v>
+        <v>0.05166</v>
       </c>
       <c r="G31" t="n">
-        <v>98.36065600000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32">
@@ -1217,19 +1217,19 @@
         <v>44469</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D32" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E32" t="n">
-        <v>0.021003</v>
+        <v>0.021057</v>
       </c>
       <c r="F32" t="n">
-        <v>0.051784</v>
+        <v>0.05166</v>
       </c>
       <c r="G32" t="n">
-        <v>98.36065600000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33">
@@ -1367,19 +1367,19 @@
         <v>44469</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D38" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E38" t="n">
         <v>5.4394</v>
       </c>
       <c r="F38" t="n">
-        <v>5.1816</v>
+        <v>5.157</v>
       </c>
       <c r="G38" t="n">
-        <v>98.36065600000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="39">
@@ -1392,19 +1392,19 @@
         <v>44469</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D39" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E39" t="n">
         <v>5.4388</v>
       </c>
       <c r="F39" t="n">
-        <v>5.181</v>
+        <v>5.1564</v>
       </c>
       <c r="G39" t="n">
-        <v>98.36065600000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40">
@@ -1667,19 +1667,19 @@
         <v>44500</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D50" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E50" t="n">
         <v>3.74306</v>
       </c>
       <c r="F50" t="n">
-        <v>2.054241</v>
+        <v>-0.474757</v>
       </c>
       <c r="G50" t="n">
-        <v>96.721311</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="51">
@@ -1692,19 +1692,19 @@
         <v>44500</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D51" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E51" t="n">
         <v>3.743473</v>
       </c>
       <c r="F51" t="n">
-        <v>2.054484</v>
+        <v>-0.474812</v>
       </c>
       <c r="G51" t="n">
-        <v>96.721311</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="52">
@@ -1917,19 +1917,19 @@
         <v>44500</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D60" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E60" t="n">
-        <v>0.00324</v>
+        <v>0.003187</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.0007470000000000001</v>
+        <v>-0.000124</v>
       </c>
       <c r="G60" t="n">
-        <v>96.721311</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="61">
@@ -1942,19 +1942,19 @@
         <v>44500</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D61" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E61" t="n">
-        <v>0.00324</v>
+        <v>0.003187</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.0007470000000000001</v>
+        <v>-0.000124</v>
       </c>
       <c r="G61" t="n">
-        <v>96.721311</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="62">

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -476,7 +476,7 @@
         <v>110979</v>
       </c>
       <c r="F2" t="n">
-        <v>183242.234375</v>
+        <v>187884.234375</v>
       </c>
       <c r="G2" t="n">
         <v>100</v>
@@ -501,7 +501,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>180.369995</v>
+        <v>184.940002</v>
       </c>
       <c r="G3" t="n">
         <v>100</v>
@@ -526,7 +526,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>109.370003</v>
+        <v>112.779999</v>
       </c>
       <c r="G4" t="n">
         <v>100</v>
@@ -551,7 +551,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>442.920013</v>
+        <v>444.200012</v>
       </c>
       <c r="G5" t="n">
         <v>100</v>
@@ -576,7 +576,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1304</v>
+        <v>5.0978</v>
       </c>
       <c r="G6" t="n">
         <v>100</v>
@@ -601,7 +601,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9502</v>
+        <v>5.9255</v>
       </c>
       <c r="G7" t="n">
         <v>100</v>
@@ -626,7 +626,7 @@
         <v>4307.540039</v>
       </c>
       <c r="F8" t="n">
-        <v>7656.77002</v>
+        <v>7696.549805</v>
       </c>
       <c r="G8" t="n">
         <v>100</v>
@@ -651,7 +651,7 @@
         <v>14448.580078</v>
       </c>
       <c r="F9" t="n">
-        <v>26157.546875</v>
+        <v>26400.578125</v>
       </c>
       <c r="G9" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
         <v>33843.921875</v>
       </c>
       <c r="F10" t="n">
-        <v>53092.410156</v>
+        <v>53321.730469</v>
       </c>
       <c r="G10" t="n">
         <v>100</v>
@@ -701,7 +701,7 @@
         <v>1755.300049</v>
       </c>
       <c r="F11" t="n">
-        <v>4431.299805</v>
+        <v>4514.799805</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
@@ -726,7 +726,7 @@
         <v>75.029999</v>
       </c>
       <c r="F12" t="n">
-        <v>89.129997</v>
+        <v>91.870003</v>
       </c>
       <c r="G12" t="n">
         <v>100</v>
@@ -751,7 +751,7 @@
         <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>93.889999</v>
+        <v>96.199997</v>
       </c>
       <c r="G13" t="n">
         <v>100</v>
@@ -776,7 +776,7 @@
         <v>1256</v>
       </c>
       <c r="F14" t="n">
-        <v>1304</v>
+        <v>1292.5</v>
       </c>
       <c r="G14" t="n">
         <v>100</v>
@@ -801,7 +801,7 @@
         <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>541</v>
+        <v>527</v>
       </c>
       <c r="G15" t="n">
         <v>100</v>
@@ -826,7 +826,7 @@
         <v>-6.738212</v>
       </c>
       <c r="F16" t="n">
-        <v>3.282193</v>
+        <v>5.898598</v>
       </c>
       <c r="G16" t="n">
         <v>98.36065600000001</v>
@@ -851,7 +851,7 @@
         <v>-6.394964</v>
       </c>
       <c r="F17" t="n">
-        <v>3.198304</v>
+        <v>5.813024</v>
       </c>
       <c r="G17" t="n">
         <v>98.36065600000001</v>
@@ -876,7 +876,7 @@
         <v>-12.715859</v>
       </c>
       <c r="F18" t="n">
-        <v>3.052865</v>
+        <v>6.265902</v>
       </c>
       <c r="G18" t="n">
         <v>98.36065600000001</v>
@@ -901,7 +901,7 @@
         <v>10.980392</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.430954</v>
+        <v>-1.146099</v>
       </c>
       <c r="G19" t="n">
         <v>98.36065600000001</v>
@@ -926,7 +926,7 @@
         <v>4.259089</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.171205</v>
+        <v>-1.799199</v>
       </c>
       <c r="G20" t="n">
         <v>98.36065600000001</v>
@@ -951,7 +951,7 @@
         <v>5.009156</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.988663</v>
+        <v>-1.399674</v>
       </c>
       <c r="G21" t="n">
         <v>98.36065600000001</v>
@@ -976,7 +976,7 @@
         <v>6.914384</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.382118</v>
+        <v>0.135434</v>
       </c>
       <c r="G22" t="n">
         <v>98.36065600000001</v>
@@ -1001,7 +1001,7 @@
         <v>7.265832</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.809012</v>
+        <v>0.112577</v>
       </c>
       <c r="G23" t="n">
         <v>98.36065600000001</v>
@@ -1026,7 +1026,7 @@
         <v>5.837493</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.175776</v>
+        <v>0.255391</v>
       </c>
       <c r="G24" t="n">
         <v>98.36065600000001</v>
@@ -1051,7 +1051,7 @@
         <v>1.578075</v>
       </c>
       <c r="F25" t="n">
-        <v>0.004507</v>
+        <v>1.888915</v>
       </c>
       <c r="G25" t="n">
         <v>98.36065600000001</v>
@@ -1076,7 +1076,7 @@
         <v>11.382115</v>
       </c>
       <c r="F26" t="n">
-        <v>3.929565</v>
+        <v>7.124534</v>
       </c>
       <c r="G26" t="n">
         <v>98.36065600000001</v>
@@ -1101,7 +1101,7 @@
         <v>7.463068</v>
       </c>
       <c r="F27" t="n">
-        <v>3.757323</v>
+        <v>6.310089</v>
       </c>
       <c r="G27" t="n">
         <v>98.36065600000001</v>
@@ -1126,7 +1126,7 @@
         <v>-1.612261</v>
       </c>
       <c r="F28" t="n">
-        <v>2.25446</v>
+        <v>1.352676</v>
       </c>
       <c r="G28" t="n">
         <v>98.36065600000001</v>
@@ -1151,7 +1151,7 @@
         <v>5.868654</v>
       </c>
       <c r="F29" t="n">
-        <v>5.048544</v>
+        <v>2.330097</v>
       </c>
       <c r="G29" t="n">
         <v>98.36065600000001</v>
@@ -1198,7 +1198,7 @@
         <v>61</v>
       </c>
       <c r="E31" t="n">
-        <v>0.021057</v>
+        <v>0.021116</v>
       </c>
       <c r="F31" t="n">
         <v>0.05166</v>
@@ -1223,7 +1223,7 @@
         <v>61</v>
       </c>
       <c r="E32" t="n">
-        <v>0.021057</v>
+        <v>0.021116</v>
       </c>
       <c r="F32" t="n">
         <v>0.05166</v>
@@ -1376,7 +1376,7 @@
         <v>5.4394</v>
       </c>
       <c r="F38" t="n">
-        <v>5.157</v>
+        <v>5.1273</v>
       </c>
       <c r="G38" t="n">
         <v>100</v>
@@ -1401,7 +1401,7 @@
         <v>5.4388</v>
       </c>
       <c r="F39" t="n">
-        <v>5.1564</v>
+        <v>5.1267</v>
       </c>
       <c r="G39" t="n">
         <v>100</v>
@@ -1676,7 +1676,7 @@
         <v>3.74306</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.474757</v>
+        <v>-1.047939</v>
       </c>
       <c r="G50" t="n">
         <v>98.36065600000001</v>
@@ -1701,7 +1701,7 @@
         <v>3.743473</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.474812</v>
+        <v>-1.04806</v>
       </c>
       <c r="G51" t="n">
         <v>98.36065600000001</v>
@@ -1923,7 +1923,7 @@
         <v>60</v>
       </c>
       <c r="E60" t="n">
-        <v>0.003187</v>
+        <v>0.003127</v>
       </c>
       <c r="F60" t="n">
         <v>-0.000124</v>
@@ -1948,7 +1948,7 @@
         <v>60</v>
       </c>
       <c r="E61" t="n">
-        <v>0.003187</v>
+        <v>0.003127</v>
       </c>
       <c r="F61" t="n">
         <v>-0.000124</v>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -476,7 +476,7 @@
         <v>110979</v>
       </c>
       <c r="F2" t="n">
-        <v>187884.234375</v>
+        <v>184429.421875</v>
       </c>
       <c r="G2" t="n">
         <v>100</v>
@@ -501,7 +501,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>184.940002</v>
+        <v>181.509995</v>
       </c>
       <c r="G3" t="n">
         <v>100</v>
@@ -526,7 +526,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>112.779999</v>
+        <v>110.269997</v>
       </c>
       <c r="G4" t="n">
         <v>100</v>
@@ -551,7 +551,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>444.200012</v>
+        <v>447.329987</v>
       </c>
       <c r="G5" t="n">
         <v>100</v>
@@ -576,7 +576,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.0978</v>
+        <v>5.1283</v>
       </c>
       <c r="G6" t="n">
         <v>100</v>
@@ -601,7 +601,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9255</v>
+        <v>5.9542</v>
       </c>
       <c r="G7" t="n">
         <v>100</v>
@@ -626,7 +626,7 @@
         <v>4307.540039</v>
       </c>
       <c r="F8" t="n">
-        <v>7696.549805</v>
+        <v>7736.689941</v>
       </c>
       <c r="G8" t="n">
         <v>100</v>
@@ -651,7 +651,7 @@
         <v>14448.580078</v>
       </c>
       <c r="F9" t="n">
-        <v>26400.578125</v>
+        <v>26610.115234</v>
       </c>
       <c r="G9" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
         <v>33843.921875</v>
       </c>
       <c r="F10" t="n">
-        <v>53321.730469</v>
+        <v>53466.398438</v>
       </c>
       <c r="G10" t="n">
         <v>100</v>
@@ -701,7 +701,7 @@
         <v>1755.300049</v>
       </c>
       <c r="F11" t="n">
-        <v>4514.799805</v>
+        <v>4469.600098</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
@@ -726,7 +726,7 @@
         <v>75.029999</v>
       </c>
       <c r="F12" t="n">
-        <v>91.870003</v>
+        <v>88.91999800000001</v>
       </c>
       <c r="G12" t="n">
         <v>100</v>
@@ -751,7 +751,7 @@
         <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>96.199997</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="G13" t="n">
         <v>100</v>
@@ -776,7 +776,7 @@
         <v>1256</v>
       </c>
       <c r="F14" t="n">
-        <v>1292.5</v>
+        <v>1307</v>
       </c>
       <c r="G14" t="n">
         <v>100</v>
@@ -788,23 +788,15 @@
           <t>yahoo_milho</t>
         </is>
       </c>
-      <c r="B15" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="C15" s="1" t="n">
-        <v>46295</v>
-      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>61</v>
-      </c>
-      <c r="E15" t="n">
-        <v>536.75</v>
-      </c>
-      <c r="F15" t="n">
-        <v>527</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -826,7 +818,7 @@
         <v>-6.738212</v>
       </c>
       <c r="F16" t="n">
-        <v>5.898598</v>
+        <v>3.951337</v>
       </c>
       <c r="G16" t="n">
         <v>98.36065600000001</v>
@@ -851,7 +843,7 @@
         <v>-6.394964</v>
       </c>
       <c r="F17" t="n">
-        <v>5.813024</v>
+        <v>3.850553</v>
       </c>
       <c r="G17" t="n">
         <v>98.36065600000001</v>
@@ -876,7 +868,7 @@
         <v>-12.715859</v>
       </c>
       <c r="F18" t="n">
-        <v>6.265902</v>
+        <v>3.900876</v>
       </c>
       <c r="G18" t="n">
         <v>98.36065600000001</v>
@@ -901,7 +893,7 @@
         <v>10.980392</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.146099</v>
+        <v>-0.449543</v>
       </c>
       <c r="G19" t="n">
         <v>98.36065600000001</v>
@@ -926,7 +918,7 @@
         <v>4.259089</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.799199</v>
+        <v>-1.211658</v>
       </c>
       <c r="G20" t="n">
         <v>98.36065600000001</v>
@@ -951,7 +943,7 @@
         <v>5.009156</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.399674</v>
+        <v>-0.922108</v>
       </c>
       <c r="G21" t="n">
         <v>98.36065600000001</v>
@@ -976,7 +968,7 @@
         <v>6.914384</v>
       </c>
       <c r="F22" t="n">
-        <v>0.135434</v>
+        <v>0.657675</v>
       </c>
       <c r="G22" t="n">
         <v>98.36065600000001</v>
@@ -1001,7 +993,7 @@
         <v>7.265832</v>
       </c>
       <c r="F23" t="n">
-        <v>0.112577</v>
+        <v>0.907154</v>
       </c>
       <c r="G23" t="n">
         <v>98.36065600000001</v>
@@ -1026,7 +1018,7 @@
         <v>5.837493</v>
       </c>
       <c r="F24" t="n">
-        <v>0.255391</v>
+        <v>0.5273949999999999</v>
       </c>
       <c r="G24" t="n">
         <v>98.36065600000001</v>
@@ -1051,7 +1043,7 @@
         <v>1.578075</v>
       </c>
       <c r="F25" t="n">
-        <v>1.888915</v>
+        <v>0.868859</v>
       </c>
       <c r="G25" t="n">
         <v>98.36065600000001</v>
@@ -1076,7 +1068,7 @@
         <v>11.382115</v>
       </c>
       <c r="F26" t="n">
-        <v>7.124534</v>
+        <v>3.684697</v>
       </c>
       <c r="G26" t="n">
         <v>98.36065600000001</v>
@@ -1101,7 +1093,7 @@
         <v>7.463068</v>
       </c>
       <c r="F27" t="n">
-        <v>6.310089</v>
+        <v>3.127419</v>
       </c>
       <c r="G27" t="n">
         <v>98.36065600000001</v>
@@ -1126,7 +1118,7 @@
         <v>-1.612261</v>
       </c>
       <c r="F28" t="n">
-        <v>1.352676</v>
+        <v>2.489708</v>
       </c>
       <c r="G28" t="n">
         <v>98.36065600000001</v>
@@ -1138,23 +1130,15 @@
           <t>yahoo_ret_milho</t>
         </is>
       </c>
-      <c r="B29" s="1" t="n">
-        <v>44500</v>
-      </c>
-      <c r="C29" s="1" t="n">
-        <v>46295</v>
-      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="n">
-        <v>60</v>
-      </c>
-      <c r="E29" t="n">
-        <v>5.868654</v>
-      </c>
-      <c r="F29" t="n">
-        <v>2.330097</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="n">
-        <v>98.36065600000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1198,7 +1182,7 @@
         <v>61</v>
       </c>
       <c r="E31" t="n">
-        <v>0.021116</v>
+        <v>0.021182</v>
       </c>
       <c r="F31" t="n">
         <v>0.05166</v>
@@ -1223,7 +1207,7 @@
         <v>61</v>
       </c>
       <c r="E32" t="n">
-        <v>0.021116</v>
+        <v>0.021182</v>
       </c>
       <c r="F32" t="n">
         <v>0.05166</v>
@@ -1376,7 +1360,7 @@
         <v>5.4394</v>
       </c>
       <c r="F38" t="n">
-        <v>5.1273</v>
+        <v>5.0962</v>
       </c>
       <c r="G38" t="n">
         <v>100</v>
@@ -1401,7 +1385,7 @@
         <v>5.4388</v>
       </c>
       <c r="F39" t="n">
-        <v>5.1267</v>
+        <v>5.0956</v>
       </c>
       <c r="G39" t="n">
         <v>100</v>
@@ -1676,7 +1660,7 @@
         <v>3.74306</v>
       </c>
       <c r="F50" t="n">
-        <v>-1.047939</v>
+        <v>-1.64814</v>
       </c>
       <c r="G50" t="n">
         <v>98.36065600000001</v>
@@ -1701,7 +1685,7 @@
         <v>3.743473</v>
       </c>
       <c r="F51" t="n">
-        <v>-1.04806</v>
+        <v>-1.64833</v>
       </c>
       <c r="G51" t="n">
         <v>98.36065600000001</v>
@@ -1923,7 +1907,7 @@
         <v>60</v>
       </c>
       <c r="E60" t="n">
-        <v>0.003127</v>
+        <v>0.003062</v>
       </c>
       <c r="F60" t="n">
         <v>-0.000124</v>
@@ -1948,7 +1932,7 @@
         <v>60</v>
       </c>
       <c r="E61" t="n">
-        <v>0.003127</v>
+        <v>0.003062</v>
       </c>
       <c r="F61" t="n">
         <v>-0.000124</v>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -476,7 +476,7 @@
         <v>110979</v>
       </c>
       <c r="F2" t="n">
-        <v>184429.421875</v>
+        <v>185147</v>
       </c>
       <c r="G2" t="n">
         <v>100</v>
@@ -501,7 +501,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>181.509995</v>
+        <v>182.25</v>
       </c>
       <c r="G3" t="n">
         <v>100</v>
@@ -526,7 +526,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>110.269997</v>
+        <v>111.059998</v>
       </c>
       <c r="G4" t="n">
         <v>100</v>
@@ -551,7 +551,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>447.329987</v>
+        <v>446</v>
       </c>
       <c r="G5" t="n">
         <v>100</v>
@@ -576,7 +576,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1283</v>
+        <v>5.1237</v>
       </c>
       <c r="G6" t="n">
         <v>100</v>
@@ -601,7 +601,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9542</v>
+        <v>5.9496</v>
       </c>
       <c r="G7" t="n">
         <v>100</v>
@@ -626,7 +626,7 @@
         <v>4307.540039</v>
       </c>
       <c r="F8" t="n">
-        <v>7736.689941</v>
+        <v>7718.600098</v>
       </c>
       <c r="G8" t="n">
         <v>100</v>
@@ -651,7 +651,7 @@
         <v>14448.580078</v>
       </c>
       <c r="F9" t="n">
-        <v>26610.115234</v>
+        <v>26506.990234</v>
       </c>
       <c r="G9" t="n">
         <v>100</v>
@@ -676,7 +676,7 @@
         <v>33843.921875</v>
       </c>
       <c r="F10" t="n">
-        <v>53466.398438</v>
+        <v>53414.25</v>
       </c>
       <c r="G10" t="n">
         <v>100</v>
@@ -701,7 +701,7 @@
         <v>1755.300049</v>
       </c>
       <c r="F11" t="n">
-        <v>4469.600098</v>
+        <v>4429.799805</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
@@ -726,7 +726,7 @@
         <v>75.029999</v>
       </c>
       <c r="F12" t="n">
-        <v>88.91999800000001</v>
+        <v>91.480003</v>
       </c>
       <c r="G12" t="n">
         <v>100</v>
@@ -751,7 +751,7 @@
         <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>93.31999999999999</v>
+        <v>96.279999</v>
       </c>
       <c r="G13" t="n">
         <v>100</v>
@@ -776,7 +776,7 @@
         <v>1256</v>
       </c>
       <c r="F14" t="n">
-        <v>1307</v>
+        <v>1293.75</v>
       </c>
       <c r="G14" t="n">
         <v>100</v>
@@ -788,15 +788,23 @@
           <t>yahoo_milho</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
+      <c r="B15" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>46295</v>
+      </c>
       <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
+        <v>61</v>
+      </c>
+      <c r="E15" t="n">
+        <v>536.75</v>
+      </c>
+      <c r="F15" t="n">
+        <v>512</v>
+      </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16">
@@ -818,7 +826,7 @@
         <v>-6.738212</v>
       </c>
       <c r="F16" t="n">
-        <v>3.951337</v>
+        <v>4.355791</v>
       </c>
       <c r="G16" t="n">
         <v>98.36065600000001</v>
@@ -843,7 +851,7 @@
         <v>-6.394964</v>
       </c>
       <c r="F17" t="n">
-        <v>3.850553</v>
+        <v>4.273945</v>
       </c>
       <c r="G17" t="n">
         <v>98.36065600000001</v>
@@ -868,7 +876,7 @@
         <v>-12.715859</v>
       </c>
       <c r="F18" t="n">
-        <v>3.900876</v>
+        <v>4.645247</v>
       </c>
       <c r="G18" t="n">
         <v>98.36065600000001</v>
@@ -893,7 +901,7 @@
         <v>10.980392</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.449543</v>
+        <v>-0.745523</v>
       </c>
       <c r="G19" t="n">
         <v>98.36065600000001</v>
@@ -918,7 +926,7 @@
         <v>4.259089</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.211658</v>
+        <v>-1.30027</v>
       </c>
       <c r="G20" t="n">
         <v>98.36065600000001</v>
@@ -943,7 +951,7 @@
         <v>5.009156</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.922108</v>
+        <v>-0.998645</v>
       </c>
       <c r="G21" t="n">
         <v>98.36065600000001</v>
@@ -968,7 +976,7 @@
         <v>6.914384</v>
       </c>
       <c r="F22" t="n">
-        <v>0.657675</v>
+        <v>0.422318</v>
       </c>
       <c r="G22" t="n">
         <v>98.36065600000001</v>
@@ -993,7 +1001,7 @@
         <v>7.265832</v>
       </c>
       <c r="F23" t="n">
-        <v>0.907154</v>
+        <v>0.5160979999999999</v>
       </c>
       <c r="G23" t="n">
         <v>98.36065600000001</v>
@@ -1018,7 +1026,7 @@
         <v>5.837493</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5273949999999999</v>
+        <v>0.429346</v>
       </c>
       <c r="G24" t="n">
         <v>98.36065600000001</v>
@@ -1043,7 +1051,7 @@
         <v>1.578075</v>
       </c>
       <c r="F25" t="n">
-        <v>0.868859</v>
+        <v>-0.029345</v>
       </c>
       <c r="G25" t="n">
         <v>98.36065600000001</v>
@@ -1068,7 +1076,7 @@
         <v>11.382115</v>
       </c>
       <c r="F26" t="n">
-        <v>3.684697</v>
+        <v>6.669777</v>
       </c>
       <c r="G26" t="n">
         <v>98.36065600000001</v>
@@ -1093,7 +1101,7 @@
         <v>7.463068</v>
       </c>
       <c r="F27" t="n">
-        <v>3.127419</v>
+        <v>6.398498</v>
       </c>
       <c r="G27" t="n">
         <v>98.36065600000001</v>
@@ -1118,7 +1126,7 @@
         <v>-1.612261</v>
       </c>
       <c r="F28" t="n">
-        <v>2.489708</v>
+        <v>1.450696</v>
       </c>
       <c r="G28" t="n">
         <v>98.36065600000001</v>
@@ -1130,15 +1138,23 @@
           <t>yahoo_ret_milho</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
+      <c r="B29" s="1" t="n">
+        <v>44500</v>
+      </c>
+      <c r="C29" s="1" t="n">
+        <v>46295</v>
+      </c>
       <c r="D29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="E29" t="n">
+        <v>5.868654</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-0.582524</v>
+      </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>98.36065600000001</v>
       </c>
     </row>
     <row r="30">
@@ -1360,7 +1376,7 @@
         <v>5.4394</v>
       </c>
       <c r="F38" t="n">
-        <v>5.0962</v>
+        <v>5.1253</v>
       </c>
       <c r="G38" t="n">
         <v>100</v>
@@ -1385,7 +1401,7 @@
         <v>5.4388</v>
       </c>
       <c r="F39" t="n">
-        <v>5.0956</v>
+        <v>5.1247</v>
       </c>
       <c r="G39" t="n">
         <v>100</v>
@@ -1660,7 +1676,7 @@
         <v>3.74306</v>
       </c>
       <c r="F50" t="n">
-        <v>-1.64814</v>
+        <v>-1.086537</v>
       </c>
       <c r="G50" t="n">
         <v>98.36065600000001</v>
@@ -1685,7 +1701,7 @@
         <v>3.743473</v>
       </c>
       <c r="F51" t="n">
-        <v>-1.64833</v>
+        <v>-1.086663</v>
       </c>
       <c r="G51" t="n">
         <v>98.36065600000001</v>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,7 +479,7 @@
         <v>185147</v>
       </c>
       <c r="G2" t="n">
-        <v>100</v>
+        <v>17.086835</v>
       </c>
     </row>
     <row r="3">
@@ -504,7 +504,7 @@
         <v>182.25</v>
       </c>
       <c r="G3" t="n">
-        <v>100</v>
+        <v>17.086835</v>
       </c>
     </row>
     <row r="4">
@@ -529,7 +529,7 @@
         <v>111.059998</v>
       </c>
       <c r="G4" t="n">
-        <v>100</v>
+        <v>17.086835</v>
       </c>
     </row>
     <row r="5">
@@ -554,7 +554,7 @@
         <v>446</v>
       </c>
       <c r="G5" t="n">
-        <v>100</v>
+        <v>17.086835</v>
       </c>
     </row>
     <row r="6">
@@ -579,7 +579,7 @@
         <v>5.1237</v>
       </c>
       <c r="G6" t="n">
-        <v>100</v>
+        <v>17.086835</v>
       </c>
     </row>
     <row r="7">
@@ -604,7 +604,7 @@
         <v>5.9496</v>
       </c>
       <c r="G7" t="n">
-        <v>100</v>
+        <v>17.086835</v>
       </c>
     </row>
     <row r="8">
@@ -629,7 +629,7 @@
         <v>7718.600098</v>
       </c>
       <c r="G8" t="n">
-        <v>100</v>
+        <v>17.086835</v>
       </c>
     </row>
     <row r="9">
@@ -654,7 +654,7 @@
         <v>26506.990234</v>
       </c>
       <c r="G9" t="n">
-        <v>100</v>
+        <v>17.086835</v>
       </c>
     </row>
     <row r="10">
@@ -679,7 +679,7 @@
         <v>53414.25</v>
       </c>
       <c r="G10" t="n">
-        <v>100</v>
+        <v>17.086835</v>
       </c>
     </row>
     <row r="11">
@@ -704,7 +704,7 @@
         <v>4429.799805</v>
       </c>
       <c r="G11" t="n">
-        <v>100</v>
+        <v>17.086835</v>
       </c>
     </row>
     <row r="12">
@@ -729,7 +729,7 @@
         <v>91.480003</v>
       </c>
       <c r="G12" t="n">
-        <v>100</v>
+        <v>17.086835</v>
       </c>
     </row>
     <row r="13">
@@ -754,7 +754,7 @@
         <v>96.279999</v>
       </c>
       <c r="G13" t="n">
-        <v>100</v>
+        <v>17.086835</v>
       </c>
     </row>
     <row r="14">
@@ -779,7 +779,7 @@
         <v>1293.75</v>
       </c>
       <c r="G14" t="n">
-        <v>100</v>
+        <v>17.086835</v>
       </c>
     </row>
     <row r="15">
@@ -804,7 +804,7 @@
         <v>512</v>
       </c>
       <c r="G15" t="n">
-        <v>100</v>
+        <v>17.086835</v>
       </c>
     </row>
     <row r="16">
@@ -829,7 +829,7 @@
         <v>4.355791</v>
       </c>
       <c r="G16" t="n">
-        <v>98.36065600000001</v>
+        <v>16.806723</v>
       </c>
     </row>
     <row r="17">
@@ -854,7 +854,7 @@
         <v>4.273945</v>
       </c>
       <c r="G17" t="n">
-        <v>98.36065600000001</v>
+        <v>16.806723</v>
       </c>
     </row>
     <row r="18">
@@ -879,7 +879,7 @@
         <v>4.645247</v>
       </c>
       <c r="G18" t="n">
-        <v>98.36065600000001</v>
+        <v>16.806723</v>
       </c>
     </row>
     <row r="19">
@@ -904,7 +904,7 @@
         <v>-0.745523</v>
       </c>
       <c r="G19" t="n">
-        <v>98.36065600000001</v>
+        <v>16.806723</v>
       </c>
     </row>
     <row r="20">
@@ -929,7 +929,7 @@
         <v>-1.30027</v>
       </c>
       <c r="G20" t="n">
-        <v>98.36065600000001</v>
+        <v>16.806723</v>
       </c>
     </row>
     <row r="21">
@@ -954,7 +954,7 @@
         <v>-0.998645</v>
       </c>
       <c r="G21" t="n">
-        <v>98.36065600000001</v>
+        <v>16.806723</v>
       </c>
     </row>
     <row r="22">
@@ -979,7 +979,7 @@
         <v>0.422318</v>
       </c>
       <c r="G22" t="n">
-        <v>98.36065600000001</v>
+        <v>16.806723</v>
       </c>
     </row>
     <row r="23">
@@ -1004,7 +1004,7 @@
         <v>0.5160979999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>98.36065600000001</v>
+        <v>16.806723</v>
       </c>
     </row>
     <row r="24">
@@ -1029,7 +1029,7 @@
         <v>0.429346</v>
       </c>
       <c r="G24" t="n">
-        <v>98.36065600000001</v>
+        <v>16.806723</v>
       </c>
     </row>
     <row r="25">
@@ -1054,7 +1054,7 @@
         <v>-0.029345</v>
       </c>
       <c r="G25" t="n">
-        <v>98.36065600000001</v>
+        <v>16.806723</v>
       </c>
     </row>
     <row r="26">
@@ -1079,7 +1079,7 @@
         <v>6.669777</v>
       </c>
       <c r="G26" t="n">
-        <v>98.36065600000001</v>
+        <v>16.806723</v>
       </c>
     </row>
     <row r="27">
@@ -1104,7 +1104,7 @@
         <v>6.398498</v>
       </c>
       <c r="G27" t="n">
-        <v>98.36065600000001</v>
+        <v>16.806723</v>
       </c>
     </row>
     <row r="28">
@@ -1129,7 +1129,7 @@
         <v>1.450696</v>
       </c>
       <c r="G28" t="n">
-        <v>98.36065600000001</v>
+        <v>16.806723</v>
       </c>
     </row>
     <row r="29">
@@ -1154,7 +1154,7 @@
         <v>-0.582524</v>
       </c>
       <c r="G29" t="n">
-        <v>98.36065600000001</v>
+        <v>16.806723</v>
       </c>
     </row>
     <row r="30">
@@ -1179,7 +1179,7 @@
         <v>14</v>
       </c>
       <c r="G30" t="n">
-        <v>100</v>
+        <v>17.086835</v>
       </c>
     </row>
     <row r="31">
@@ -1204,7 +1204,7 @@
         <v>0.05166</v>
       </c>
       <c r="G31" t="n">
-        <v>100</v>
+        <v>17.086835</v>
       </c>
     </row>
     <row r="32">
@@ -1229,7 +1229,7 @@
         <v>0.05166</v>
       </c>
       <c r="G32" t="n">
-        <v>100</v>
+        <v>17.086835</v>
       </c>
     </row>
     <row r="33">
@@ -1254,7 +1254,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="G33" t="n">
-        <v>96.721311</v>
+        <v>16.526611</v>
       </c>
     </row>
     <row r="34">
@@ -1279,7 +1279,7 @@
         <v>-0.22</v>
       </c>
       <c r="G34" t="n">
-        <v>98.36065600000001</v>
+        <v>16.806723</v>
       </c>
     </row>
     <row r="35">
@@ -1304,7 +1304,7 @@
         <v>-0.01</v>
       </c>
       <c r="G35" t="n">
-        <v>96.721311</v>
+        <v>16.526611</v>
       </c>
     </row>
     <row r="36">
@@ -1329,7 +1329,7 @@
         <v>110.22154</v>
       </c>
       <c r="G36" t="n">
-        <v>95.08196700000001</v>
+        <v>16.246499</v>
       </c>
     </row>
     <row r="37">
@@ -1354,7 +1354,7 @@
         <v>109.89427</v>
       </c>
       <c r="G37" t="n">
-        <v>95.08196700000001</v>
+        <v>16.246499</v>
       </c>
     </row>
     <row r="38">
@@ -1379,7 +1379,7 @@
         <v>5.1253</v>
       </c>
       <c r="G38" t="n">
-        <v>100</v>
+        <v>17.086835</v>
       </c>
     </row>
     <row r="39">
@@ -1404,7 +1404,7 @@
         <v>5.1247</v>
       </c>
       <c r="G39" t="n">
-        <v>100</v>
+        <v>17.086835</v>
       </c>
     </row>
     <row r="40">
@@ -1429,7 +1429,7 @@
         <v>7372243</v>
       </c>
       <c r="G40" t="n">
-        <v>96.721311</v>
+        <v>16.526611</v>
       </c>
     </row>
     <row r="41">
@@ -1454,7 +1454,7 @@
         <v>2731513</v>
       </c>
       <c r="G41" t="n">
-        <v>96.721311</v>
+        <v>16.526611</v>
       </c>
     </row>
     <row r="42">
@@ -1479,7 +1479,7 @@
         <v>4640730</v>
       </c>
       <c r="G42" t="n">
-        <v>96.721311</v>
+        <v>16.526611</v>
       </c>
     </row>
     <row r="43">
@@ -1504,7 +1504,7 @@
         <v>4.88</v>
       </c>
       <c r="G43" t="n">
-        <v>96.721311</v>
+        <v>16.526611</v>
       </c>
     </row>
     <row r="44">
@@ -1529,7 +1529,7 @@
         <v>3.31</v>
       </c>
       <c r="G44" t="n">
-        <v>96.721311</v>
+        <v>16.526611</v>
       </c>
     </row>
     <row r="45">
@@ -1554,7 +1554,7 @@
         <v>5.81</v>
       </c>
       <c r="G45" t="n">
-        <v>96.721311</v>
+        <v>16.526611</v>
       </c>
     </row>
     <row r="46">
@@ -1579,7 +1579,7 @@
         <v>32.08</v>
       </c>
       <c r="G46" t="n">
-        <v>96.721311</v>
+        <v>16.526611</v>
       </c>
     </row>
     <row r="47">
@@ -1604,7 +1604,7 @@
         <v>369742</v>
       </c>
       <c r="G47" t="n">
-        <v>96.721311</v>
+        <v>16.526611</v>
       </c>
     </row>
     <row r="48">
@@ -1629,7 +1629,7 @@
         <v>-0.6395690000000001</v>
       </c>
       <c r="G48" t="n">
-        <v>93.442623</v>
+        <v>15.966387</v>
       </c>
     </row>
     <row r="49">
@@ -1654,7 +1654,7 @@
         <v>0.332557</v>
       </c>
       <c r="G49" t="n">
-        <v>93.442623</v>
+        <v>15.966387</v>
       </c>
     </row>
     <row r="50">
@@ -1679,7 +1679,7 @@
         <v>-1.086537</v>
       </c>
       <c r="G50" t="n">
-        <v>98.36065600000001</v>
+        <v>16.806723</v>
       </c>
     </row>
     <row r="51">
@@ -1704,7 +1704,7 @@
         <v>-1.086663</v>
       </c>
       <c r="G51" t="n">
-        <v>98.36065600000001</v>
+        <v>16.806723</v>
       </c>
     </row>
     <row r="52">
@@ -1729,7 +1729,7 @@
         <v>0.257708</v>
       </c>
       <c r="G52" t="n">
-        <v>95.08196700000001</v>
+        <v>16.246499</v>
       </c>
     </row>
     <row r="53">
@@ -1754,7 +1754,7 @@
         <v>-0.694824</v>
       </c>
       <c r="G53" t="n">
-        <v>95.08196700000001</v>
+        <v>16.246499</v>
       </c>
     </row>
     <row r="54">
@@ -1779,7 +1779,7 @@
         <v>0.826955</v>
       </c>
       <c r="G54" t="n">
-        <v>95.08196700000001</v>
+        <v>16.246499</v>
       </c>
     </row>
     <row r="55">
@@ -1804,7 +1804,7 @@
         <v>0.5941920000000001</v>
       </c>
       <c r="G55" t="n">
-        <v>95.08196700000001</v>
+        <v>16.246499</v>
       </c>
     </row>
     <row r="56">
@@ -1829,7 +1829,7 @@
         <v>4.443025</v>
       </c>
       <c r="G56" t="n">
-        <v>78.688525</v>
+        <v>13.445378</v>
       </c>
     </row>
     <row r="57">
@@ -1854,7 +1854,7 @@
         <v>2.178243</v>
       </c>
       <c r="G57" t="n">
-        <v>80.32786900000001</v>
+        <v>13.72549</v>
       </c>
     </row>
     <row r="58">
@@ -1879,7 +1879,7 @@
         <v>4.098046</v>
       </c>
       <c r="G58" t="n">
-        <v>78.688525</v>
+        <v>13.445378</v>
       </c>
     </row>
     <row r="59">
@@ -1904,7 +1904,7 @@
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>98.36065600000001</v>
+        <v>16.806723</v>
       </c>
     </row>
     <row r="60">
@@ -1929,7 +1929,7 @@
         <v>-0.000124</v>
       </c>
       <c r="G60" t="n">
-        <v>98.36065600000001</v>
+        <v>16.806723</v>
       </c>
     </row>
     <row r="61">
@@ -1954,7 +1954,7 @@
         <v>-0.000124</v>
       </c>
       <c r="G61" t="n">
-        <v>98.36065600000001</v>
+        <v>16.806723</v>
       </c>
     </row>
     <row r="62">
@@ -1979,7 +1979,7 @@
         <v>0.3</v>
       </c>
       <c r="G62" t="n">
-        <v>95.08196700000001</v>
+        <v>16.246499</v>
       </c>
     </row>
     <row r="63">
@@ -2004,7 +2004,7 @@
         <v>0.13</v>
       </c>
       <c r="G63" t="n">
-        <v>95.08196700000001</v>
+        <v>16.246499</v>
       </c>
     </row>
     <row r="64">
@@ -2029,7 +2029,7 @@
         <v>0.39</v>
       </c>
       <c r="G64" t="n">
-        <v>95.08196700000001</v>
+        <v>16.246499</v>
       </c>
     </row>
     <row r="65">
@@ -2054,7 +2054,232 @@
         <v>-1.25</v>
       </c>
       <c r="G65" t="n">
-        <v>95.08196700000001</v>
+        <v>16.246499</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>comexstat_comex_exportacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="B66" s="1" t="n">
+        <v>35461</v>
+      </c>
+      <c r="C66" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D66" t="n">
+        <v>356</v>
+      </c>
+      <c r="E66" t="n">
+        <v>3680971118</v>
+      </c>
+      <c r="F66" t="n">
+        <v>33157804370</v>
+      </c>
+      <c r="G66" t="n">
+        <v>99.719888</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>comexstat_comex_importacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="B67" s="1" t="n">
+        <v>35461</v>
+      </c>
+      <c r="C67" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D67" t="n">
+        <v>356</v>
+      </c>
+      <c r="E67" t="n">
+        <v>2588659779</v>
+      </c>
+      <c r="F67" t="n">
+        <v>25763862100</v>
+      </c>
+      <c r="G67" t="n">
+        <v>99.719888</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>comexstat_comex_saldo_comercial_usd</t>
+        </is>
+      </c>
+      <c r="B68" s="1" t="n">
+        <v>35461</v>
+      </c>
+      <c r="C68" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D68" t="n">
+        <v>356</v>
+      </c>
+      <c r="E68" t="n">
+        <v>1092311339</v>
+      </c>
+      <c r="F68" t="n">
+        <v>7393942270</v>
+      </c>
+      <c r="G68" t="n">
+        <v>99.719888</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>comexstat_comex_corrente_comercio_usd</t>
+        </is>
+      </c>
+      <c r="B69" s="1" t="n">
+        <v>35461</v>
+      </c>
+      <c r="C69" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D69" t="n">
+        <v>356</v>
+      </c>
+      <c r="E69" t="n">
+        <v>6269630897</v>
+      </c>
+      <c r="F69" t="n">
+        <v>58921666470</v>
+      </c>
+      <c r="G69" t="n">
+        <v>99.719888</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>comexstat_comex_exportacoes_kg</t>
+        </is>
+      </c>
+      <c r="B70" s="1" t="n">
+        <v>35461</v>
+      </c>
+      <c r="C70" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D70" t="n">
+        <v>356</v>
+      </c>
+      <c r="E70" t="n">
+        <v>17370770826</v>
+      </c>
+      <c r="F70" t="n">
+        <v>77119199389</v>
+      </c>
+      <c r="G70" t="n">
+        <v>99.719888</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>comexstat_comex_importacoes_kg</t>
+        </is>
+      </c>
+      <c r="B71" s="1" t="n">
+        <v>35461</v>
+      </c>
+      <c r="C71" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D71" t="n">
+        <v>356</v>
+      </c>
+      <c r="E71" t="n">
+        <v>1569629726</v>
+      </c>
+      <c r="F71" t="n">
+        <v>14073182023</v>
+      </c>
+      <c r="G71" t="n">
+        <v>99.719888</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>comexstat_comex_importacoes_frete_usd</t>
+        </is>
+      </c>
+      <c r="B72" s="1" t="n">
+        <v>35461</v>
+      </c>
+      <c r="C72" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D72" t="n">
+        <v>356</v>
+      </c>
+      <c r="E72" t="n">
+        <v>154149785</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1548184686</v>
+      </c>
+      <c r="G72" t="n">
+        <v>99.719888</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>comexstat_comex_importacoes_seguro_usd</t>
+        </is>
+      </c>
+      <c r="B73" s="1" t="n">
+        <v>35461</v>
+      </c>
+      <c r="C73" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D73" t="n">
+        <v>356</v>
+      </c>
+      <c r="E73" t="n">
+        <v>7008789</v>
+      </c>
+      <c r="F73" t="n">
+        <v>19241881</v>
+      </c>
+      <c r="G73" t="n">
+        <v>99.719888</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>comexstat_comex_importacoes_cif_usd</t>
+        </is>
+      </c>
+      <c r="B74" s="1" t="n">
+        <v>35461</v>
+      </c>
+      <c r="C74" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D74" t="n">
+        <v>356</v>
+      </c>
+      <c r="E74" t="n">
+        <v>2749818353</v>
+      </c>
+      <c r="F74" t="n">
+        <v>27331288667</v>
+      </c>
+      <c r="G74" t="n">
+        <v>99.719888</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,7 +479,7 @@
         <v>185147</v>
       </c>
       <c r="G2" t="n">
-        <v>17.086835</v>
+        <v>75.30864200000001</v>
       </c>
     </row>
     <row r="3">
@@ -501,10 +501,10 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>182.25</v>
+        <v>181.940002</v>
       </c>
       <c r="G3" t="n">
-        <v>17.086835</v>
+        <v>75.30864200000001</v>
       </c>
     </row>
     <row r="4">
@@ -526,10 +526,10 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>111.059998</v>
+        <v>110.989998</v>
       </c>
       <c r="G4" t="n">
-        <v>17.086835</v>
+        <v>75.30864200000001</v>
       </c>
     </row>
     <row r="5">
@@ -551,10 +551,10 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>446</v>
+        <v>447.350006</v>
       </c>
       <c r="G5" t="n">
-        <v>17.086835</v>
+        <v>75.30864200000001</v>
       </c>
     </row>
     <row r="6">
@@ -579,7 +579,7 @@
         <v>5.1237</v>
       </c>
       <c r="G6" t="n">
-        <v>17.086835</v>
+        <v>75.30864200000001</v>
       </c>
     </row>
     <row r="7">
@@ -604,7 +604,7 @@
         <v>5.9496</v>
       </c>
       <c r="G7" t="n">
-        <v>17.086835</v>
+        <v>75.30864200000001</v>
       </c>
     </row>
     <row r="8">
@@ -629,7 +629,7 @@
         <v>7718.600098</v>
       </c>
       <c r="G8" t="n">
-        <v>17.086835</v>
+        <v>75.30864200000001</v>
       </c>
     </row>
     <row r="9">
@@ -654,7 +654,7 @@
         <v>26506.990234</v>
       </c>
       <c r="G9" t="n">
-        <v>17.086835</v>
+        <v>75.30864200000001</v>
       </c>
     </row>
     <row r="10">
@@ -679,7 +679,7 @@
         <v>53414.25</v>
       </c>
       <c r="G10" t="n">
-        <v>17.086835</v>
+        <v>75.30864200000001</v>
       </c>
     </row>
     <row r="11">
@@ -704,7 +704,7 @@
         <v>4429.799805</v>
       </c>
       <c r="G11" t="n">
-        <v>17.086835</v>
+        <v>75.30864200000001</v>
       </c>
     </row>
     <row r="12">
@@ -729,7 +729,7 @@
         <v>91.480003</v>
       </c>
       <c r="G12" t="n">
-        <v>17.086835</v>
+        <v>75.30864200000001</v>
       </c>
     </row>
     <row r="13">
@@ -754,7 +754,7 @@
         <v>96.279999</v>
       </c>
       <c r="G13" t="n">
-        <v>17.086835</v>
+        <v>75.30864200000001</v>
       </c>
     </row>
     <row r="14">
@@ -779,7 +779,7 @@
         <v>1293.75</v>
       </c>
       <c r="G14" t="n">
-        <v>17.086835</v>
+        <v>75.30864200000001</v>
       </c>
     </row>
     <row r="15">
@@ -804,7 +804,7 @@
         <v>512</v>
       </c>
       <c r="G15" t="n">
-        <v>17.086835</v>
+        <v>75.30864200000001</v>
       </c>
     </row>
     <row r="16">
@@ -829,7 +829,7 @@
         <v>4.355791</v>
       </c>
       <c r="G16" t="n">
-        <v>16.806723</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="17">
@@ -851,10 +851,10 @@
         <v>-6.394964</v>
       </c>
       <c r="F17" t="n">
-        <v>4.273945</v>
+        <v>4.096581</v>
       </c>
       <c r="G17" t="n">
-        <v>16.806723</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="18">
@@ -876,10 +876,10 @@
         <v>-12.715859</v>
       </c>
       <c r="F18" t="n">
-        <v>4.645247</v>
+        <v>4.57929</v>
       </c>
       <c r="G18" t="n">
-        <v>16.806723</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="19">
@@ -901,10 +901,10 @@
         <v>10.980392</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.745523</v>
+        <v>-0.445087</v>
       </c>
       <c r="G19" t="n">
-        <v>16.806723</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="20">
@@ -929,7 +929,7 @@
         <v>-1.30027</v>
       </c>
       <c r="G20" t="n">
-        <v>16.806723</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="21">
@@ -954,7 +954,7 @@
         <v>-0.998645</v>
       </c>
       <c r="G21" t="n">
-        <v>16.806723</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="22">
@@ -979,7 +979,7 @@
         <v>0.422318</v>
       </c>
       <c r="G22" t="n">
-        <v>16.806723</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="23">
@@ -1004,7 +1004,7 @@
         <v>0.5160979999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>16.806723</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="24">
@@ -1029,7 +1029,7 @@
         <v>0.429346</v>
       </c>
       <c r="G24" t="n">
-        <v>16.806723</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="25">
@@ -1054,7 +1054,7 @@
         <v>-0.029345</v>
       </c>
       <c r="G25" t="n">
-        <v>16.806723</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="26">
@@ -1079,7 +1079,7 @@
         <v>6.669777</v>
       </c>
       <c r="G26" t="n">
-        <v>16.806723</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="27">
@@ -1104,7 +1104,7 @@
         <v>6.398498</v>
       </c>
       <c r="G27" t="n">
-        <v>16.806723</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="28">
@@ -1129,7 +1129,7 @@
         <v>1.450696</v>
       </c>
       <c r="G28" t="n">
-        <v>16.806723</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="29">
@@ -1154,13 +1154,13 @@
         <v>-0.582524</v>
       </c>
       <c r="G29" t="n">
-        <v>16.806723</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_meta</t>
+          <t>bcb_sgs_selic_over</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
@@ -1173,19 +1173,19 @@
         <v>61</v>
       </c>
       <c r="E30" t="n">
-        <v>6.25</v>
+        <v>0.021182</v>
       </c>
       <c r="F30" t="n">
-        <v>14</v>
+        <v>0.05166</v>
       </c>
       <c r="G30" t="n">
-        <v>17.086835</v>
+        <v>75.30864200000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_over</t>
+          <t>bcb_sgs_cdi</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1204,113 +1204,113 @@
         <v>0.05166</v>
       </c>
       <c r="G31" t="n">
-        <v>17.086835</v>
+        <v>75.30864200000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bcb_sgs_cdi</t>
+          <t>bcb_sgs_ipca</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D32" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E32" t="n">
-        <v>0.021182</v>
+        <v>1.16</v>
       </c>
       <c r="F32" t="n">
-        <v>0.05166</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G32" t="n">
-        <v>17.086835</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca</t>
+          <t>bcb_sgs_igp_m</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D33" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>1.16</v>
+        <v>-0.64</v>
       </c>
       <c r="F33" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.22</v>
       </c>
       <c r="G33" t="n">
-        <v>16.526611</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m</t>
+          <t>bcb_sgs_inpc</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D34" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.64</v>
+        <v>1.2</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.22</v>
+        <v>-0.01</v>
       </c>
       <c r="G34" t="n">
-        <v>16.806723</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc</t>
+          <t>bcb_sgs_ibc_br_sa</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D35" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E35" t="n">
-        <v>1.2</v>
+        <v>96.95313</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.01</v>
+        <v>110.22154</v>
       </c>
       <c r="G35" t="n">
-        <v>16.526611</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br_sa</t>
+          <t>bcb_sgs_ibc_br</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
@@ -1323,44 +1323,44 @@
         <v>58</v>
       </c>
       <c r="E36" t="n">
-        <v>96.95313</v>
+        <v>97.10569</v>
       </c>
       <c r="F36" t="n">
-        <v>110.22154</v>
+        <v>109.89427</v>
       </c>
       <c r="G36" t="n">
-        <v>16.246499</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br</t>
+          <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46203</v>
+        <v>46295</v>
       </c>
       <c r="D37" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E37" t="n">
-        <v>97.10569</v>
+        <v>5.4394</v>
       </c>
       <c r="F37" t="n">
-        <v>109.89427</v>
+        <v>5.1253</v>
       </c>
       <c r="G37" t="n">
-        <v>16.246499</v>
+        <v>75.30864200000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_venda_usd</t>
+          <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
@@ -1373,44 +1373,44 @@
         <v>61</v>
       </c>
       <c r="E38" t="n">
-        <v>5.4394</v>
+        <v>5.4388</v>
       </c>
       <c r="F38" t="n">
-        <v>5.1253</v>
+        <v>5.1247</v>
       </c>
       <c r="G38" t="n">
-        <v>17.086835</v>
+        <v>75.30864200000001</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_compra_usd</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D39" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E39" t="n">
-        <v>5.4388</v>
+        <v>4441056</v>
       </c>
       <c r="F39" t="n">
-        <v>5.1247</v>
+        <v>7372243</v>
       </c>
       <c r="G39" t="n">
-        <v>17.086835</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
@@ -1423,19 +1423,19 @@
         <v>59</v>
       </c>
       <c r="E40" t="n">
-        <v>4441056</v>
+        <v>1894119</v>
       </c>
       <c r="F40" t="n">
-        <v>7372243</v>
+        <v>2731513</v>
       </c>
       <c r="G40" t="n">
-        <v>16.526611</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
@@ -1448,19 +1448,19 @@
         <v>59</v>
       </c>
       <c r="E41" t="n">
-        <v>1894119</v>
+        <v>2546936</v>
       </c>
       <c r="F41" t="n">
-        <v>2731513</v>
+        <v>4640730</v>
       </c>
       <c r="G41" t="n">
-        <v>16.526611</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
@@ -1473,19 +1473,19 @@
         <v>59</v>
       </c>
       <c r="E42" t="n">
-        <v>2546936</v>
+        <v>2.34</v>
       </c>
       <c r="F42" t="n">
-        <v>4640730</v>
+        <v>4.88</v>
       </c>
       <c r="G42" t="n">
-        <v>16.526611</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
@@ -1498,19 +1498,19 @@
         <v>59</v>
       </c>
       <c r="E43" t="n">
-        <v>2.34</v>
+        <v>1.43</v>
       </c>
       <c r="F43" t="n">
-        <v>4.88</v>
+        <v>3.31</v>
       </c>
       <c r="G43" t="n">
-        <v>16.526611</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
@@ -1523,19 +1523,19 @@
         <v>59</v>
       </c>
       <c r="E44" t="n">
-        <v>1.43</v>
+        <v>3.01</v>
       </c>
       <c r="F44" t="n">
-        <v>3.31</v>
+        <v>5.81</v>
       </c>
       <c r="G44" t="n">
-        <v>16.526611</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
@@ -1548,19 +1548,19 @@
         <v>59</v>
       </c>
       <c r="E45" t="n">
-        <v>3.01</v>
+        <v>21.42</v>
       </c>
       <c r="F45" t="n">
-        <v>5.81</v>
+        <v>32.08</v>
       </c>
       <c r="G45" t="n">
-        <v>16.526611</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
@@ -1573,44 +1573,44 @@
         <v>59</v>
       </c>
       <c r="E46" t="n">
-        <v>21.42</v>
+        <v>368886</v>
       </c>
       <c r="F46" t="n">
-        <v>32.08</v>
+        <v>369742</v>
       </c>
       <c r="G46" t="n">
-        <v>16.526611</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D47" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E47" t="n">
-        <v>368886</v>
+        <v>0.541272</v>
       </c>
       <c r="F47" t="n">
-        <v>369742</v>
+        <v>-0.6395690000000001</v>
       </c>
       <c r="G47" t="n">
-        <v>16.526611</v>
+        <v>70.37036999999999</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
@@ -1623,44 +1623,44 @@
         <v>57</v>
       </c>
       <c r="E48" t="n">
-        <v>0.541272</v>
+        <v>-0.59426</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.6395690000000001</v>
+        <v>0.332557</v>
       </c>
       <c r="G48" t="n">
-        <v>15.966387</v>
+        <v>70.37036999999999</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46203</v>
+        <v>46295</v>
       </c>
       <c r="D49" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.59426</v>
+        <v>3.74306</v>
       </c>
       <c r="F49" t="n">
-        <v>0.332557</v>
+        <v>-1.086537</v>
       </c>
       <c r="G49" t="n">
-        <v>15.966387</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
@@ -1673,44 +1673,44 @@
         <v>60</v>
       </c>
       <c r="E50" t="n">
-        <v>3.74306</v>
+        <v>3.743473</v>
       </c>
       <c r="F50" t="n">
-        <v>-1.086537</v>
+        <v>-1.086663</v>
       </c>
       <c r="G50" t="n">
-        <v>16.806723</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D51" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E51" t="n">
-        <v>3.743473</v>
+        <v>1.596467</v>
       </c>
       <c r="F51" t="n">
-        <v>-1.086663</v>
+        <v>0.257708</v>
       </c>
       <c r="G51" t="n">
-        <v>16.806723</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
@@ -1723,19 +1723,19 @@
         <v>58</v>
       </c>
       <c r="E52" t="n">
-        <v>1.596467</v>
+        <v>0.888065</v>
       </c>
       <c r="F52" t="n">
-        <v>0.257708</v>
+        <v>-0.694824</v>
       </c>
       <c r="G52" t="n">
-        <v>16.246499</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
@@ -1748,19 +1748,19 @@
         <v>58</v>
       </c>
       <c r="E53" t="n">
-        <v>0.888065</v>
+        <v>2.123375</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.694824</v>
+        <v>0.826955</v>
       </c>
       <c r="G53" t="n">
-        <v>16.246499</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
@@ -1773,119 +1773,119 @@
         <v>58</v>
       </c>
       <c r="E54" t="n">
-        <v>2.123375</v>
+        <v>-0.259972</v>
       </c>
       <c r="F54" t="n">
-        <v>0.826955</v>
+        <v>0.5941920000000001</v>
       </c>
       <c r="G54" t="n">
-        <v>16.246499</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C55" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D55" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.259972</v>
+        <v>8.727061000000001</v>
       </c>
       <c r="F55" t="n">
-        <v>0.5941920000000001</v>
+        <v>4.443025</v>
       </c>
       <c r="G55" t="n">
-        <v>16.246499</v>
+        <v>59.259259</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
         <v>44804</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D56" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E56" t="n">
-        <v>8.727061000000001</v>
+        <v>8.58755</v>
       </c>
       <c r="F56" t="n">
-        <v>4.443025</v>
+        <v>2.178243</v>
       </c>
       <c r="G56" t="n">
-        <v>13.445378</v>
+        <v>60.493827</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
         <v>44804</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D57" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E57" t="n">
-        <v>8.58755</v>
+        <v>8.825751</v>
       </c>
       <c r="F57" t="n">
-        <v>2.178243</v>
+        <v>4.098046</v>
       </c>
       <c r="G57" t="n">
-        <v>13.72549</v>
+        <v>59.259259</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D58" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="E58" t="n">
-        <v>8.825751</v>
+        <v>0.003062</v>
       </c>
       <c r="F58" t="n">
-        <v>4.098046</v>
+        <v>-0.000124</v>
       </c>
       <c r="G58" t="n">
-        <v>13.445378</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
@@ -1898,69 +1898,69 @@
         <v>60</v>
       </c>
       <c r="E59" t="n">
-        <v>1.5</v>
+        <v>0.003062</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>-0.000124</v>
       </c>
       <c r="G59" t="n">
-        <v>16.806723</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D60" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E60" t="n">
-        <v>0.003062</v>
+        <v>-0.01</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.000124</v>
+        <v>0.3</v>
       </c>
       <c r="G60" t="n">
-        <v>16.806723</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D61" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E61" t="n">
-        <v>0.003062</v>
+        <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.000124</v>
+        <v>0.13</v>
       </c>
       <c r="G61" t="n">
-        <v>16.806723</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
@@ -1973,19 +1973,19 @@
         <v>58</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="F62" t="n">
-        <v>0.3</v>
+        <v>0.39</v>
       </c>
       <c r="G62" t="n">
-        <v>16.246499</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
@@ -1998,288 +1998,1238 @@
         <v>58</v>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="F63" t="n">
-        <v>0.13</v>
+        <v>-1.25</v>
       </c>
       <c r="G63" t="n">
-        <v>16.246499</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
+          <t>comexstat_comex_exportacoes_fob_usd</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>44500</v>
+        <v>43861</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D64" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.02</v>
+        <v>14429715267</v>
       </c>
       <c r="F64" t="n">
-        <v>0.39</v>
+        <v>33157804370</v>
       </c>
       <c r="G64" t="n">
-        <v>16.246499</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>comexstat_comex_importacoes_fob_usd</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>44500</v>
+        <v>43861</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D65" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="E65" t="n">
-        <v>1.47</v>
+        <v>17190165488</v>
       </c>
       <c r="F65" t="n">
-        <v>-1.25</v>
+        <v>25763862100</v>
       </c>
       <c r="G65" t="n">
-        <v>16.246499</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_fob_usd</t>
+          <t>comexstat_comex_saldo_comercial_usd</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
-        <v>35461</v>
+        <v>43861</v>
       </c>
       <c r="C66" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D66" t="n">
-        <v>356</v>
+        <v>80</v>
       </c>
       <c r="E66" t="n">
-        <v>3680971118</v>
+        <v>-2760450221</v>
       </c>
       <c r="F66" t="n">
-        <v>33157804370</v>
+        <v>7393942270</v>
       </c>
       <c r="G66" t="n">
-        <v>99.719888</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_fob_usd</t>
+          <t>comexstat_comex_corrente_comercio_usd</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
-        <v>35461</v>
+        <v>43861</v>
       </c>
       <c r="C67" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D67" t="n">
-        <v>356</v>
+        <v>80</v>
       </c>
       <c r="E67" t="n">
-        <v>2588659779</v>
+        <v>31619880755</v>
       </c>
       <c r="F67" t="n">
-        <v>25763862100</v>
+        <v>58921666470</v>
       </c>
       <c r="G67" t="n">
-        <v>99.719888</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>comexstat_comex_saldo_comercial_usd</t>
+          <t>comexstat_comex_exportacoes_kg</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
-        <v>35461</v>
+        <v>43861</v>
       </c>
       <c r="C68" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D68" t="n">
-        <v>356</v>
+        <v>80</v>
       </c>
       <c r="E68" t="n">
-        <v>1092311339</v>
+        <v>46718273016</v>
       </c>
       <c r="F68" t="n">
-        <v>7393942270</v>
+        <v>77119199389</v>
       </c>
       <c r="G68" t="n">
-        <v>99.719888</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>comexstat_comex_corrente_comercio_usd</t>
+          <t>comexstat_comex_importacoes_kg</t>
         </is>
       </c>
       <c r="B69" s="1" t="n">
-        <v>35461</v>
+        <v>43861</v>
       </c>
       <c r="C69" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D69" t="n">
-        <v>356</v>
+        <v>80</v>
       </c>
       <c r="E69" t="n">
-        <v>6269630897</v>
+        <v>12206525099</v>
       </c>
       <c r="F69" t="n">
-        <v>58921666470</v>
+        <v>14073182023</v>
       </c>
       <c r="G69" t="n">
-        <v>99.719888</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_kg</t>
+          <t>comexstat_comex_importacoes_frete_usd</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
-        <v>35461</v>
+        <v>43861</v>
       </c>
       <c r="C70" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D70" t="n">
-        <v>356</v>
+        <v>80</v>
       </c>
       <c r="E70" t="n">
-        <v>17370770826</v>
+        <v>641249369</v>
       </c>
       <c r="F70" t="n">
-        <v>77119199389</v>
+        <v>1548184686</v>
       </c>
       <c r="G70" t="n">
-        <v>99.719888</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_kg</t>
+          <t>comexstat_comex_importacoes_seguro_usd</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
-        <v>35461</v>
+        <v>43861</v>
       </c>
       <c r="C71" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D71" t="n">
-        <v>356</v>
+        <v>80</v>
       </c>
       <c r="E71" t="n">
-        <v>1569629726</v>
+        <v>11309879</v>
       </c>
       <c r="F71" t="n">
-        <v>14073182023</v>
+        <v>19241881</v>
       </c>
       <c r="G71" t="n">
-        <v>99.719888</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_frete_usd</t>
+          <t>comexstat_comex_importacoes_cif_usd</t>
         </is>
       </c>
       <c r="B72" s="1" t="n">
-        <v>35461</v>
+        <v>43861</v>
       </c>
       <c r="C72" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D72" t="n">
-        <v>356</v>
+        <v>80</v>
       </c>
       <c r="E72" t="n">
-        <v>154149785</v>
+        <v>17842724736</v>
       </c>
       <c r="F72" t="n">
-        <v>1548184686</v>
+        <v>27331288667</v>
       </c>
       <c r="G72" t="n">
-        <v>99.719888</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_seguro_usd</t>
+          <t>comexstat_comex_ncm_02023000_carne_bovina_congelada_exportacoes_fob_usd</t>
         </is>
       </c>
       <c r="B73" s="1" t="n">
-        <v>35461</v>
+        <v>43861</v>
       </c>
       <c r="C73" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D73" t="n">
-        <v>356</v>
+        <v>80</v>
       </c>
       <c r="E73" t="n">
-        <v>7008789</v>
+        <v>500185177</v>
       </c>
       <c r="F73" t="n">
-        <v>19241881</v>
+        <v>967242706</v>
       </c>
       <c r="G73" t="n">
-        <v>99.719888</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_cif_usd</t>
+          <t>comexstat_comex_ncm_02023000_carne_bovina_congelada_exportacoes_kg</t>
         </is>
       </c>
       <c r="B74" s="1" t="n">
-        <v>35461</v>
+        <v>43861</v>
       </c>
       <c r="C74" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D74" t="n">
-        <v>356</v>
+        <v>80</v>
       </c>
       <c r="E74" t="n">
-        <v>2749818353</v>
+        <v>103909023</v>
       </c>
       <c r="F74" t="n">
-        <v>27331288667</v>
+        <v>162300453</v>
       </c>
       <c r="G74" t="n">
-        <v>99.719888</v>
+        <v>98.765432</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_02023000_carne_bovina_congelada_importacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="B75" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C75" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D75" t="n">
+        <v>80</v>
+      </c>
+      <c r="E75" t="n">
+        <v>9788257</v>
+      </c>
+      <c r="F75" t="n">
+        <v>9868969</v>
+      </c>
+      <c r="G75" t="n">
+        <v>98.765432</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_02023000_carne_bovina_congelada_importacoes_kg</t>
+        </is>
+      </c>
+      <c r="B76" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C76" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D76" t="n">
+        <v>80</v>
+      </c>
+      <c r="E76" t="n">
+        <v>1182973</v>
+      </c>
+      <c r="F76" t="n">
+        <v>942383</v>
+      </c>
+      <c r="G76" t="n">
+        <v>98.765432</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_09011110_cafe_nao_torrado_exportacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="B77" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C77" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D77" t="n">
+        <v>80</v>
+      </c>
+      <c r="E77" t="n">
+        <v>357877575</v>
+      </c>
+      <c r="F77" t="n">
+        <v>1094109253</v>
+      </c>
+      <c r="G77" t="n">
+        <v>98.765432</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_09011110_cafe_nao_torrado_exportacoes_kg</t>
+        </is>
+      </c>
+      <c r="B78" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C78" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D78" t="n">
+        <v>80</v>
+      </c>
+      <c r="E78" t="n">
+        <v>163332129</v>
+      </c>
+      <c r="F78" t="n">
+        <v>206264157</v>
+      </c>
+      <c r="G78" t="n">
+        <v>98.765432</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_09011110_cafe_nao_torrado_importacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="B79" s="1" t="n">
+        <v>44043</v>
+      </c>
+      <c r="C79" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="D79" t="n">
+        <v>22</v>
+      </c>
+      <c r="E79" t="n">
+        <v>31418</v>
+      </c>
+      <c r="F79" t="n">
+        <v>6294</v>
+      </c>
+      <c r="G79" t="n">
+        <v>27.160494</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_09011110_cafe_nao_torrado_importacoes_kg</t>
+        </is>
+      </c>
+      <c r="B80" s="1" t="n">
+        <v>44043</v>
+      </c>
+      <c r="C80" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="D80" t="n">
+        <v>22</v>
+      </c>
+      <c r="E80" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F80" t="n">
+        <v>1560</v>
+      </c>
+      <c r="G80" t="n">
+        <v>27.160494</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_10059010_milho_em_grao_exportacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="B81" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C81" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D81" t="n">
+        <v>80</v>
+      </c>
+      <c r="E81" t="n">
+        <v>349915062</v>
+      </c>
+      <c r="F81" t="n">
+        <v>1002656682</v>
+      </c>
+      <c r="G81" t="n">
+        <v>98.765432</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_10059010_milho_em_grao_exportacoes_kg</t>
+        </is>
+      </c>
+      <c r="B82" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C82" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D82" t="n">
+        <v>80</v>
+      </c>
+      <c r="E82" t="n">
+        <v>2083530104</v>
+      </c>
+      <c r="F82" t="n">
+        <v>4653100189</v>
+      </c>
+      <c r="G82" t="n">
+        <v>98.765432</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_10059010_milho_em_grao_importacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="B83" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C83" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D83" t="n">
+        <v>80</v>
+      </c>
+      <c r="E83" t="n">
+        <v>26216991</v>
+      </c>
+      <c r="F83" t="n">
+        <v>33273820</v>
+      </c>
+      <c r="G83" t="n">
+        <v>98.765432</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_10059010_milho_em_grao_importacoes_kg</t>
+        </is>
+      </c>
+      <c r="B84" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C84" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D84" t="n">
+        <v>80</v>
+      </c>
+      <c r="E84" t="n">
+        <v>196178640</v>
+      </c>
+      <c r="F84" t="n">
+        <v>199281400</v>
+      </c>
+      <c r="G84" t="n">
+        <v>98.765432</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_12019000_soja_exceto_semeadura_exportacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="B85" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C85" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D85" t="n">
+        <v>80</v>
+      </c>
+      <c r="E85" t="n">
+        <v>504774218</v>
+      </c>
+      <c r="F85" t="n">
+        <v>4410039153</v>
+      </c>
+      <c r="G85" t="n">
+        <v>98.765432</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_12019000_soja_exceto_semeadura_exportacoes_kg</t>
+        </is>
+      </c>
+      <c r="B86" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C86" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D86" t="n">
+        <v>80</v>
+      </c>
+      <c r="E86" t="n">
+        <v>1397018249</v>
+      </c>
+      <c r="F86" t="n">
+        <v>9808807495</v>
+      </c>
+      <c r="G86" t="n">
+        <v>98.765432</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_12019000_soja_exceto_semeadura_importacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="B87" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C87" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D87" t="n">
+        <v>76</v>
+      </c>
+      <c r="E87" t="n">
+        <v>6305340</v>
+      </c>
+      <c r="F87" t="n">
+        <v>44621019</v>
+      </c>
+      <c r="G87" t="n">
+        <v>93.82716000000001</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_12019000_soja_exceto_semeadura_importacoes_kg</t>
+        </is>
+      </c>
+      <c r="B88" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C88" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D88" t="n">
+        <v>76</v>
+      </c>
+      <c r="E88" t="n">
+        <v>19690000</v>
+      </c>
+      <c r="F88" t="n">
+        <v>109088024</v>
+      </c>
+      <c r="G88" t="n">
+        <v>93.82716000000001</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_17011400_acucares_cana_exportacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="B89" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C89" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D89" t="n">
+        <v>80</v>
+      </c>
+      <c r="E89" t="n">
+        <v>395907378</v>
+      </c>
+      <c r="F89" t="n">
+        <v>753147930</v>
+      </c>
+      <c r="G89" t="n">
+        <v>98.765432</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_17011400_acucares_cana_exportacoes_kg</t>
+        </is>
+      </c>
+      <c r="B90" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C90" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D90" t="n">
+        <v>80</v>
+      </c>
+      <c r="E90" t="n">
+        <v>1403790404</v>
+      </c>
+      <c r="F90" t="n">
+        <v>2221291720</v>
+      </c>
+      <c r="G90" t="n">
+        <v>98.765432</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_17011400_acucares_cana_importacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="B91" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C91" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D91" t="n">
+        <v>79</v>
+      </c>
+      <c r="E91" t="n">
+        <v>42579</v>
+      </c>
+      <c r="F91" t="n">
+        <v>170442</v>
+      </c>
+      <c r="G91" t="n">
+        <v>97.53086399999999</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_17011400_acucares_cana_importacoes_kg</t>
+        </is>
+      </c>
+      <c r="B92" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C92" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D92" t="n">
+        <v>79</v>
+      </c>
+      <c r="E92" t="n">
+        <v>41657</v>
+      </c>
+      <c r="F92" t="n">
+        <v>143344</v>
+      </c>
+      <c r="G92" t="n">
+        <v>97.53086399999999</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_23040090_residuos_oleo_soja_exportacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="B93" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C93" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D93" t="n">
+        <v>80</v>
+      </c>
+      <c r="E93" t="n">
+        <v>281324952</v>
+      </c>
+      <c r="F93" t="n">
+        <v>646488066</v>
+      </c>
+      <c r="G93" t="n">
+        <v>98.765432</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_23040090_residuos_oleo_soja_exportacoes_kg</t>
+        </is>
+      </c>
+      <c r="B94" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C94" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D94" t="n">
+        <v>80</v>
+      </c>
+      <c r="E94" t="n">
+        <v>831821378</v>
+      </c>
+      <c r="F94" t="n">
+        <v>1790486389</v>
+      </c>
+      <c r="G94" t="n">
+        <v>98.765432</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_23040090_residuos_oleo_soja_importacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="B95" s="1" t="n">
+        <v>43890</v>
+      </c>
+      <c r="C95" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D95" t="n">
+        <v>5</v>
+      </c>
+      <c r="E95" t="n">
+        <v>2282</v>
+      </c>
+      <c r="F95" t="n">
+        <v>360</v>
+      </c>
+      <c r="G95" t="n">
+        <v>6.17284</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_23040090_residuos_oleo_soja_importacoes_kg</t>
+        </is>
+      </c>
+      <c r="B96" s="1" t="n">
+        <v>43890</v>
+      </c>
+      <c r="C96" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D96" t="n">
+        <v>5</v>
+      </c>
+      <c r="E96" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="n">
+        <v>6.17284</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_26011100_minerio_ferro_nao_aglomerado_exportacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="B97" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C97" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D97" t="n">
+        <v>80</v>
+      </c>
+      <c r="E97" t="n">
+        <v>1627139024</v>
+      </c>
+      <c r="F97" t="n">
+        <v>2051566400</v>
+      </c>
+      <c r="G97" t="n">
+        <v>98.765432</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_26011100_minerio_ferro_nao_aglomerado_exportacoes_kg</t>
+        </is>
+      </c>
+      <c r="B98" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C98" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D98" t="n">
+        <v>80</v>
+      </c>
+      <c r="E98" t="n">
+        <v>25418986258</v>
+      </c>
+      <c r="F98" t="n">
+        <v>34406447895</v>
+      </c>
+      <c r="G98" t="n">
+        <v>98.765432</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_26011100_minerio_ferro_nao_aglomerado_importacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="B99" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C99" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D99" t="n">
+        <v>66</v>
+      </c>
+      <c r="E99" t="n">
+        <v>6207</v>
+      </c>
+      <c r="F99" t="n">
+        <v>6950029</v>
+      </c>
+      <c r="G99" t="n">
+        <v>81.481481</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_26011100_minerio_ferro_nao_aglomerado_importacoes_kg</t>
+        </is>
+      </c>
+      <c r="B100" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C100" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D100" t="n">
+        <v>66</v>
+      </c>
+      <c r="E100" t="n">
+        <v>7200</v>
+      </c>
+      <c r="F100" t="n">
+        <v>78331372</v>
+      </c>
+      <c r="G100" t="n">
+        <v>81.481481</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_27090010_oleos_brutos_petroleo_exportacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="B101" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C101" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D101" t="n">
+        <v>80</v>
+      </c>
+      <c r="E101" t="n">
+        <v>1707992437</v>
+      </c>
+      <c r="F101" t="n">
+        <v>4828191084</v>
+      </c>
+      <c r="G101" t="n">
+        <v>98.765432</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_27090010_oleos_brutos_petroleo_exportacoes_kg</t>
+        </is>
+      </c>
+      <c r="B102" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C102" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D102" t="n">
+        <v>80</v>
+      </c>
+      <c r="E102" t="n">
+        <v>4221906804</v>
+      </c>
+      <c r="F102" t="n">
+        <v>8379911835</v>
+      </c>
+      <c r="G102" t="n">
+        <v>98.765432</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_27090010_oleos_brutos_petroleo_importacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="B103" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C103" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D103" t="n">
+        <v>80</v>
+      </c>
+      <c r="E103" t="n">
+        <v>207990371</v>
+      </c>
+      <c r="F103" t="n">
+        <v>547298813</v>
+      </c>
+      <c r="G103" t="n">
+        <v>98.765432</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_27090010_oleos_brutos_petroleo_importacoes_kg</t>
+        </is>
+      </c>
+      <c r="B104" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C104" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D104" t="n">
+        <v>80</v>
+      </c>
+      <c r="E104" t="n">
+        <v>432290309</v>
+      </c>
+      <c r="F104" t="n">
+        <v>797225701</v>
+      </c>
+      <c r="G104" t="n">
+        <v>98.765432</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_27101922_fuel_oil_exportacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="B105" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C105" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D105" t="n">
+        <v>80</v>
+      </c>
+      <c r="E105" t="n">
+        <v>401663716</v>
+      </c>
+      <c r="F105" t="n">
+        <v>893582419</v>
+      </c>
+      <c r="G105" t="n">
+        <v>98.765432</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_27101922_fuel_oil_exportacoes_kg</t>
+        </is>
+      </c>
+      <c r="B106" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C106" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D106" t="n">
+        <v>80</v>
+      </c>
+      <c r="E106" t="n">
+        <v>955961547</v>
+      </c>
+      <c r="F106" t="n">
+        <v>1438094595</v>
+      </c>
+      <c r="G106" t="n">
+        <v>98.765432</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_27101922_fuel_oil_importacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="B107" s="1" t="n">
+        <v>44196</v>
+      </c>
+      <c r="C107" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="D107" t="n">
+        <v>43</v>
+      </c>
+      <c r="E107" t="n">
+        <v>13124930</v>
+      </c>
+      <c r="F107" t="n">
+        <v>60</v>
+      </c>
+      <c r="G107" t="n">
+        <v>53.08642</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_27101922_fuel_oil_importacoes_kg</t>
+        </is>
+      </c>
+      <c r="B108" s="1" t="n">
+        <v>44196</v>
+      </c>
+      <c r="C108" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="D108" t="n">
+        <v>43</v>
+      </c>
+      <c r="E108" t="n">
+        <v>40054409</v>
+      </c>
+      <c r="F108" t="n">
+        <v>24</v>
+      </c>
+      <c r="G108" t="n">
+        <v>53.08642</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_47032900_celulose_nao_coniferas_exportacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="B109" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C109" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D109" t="n">
+        <v>80</v>
+      </c>
+      <c r="E109" t="n">
+        <v>488810441</v>
+      </c>
+      <c r="F109" t="n">
+        <v>748163251</v>
+      </c>
+      <c r="G109" t="n">
+        <v>98.765432</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_47032900_celulose_nao_coniferas_exportacoes_kg</t>
+        </is>
+      </c>
+      <c r="B110" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C110" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D110" t="n">
+        <v>80</v>
+      </c>
+      <c r="E110" t="n">
+        <v>1351894846</v>
+      </c>
+      <c r="F110" t="n">
+        <v>1412673002</v>
+      </c>
+      <c r="G110" t="n">
+        <v>98.765432</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_47032900_celulose_nao_coniferas_importacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="B111" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C111" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D111" t="n">
+        <v>70</v>
+      </c>
+      <c r="E111" t="n">
+        <v>23393</v>
+      </c>
+      <c r="F111" t="n">
+        <v>1381516</v>
+      </c>
+      <c r="G111" t="n">
+        <v>86.419753</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_47032900_celulose_nao_coniferas_importacoes_kg</t>
+        </is>
+      </c>
+      <c r="B112" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C112" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D112" t="n">
+        <v>70</v>
+      </c>
+      <c r="E112" t="n">
+        <v>40720</v>
+      </c>
+      <c r="F112" t="n">
+        <v>1452782</v>
+      </c>
+      <c r="G112" t="n">
+        <v>86.419753</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G112"/>
+  <dimension ref="A1:G114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1160,7 +1160,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_over</t>
+          <t>bcb_sgs_selic_meta</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
@@ -1173,10 +1173,10 @@
         <v>61</v>
       </c>
       <c r="E30" t="n">
-        <v>0.021182</v>
+        <v>6.25</v>
       </c>
       <c r="F30" t="n">
-        <v>0.05166</v>
+        <v>14</v>
       </c>
       <c r="G30" t="n">
         <v>75.30864200000001</v>
@@ -1185,7 +1185,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>bcb_sgs_cdi</t>
+          <t>bcb_sgs_selic_over</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -1210,107 +1210,107 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca</t>
+          <t>bcb_sgs_cdi</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D32" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E32" t="n">
-        <v>1.16</v>
+        <v>0.021182</v>
       </c>
       <c r="F32" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05166</v>
       </c>
       <c r="G32" t="n">
-        <v>72.839506</v>
+        <v>75.30864200000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m</t>
+          <t>bcb_sgs_ipca</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D33" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.64</v>
+        <v>1.16</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.22</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G33" t="n">
-        <v>74.074074</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc</t>
+          <t>bcb_sgs_igp_m</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D34" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E34" t="n">
-        <v>1.2</v>
+        <v>-0.64</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.01</v>
+        <v>-0.22</v>
       </c>
       <c r="G34" t="n">
-        <v>72.839506</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br_sa</t>
+          <t>bcb_sgs_inpc</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D35" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E35" t="n">
-        <v>96.95313</v>
+        <v>1.2</v>
       </c>
       <c r="F35" t="n">
-        <v>110.22154</v>
+        <v>-0.01</v>
       </c>
       <c r="G35" t="n">
-        <v>71.604938</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br</t>
+          <t>bcb_sgs_ibc_br_sa</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
@@ -1323,10 +1323,10 @@
         <v>58</v>
       </c>
       <c r="E36" t="n">
-        <v>97.10569</v>
+        <v>96.95313</v>
       </c>
       <c r="F36" t="n">
-        <v>109.89427</v>
+        <v>110.22154</v>
       </c>
       <c r="G36" t="n">
         <v>71.604938</v>
@@ -1335,32 +1335,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_venda_usd</t>
+          <t>bcb_sgs_ibc_br</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46295</v>
+        <v>46203</v>
       </c>
       <c r="D37" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E37" t="n">
-        <v>5.4394</v>
+        <v>97.10569</v>
       </c>
       <c r="F37" t="n">
-        <v>5.1253</v>
+        <v>109.89427</v>
       </c>
       <c r="G37" t="n">
-        <v>75.30864200000001</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_compra_usd</t>
+          <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
@@ -1373,10 +1373,10 @@
         <v>61</v>
       </c>
       <c r="E38" t="n">
-        <v>5.4388</v>
+        <v>5.4394</v>
       </c>
       <c r="F38" t="n">
-        <v>5.1247</v>
+        <v>5.1253</v>
       </c>
       <c r="G38" t="n">
         <v>75.30864200000001</v>
@@ -1385,32 +1385,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D39" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E39" t="n">
-        <v>4441056</v>
+        <v>5.4388</v>
       </c>
       <c r="F39" t="n">
-        <v>7372243</v>
+        <v>5.1247</v>
       </c>
       <c r="G39" t="n">
-        <v>72.839506</v>
+        <v>75.30864200000001</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
@@ -1423,10 +1423,10 @@
         <v>59</v>
       </c>
       <c r="E40" t="n">
-        <v>1894119</v>
+        <v>4441056</v>
       </c>
       <c r="F40" t="n">
-        <v>2731513</v>
+        <v>7372243</v>
       </c>
       <c r="G40" t="n">
         <v>72.839506</v>
@@ -1435,7 +1435,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
@@ -1448,10 +1448,10 @@
         <v>59</v>
       </c>
       <c r="E41" t="n">
-        <v>2546936</v>
+        <v>1894119</v>
       </c>
       <c r="F41" t="n">
-        <v>4640730</v>
+        <v>2731513</v>
       </c>
       <c r="G41" t="n">
         <v>72.839506</v>
@@ -1460,7 +1460,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
@@ -1473,10 +1473,10 @@
         <v>59</v>
       </c>
       <c r="E42" t="n">
-        <v>2.34</v>
+        <v>2546936</v>
       </c>
       <c r="F42" t="n">
-        <v>4.88</v>
+        <v>4640730</v>
       </c>
       <c r="G42" t="n">
         <v>72.839506</v>
@@ -1485,7 +1485,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
@@ -1498,10 +1498,10 @@
         <v>59</v>
       </c>
       <c r="E43" t="n">
-        <v>1.43</v>
+        <v>2.34</v>
       </c>
       <c r="F43" t="n">
-        <v>3.31</v>
+        <v>4.88</v>
       </c>
       <c r="G43" t="n">
         <v>72.839506</v>
@@ -1510,7 +1510,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
@@ -1523,10 +1523,10 @@
         <v>59</v>
       </c>
       <c r="E44" t="n">
-        <v>3.01</v>
+        <v>1.43</v>
       </c>
       <c r="F44" t="n">
-        <v>5.81</v>
+        <v>3.31</v>
       </c>
       <c r="G44" t="n">
         <v>72.839506</v>
@@ -1535,7 +1535,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
@@ -1548,10 +1548,10 @@
         <v>59</v>
       </c>
       <c r="E45" t="n">
-        <v>21.42</v>
+        <v>3.01</v>
       </c>
       <c r="F45" t="n">
-        <v>32.08</v>
+        <v>5.81</v>
       </c>
       <c r="G45" t="n">
         <v>72.839506</v>
@@ -1560,7 +1560,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
@@ -1573,10 +1573,10 @@
         <v>59</v>
       </c>
       <c r="E46" t="n">
-        <v>368886</v>
+        <v>21.42</v>
       </c>
       <c r="F46" t="n">
-        <v>369742</v>
+        <v>32.08</v>
       </c>
       <c r="G46" t="n">
         <v>72.839506</v>
@@ -1585,32 +1585,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>44500</v>
+        <v>44469</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="D47" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E47" t="n">
-        <v>0.541272</v>
+        <v>368886</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.6395690000000001</v>
+        <v>369742</v>
       </c>
       <c r="G47" t="n">
-        <v>70.37036999999999</v>
+        <v>72.839506</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
@@ -1623,10 +1623,10 @@
         <v>57</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.59426</v>
+        <v>0.541272</v>
       </c>
       <c r="F48" t="n">
-        <v>0.332557</v>
+        <v>-0.6395690000000001</v>
       </c>
       <c r="G48" t="n">
         <v>70.37036999999999</v>
@@ -1635,32 +1635,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46295</v>
+        <v>46203</v>
       </c>
       <c r="D49" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E49" t="n">
-        <v>3.74306</v>
+        <v>-0.59426</v>
       </c>
       <c r="F49" t="n">
-        <v>-1.086537</v>
+        <v>0.332557</v>
       </c>
       <c r="G49" t="n">
-        <v>74.074074</v>
+        <v>70.37036999999999</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
@@ -1673,10 +1673,10 @@
         <v>60</v>
       </c>
       <c r="E50" t="n">
-        <v>3.743473</v>
+        <v>3.74306</v>
       </c>
       <c r="F50" t="n">
-        <v>-1.086663</v>
+        <v>-1.086537</v>
       </c>
       <c r="G50" t="n">
         <v>74.074074</v>
@@ -1685,32 +1685,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D51" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E51" t="n">
-        <v>1.596467</v>
+        <v>3.743473</v>
       </c>
       <c r="F51" t="n">
-        <v>0.257708</v>
+        <v>-1.086663</v>
       </c>
       <c r="G51" t="n">
-        <v>71.604938</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
@@ -1723,10 +1723,10 @@
         <v>58</v>
       </c>
       <c r="E52" t="n">
-        <v>0.888065</v>
+        <v>1.596467</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.694824</v>
+        <v>0.257708</v>
       </c>
       <c r="G52" t="n">
         <v>71.604938</v>
@@ -1735,7 +1735,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
@@ -1748,10 +1748,10 @@
         <v>58</v>
       </c>
       <c r="E53" t="n">
-        <v>2.123375</v>
+        <v>0.888065</v>
       </c>
       <c r="F53" t="n">
-        <v>0.826955</v>
+        <v>-0.694824</v>
       </c>
       <c r="G53" t="n">
         <v>71.604938</v>
@@ -1760,7 +1760,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
@@ -1773,10 +1773,10 @@
         <v>58</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.259972</v>
+        <v>2.123375</v>
       </c>
       <c r="F54" t="n">
-        <v>0.5941920000000001</v>
+        <v>0.826955</v>
       </c>
       <c r="G54" t="n">
         <v>71.604938</v>
@@ -1785,107 +1785,107 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>44804</v>
+        <v>44500</v>
       </c>
       <c r="C55" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D55" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="E55" t="n">
-        <v>8.727061000000001</v>
+        <v>-0.259972</v>
       </c>
       <c r="F55" t="n">
-        <v>4.443025</v>
+        <v>0.5941920000000001</v>
       </c>
       <c r="G55" t="n">
-        <v>59.259259</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
         <v>44804</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D56" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E56" t="n">
-        <v>8.58755</v>
+        <v>8.727061000000001</v>
       </c>
       <c r="F56" t="n">
-        <v>2.178243</v>
+        <v>4.443025</v>
       </c>
       <c r="G56" t="n">
-        <v>60.493827</v>
+        <v>59.259259</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
         <v>44804</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D57" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E57" t="n">
-        <v>8.825751</v>
+        <v>8.58755</v>
       </c>
       <c r="F57" t="n">
-        <v>4.098046</v>
+        <v>2.178243</v>
       </c>
       <c r="G57" t="n">
-        <v>59.259259</v>
+        <v>60.493827</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>44500</v>
+        <v>44804</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="D58" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="E58" t="n">
-        <v>0.003062</v>
+        <v>8.825751</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.000124</v>
+        <v>4.098046</v>
       </c>
       <c r="G58" t="n">
-        <v>74.074074</v>
+        <v>59.259259</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
@@ -1898,10 +1898,10 @@
         <v>60</v>
       </c>
       <c r="E59" t="n">
-        <v>0.003062</v>
+        <v>1.5</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.000124</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
         <v>74.074074</v>
@@ -1910,57 +1910,57 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D60" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.01</v>
+        <v>0.003062</v>
       </c>
       <c r="F60" t="n">
-        <v>0.3</v>
+        <v>-0.000124</v>
       </c>
       <c r="G60" t="n">
-        <v>71.604938</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="D61" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>0.003062</v>
       </c>
       <c r="F61" t="n">
-        <v>0.13</v>
+        <v>-0.000124</v>
       </c>
       <c r="G61" t="n">
-        <v>71.604938</v>
+        <v>74.074074</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
@@ -1973,10 +1973,10 @@
         <v>58</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="F62" t="n">
-        <v>0.39</v>
+        <v>0.3</v>
       </c>
       <c r="G62" t="n">
         <v>71.604938</v>
@@ -1985,7 +1985,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
@@ -1998,10 +1998,10 @@
         <v>58</v>
       </c>
       <c r="E63" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>-1.25</v>
+        <v>0.13</v>
       </c>
       <c r="G63" t="n">
         <v>71.604938</v>
@@ -2010,57 +2010,57 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_fob_usd</t>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>43861</v>
+        <v>44500</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D64" t="n">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="E64" t="n">
-        <v>14429715267</v>
+        <v>-0.02</v>
       </c>
       <c r="F64" t="n">
-        <v>33157804370</v>
+        <v>0.39</v>
       </c>
       <c r="G64" t="n">
-        <v>98.765432</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_fob_usd</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>43861</v>
+        <v>44500</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D65" t="n">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="E65" t="n">
-        <v>17190165488</v>
+        <v>1.47</v>
       </c>
       <c r="F65" t="n">
-        <v>25763862100</v>
+        <v>-1.25</v>
       </c>
       <c r="G65" t="n">
-        <v>98.765432</v>
+        <v>71.604938</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>comexstat_comex_saldo_comercial_usd</t>
+          <t>comexstat_comex_exportacoes_fob_usd</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
@@ -2073,10 +2073,10 @@
         <v>80</v>
       </c>
       <c r="E66" t="n">
-        <v>-2760450221</v>
+        <v>14429715267</v>
       </c>
       <c r="F66" t="n">
-        <v>7393942270</v>
+        <v>33157804370</v>
       </c>
       <c r="G66" t="n">
         <v>98.765432</v>
@@ -2085,7 +2085,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>comexstat_comex_corrente_comercio_usd</t>
+          <t>comexstat_comex_importacoes_fob_usd</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
@@ -2098,10 +2098,10 @@
         <v>80</v>
       </c>
       <c r="E67" t="n">
-        <v>31619880755</v>
+        <v>17190165488</v>
       </c>
       <c r="F67" t="n">
-        <v>58921666470</v>
+        <v>25763862100</v>
       </c>
       <c r="G67" t="n">
         <v>98.765432</v>
@@ -2110,7 +2110,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_kg</t>
+          <t>comexstat_comex_saldo_comercial_usd</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
@@ -2123,10 +2123,10 @@
         <v>80</v>
       </c>
       <c r="E68" t="n">
-        <v>46718273016</v>
+        <v>-2760450221</v>
       </c>
       <c r="F68" t="n">
-        <v>77119199389</v>
+        <v>7393942270</v>
       </c>
       <c r="G68" t="n">
         <v>98.765432</v>
@@ -2135,7 +2135,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_kg</t>
+          <t>comexstat_comex_corrente_comercio_usd</t>
         </is>
       </c>
       <c r="B69" s="1" t="n">
@@ -2148,10 +2148,10 @@
         <v>80</v>
       </c>
       <c r="E69" t="n">
-        <v>12206525099</v>
+        <v>31619880755</v>
       </c>
       <c r="F69" t="n">
-        <v>14073182023</v>
+        <v>58921666470</v>
       </c>
       <c r="G69" t="n">
         <v>98.765432</v>
@@ -2160,7 +2160,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_frete_usd</t>
+          <t>comexstat_comex_exportacoes_kg</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
@@ -2173,10 +2173,10 @@
         <v>80</v>
       </c>
       <c r="E70" t="n">
-        <v>641249369</v>
+        <v>46718273016</v>
       </c>
       <c r="F70" t="n">
-        <v>1548184686</v>
+        <v>77119199389</v>
       </c>
       <c r="G70" t="n">
         <v>98.765432</v>
@@ -2185,7 +2185,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_seguro_usd</t>
+          <t>comexstat_comex_importacoes_kg</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
@@ -2198,10 +2198,10 @@
         <v>80</v>
       </c>
       <c r="E71" t="n">
-        <v>11309879</v>
+        <v>12206525099</v>
       </c>
       <c r="F71" t="n">
-        <v>19241881</v>
+        <v>14073182023</v>
       </c>
       <c r="G71" t="n">
         <v>98.765432</v>
@@ -2210,7 +2210,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_cif_usd</t>
+          <t>comexstat_comex_importacoes_frete_usd</t>
         </is>
       </c>
       <c r="B72" s="1" t="n">
@@ -2223,10 +2223,10 @@
         <v>80</v>
       </c>
       <c r="E72" t="n">
-        <v>17842724736</v>
+        <v>641249369</v>
       </c>
       <c r="F72" t="n">
-        <v>27331288667</v>
+        <v>1548184686</v>
       </c>
       <c r="G72" t="n">
         <v>98.765432</v>
@@ -2235,7 +2235,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_02023000_carne_bovina_congelada_exportacoes_fob_usd</t>
+          <t>comexstat_comex_importacoes_seguro_usd</t>
         </is>
       </c>
       <c r="B73" s="1" t="n">
@@ -2248,10 +2248,10 @@
         <v>80</v>
       </c>
       <c r="E73" t="n">
-        <v>500185177</v>
+        <v>11309879</v>
       </c>
       <c r="F73" t="n">
-        <v>967242706</v>
+        <v>19241881</v>
       </c>
       <c r="G73" t="n">
         <v>98.765432</v>
@@ -2260,7 +2260,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_02023000_carne_bovina_congelada_exportacoes_kg</t>
+          <t>comexstat_comex_importacoes_cif_usd</t>
         </is>
       </c>
       <c r="B74" s="1" t="n">
@@ -2273,10 +2273,10 @@
         <v>80</v>
       </c>
       <c r="E74" t="n">
-        <v>103909023</v>
+        <v>17842724736</v>
       </c>
       <c r="F74" t="n">
-        <v>162300453</v>
+        <v>27331288667</v>
       </c>
       <c r="G74" t="n">
         <v>98.765432</v>
@@ -2285,7 +2285,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_02023000_carne_bovina_congelada_importacoes_fob_usd</t>
+          <t>comexstat_acucares_cana_exp_fob</t>
         </is>
       </c>
       <c r="B75" s="1" t="n">
@@ -2298,10 +2298,10 @@
         <v>80</v>
       </c>
       <c r="E75" t="n">
-        <v>9788257</v>
+        <v>395907378</v>
       </c>
       <c r="F75" t="n">
-        <v>9868969</v>
+        <v>753147930</v>
       </c>
       <c r="G75" t="n">
         <v>98.765432</v>
@@ -2310,7 +2310,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_02023000_carne_bovina_congelada_importacoes_kg</t>
+          <t>comexstat_acucares_cana_exp_kg</t>
         </is>
       </c>
       <c r="B76" s="1" t="n">
@@ -2323,10 +2323,10 @@
         <v>80</v>
       </c>
       <c r="E76" t="n">
-        <v>1182973</v>
+        <v>1403790404</v>
       </c>
       <c r="F76" t="n">
-        <v>942383</v>
+        <v>2221291720</v>
       </c>
       <c r="G76" t="n">
         <v>98.765432</v>
@@ -2335,7 +2335,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_09011110_cafe_nao_torrado_exportacoes_fob_usd</t>
+          <t>comexstat_acucares_cana_imp_fob</t>
         </is>
       </c>
       <c r="B77" s="1" t="n">
@@ -2345,22 +2345,22 @@
         <v>46265</v>
       </c>
       <c r="D77" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E77" t="n">
-        <v>357877575</v>
+        <v>42579</v>
       </c>
       <c r="F77" t="n">
-        <v>1094109253</v>
+        <v>170442</v>
       </c>
       <c r="G77" t="n">
-        <v>98.765432</v>
+        <v>97.53086399999999</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_09011110_cafe_nao_torrado_exportacoes_kg</t>
+          <t>comexstat_acucares_cana_imp_kg</t>
         </is>
       </c>
       <c r="B78" s="1" t="n">
@@ -2370,122 +2370,122 @@
         <v>46265</v>
       </c>
       <c r="D78" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E78" t="n">
-        <v>163332129</v>
+        <v>41657</v>
       </c>
       <c r="F78" t="n">
-        <v>206264157</v>
+        <v>143344</v>
       </c>
       <c r="G78" t="n">
-        <v>98.765432</v>
+        <v>97.53086399999999</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_09011110_cafe_nao_torrado_importacoes_fob_usd</t>
+          <t>comexstat_cafe_nao_torrado_exp_fob</t>
         </is>
       </c>
       <c r="B79" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D79" t="n">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="E79" t="n">
-        <v>31418</v>
+        <v>357877575</v>
       </c>
       <c r="F79" t="n">
-        <v>6294</v>
+        <v>1094109253</v>
       </c>
       <c r="G79" t="n">
-        <v>27.160494</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_09011110_cafe_nao_torrado_importacoes_kg</t>
+          <t>comexstat_cafe_nao_torrado_exp_kg</t>
         </is>
       </c>
       <c r="B80" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D80" t="n">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="E80" t="n">
-        <v>20000</v>
+        <v>163332129</v>
       </c>
       <c r="F80" t="n">
-        <v>1560</v>
+        <v>206264157</v>
       </c>
       <c r="G80" t="n">
-        <v>27.160494</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_10059010_milho_em_grao_exportacoes_fob_usd</t>
+          <t>comexstat_cafe_nao_torrado_imp_fob</t>
         </is>
       </c>
       <c r="B81" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D81" t="n">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="E81" t="n">
-        <v>349915062</v>
+        <v>31418</v>
       </c>
       <c r="F81" t="n">
-        <v>1002656682</v>
+        <v>6294</v>
       </c>
       <c r="G81" t="n">
-        <v>98.765432</v>
+        <v>27.160494</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_10059010_milho_em_grao_exportacoes_kg</t>
+          <t>comexstat_cafe_nao_torrado_imp_kg</t>
         </is>
       </c>
       <c r="B82" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D82" t="n">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="E82" t="n">
-        <v>2083530104</v>
+        <v>20000</v>
       </c>
       <c r="F82" t="n">
-        <v>4653100189</v>
+        <v>1560</v>
       </c>
       <c r="G82" t="n">
-        <v>98.765432</v>
+        <v>27.160494</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_10059010_milho_em_grao_importacoes_fob_usd</t>
+          <t>comexstat_carne_bovina_congelada_exp_fob</t>
         </is>
       </c>
       <c r="B83" s="1" t="n">
@@ -2498,10 +2498,10 @@
         <v>80</v>
       </c>
       <c r="E83" t="n">
-        <v>26216991</v>
+        <v>500185177</v>
       </c>
       <c r="F83" t="n">
-        <v>33273820</v>
+        <v>967242706</v>
       </c>
       <c r="G83" t="n">
         <v>98.765432</v>
@@ -2510,7 +2510,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_10059010_milho_em_grao_importacoes_kg</t>
+          <t>comexstat_carne_bovina_congelada_exp_kg</t>
         </is>
       </c>
       <c r="B84" s="1" t="n">
@@ -2523,10 +2523,10 @@
         <v>80</v>
       </c>
       <c r="E84" t="n">
-        <v>196178640</v>
+        <v>103909023</v>
       </c>
       <c r="F84" t="n">
-        <v>199281400</v>
+        <v>162300453</v>
       </c>
       <c r="G84" t="n">
         <v>98.765432</v>
@@ -2535,7 +2535,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_12019000_soja_exceto_semeadura_exportacoes_fob_usd</t>
+          <t>comexstat_carne_bovina_congelada_imp_fob</t>
         </is>
       </c>
       <c r="B85" s="1" t="n">
@@ -2548,10 +2548,10 @@
         <v>80</v>
       </c>
       <c r="E85" t="n">
-        <v>504774218</v>
+        <v>9788257</v>
       </c>
       <c r="F85" t="n">
-        <v>4410039153</v>
+        <v>9868969</v>
       </c>
       <c r="G85" t="n">
         <v>98.765432</v>
@@ -2560,7 +2560,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_12019000_soja_exceto_semeadura_exportacoes_kg</t>
+          <t>comexstat_carne_bovina_congelada_imp_kg</t>
         </is>
       </c>
       <c r="B86" s="1" t="n">
@@ -2573,10 +2573,10 @@
         <v>80</v>
       </c>
       <c r="E86" t="n">
-        <v>1397018249</v>
+        <v>1182973</v>
       </c>
       <c r="F86" t="n">
-        <v>9808807495</v>
+        <v>942383</v>
       </c>
       <c r="G86" t="n">
         <v>98.765432</v>
@@ -2585,7 +2585,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_12019000_soja_exceto_semeadura_importacoes_fob_usd</t>
+          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
         </is>
       </c>
       <c r="B87" s="1" t="n">
@@ -2595,22 +2595,22 @@
         <v>46265</v>
       </c>
       <c r="D87" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E87" t="n">
-        <v>6305340</v>
+        <v>488810441</v>
       </c>
       <c r="F87" t="n">
-        <v>44621019</v>
+        <v>748163251</v>
       </c>
       <c r="G87" t="n">
-        <v>93.82716000000001</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_12019000_soja_exceto_semeadura_importacoes_kg</t>
+          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
         </is>
       </c>
       <c r="B88" s="1" t="n">
@@ -2620,22 +2620,22 @@
         <v>46265</v>
       </c>
       <c r="D88" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E88" t="n">
-        <v>19690000</v>
+        <v>1351894846</v>
       </c>
       <c r="F88" t="n">
-        <v>109088024</v>
+        <v>1412673002</v>
       </c>
       <c r="G88" t="n">
-        <v>93.82716000000001</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_17011400_acucares_cana_exportacoes_fob_usd</t>
+          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
         </is>
       </c>
       <c r="B89" s="1" t="n">
@@ -2645,22 +2645,22 @@
         <v>46265</v>
       </c>
       <c r="D89" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E89" t="n">
-        <v>395907378</v>
+        <v>23393</v>
       </c>
       <c r="F89" t="n">
-        <v>753147930</v>
+        <v>1381516</v>
       </c>
       <c r="G89" t="n">
-        <v>98.765432</v>
+        <v>86.419753</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_17011400_acucares_cana_exportacoes_kg</t>
+          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
         </is>
       </c>
       <c r="B90" s="1" t="n">
@@ -2670,22 +2670,22 @@
         <v>46265</v>
       </c>
       <c r="D90" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E90" t="n">
-        <v>1403790404</v>
+        <v>40720</v>
       </c>
       <c r="F90" t="n">
-        <v>2221291720</v>
+        <v>1452782</v>
       </c>
       <c r="G90" t="n">
-        <v>98.765432</v>
+        <v>86.419753</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_17011400_acucares_cana_importacoes_fob_usd</t>
+          <t>comexstat_fuel_oil_exp_fob</t>
         </is>
       </c>
       <c r="B91" s="1" t="n">
@@ -2695,22 +2695,22 @@
         <v>46265</v>
       </c>
       <c r="D91" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E91" t="n">
-        <v>42579</v>
+        <v>401663716</v>
       </c>
       <c r="F91" t="n">
-        <v>170442</v>
+        <v>893582419</v>
       </c>
       <c r="G91" t="n">
-        <v>97.53086399999999</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_17011400_acucares_cana_importacoes_kg</t>
+          <t>comexstat_fuel_oil_exp_kg</t>
         </is>
       </c>
       <c r="B92" s="1" t="n">
@@ -2720,122 +2720,122 @@
         <v>46265</v>
       </c>
       <c r="D92" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E92" t="n">
-        <v>41657</v>
+        <v>955961547</v>
       </c>
       <c r="F92" t="n">
-        <v>143344</v>
+        <v>1438094595</v>
       </c>
       <c r="G92" t="n">
-        <v>97.53086399999999</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_23040090_residuos_oleo_soja_exportacoes_fob_usd</t>
+          <t>comexstat_fuel_oil_imp_fob</t>
         </is>
       </c>
       <c r="B93" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D93" t="n">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="E93" t="n">
-        <v>281324952</v>
+        <v>13124930</v>
       </c>
       <c r="F93" t="n">
-        <v>646488066</v>
+        <v>60</v>
       </c>
       <c r="G93" t="n">
-        <v>98.765432</v>
+        <v>53.08642</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_23040090_residuos_oleo_soja_exportacoes_kg</t>
+          <t>comexstat_fuel_oil_imp_kg</t>
         </is>
       </c>
       <c r="B94" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D94" t="n">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="E94" t="n">
-        <v>831821378</v>
+        <v>40054409</v>
       </c>
       <c r="F94" t="n">
-        <v>1790486389</v>
+        <v>24</v>
       </c>
       <c r="G94" t="n">
-        <v>98.765432</v>
+        <v>53.08642</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_23040090_residuos_oleo_soja_importacoes_fob_usd</t>
+          <t>comexstat_milho_em_grao_exp_fob</t>
         </is>
       </c>
       <c r="B95" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C95" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D95" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="E95" t="n">
-        <v>2282</v>
+        <v>349915062</v>
       </c>
       <c r="F95" t="n">
-        <v>360</v>
+        <v>1002656682</v>
       </c>
       <c r="G95" t="n">
-        <v>6.17284</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_23040090_residuos_oleo_soja_importacoes_kg</t>
+          <t>comexstat_milho_em_grao_exp_kg</t>
         </is>
       </c>
       <c r="B96" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="C96" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D96" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="E96" t="n">
-        <v>2500</v>
+        <v>2083530104</v>
       </c>
       <c r="F96" t="n">
-        <v>0</v>
+        <v>4653100189</v>
       </c>
       <c r="G96" t="n">
-        <v>6.17284</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_26011100_minerio_ferro_nao_aglomerado_exportacoes_fob_usd</t>
+          <t>comexstat_milho_em_grao_imp_fob</t>
         </is>
       </c>
       <c r="B97" s="1" t="n">
@@ -2848,10 +2848,10 @@
         <v>80</v>
       </c>
       <c r="E97" t="n">
-        <v>1627139024</v>
+        <v>26216991</v>
       </c>
       <c r="F97" t="n">
-        <v>2051566400</v>
+        <v>33273820</v>
       </c>
       <c r="G97" t="n">
         <v>98.765432</v>
@@ -2860,7 +2860,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_26011100_minerio_ferro_nao_aglomerado_exportacoes_kg</t>
+          <t>comexstat_milho_em_grao_imp_kg</t>
         </is>
       </c>
       <c r="B98" s="1" t="n">
@@ -2873,10 +2873,10 @@
         <v>80</v>
       </c>
       <c r="E98" t="n">
-        <v>25418986258</v>
+        <v>196178640</v>
       </c>
       <c r="F98" t="n">
-        <v>34406447895</v>
+        <v>199281400</v>
       </c>
       <c r="G98" t="n">
         <v>98.765432</v>
@@ -2885,7 +2885,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_26011100_minerio_ferro_nao_aglomerado_importacoes_fob_usd</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
         </is>
       </c>
       <c r="B99" s="1" t="n">
@@ -2895,22 +2895,22 @@
         <v>46265</v>
       </c>
       <c r="D99" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="E99" t="n">
-        <v>6207</v>
+        <v>1627139024</v>
       </c>
       <c r="F99" t="n">
-        <v>6950029</v>
+        <v>2051566400</v>
       </c>
       <c r="G99" t="n">
-        <v>81.481481</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_26011100_minerio_ferro_nao_aglomerado_importacoes_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
         </is>
       </c>
       <c r="B100" s="1" t="n">
@@ -2920,22 +2920,22 @@
         <v>46265</v>
       </c>
       <c r="D100" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="E100" t="n">
-        <v>7200</v>
+        <v>25418986258</v>
       </c>
       <c r="F100" t="n">
-        <v>78331372</v>
+        <v>34406447895</v>
       </c>
       <c r="G100" t="n">
-        <v>81.481481</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_27090010_oleos_brutos_petroleo_exportacoes_fob_usd</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
         </is>
       </c>
       <c r="B101" s="1" t="n">
@@ -2945,22 +2945,22 @@
         <v>46265</v>
       </c>
       <c r="D101" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E101" t="n">
-        <v>1707992437</v>
+        <v>6207</v>
       </c>
       <c r="F101" t="n">
-        <v>4828191084</v>
+        <v>6950029</v>
       </c>
       <c r="G101" t="n">
-        <v>98.765432</v>
+        <v>81.481481</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_27090010_oleos_brutos_petroleo_exportacoes_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
         </is>
       </c>
       <c r="B102" s="1" t="n">
@@ -2970,22 +2970,22 @@
         <v>46265</v>
       </c>
       <c r="D102" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E102" t="n">
-        <v>4221906804</v>
+        <v>7200</v>
       </c>
       <c r="F102" t="n">
-        <v>8379911835</v>
+        <v>78331372</v>
       </c>
       <c r="G102" t="n">
-        <v>98.765432</v>
+        <v>81.481481</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_27090010_oleos_brutos_petroleo_importacoes_fob_usd</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
         </is>
       </c>
       <c r="B103" s="1" t="n">
@@ -2998,10 +2998,10 @@
         <v>80</v>
       </c>
       <c r="E103" t="n">
-        <v>207990371</v>
+        <v>1707992437</v>
       </c>
       <c r="F103" t="n">
-        <v>547298813</v>
+        <v>4828191084</v>
       </c>
       <c r="G103" t="n">
         <v>98.765432</v>
@@ -3010,7 +3010,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_27090010_oleos_brutos_petroleo_importacoes_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
         </is>
       </c>
       <c r="B104" s="1" t="n">
@@ -3023,10 +3023,10 @@
         <v>80</v>
       </c>
       <c r="E104" t="n">
-        <v>432290309</v>
+        <v>4221906804</v>
       </c>
       <c r="F104" t="n">
-        <v>797225701</v>
+        <v>8379911835</v>
       </c>
       <c r="G104" t="n">
         <v>98.765432</v>
@@ -3035,7 +3035,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_27101922_fuel_oil_exportacoes_fob_usd</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
         </is>
       </c>
       <c r="B105" s="1" t="n">
@@ -3048,10 +3048,10 @@
         <v>80</v>
       </c>
       <c r="E105" t="n">
-        <v>401663716</v>
+        <v>207990371</v>
       </c>
       <c r="F105" t="n">
-        <v>893582419</v>
+        <v>547298813</v>
       </c>
       <c r="G105" t="n">
         <v>98.765432</v>
@@ -3060,7 +3060,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_27101922_fuel_oil_exportacoes_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
         </is>
       </c>
       <c r="B106" s="1" t="n">
@@ -3073,10 +3073,10 @@
         <v>80</v>
       </c>
       <c r="E106" t="n">
-        <v>955961547</v>
+        <v>432290309</v>
       </c>
       <c r="F106" t="n">
-        <v>1438094595</v>
+        <v>797225701</v>
       </c>
       <c r="G106" t="n">
         <v>98.765432</v>
@@ -3085,107 +3085,107 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_27101922_fuel_oil_importacoes_fob_usd</t>
+          <t>comexstat_residuos_oleo_soja_exp_fob</t>
         </is>
       </c>
       <c r="B107" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D107" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="E107" t="n">
-        <v>13124930</v>
+        <v>281324952</v>
       </c>
       <c r="F107" t="n">
-        <v>60</v>
+        <v>646488066</v>
       </c>
       <c r="G107" t="n">
-        <v>53.08642</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_27101922_fuel_oil_importacoes_kg</t>
+          <t>comexstat_residuos_oleo_soja_exp_kg</t>
         </is>
       </c>
       <c r="B108" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D108" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="E108" t="n">
-        <v>40054409</v>
+        <v>831821378</v>
       </c>
       <c r="F108" t="n">
-        <v>24</v>
+        <v>1790486389</v>
       </c>
       <c r="G108" t="n">
-        <v>53.08642</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_47032900_celulose_nao_coniferas_exportacoes_fob_usd</t>
+          <t>comexstat_residuos_oleo_soja_imp_fob</t>
         </is>
       </c>
       <c r="B109" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="C109" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D109" t="n">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="E109" t="n">
-        <v>488810441</v>
+        <v>2282</v>
       </c>
       <c r="F109" t="n">
-        <v>748163251</v>
+        <v>360</v>
       </c>
       <c r="G109" t="n">
-        <v>98.765432</v>
+        <v>6.17284</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_47032900_celulose_nao_coniferas_exportacoes_kg</t>
+          <t>comexstat_residuos_oleo_soja_imp_kg</t>
         </is>
       </c>
       <c r="B110" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="C110" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D110" t="n">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="E110" t="n">
-        <v>1351894846</v>
+        <v>2500</v>
       </c>
       <c r="F110" t="n">
-        <v>1412673002</v>
+        <v>0</v>
       </c>
       <c r="G110" t="n">
-        <v>98.765432</v>
+        <v>6.17284</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_47032900_celulose_nao_coniferas_importacoes_fob_usd</t>
+          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
         </is>
       </c>
       <c r="B111" s="1" t="n">
@@ -3195,22 +3195,22 @@
         <v>46265</v>
       </c>
       <c r="D111" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E111" t="n">
-        <v>23393</v>
+        <v>504774218</v>
       </c>
       <c r="F111" t="n">
-        <v>1381516</v>
+        <v>4410039153</v>
       </c>
       <c r="G111" t="n">
-        <v>86.419753</v>
+        <v>98.765432</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_47032900_celulose_nao_coniferas_importacoes_kg</t>
+          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
         </is>
       </c>
       <c r="B112" s="1" t="n">
@@ -3220,16 +3220,66 @@
         <v>46265</v>
       </c>
       <c r="D112" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E112" t="n">
-        <v>40720</v>
+        <v>1397018249</v>
       </c>
       <c r="F112" t="n">
-        <v>1452782</v>
+        <v>9808807495</v>
       </c>
       <c r="G112" t="n">
-        <v>86.419753</v>
+        <v>98.765432</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
+        </is>
+      </c>
+      <c r="B113" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C113" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D113" t="n">
+        <v>76</v>
+      </c>
+      <c r="E113" t="n">
+        <v>6305340</v>
+      </c>
+      <c r="F113" t="n">
+        <v>44621019</v>
+      </c>
+      <c r="G113" t="n">
+        <v>93.82716000000001</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>comexstat_soja_exceto_semeadura_imp_kg</t>
+        </is>
+      </c>
+      <c r="B114" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C114" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D114" t="n">
+        <v>76</v>
+      </c>
+      <c r="E114" t="n">
+        <v>19690000</v>
+      </c>
+      <c r="F114" t="n">
+        <v>109088024</v>
+      </c>
+      <c r="G114" t="n">
+        <v>93.82716000000001</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
+++ b/data/final/consolidada/resumo_disponibilidade_consolidada.xlsx
@@ -701,7 +701,7 @@
         <v>1755.300049</v>
       </c>
       <c r="F11" t="n">
-        <v>4429.799805</v>
+        <v>4476.600098</v>
       </c>
       <c r="G11" t="n">
         <v>75.30864200000001</v>
@@ -776,7 +776,7 @@
         <v>1256</v>
       </c>
       <c r="F14" t="n">
-        <v>1293.75</v>
+        <v>1309.75</v>
       </c>
       <c r="G14" t="n">
         <v>75.30864200000001</v>
@@ -801,7 +801,7 @@
         <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>512</v>
+        <v>536.75</v>
       </c>
       <c r="G15" t="n">
         <v>75.30864200000001</v>
@@ -1051,7 +1051,7 @@
         <v>1.578075</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.029345</v>
+        <v>1.026833</v>
       </c>
       <c r="G25" t="n">
         <v>74.074074</v>
@@ -1126,7 +1126,7 @@
         <v>-1.612261</v>
       </c>
       <c r="F28" t="n">
-        <v>1.450696</v>
+        <v>2.705352</v>
       </c>
       <c r="G28" t="n">
         <v>74.074074</v>
@@ -1151,7 +1151,7 @@
         <v>5.868654</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.582524</v>
+        <v>4.223301</v>
       </c>
       <c r="G29" t="n">
         <v>74.074074</v>
